--- a/data/2026 GSMUD.xlsx
+++ b/data/2026 GSMUD.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\From M Drive\MD DO NOT DELETE\General School Stuff\Graduation Marching Class Day Marching\2026\2026 Web\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code Space\Git 2026 Grad\2026-Grad\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017A274B-6EEA-401B-AF7A-6E0CD4AA8867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5677C2-95E5-4FC1-AC9E-1C803C1297C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DIRECTIONS" sheetId="9" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3972" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3974" uniqueCount="479">
   <si>
     <t>DIRECTIONS FOR SPREADSHEET USE</t>
   </si>
@@ -9524,13 +9524,11 @@
       <c r="I60" s="42"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="39">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-      <c r="B61" s="39">
-        <f t="shared" si="0"/>
-        <v>56</v>
+      <c r="A61" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="C61" s="39" t="str">
         <f>'Raw Name Splitter'!C61</f>
@@ -9554,11 +9552,11 @@
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="39">
         <f t="shared" si="1"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" s="39">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C62" s="39" t="str">
         <f>'Raw Name Splitter'!C62</f>
@@ -9608,11 +9606,11 @@
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="39">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B64" s="39">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C64" s="39" t="str">
         <f>'Raw Name Splitter'!C64</f>
@@ -9636,11 +9634,11 @@
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="39">
         <f t="shared" si="1"/>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B65" s="39">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C65" s="39" t="str">
         <f>'Raw Name Splitter'!C65</f>
@@ -9664,11 +9662,11 @@
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="39">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B66" s="39">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C66" s="39" t="str">
         <f>'Raw Name Splitter'!C66</f>
@@ -9692,11 +9690,11 @@
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="39">
         <f t="shared" si="1"/>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B67" s="39">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C67" s="39" t="str">
         <f>'Raw Name Splitter'!C67</f>
@@ -9720,11 +9718,11 @@
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="39">
         <f t="shared" si="1"/>
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B68" s="39">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C68" s="39" t="str">
         <f>'Raw Name Splitter'!C68</f>
@@ -9748,11 +9746,11 @@
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="39">
         <f t="shared" si="1"/>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B69" s="39">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C69" s="39" t="str">
         <f>'Raw Name Splitter'!C69</f>
@@ -9776,11 +9774,11 @@
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="39">
         <f t="shared" si="1"/>
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B70" s="39">
         <f t="shared" si="1"/>
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C70" s="39" t="str">
         <f>'Raw Name Splitter'!C70</f>
@@ -9804,11 +9802,11 @@
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="39">
         <f t="shared" ref="A71:B85" si="2">IF(ISTEXT(A70)=TRUE,IF(ISTEXT(A69)=TRUE,A68+1,A69+1),A70+1)</f>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B71" s="39">
         <f t="shared" si="2"/>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C71" s="39" t="str">
         <f>'Raw Name Splitter'!C71</f>
@@ -9832,11 +9830,11 @@
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="39">
         <f t="shared" si="2"/>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B72" s="39">
         <f t="shared" si="2"/>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C72" s="39" t="str">
         <f>'Raw Name Splitter'!C72</f>
@@ -9860,11 +9858,11 @@
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="39">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B73" s="39">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C73" s="39" t="str">
         <f>'Raw Name Splitter'!C73</f>
@@ -9888,11 +9886,11 @@
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="39">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B74" s="39">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C74" s="39" t="str">
         <f>'Raw Name Splitter'!C74</f>
@@ -9916,11 +9914,11 @@
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="39">
         <f t="shared" si="2"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B75" s="39">
         <f t="shared" si="2"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C75" s="39" t="str">
         <f>'Raw Name Splitter'!C75</f>
@@ -9944,11 +9942,11 @@
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="39">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B76" s="39">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C76" s="39" t="str">
         <f>'Raw Name Splitter'!C76</f>
@@ -9972,11 +9970,11 @@
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="39">
         <f t="shared" si="2"/>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B77" s="39">
         <f t="shared" si="2"/>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C77" s="39" t="str">
         <f>'Raw Name Splitter'!C77</f>
@@ -10000,11 +9998,11 @@
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="39">
         <f t="shared" si="2"/>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B78" s="39">
         <f t="shared" si="2"/>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C78" s="39" t="str">
         <f>'Raw Name Splitter'!C78</f>
@@ -10028,11 +10026,11 @@
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="39">
         <f t="shared" si="2"/>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B79" s="39">
         <f t="shared" si="2"/>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C79" s="39" t="str">
         <f>'Raw Name Splitter'!C79</f>
@@ -10056,11 +10054,11 @@
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="39">
         <f t="shared" si="2"/>
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B80" s="39">
         <f t="shared" si="2"/>
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C80" s="39" t="str">
         <f>'Raw Name Splitter'!C80</f>
@@ -10084,11 +10082,11 @@
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="39">
         <f t="shared" si="2"/>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B81" s="39">
         <f t="shared" si="2"/>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C81" s="39" t="str">
         <f>'Raw Name Splitter'!C81</f>
@@ -10111,11 +10109,11 @@
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="39">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B82" s="39">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C82" s="39" t="str">
         <f>'Raw Name Splitter'!C82</f>
@@ -10139,11 +10137,11 @@
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="39">
         <f t="shared" si="2"/>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B83" s="39">
         <f t="shared" si="2"/>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C83" s="39" t="str">
         <f>'Raw Name Splitter'!C83</f>
@@ -10167,11 +10165,11 @@
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="39">
         <f t="shared" si="2"/>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B84" s="39">
         <f t="shared" si="2"/>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C84" s="39" t="str">
         <f>'Raw Name Splitter'!C84</f>
@@ -10195,11 +10193,11 @@
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="39">
         <f t="shared" si="2"/>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B85" s="39">
         <f t="shared" si="2"/>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C85" s="39" t="str">
         <f>'Raw Name Splitter'!C85</f>
@@ -10249,11 +10247,11 @@
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="39">
         <f t="shared" ref="A87:B102" si="3">IF(ISTEXT(A86)=TRUE,IF(ISTEXT(A85)=TRUE,A84+1,A85+1),A86+1)</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B87" s="39">
         <f t="shared" si="3"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C87" s="39" t="str">
         <f>'Raw Name Splitter'!C87</f>
@@ -10277,11 +10275,11 @@
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="39">
         <f t="shared" si="3"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B88" s="39">
         <f t="shared" si="3"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C88" s="39" t="str">
         <f>'Raw Name Splitter'!C88</f>
@@ -10305,11 +10303,11 @@
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="39">
         <f t="shared" si="3"/>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B89" s="39">
         <f t="shared" si="3"/>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C89" s="39" t="str">
         <f>'Raw Name Splitter'!C89</f>
@@ -10333,11 +10331,11 @@
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="39">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B90" s="39">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C90" s="39" t="str">
         <f>'Raw Name Splitter'!C90</f>
@@ -10361,11 +10359,11 @@
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="39">
         <f t="shared" si="3"/>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B91" s="39">
         <f t="shared" si="3"/>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C91" s="39" t="str">
         <f>'Raw Name Splitter'!C91</f>
@@ -10389,11 +10387,11 @@
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="39">
         <f t="shared" si="3"/>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B92" s="39">
         <f t="shared" si="3"/>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C92" s="39" t="str">
         <f>'Raw Name Splitter'!C92</f>
@@ -10417,11 +10415,11 @@
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="39">
         <f t="shared" si="3"/>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B93" s="39">
         <f t="shared" si="3"/>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C93" s="39" t="str">
         <f>'Raw Name Splitter'!C93</f>
@@ -10445,11 +10443,11 @@
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="39">
         <f t="shared" si="3"/>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B94" s="39">
         <f t="shared" si="3"/>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C94" s="39" t="str">
         <f>'Raw Name Splitter'!C94</f>
@@ -10473,11 +10471,11 @@
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="39">
         <f t="shared" si="3"/>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B95" s="39">
         <f t="shared" si="3"/>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C95" s="39" t="str">
         <f>'Raw Name Splitter'!C95</f>
@@ -10501,11 +10499,11 @@
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="39">
         <f t="shared" si="3"/>
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B96" s="39">
         <f t="shared" si="3"/>
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C96" s="39" t="str">
         <f>'Raw Name Splitter'!C96</f>
@@ -10529,11 +10527,11 @@
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="39">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B97" s="39">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C97" s="39" t="str">
         <f>'Raw Name Splitter'!C97</f>
@@ -10557,11 +10555,11 @@
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="39">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B98" s="39">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C98" s="39" t="str">
         <f>'Raw Name Splitter'!C98</f>
@@ -10585,11 +10583,11 @@
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="39">
         <f t="shared" si="3"/>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B99" s="39">
         <f t="shared" si="3"/>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C99" s="39" t="str">
         <f>'Raw Name Splitter'!C99</f>
@@ -10613,11 +10611,11 @@
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="39">
         <f t="shared" si="3"/>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B100" s="39">
         <f t="shared" si="3"/>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C100" s="39" t="str">
         <f>'Raw Name Splitter'!C100</f>
@@ -10641,11 +10639,11 @@
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="39">
         <f t="shared" si="3"/>
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B101" s="39">
         <f t="shared" si="3"/>
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C101" s="39" t="str">
         <f>'Raw Name Splitter'!C101</f>
@@ -10669,11 +10667,11 @@
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="39">
         <f t="shared" si="3"/>
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B102" s="39">
         <f t="shared" si="3"/>
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C102" s="39" t="str">
         <f>'Raw Name Splitter'!C102</f>
@@ -10696,12 +10694,12 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="39">
-        <f t="shared" ref="A103:B118" si="4">IF(ISTEXT(A102)=TRUE,IF(ISTEXT(A101)=TRUE,A100+1,A101+1),A102+1)</f>
-        <v>96</v>
+        <f t="shared" ref="A103:B117" si="4">IF(ISTEXT(A102)=TRUE,IF(ISTEXT(A101)=TRUE,A100+1,A101+1),A102+1)</f>
+        <v>95</v>
       </c>
       <c r="B103" s="39">
         <f t="shared" si="4"/>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C103" s="39" t="str">
         <f>'Raw Name Splitter'!C103</f>
@@ -10725,11 +10723,11 @@
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="39">
         <f t="shared" si="4"/>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B104" s="39">
         <f t="shared" si="4"/>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C104" s="39" t="str">
         <f>'Raw Name Splitter'!C104</f>
@@ -10753,11 +10751,11 @@
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="39">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B105" s="39">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C105" s="39" t="str">
         <f>'Raw Name Splitter'!C105</f>
@@ -10781,11 +10779,11 @@
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="39">
         <f t="shared" si="4"/>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B106" s="39">
         <f t="shared" si="4"/>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C106" s="39" t="str">
         <f>'Raw Name Splitter'!C106</f>
@@ -10809,11 +10807,11 @@
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="39">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B107" s="39">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C107" s="39" t="str">
         <f>'Raw Name Splitter'!C107</f>
@@ -10837,11 +10835,11 @@
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="39">
         <f t="shared" si="4"/>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B108" s="39">
         <f t="shared" si="4"/>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C108" s="39" t="str">
         <f>'Raw Name Splitter'!C108</f>
@@ -10865,11 +10863,11 @@
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="39">
         <f t="shared" si="4"/>
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B109" s="39">
         <f t="shared" si="4"/>
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C109" s="39" t="str">
         <f>'Raw Name Splitter'!C109</f>
@@ -10893,11 +10891,11 @@
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="39">
         <f t="shared" si="4"/>
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B110" s="39">
         <f t="shared" si="4"/>
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C110" s="39" t="str">
         <f>'Raw Name Splitter'!C110</f>
@@ -10921,11 +10919,11 @@
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="39">
         <f t="shared" si="4"/>
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B111" s="39">
         <f t="shared" si="4"/>
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C111" s="39" t="str">
         <f>'Raw Name Splitter'!C111</f>
@@ -10949,11 +10947,11 @@
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="39">
         <f t="shared" si="4"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B112" s="39">
         <f t="shared" si="4"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C112" s="39" t="str">
         <f>'Raw Name Splitter'!C112</f>
@@ -11003,11 +11001,11 @@
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="39">
         <f t="shared" si="4"/>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B114" s="39">
         <f t="shared" si="4"/>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C114" s="39" t="str">
         <f>'Raw Name Splitter'!C114</f>
@@ -11057,11 +11055,11 @@
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="39">
         <f t="shared" si="4"/>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B116" s="39">
         <f t="shared" si="4"/>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C116" s="39" t="str">
         <f>'Raw Name Splitter'!C116</f>
@@ -11085,11 +11083,11 @@
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="39">
         <f t="shared" si="4"/>
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B117" s="39">
         <f t="shared" si="4"/>
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C117" s="39" t="str">
         <f>'Raw Name Splitter'!C117</f>
@@ -11139,11 +11137,11 @@
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="39">
         <f t="shared" ref="A119:B134" si="5">IF(ISTEXT(A118)=TRUE,IF(ISTEXT(A117)=TRUE,A116+1,A117+1),A118+1)</f>
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B119" s="39">
         <f t="shared" si="5"/>
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C119" s="39" t="str">
         <f>'Raw Name Splitter'!C119</f>
@@ -11167,11 +11165,11 @@
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="39">
         <f t="shared" si="5"/>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B120" s="39">
         <f t="shared" si="5"/>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C120" s="39" t="str">
         <f>'Raw Name Splitter'!C120</f>
@@ -11195,11 +11193,11 @@
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="39">
         <f t="shared" si="5"/>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B121" s="39">
         <f t="shared" si="5"/>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C121" s="39" t="str">
         <f>'Raw Name Splitter'!C121</f>
@@ -11223,11 +11221,11 @@
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="39">
         <f t="shared" si="5"/>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B122" s="39">
         <f t="shared" si="5"/>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C122" s="39" t="str">
         <f>'Raw Name Splitter'!C122</f>
@@ -11251,11 +11249,11 @@
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="39">
         <f t="shared" si="5"/>
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B123" s="39">
         <f t="shared" si="5"/>
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C123" s="39" t="str">
         <f>'Raw Name Splitter'!C123</f>
@@ -11279,11 +11277,11 @@
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="39">
         <f t="shared" si="5"/>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B124" s="39">
         <f t="shared" si="5"/>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C124" s="39" t="str">
         <f>'Raw Name Splitter'!C124</f>
@@ -11307,11 +11305,11 @@
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="39">
         <f t="shared" si="5"/>
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B125" s="39">
         <f t="shared" si="5"/>
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C125" s="39" t="str">
         <f>'Raw Name Splitter'!C125</f>
@@ -11335,11 +11333,11 @@
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="39">
         <f t="shared" si="5"/>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B126" s="39">
         <f t="shared" si="5"/>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C126" s="39" t="str">
         <f>'Raw Name Splitter'!C126</f>
@@ -11363,11 +11361,11 @@
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="39">
         <f t="shared" si="5"/>
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B127" s="39">
         <f t="shared" si="5"/>
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C127" s="39" t="str">
         <f>'Raw Name Splitter'!C127</f>
@@ -11391,11 +11389,11 @@
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="39">
         <f t="shared" si="5"/>
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B128" s="39">
         <f t="shared" si="5"/>
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C128" s="39" t="str">
         <f>'Raw Name Splitter'!C128</f>
@@ -11419,11 +11417,11 @@
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="39">
         <f t="shared" si="5"/>
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B129" s="39">
         <f t="shared" si="5"/>
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C129" s="39" t="str">
         <f>'Raw Name Splitter'!C129</f>
@@ -11447,11 +11445,11 @@
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="39">
         <f t="shared" si="5"/>
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B130" s="39">
         <f t="shared" si="5"/>
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C130" s="39" t="str">
         <f>'Raw Name Splitter'!C130</f>
@@ -11475,11 +11473,11 @@
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="39">
         <f t="shared" si="5"/>
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B131" s="39">
         <f t="shared" si="5"/>
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C131" s="39" t="str">
         <f>'Raw Name Splitter'!C131</f>
@@ -11503,11 +11501,11 @@
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="39">
         <f t="shared" si="5"/>
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B132" s="39">
         <f t="shared" si="5"/>
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C132" s="39" t="str">
         <f>'Raw Name Splitter'!C132</f>
@@ -11531,11 +11529,11 @@
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="39">
         <f t="shared" si="5"/>
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B133" s="39">
         <f t="shared" si="5"/>
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C133" s="39" t="str">
         <f>'Raw Name Splitter'!C133</f>
@@ -11559,11 +11557,11 @@
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="39">
         <f t="shared" si="5"/>
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B134" s="39">
         <f t="shared" si="5"/>
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C134" s="39" t="str">
         <f>'Raw Name Splitter'!C134</f>
@@ -11587,11 +11585,11 @@
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="39">
         <f t="shared" ref="A135:B150" si="6">IF(ISTEXT(A134)=TRUE,IF(ISTEXT(A133)=TRUE,A132+1,A133+1),A134+1)</f>
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B135" s="39">
         <f t="shared" si="6"/>
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C135" s="39" t="str">
         <f>'Raw Name Splitter'!C135</f>
@@ -11615,11 +11613,11 @@
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="39">
         <f t="shared" si="6"/>
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B136" s="39">
         <f t="shared" si="6"/>
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C136" s="39" t="str">
         <f>'Raw Name Splitter'!C136</f>
@@ -11643,11 +11641,11 @@
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="39">
         <f t="shared" si="6"/>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B137" s="39">
         <f t="shared" si="6"/>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C137" s="39" t="str">
         <f>'Raw Name Splitter'!C137</f>
@@ -11671,11 +11669,11 @@
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="39">
         <f t="shared" si="6"/>
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B138" s="39">
         <f t="shared" si="6"/>
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C138" s="39" t="str">
         <f>'Raw Name Splitter'!C138</f>
@@ -11699,11 +11697,11 @@
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="39">
         <f t="shared" si="6"/>
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B139" s="39">
         <f t="shared" si="6"/>
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C139" s="39" t="str">
         <f>'Raw Name Splitter'!C139</f>
@@ -11727,11 +11725,11 @@
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="39">
         <f t="shared" si="6"/>
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B140" s="39">
         <f t="shared" si="6"/>
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C140" s="39" t="str">
         <f>'Raw Name Splitter'!C140</f>
@@ -11755,11 +11753,11 @@
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="39">
         <f t="shared" si="6"/>
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B141" s="39">
         <f t="shared" si="6"/>
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C141" s="39" t="str">
         <f>'Raw Name Splitter'!C141</f>
@@ -11783,11 +11781,11 @@
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="39">
         <f t="shared" si="6"/>
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B142" s="39">
         <f t="shared" si="6"/>
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C142" s="39" t="str">
         <f>'Raw Name Splitter'!C142</f>
@@ -11811,11 +11809,11 @@
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="39">
         <f t="shared" si="6"/>
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B143" s="39">
         <f t="shared" si="6"/>
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C143" s="39" t="str">
         <f>'Raw Name Splitter'!C143</f>
@@ -11839,11 +11837,11 @@
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="39">
         <f t="shared" si="6"/>
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B144" s="39">
         <f t="shared" si="6"/>
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C144" s="39" t="str">
         <f>'Raw Name Splitter'!C144</f>
@@ -11867,11 +11865,11 @@
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="39">
         <f t="shared" si="6"/>
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B145" s="39">
         <f t="shared" si="6"/>
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C145" s="39" t="str">
         <f>'Raw Name Splitter'!C145</f>
@@ -11895,11 +11893,11 @@
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="39">
         <f t="shared" si="6"/>
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B146" s="39">
         <f t="shared" si="6"/>
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C146" s="39" t="str">
         <f>'Raw Name Splitter'!C146</f>
@@ -11923,11 +11921,11 @@
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="39">
         <f t="shared" si="6"/>
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B147" s="39">
         <f t="shared" si="6"/>
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C147" s="39" t="str">
         <f>'Raw Name Splitter'!C147</f>
@@ -11951,11 +11949,11 @@
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="39">
         <f t="shared" si="6"/>
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B148" s="39">
         <f t="shared" si="6"/>
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C148" s="39" t="str">
         <f>'Raw Name Splitter'!C148</f>
@@ -11979,11 +11977,11 @@
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="39">
         <f t="shared" si="6"/>
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B149" s="39">
         <f t="shared" si="6"/>
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C149" s="39" t="str">
         <f>'Raw Name Splitter'!C149</f>
@@ -12007,11 +12005,11 @@
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="39">
         <f t="shared" si="6"/>
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B150" s="39">
         <f t="shared" si="6"/>
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C150" s="39" t="str">
         <f>'Raw Name Splitter'!C150</f>
@@ -12035,11 +12033,11 @@
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="39">
         <f t="shared" ref="A151:B166" si="7">IF(ISTEXT(A150)=TRUE,IF(ISTEXT(A149)=TRUE,A148+1,A149+1),A150+1)</f>
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B151" s="39">
         <f t="shared" si="7"/>
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C151" s="39" t="str">
         <f>'Raw Name Splitter'!C151</f>
@@ -12063,11 +12061,11 @@
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="39">
         <f t="shared" si="7"/>
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B152" s="39">
         <f t="shared" si="7"/>
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C152" s="39" t="str">
         <f>'Raw Name Splitter'!C152</f>
@@ -12091,11 +12089,11 @@
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="39">
         <f t="shared" si="7"/>
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B153" s="39">
         <f t="shared" si="7"/>
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C153" s="39" t="str">
         <f>'Raw Name Splitter'!C153</f>
@@ -12119,11 +12117,11 @@
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="39">
         <f t="shared" si="7"/>
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B154" s="39">
         <f t="shared" si="7"/>
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C154" s="39" t="str">
         <f>'Raw Name Splitter'!C154</f>
@@ -12147,11 +12145,11 @@
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="39">
         <f t="shared" si="7"/>
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B155" s="39">
         <f t="shared" si="7"/>
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C155" s="39" t="str">
         <f>'Raw Name Splitter'!C155</f>
@@ -12175,11 +12173,11 @@
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="39">
         <f t="shared" si="7"/>
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B156" s="39">
         <f t="shared" si="7"/>
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C156" s="39" t="str">
         <f>'Raw Name Splitter'!C156</f>
@@ -12203,11 +12201,11 @@
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="39">
         <f t="shared" si="7"/>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B157" s="39">
         <f t="shared" si="7"/>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C157" s="39" t="str">
         <f>'Raw Name Splitter'!C157</f>
@@ -12231,11 +12229,11 @@
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="39">
         <f t="shared" si="7"/>
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B158" s="39">
         <f t="shared" si="7"/>
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C158" s="39" t="str">
         <f>'Raw Name Splitter'!C158</f>
@@ -12942,7 +12940,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="39">
-        <f t="shared" ref="A183:B198" si="9">IF(ISTEXT(A183)=TRUE,IF(ISTEXT(A182)=TRUE,A181+1,A182+1),A183+1)</f>
+        <f t="shared" ref="A184:B198" si="9">IF(ISTEXT(A183)=TRUE,IF(ISTEXT(A182)=TRUE,A181+1,A182+1),A183+1)</f>
         <v>167</v>
       </c>
       <c r="B184" s="39">
@@ -18291,11 +18289,11 @@
       </c>
       <c r="H69" s="1" t="str">
         <f>VLOOKUP(J69,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Dankers</v>
+        <v>Silva</v>
       </c>
       <c r="I69" s="1" t="str">
         <f>VLOOKUP(J69,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Hans</v>
+        <v>Walick</v>
       </c>
       <c r="J69">
         <v>56</v>
@@ -18304,9 +18302,9 @@
         <f>VLOOKUP(J68,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L69" s="1">
+      <c r="L69" s="1" t="str">
         <f>VLOOKUP(J69,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Wall-lick Duh Silva</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -18334,22 +18332,22 @@
       </c>
       <c r="H70" s="1" t="str">
         <f>VLOOKUP(J70,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Silva</v>
+        <v>Dean</v>
       </c>
       <c r="I70" s="1" t="str">
         <f>VLOOKUP(J70,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Walick</v>
+        <v>Cooper</v>
       </c>
       <c r="J70">
         <v>57</v>
       </c>
       <c r="K70" t="str">
         <f>VLOOKUP(J69,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
+        <v>Da</v>
       </c>
       <c r="L70" s="1" t="str">
         <f>VLOOKUP(J70,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Wall-lick Duh Silva</v>
+        <v>(Coo-pur) (Joe-Sef) (Deen)</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -18377,22 +18375,22 @@
       </c>
       <c r="H71" s="1" t="str">
         <f>VLOOKUP(J71,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Dean</v>
+        <v>Deji</v>
       </c>
       <c r="I71" s="1" t="str">
         <f>VLOOKUP(J71,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Cooper</v>
+        <v>Happiness</v>
       </c>
       <c r="J71">
         <v>58</v>
       </c>
       <c r="K71" t="str">
         <f>VLOOKUP(J70,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Da</v>
+        <v>Joseph</v>
       </c>
       <c r="L71" s="1" t="str">
         <f>VLOOKUP(J71,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>(Coo-pur) (Joe-Sef) (Deen)</v>
+        <v xml:space="preserve">o sa ru gue </v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -18420,22 +18418,22 @@
       </c>
       <c r="H72" s="1" t="str">
         <f>VLOOKUP(J72,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Deji</v>
+        <v>Denmark</v>
       </c>
       <c r="I72" s="1" t="str">
         <f>VLOOKUP(J72,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Happiness</v>
+        <v>Jack</v>
       </c>
       <c r="J72">
         <v>59</v>
       </c>
       <c r="K72" t="str">
         <f>VLOOKUP(J71,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Joseph</v>
-      </c>
-      <c r="L72" s="1" t="str">
+        <v>osarugue</v>
+      </c>
+      <c r="L72" s="1">
         <f>VLOOKUP(J72,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v xml:space="preserve">o sa ru gue </v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -18463,22 +18461,22 @@
       </c>
       <c r="H73" s="1" t="str">
         <f>VLOOKUP(J73,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Denmark</v>
+        <v>DiDonato</v>
       </c>
       <c r="I73" s="1" t="str">
         <f>VLOOKUP(J73,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jack</v>
+        <v>Julie</v>
       </c>
       <c r="J73">
         <v>60</v>
       </c>
       <c r="K73" t="str">
         <f>VLOOKUP(J72,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>osarugue</v>
-      </c>
-      <c r="L73" s="1">
+        <v/>
+      </c>
+      <c r="L73" s="1" t="str">
         <f>VLOOKUP(J73,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Dee-doe-na-to</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18506,11 +18504,11 @@
       </c>
       <c r="H74" s="1" t="str">
         <f>VLOOKUP(J74,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>DiDonato</v>
+        <v>DiSerio</v>
       </c>
       <c r="I74" s="1" t="str">
         <f>VLOOKUP(J74,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Julie</v>
+        <v>Dante</v>
       </c>
       <c r="J74" s="3">
         <v>61</v>
@@ -18519,9 +18517,9 @@
         <f>VLOOKUP(J73,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L74" s="1" t="str">
+      <c r="L74" s="1">
         <f>VLOOKUP(J74,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Dee-doe-na-to</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -18553,7 +18551,7 @@
       </c>
       <c r="I75" s="1" t="str">
         <f>VLOOKUP(J75,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="J75">
         <v>62</v>
@@ -18562,9 +18560,9 @@
         <f>VLOOKUP(J74,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L75" s="1">
+      <c r="L75" s="1" t="str">
         <f>VLOOKUP(J75,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Dis-ear-e-o</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -18592,22 +18590,22 @@
       </c>
       <c r="H76" s="1" t="str">
         <f>VLOOKUP(J76,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>DiSerio</v>
+        <v>Donaghey</v>
       </c>
       <c r="I76" s="1" t="str">
         <f>VLOOKUP(J76,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Antonio</v>
+        <v>Caitlin</v>
       </c>
       <c r="J76">
         <v>63</v>
       </c>
       <c r="K76" t="str">
         <f>VLOOKUP(J75,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="L76" s="1" t="str">
         <f>VLOOKUP(J76,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Dis-ear-e-o</v>
+        <v>Don-a-hee</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -18635,22 +18633,22 @@
       </c>
       <c r="H77" s="1" t="str">
         <f>VLOOKUP(J77,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Donaghey</v>
+        <v>Donahue</v>
       </c>
       <c r="I77" s="1" t="str">
         <f>VLOOKUP(J77,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Caitlin</v>
+        <v>Quinn</v>
       </c>
       <c r="J77">
         <v>64</v>
       </c>
       <c r="K77" t="str">
         <f>VLOOKUP(J76,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Joseph</v>
-      </c>
-      <c r="L77" s="1" t="str">
+        <v>Anne</v>
+      </c>
+      <c r="L77" s="1">
         <f>VLOOKUP(J77,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Don-a-hee</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:12" s="3" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18678,22 +18676,22 @@
       </c>
       <c r="H78" s="37" t="str">
         <f>VLOOKUP(J78,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Donahue</v>
+        <v>Doroquez</v>
       </c>
       <c r="I78" s="2" t="str">
         <f>VLOOKUP(J78,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Quinn</v>
+        <v>Alana</v>
       </c>
       <c r="J78">
         <v>65</v>
       </c>
       <c r="K78" t="str">
         <f>VLOOKUP(J77,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Anne</v>
-      </c>
-      <c r="L78" s="1">
+        <v>Kendall</v>
+      </c>
+      <c r="L78" s="1" t="str">
         <f>VLOOKUP(J78,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Ah-lah-na May-Lynn Yah-mah-key Door-o-kez</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -18721,22 +18719,22 @@
       </c>
       <c r="H79" s="1" t="str">
         <f>VLOOKUP(J79,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Doroquez</v>
+        <v>Duca</v>
       </c>
       <c r="I79" s="1" t="str">
         <f>VLOOKUP(J79,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Alana</v>
+        <v>Cassidy</v>
       </c>
       <c r="J79">
         <v>66</v>
       </c>
       <c r="K79" s="3" t="str">
         <f>VLOOKUP(J78,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Kendall</v>
-      </c>
-      <c r="L79" s="1" t="str">
+        <v>Mei-Lin Yamaki</v>
+      </c>
+      <c r="L79" s="1">
         <f>VLOOKUP(J79,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Ah-lah-na May-Lynn Yah-mah-key Door-o-kez</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -18764,22 +18762,22 @@
       </c>
       <c r="H80" s="1" t="str">
         <f>VLOOKUP(J80,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Duca</v>
+        <v>DuRoss</v>
       </c>
       <c r="I80" s="1" t="str">
         <f>VLOOKUP(J80,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Cassidy</v>
+        <v>Kyle</v>
       </c>
       <c r="J80">
         <v>67</v>
       </c>
       <c r="K80" t="str">
         <f>VLOOKUP(J79,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Mei-Lin Yamaki</v>
-      </c>
-      <c r="L80" s="1">
+        <v/>
+      </c>
+      <c r="L80" s="1" t="str">
         <f>VLOOKUP(J80,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Dew-Ross</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -18811,7 +18809,7 @@
       </c>
       <c r="I81" s="1" t="str">
         <f>VLOOKUP(J81,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Kyle</v>
+        <v>Sean</v>
       </c>
       <c r="J81">
         <v>68</v>
@@ -18820,9 +18818,9 @@
         <f>VLOOKUP(J80,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L81" s="1" t="str">
+      <c r="L81" s="1">
         <f>VLOOKUP(J81,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Dew-Ross</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -18850,11 +18848,11 @@
       </c>
       <c r="H82" s="1" t="str">
         <f>VLOOKUP(J82,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>DuRoss</v>
+        <v>Dyment</v>
       </c>
       <c r="I82" s="1" t="str">
         <f>VLOOKUP(J82,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Sean</v>
+        <v>William</v>
       </c>
       <c r="J82">
         <v>69</v>
@@ -18893,11 +18891,11 @@
       </c>
       <c r="H83" s="1" t="str">
         <f>VLOOKUP(J83,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Dyment</v>
+        <v>Eliet</v>
       </c>
       <c r="I83" s="1" t="str">
         <f>VLOOKUP(J83,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>William</v>
+        <v>Luca</v>
       </c>
       <c r="J83">
         <v>70</v>
@@ -18936,11 +18934,11 @@
       </c>
       <c r="H84" s="1" t="str">
         <f>VLOOKUP(J84,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Eliet</v>
+        <v>Ellis</v>
       </c>
       <c r="I84" s="1" t="str">
         <f>VLOOKUP(J84,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Luca</v>
+        <v>Finn</v>
       </c>
       <c r="J84">
         <v>71</v>
@@ -18979,11 +18977,11 @@
       </c>
       <c r="H85" s="1" t="str">
         <f>VLOOKUP(J85,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Ellis</v>
+        <v>Emmanuel</v>
       </c>
       <c r="I85" s="1" t="str">
         <f>VLOOKUP(J85,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Finn</v>
+        <v>Levi</v>
       </c>
       <c r="J85">
         <v>72</v>
@@ -19022,11 +19020,11 @@
       </c>
       <c r="H86" s="1" t="str">
         <f>VLOOKUP(J86,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Emmanuel</v>
+        <v>Encarnacao</v>
       </c>
       <c r="I86" s="1" t="str">
         <f>VLOOKUP(J86,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Levi</v>
+        <v>Kamryn</v>
       </c>
       <c r="J86" s="3">
         <v>73</v>
@@ -19035,9 +19033,9 @@
         <f>VLOOKUP(J85,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L86" s="1">
+      <c r="L86" s="1" t="str">
         <f>VLOOKUP(J86,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>In - car - naw - see - oh</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -19065,11 +19063,11 @@
       </c>
       <c r="H87" s="1" t="str">
         <f>VLOOKUP(J87,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Encarnacao</v>
+        <v>Fortes</v>
       </c>
       <c r="I87" s="1" t="str">
         <f>VLOOKUP(J87,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Kamryn</v>
+        <v>Samuel</v>
       </c>
       <c r="J87">
         <v>74</v>
@@ -19080,7 +19078,7 @@
       </c>
       <c r="L87" s="1" t="str">
         <f>VLOOKUP(J87,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>In - car - naw - see - oh</v>
+        <v xml:space="preserve">Eee-wald </v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -19108,11 +19106,11 @@
       </c>
       <c r="H88" s="1" t="str">
         <f>VLOOKUP(J88,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Fortes</v>
+        <v>Fantasia</v>
       </c>
       <c r="I88" s="1" t="str">
         <f>VLOOKUP(J88,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Samuel</v>
+        <v>Kaylie</v>
       </c>
       <c r="J88">
         <v>75</v>
@@ -19123,7 +19121,7 @@
       </c>
       <c r="L88" s="1" t="str">
         <f>VLOOKUP(J88,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v xml:space="preserve">Eee-wald </v>
+        <v>kay-lee</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -19151,11 +19149,11 @@
       </c>
       <c r="H89" s="1" t="str">
         <f>VLOOKUP(J89,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Fantasia</v>
+        <v>Farnham</v>
       </c>
       <c r="I89" s="1" t="str">
         <f>VLOOKUP(J89,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Kaylie</v>
+        <v>Vince</v>
       </c>
       <c r="J89">
         <v>76</v>
@@ -19164,9 +19162,9 @@
         <f>VLOOKUP(J88,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L89" s="1" t="str">
+      <c r="L89" s="1">
         <f>VLOOKUP(J89,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>kay-lee</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19194,11 +19192,11 @@
       </c>
       <c r="H90" s="37" t="str">
         <f>VLOOKUP(J90,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Farnham</v>
+        <v>Farris</v>
       </c>
       <c r="I90" s="2" t="str">
         <f>VLOOKUP(J90,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Vince</v>
+        <v>Colby</v>
       </c>
       <c r="J90">
         <v>77</v>
@@ -19237,11 +19235,11 @@
       </c>
       <c r="H91" s="1" t="str">
         <f>VLOOKUP(J91,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Farris</v>
+        <v>Fernandez</v>
       </c>
       <c r="I91" s="1" t="str">
         <f>VLOOKUP(J91,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Colby</v>
+        <v>Bryan</v>
       </c>
       <c r="J91">
         <v>78</v>
@@ -19280,11 +19278,11 @@
       </c>
       <c r="H92" s="1" t="str">
         <f>VLOOKUP(J92,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Fernandez</v>
+        <v>Fiore</v>
       </c>
       <c r="I92" s="1" t="str">
         <f>VLOOKUP(J92,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Bryan</v>
+        <v>Thomas</v>
       </c>
       <c r="J92">
         <v>79</v>
@@ -19323,11 +19321,11 @@
       </c>
       <c r="H93" s="1" t="str">
         <f>VLOOKUP(J93,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Fiore</v>
+        <v>Flaherty</v>
       </c>
       <c r="I93" s="1" t="str">
         <f>VLOOKUP(J93,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Thomas</v>
+        <v>Finn</v>
       </c>
       <c r="J93">
         <v>80</v>
@@ -19366,22 +19364,22 @@
       </c>
       <c r="H94" s="1" t="str">
         <f>VLOOKUP(J94,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Flaherty</v>
+        <v>Forse</v>
       </c>
       <c r="I94" s="1" t="str">
         <f>VLOOKUP(J94,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Finn</v>
+        <v>Matthew</v>
       </c>
       <c r="J94">
         <v>81</v>
       </c>
       <c r="K94" t="str">
         <f>VLOOKUP(J93,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="L94" s="1">
+        <v>Patrick</v>
+      </c>
+      <c r="L94" s="1" t="str">
         <f>VLOOKUP(J94,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v xml:space="preserve">"Force",   rhymes with HORSE </v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -19409,22 +19407,22 @@
       </c>
       <c r="H95" s="1" t="str">
         <f>VLOOKUP(J95,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Forse</v>
+        <v>Frank</v>
       </c>
       <c r="I95" s="1" t="str">
         <f>VLOOKUP(J95,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Matthew</v>
+        <v>Jacob</v>
       </c>
       <c r="J95">
         <v>82</v>
       </c>
       <c r="K95" t="str">
         <f>VLOOKUP(J94,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Patrick</v>
-      </c>
-      <c r="L95" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L95" s="1">
         <f>VLOOKUP(J95,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v xml:space="preserve">"Force",   rhymes with HORSE </v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -19452,11 +19450,11 @@
       </c>
       <c r="H96" s="1" t="str">
         <f>VLOOKUP(J96,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Frank</v>
+        <v>Fratto</v>
       </c>
       <c r="I96" s="1" t="str">
         <f>VLOOKUP(J96,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jacob</v>
+        <v>Anthony</v>
       </c>
       <c r="J96">
         <v>83</v>
@@ -19495,11 +19493,11 @@
       </c>
       <c r="H97" s="1" t="str">
         <f>VLOOKUP(J97,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Fratto</v>
+        <v>Fucarile</v>
       </c>
       <c r="I97" s="1" t="str">
         <f>VLOOKUP(J97,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Anthony</v>
+        <v>Gavin</v>
       </c>
       <c r="J97">
         <v>84</v>
@@ -19508,9 +19506,9 @@
         <f>VLOOKUP(J96,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L97" s="1">
+      <c r="L97" s="1" t="str">
         <f>VLOOKUP(J97,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Fuke-ah-rill</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19538,11 +19536,11 @@
       </c>
       <c r="H98" s="1" t="str">
         <f>VLOOKUP(J98,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Fucarile</v>
+        <v>Fusco</v>
       </c>
       <c r="I98" s="1" t="str">
         <f>VLOOKUP(J98,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Gavin</v>
+        <v>Cole</v>
       </c>
       <c r="J98" s="3">
         <v>85</v>
@@ -19551,9 +19549,9 @@
         <f>VLOOKUP(J97,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L98" s="1" t="str">
+      <c r="L98" s="1">
         <f>VLOOKUP(J98,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Fuke-ah-rill</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -19581,11 +19579,11 @@
       </c>
       <c r="H99" s="1" t="str">
         <f>VLOOKUP(J99,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Fusco</v>
+        <v>Gaeta</v>
       </c>
       <c r="I99" s="1" t="str">
         <f>VLOOKUP(J99,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Cole</v>
+        <v>Paul</v>
       </c>
       <c r="J99">
         <v>86</v>
@@ -19624,22 +19622,22 @@
       </c>
       <c r="H100" s="1" t="str">
         <f>VLOOKUP(J100,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Gaeta</v>
+        <v>Gager</v>
       </c>
       <c r="I100" s="1" t="str">
         <f>VLOOKUP(J100,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Paul</v>
+        <v>Lucas</v>
       </c>
       <c r="J100">
         <v>87</v>
       </c>
       <c r="K100" t="str">
         <f>VLOOKUP(J99,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="L100" s="1">
+        <v>Richard</v>
+      </c>
+      <c r="L100" s="1" t="str">
         <f>VLOOKUP(J100,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Gay-jer</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -19667,22 +19665,22 @@
       </c>
       <c r="H101" s="1" t="str">
         <f>VLOOKUP(J101,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Gager</v>
+        <v>Galindo</v>
       </c>
       <c r="I101" s="1" t="str">
         <f>VLOOKUP(J101,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Lucas</v>
+        <v>Nevaeh</v>
       </c>
       <c r="J101">
         <v>88</v>
       </c>
       <c r="K101" t="str">
         <f>VLOOKUP(J100,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Richard</v>
-      </c>
-      <c r="L101" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L101" s="1">
         <f>VLOOKUP(J101,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Gay-jer</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19710,11 +19708,11 @@
       </c>
       <c r="H102" s="37" t="str">
         <f>VLOOKUP(J102,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Galindo</v>
+        <v>Gallagher</v>
       </c>
       <c r="I102" s="2" t="str">
         <f>VLOOKUP(J102,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Nevaeh</v>
+        <v>Joseph</v>
       </c>
       <c r="J102">
         <v>89</v>
@@ -19723,9 +19721,9 @@
         <f>VLOOKUP(J101,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L102" s="1">
+      <c r="L102" s="1" t="str">
         <f>VLOOKUP(J102,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Joseph Gallagher</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -19754,11 +19752,11 @@
       </c>
       <c r="H103" s="1" t="str">
         <f>VLOOKUP(J103,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Gallagher</v>
+        <v>Gauvin</v>
       </c>
       <c r="I103" s="1" t="str">
         <f>VLOOKUP(J103,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Joseph</v>
+        <v>Brendan</v>
       </c>
       <c r="J103">
         <v>90</v>
@@ -19769,7 +19767,7 @@
       </c>
       <c r="L103" s="1" t="str">
         <f>VLOOKUP(J103,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Joseph Gallagher</v>
+        <v>Gau-vin</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -19798,11 +19796,11 @@
       </c>
       <c r="H104" s="1" t="str">
         <f>VLOOKUP(J104,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Gauvin</v>
+        <v>Gebeyaw</v>
       </c>
       <c r="I104" s="1" t="str">
         <f>VLOOKUP(J104,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Brendan</v>
+        <v>Bereket</v>
       </c>
       <c r="J104">
         <v>91</v>
@@ -19811,9 +19809,9 @@
         <f>VLOOKUP(J103,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L104" s="1" t="str">
+      <c r="L104" s="1">
         <f>VLOOKUP(J104,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Gau-vin</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -19842,11 +19840,11 @@
       </c>
       <c r="H105" s="1" t="str">
         <f>VLOOKUP(J105,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Gebeyaw</v>
+        <v>Gellot</v>
       </c>
       <c r="I105" s="1" t="str">
         <f>VLOOKUP(J105,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Bereket</v>
+        <v>Alix</v>
       </c>
       <c r="J105">
         <v>92</v>
@@ -19886,11 +19884,11 @@
       </c>
       <c r="H106" s="1" t="str">
         <f>VLOOKUP(J106,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Gellot</v>
+        <v>Gigler</v>
       </c>
       <c r="I106" s="1" t="str">
         <f>VLOOKUP(J106,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Alix</v>
+        <v>Cameron</v>
       </c>
       <c r="J106">
         <v>93</v>
@@ -19930,11 +19928,11 @@
       </c>
       <c r="H107" s="1" t="str">
         <f>VLOOKUP(J107,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Gigler</v>
+        <v>Gisetto</v>
       </c>
       <c r="I107" s="1" t="str">
         <f>VLOOKUP(J107,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Cameron</v>
+        <v>Alex</v>
       </c>
       <c r="J107">
         <v>94</v>
@@ -19974,11 +19972,11 @@
       </c>
       <c r="H108" s="1" t="str">
         <f>VLOOKUP(J108,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Gisetto</v>
+        <v>Goldlust</v>
       </c>
       <c r="I108" s="1" t="str">
         <f>VLOOKUP(J108,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Alex</v>
+        <v>Benjamin</v>
       </c>
       <c r="J108">
         <v>95</v>
@@ -20018,11 +20016,11 @@
       </c>
       <c r="H109" s="1" t="str">
         <f>VLOOKUP(J109,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Goldlust</v>
+        <v>Goodfellow</v>
       </c>
       <c r="I109" s="1" t="str">
         <f>VLOOKUP(J109,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Benjamin</v>
+        <v>Jack</v>
       </c>
       <c r="J109">
         <v>96</v>
@@ -20062,11 +20060,11 @@
       </c>
       <c r="H110" s="1" t="str">
         <f>VLOOKUP(J110,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Goodfellow</v>
+        <v>Gorski</v>
       </c>
       <c r="I110" s="1" t="str">
         <f>VLOOKUP(J110,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jack</v>
+        <v>Drew</v>
       </c>
       <c r="J110" s="3">
         <v>97</v>
@@ -20075,9 +20073,9 @@
         <f>VLOOKUP(J109,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L110" s="1">
+      <c r="L110" s="1" t="str">
         <f>VLOOKUP(J110,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Drew</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -20106,11 +20104,11 @@
       </c>
       <c r="H111" s="1" t="str">
         <f>VLOOKUP(J111,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Gorski</v>
+        <v>Gosdanian</v>
       </c>
       <c r="I111" s="1" t="str">
         <f>VLOOKUP(J111,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Drew</v>
+        <v>Lila</v>
       </c>
       <c r="J111">
         <v>98</v>
@@ -20121,7 +20119,7 @@
       </c>
       <c r="L111" s="1" t="str">
         <f>VLOOKUP(J111,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Drew</v>
+        <v>Lylah Gosdainian</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -20150,11 +20148,11 @@
       </c>
       <c r="H112" s="1" t="str">
         <f>VLOOKUP(J112,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Gosdanian</v>
+        <v>Grant</v>
       </c>
       <c r="I112" s="1" t="str">
         <f>VLOOKUP(J112,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Lila</v>
+        <v>Cole</v>
       </c>
       <c r="J112">
         <v>99</v>
@@ -20163,9 +20161,9 @@
         <f>VLOOKUP(J111,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L112" s="1" t="str">
+      <c r="L112" s="1">
         <f>VLOOKUP(J112,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Lylah Gosdainian</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -20194,18 +20192,18 @@
       </c>
       <c r="H113" s="1" t="str">
         <f>VLOOKUP(J113,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Grant</v>
+        <v>Graves</v>
       </c>
       <c r="I113" s="1" t="str">
         <f>VLOOKUP(J113,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Cole</v>
+        <v>Kendall</v>
       </c>
       <c r="J113">
         <v>100</v>
       </c>
       <c r="K113" t="str">
         <f>VLOOKUP(J112,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
+        <v>Sebastian</v>
       </c>
       <c r="L113" s="1">
         <f>VLOOKUP(J113,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -20238,18 +20236,18 @@
       </c>
       <c r="H114" s="37" t="str">
         <f>VLOOKUP(J114,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Graves</v>
+        <v>Haggerty</v>
       </c>
       <c r="I114" s="2" t="str">
         <f>VLOOKUP(J114,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Kendall</v>
+        <v>Griffin</v>
       </c>
       <c r="J114">
         <v>101</v>
       </c>
       <c r="K114" t="str">
         <f>VLOOKUP(J113,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Sebastian</v>
+        <v/>
       </c>
       <c r="L114" s="1">
         <f>VLOOKUP(J114,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -20282,22 +20280,22 @@
       </c>
       <c r="H115" s="1" t="str">
         <f>VLOOKUP(J115,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Haggerty</v>
+        <v>Hall</v>
       </c>
       <c r="I115" s="1" t="str">
         <f>VLOOKUP(J115,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Griffin</v>
+        <v>Andrea</v>
       </c>
       <c r="J115">
         <v>102</v>
       </c>
       <c r="K115" s="3" t="str">
         <f>VLOOKUP(J114,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="L115" s="1">
+        <v>James</v>
+      </c>
+      <c r="L115" s="1" t="str">
         <f>VLOOKUP(J115,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Alpha, November, Delta, Romeo, Echo, alpha</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -20326,22 +20324,22 @@
       </c>
       <c r="H116" s="1" t="str">
         <f>VLOOKUP(J116,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Hall</v>
+        <v>Hamilton</v>
       </c>
       <c r="I116" s="1" t="str">
         <f>VLOOKUP(J116,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Andrea</v>
+        <v>Sarah</v>
       </c>
       <c r="J116">
         <v>103</v>
       </c>
       <c r="K116" t="str">
         <f>VLOOKUP(J115,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>James</v>
-      </c>
-      <c r="L116" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L116" s="1">
         <f>VLOOKUP(J116,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Alpha, November, Delta, Romeo, Echo, alpha</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -20370,11 +20368,11 @@
       </c>
       <c r="H117" s="1" t="str">
         <f>VLOOKUP(J117,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Hamilton</v>
+        <v>Hanifan</v>
       </c>
       <c r="I117" s="1" t="str">
         <f>VLOOKUP(J117,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Sarah</v>
+        <v>Margaret</v>
       </c>
       <c r="J117">
         <v>104</v>
@@ -20414,11 +20412,11 @@
       </c>
       <c r="H118" s="1" t="str">
         <f>VLOOKUP(J118,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Hanifan</v>
+        <v>Harrigan</v>
       </c>
       <c r="I118" s="1" t="str">
         <f>VLOOKUP(J118,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Margaret</v>
+        <v>Cameron</v>
       </c>
       <c r="J118">
         <v>105</v>
@@ -20458,11 +20456,11 @@
       </c>
       <c r="H119" s="1" t="str">
         <f>VLOOKUP(J119,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Harrigan</v>
+        <v>Henri</v>
       </c>
       <c r="I119" s="1" t="str">
         <f>VLOOKUP(J119,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Cameron</v>
+        <v>Victoria</v>
       </c>
       <c r="J119">
         <v>106</v>
@@ -20471,9 +20469,9 @@
         <f>VLOOKUP(J118,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L119" s="1">
+      <c r="L119" s="1" t="str">
         <f>VLOOKUP(J119,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Vic-tor-ee-a Hen-ree</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -20502,11 +20500,11 @@
       </c>
       <c r="H120" s="1" t="str">
         <f>VLOOKUP(J120,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Henri</v>
+        <v>Henrique</v>
       </c>
       <c r="I120" s="1" t="str">
         <f>VLOOKUP(J120,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Victoria</v>
+        <v>Kayke</v>
       </c>
       <c r="J120">
         <v>107</v>
@@ -20515,9 +20513,9 @@
         <f>VLOOKUP(J119,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L120" s="1" t="str">
+      <c r="L120" s="1">
         <f>VLOOKUP(J120,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Vic-tor-ee-a Hen-ree</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -20546,11 +20544,11 @@
       </c>
       <c r="H121" s="1" t="str">
         <f>VLOOKUP(J121,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Henrique</v>
+        <v>Hobson</v>
       </c>
       <c r="I121" s="1" t="str">
         <f>VLOOKUP(J121,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Kayke</v>
+        <v>Jahkye</v>
       </c>
       <c r="J121">
         <v>108</v>
@@ -20559,9 +20557,9 @@
         <f>VLOOKUP(J120,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L121" s="1">
+      <c r="L121" s="1" t="str">
         <f>VLOOKUP(J121,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>JAH-KIA</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20590,11 +20588,11 @@
       </c>
       <c r="H122" s="1" t="str">
         <f>VLOOKUP(J122,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Hobson</v>
+        <v>Holt</v>
       </c>
       <c r="I122" s="1" t="str">
         <f>VLOOKUP(J122,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jahkye</v>
+        <v>Sam</v>
       </c>
       <c r="J122" s="3">
         <v>109</v>
@@ -20603,9 +20601,9 @@
         <f>VLOOKUP(J121,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L122" s="1" t="str">
+      <c r="L122" s="1">
         <f>VLOOKUP(J122,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>JAH-KIA</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -20634,11 +20632,11 @@
       </c>
       <c r="H123" s="1" t="str">
         <f>VLOOKUP(J123,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Holt</v>
+        <v>Houle</v>
       </c>
       <c r="I123" s="1" t="str">
         <f>VLOOKUP(J123,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Sam</v>
+        <v>Benjamin</v>
       </c>
       <c r="J123">
         <v>110</v>
@@ -20647,9 +20645,9 @@
         <f>VLOOKUP(J122,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L123" s="1">
+      <c r="L123" s="1" t="str">
         <f>VLOOKUP(J123,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>H-oo-l</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -20678,11 +20676,11 @@
       </c>
       <c r="H124" s="1" t="str">
         <f>VLOOKUP(J124,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Houle</v>
+        <v>Howell</v>
       </c>
       <c r="I124" s="1" t="str">
         <f>VLOOKUP(J124,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Benjamin</v>
+        <v>Evin</v>
       </c>
       <c r="J124">
         <v>111</v>
@@ -20691,9 +20689,9 @@
         <f>VLOOKUP(J123,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L124" s="1" t="str">
+      <c r="L124" s="1">
         <f>VLOOKUP(J124,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>H-oo-l</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -20722,11 +20720,11 @@
       </c>
       <c r="H125" s="1" t="str">
         <f>VLOOKUP(J125,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Howell</v>
+        <v>Iosua</v>
       </c>
       <c r="I125" s="1" t="str">
         <f>VLOOKUP(J125,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Evin</v>
+        <v>Paul</v>
       </c>
       <c r="J125">
         <v>112</v>
@@ -20735,9 +20733,9 @@
         <f>VLOOKUP(J124,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L125" s="1">
+      <c r="L125" s="1" t="str">
         <f>VLOOKUP(J125,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>I-osh-u-ah</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -20766,22 +20764,22 @@
       </c>
       <c r="H126" s="37" t="str">
         <f>VLOOKUP(J126,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Iosua</v>
+        <v>Jackvony</v>
       </c>
       <c r="I126" s="2" t="str">
         <f>VLOOKUP(J126,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Paul</v>
+        <v>Leah</v>
       </c>
       <c r="J126">
         <v>113</v>
       </c>
       <c r="K126" t="str">
         <f>VLOOKUP(J125,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="L126" s="1" t="str">
+        <v>Joseph</v>
+      </c>
+      <c r="L126" s="1">
         <f>VLOOKUP(J126,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>I-osh-u-ah</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -20810,18 +20808,18 @@
       </c>
       <c r="H127" s="1" t="str">
         <f>VLOOKUP(J127,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Jackvony</v>
+        <v>Jankun</v>
       </c>
       <c r="I127" s="1" t="str">
         <f>VLOOKUP(J127,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Leah</v>
+        <v>Wayne</v>
       </c>
       <c r="J127">
         <v>114</v>
       </c>
       <c r="K127" s="3" t="str">
         <f>VLOOKUP(J126,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="L127" s="1">
         <f>VLOOKUP(J127,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -20854,11 +20852,11 @@
       </c>
       <c r="H128" s="1" t="str">
         <f>VLOOKUP(J128,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Jankun</v>
+        <v>Jenkins</v>
       </c>
       <c r="I128" s="1" t="str">
         <f>VLOOKUP(J128,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Wayne</v>
+        <v>Tristan</v>
       </c>
       <c r="J128">
         <v>115</v>
@@ -20898,11 +20896,11 @@
       </c>
       <c r="H129" s="1" t="str">
         <f>VLOOKUP(J129,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Jenkins</v>
+        <v>Jenney</v>
       </c>
       <c r="I129" s="1" t="str">
         <f>VLOOKUP(J129,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Tristan</v>
+        <v>Evan</v>
       </c>
       <c r="J129">
         <v>116</v>
@@ -20946,7 +20944,7 @@
       </c>
       <c r="I130" s="1" t="str">
         <f>VLOOKUP(J130,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Evan</v>
+        <v>Michael</v>
       </c>
       <c r="J130">
         <v>117</v>
@@ -20986,11 +20984,11 @@
       </c>
       <c r="H131" s="1" t="str">
         <f>VLOOKUP(J131,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Jenney</v>
+        <v>Johnson</v>
       </c>
       <c r="I131" s="1" t="str">
         <f>VLOOKUP(J131,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Michael</v>
+        <v>Luke</v>
       </c>
       <c r="J131">
         <v>118</v>
@@ -21030,11 +21028,11 @@
       </c>
       <c r="H132" s="1" t="str">
         <f>VLOOKUP(J132,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Johnson</v>
+        <v>Jones</v>
       </c>
       <c r="I132" s="1" t="str">
         <f>VLOOKUP(J132,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Luke</v>
+        <v>Maeve</v>
       </c>
       <c r="J132">
         <v>119</v>
@@ -21074,11 +21072,11 @@
       </c>
       <c r="H133" s="1" t="str">
         <f>VLOOKUP(J133,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Jones</v>
+        <v>Jordan</v>
       </c>
       <c r="I133" s="1" t="str">
         <f>VLOOKUP(J133,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Maeve</v>
+        <v>Nolan</v>
       </c>
       <c r="J133">
         <v>120</v>
@@ -21118,11 +21116,11 @@
       </c>
       <c r="H134" s="1" t="str">
         <f>VLOOKUP(J134,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Jordan</v>
+        <v>Kaberle</v>
       </c>
       <c r="I134" s="1" t="str">
         <f>VLOOKUP(J134,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Nolan</v>
+        <v>Emma</v>
       </c>
       <c r="J134" s="3">
         <v>121</v>
@@ -21131,9 +21129,9 @@
         <f>VLOOKUP(J133,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L134" s="1">
+      <c r="L134" s="1" t="str">
         <f>VLOOKUP(J134,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v xml:space="preserve">K-ber-le </v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -21162,11 +21160,11 @@
       </c>
       <c r="H135" s="1" t="str">
         <f>VLOOKUP(J135,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Kaberle</v>
+        <v>Kadric</v>
       </c>
       <c r="I135" s="1" t="str">
         <f>VLOOKUP(J135,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Emma</v>
+        <v>Azra</v>
       </c>
       <c r="J135">
         <v>122</v>
@@ -21177,7 +21175,7 @@
       </c>
       <c r="L135" s="1" t="str">
         <f>VLOOKUP(J135,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v xml:space="preserve">K-ber-le </v>
+        <v xml:space="preserve">(Uh-zra) - The "Uh" part is more slower than the next part "zra". The zra part is quicker, and you roll the r. "Kud-reech" - you also roll the r, and my last name goes by slower. If you can't pronounce it, you can say, "Ah-zra" "Kadrick" </v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -21206,11 +21204,11 @@
       </c>
       <c r="H136" s="1" t="str">
         <f>VLOOKUP(J136,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Kadric</v>
+        <v>Keaveney</v>
       </c>
       <c r="I136" s="1" t="str">
         <f>VLOOKUP(J136,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Azra</v>
+        <v>Brady</v>
       </c>
       <c r="J136">
         <v>123</v>
@@ -21221,7 +21219,7 @@
       </c>
       <c r="L136" s="1" t="str">
         <f>VLOOKUP(J136,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v xml:space="preserve">(Uh-zra) - The "Uh" part is more slower than the next part "zra". The zra part is quicker, and you roll the r. "Kud-reech" - you also roll the r, and my last name goes by slower. If you can't pronounce it, you can say, "Ah-zra" "Kadrick" </v>
+        <v>Key van e</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -21250,11 +21248,11 @@
       </c>
       <c r="H137" s="1" t="str">
         <f>VLOOKUP(J137,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Keaveney</v>
+        <v>Kenton</v>
       </c>
       <c r="I137" s="1" t="str">
         <f>VLOOKUP(J137,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Brady</v>
+        <v>Hannah</v>
       </c>
       <c r="J137">
         <v>124</v>
@@ -21265,7 +21263,7 @@
       </c>
       <c r="L137" s="1" t="str">
         <f>VLOOKUP(J137,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Key van e</v>
+        <v xml:space="preserve">Ken-tin </v>
       </c>
     </row>
     <row r="138" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -21294,11 +21292,11 @@
       </c>
       <c r="H138" s="37" t="str">
         <f>VLOOKUP(J138,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Kenton</v>
+        <v>Kiley</v>
       </c>
       <c r="I138" s="2" t="str">
         <f>VLOOKUP(J138,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Hannah</v>
+        <v>Aiden</v>
       </c>
       <c r="J138">
         <v>125</v>
@@ -21309,7 +21307,7 @@
       </c>
       <c r="L138" s="1" t="str">
         <f>VLOOKUP(J138,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v xml:space="preserve">Ken-tin </v>
+        <v>Aiden Liley</v>
       </c>
     </row>
     <row r="139" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -21338,11 +21336,11 @@
       </c>
       <c r="H139" s="1" t="str">
         <f>VLOOKUP(J139,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Kiley</v>
+        <v>King</v>
       </c>
       <c r="I139" s="1" t="str">
         <f>VLOOKUP(J139,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Aiden</v>
+        <v>Clinton</v>
       </c>
       <c r="J139">
         <v>126</v>
@@ -21351,9 +21349,9 @@
         <f>VLOOKUP(J138,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L139" s="1" t="str">
+      <c r="L139" s="1">
         <f>VLOOKUP(J139,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Aiden Liley</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -21382,11 +21380,11 @@
       </c>
       <c r="H140" s="1" t="str">
         <f>VLOOKUP(J140,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>King</v>
+        <v>Koster</v>
       </c>
       <c r="I140" s="1" t="str">
         <f>VLOOKUP(J140,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Clinton</v>
+        <v>Kyle</v>
       </c>
       <c r="J140">
         <v>127</v>
@@ -21426,11 +21424,11 @@
       </c>
       <c r="H141" s="1" t="str">
         <f>VLOOKUP(J141,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Koster</v>
+        <v>Lalicata</v>
       </c>
       <c r="I141" s="1" t="str">
         <f>VLOOKUP(J141,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Kyle</v>
+        <v>Enzo</v>
       </c>
       <c r="J141">
         <v>128</v>
@@ -21439,9 +21437,9 @@
         <f>VLOOKUP(J140,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L141" s="1">
+      <c r="L141" s="1" t="str">
         <f>VLOOKUP(J141,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Enzo George Lahlicatah</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -21470,22 +21468,22 @@
       </c>
       <c r="H142" s="1" t="str">
         <f>VLOOKUP(J142,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Lalicata</v>
+        <v>Laurino</v>
       </c>
       <c r="I142" s="1" t="str">
         <f>VLOOKUP(J142,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Enzo</v>
+        <v>Matthew</v>
       </c>
       <c r="J142">
         <v>129</v>
       </c>
       <c r="K142" t="str">
         <f>VLOOKUP(J141,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
+        <v>George</v>
       </c>
       <c r="L142" s="1" t="str">
         <f>VLOOKUP(J142,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Enzo George Lahlicatah</v>
+        <v>Matthew La-Ree-No</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -21518,18 +21516,18 @@
       </c>
       <c r="I143" s="1" t="str">
         <f>VLOOKUP(J143,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="J143">
         <v>130</v>
       </c>
       <c r="K143" t="str">
         <f>VLOOKUP(J142,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>George</v>
-      </c>
-      <c r="L143" s="1" t="str">
+        <v/>
+      </c>
+      <c r="L143" s="1">
         <f>VLOOKUP(J143,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Matthew La-Ree-No</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -21558,11 +21556,11 @@
       </c>
       <c r="H144" s="1" t="str">
         <f>VLOOKUP(J144,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Laurino</v>
+        <v>Layne</v>
       </c>
       <c r="I144" s="1" t="str">
         <f>VLOOKUP(J144,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jonathan</v>
+        <v>Asad</v>
       </c>
       <c r="J144">
         <v>131</v>
@@ -21571,9 +21569,9 @@
         <f>VLOOKUP(J143,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L144" s="1">
+      <c r="L144" s="1" t="str">
         <f>VLOOKUP(J144,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Uh-Sod</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -21602,11 +21600,11 @@
       </c>
       <c r="H145" s="1" t="str">
         <f>VLOOKUP(J145,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Layne</v>
+        <v>Lee</v>
       </c>
       <c r="I145" s="1" t="str">
         <f>VLOOKUP(J145,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Asad</v>
+        <v>Jonathan</v>
       </c>
       <c r="J145">
         <v>132</v>
@@ -21615,9 +21613,9 @@
         <f>VLOOKUP(J144,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L145" s="1" t="str">
+      <c r="L145" s="1">
         <f>VLOOKUP(J145,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Uh-Sod</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -21650,7 +21648,7 @@
       </c>
       <c r="I146" s="1" t="str">
         <f>VLOOKUP(J146,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="J146" s="3">
         <v>133</v>
@@ -21690,18 +21688,18 @@
       </c>
       <c r="H147" s="1" t="str">
         <f>VLOOKUP(J147,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Lee</v>
+        <v>Lethin</v>
       </c>
       <c r="I147" s="1" t="str">
         <f>VLOOKUP(J147,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Austin</v>
+        <v>Desmond</v>
       </c>
       <c r="J147">
         <v>134</v>
       </c>
       <c r="K147" t="str">
         <f>VLOOKUP(J146,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
+        <v>James</v>
       </c>
       <c r="L147" s="1">
         <f>VLOOKUP(J147,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -21734,18 +21732,18 @@
       </c>
       <c r="H148" s="1" t="str">
         <f>VLOOKUP(J148,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Lethin</v>
+        <v>Lewis</v>
       </c>
       <c r="I148" s="1" t="str">
         <f>VLOOKUP(J148,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Desmond</v>
+        <v>Katie</v>
       </c>
       <c r="J148">
         <v>135</v>
       </c>
       <c r="K148" t="str">
         <f>VLOOKUP(J147,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>James</v>
+        <v/>
       </c>
       <c r="L148" s="1">
         <f>VLOOKUP(J148,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -21778,11 +21776,11 @@
       </c>
       <c r="H149" s="1" t="str">
         <f>VLOOKUP(J149,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Lewis</v>
+        <v>Lightbody</v>
       </c>
       <c r="I149" s="1" t="str">
         <f>VLOOKUP(J149,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Katie</v>
+        <v>Isabelle</v>
       </c>
       <c r="J149">
         <v>136</v>
@@ -21822,11 +21820,11 @@
       </c>
       <c r="H150" s="37" t="str">
         <f>VLOOKUP(J150,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Lightbody</v>
+        <v>Lin</v>
       </c>
       <c r="I150" s="2" t="str">
         <f>VLOOKUP(J150,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Isabelle</v>
+        <v>Steven</v>
       </c>
       <c r="J150">
         <v>137</v>
@@ -21866,11 +21864,11 @@
       </c>
       <c r="H151" s="1" t="str">
         <f>VLOOKUP(J151,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Lin</v>
+        <v>Lizotte</v>
       </c>
       <c r="I151" s="1" t="str">
         <f>VLOOKUP(J151,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Steven</v>
+        <v>Zackary</v>
       </c>
       <c r="J151">
         <v>138</v>
@@ -21879,9 +21877,9 @@
         <f>VLOOKUP(J150,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L151" s="1">
+      <c r="L151" s="1" t="str">
         <f>VLOOKUP(J151,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Liz-ought</v>
       </c>
     </row>
     <row r="152" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -21910,11 +21908,11 @@
       </c>
       <c r="H152" s="1" t="str">
         <f>VLOOKUP(J152,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Lizotte</v>
+        <v>Lusk</v>
       </c>
       <c r="I152" s="1" t="str">
         <f>VLOOKUP(J152,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Zackary</v>
+        <v>Isla</v>
       </c>
       <c r="J152">
         <v>139</v>
@@ -21925,7 +21923,7 @@
       </c>
       <c r="L152" s="1" t="str">
         <f>VLOOKUP(J152,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Liz-ought</v>
+        <v>eye-la</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -21954,11 +21952,11 @@
       </c>
       <c r="H153" s="1" t="str">
         <f>VLOOKUP(J153,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Lusk</v>
+        <v>Madden</v>
       </c>
       <c r="I153" s="1" t="str">
         <f>VLOOKUP(J153,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Isla</v>
+        <v>Lilyana</v>
       </c>
       <c r="J153">
         <v>140</v>
@@ -21967,9 +21965,9 @@
         <f>VLOOKUP(J152,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L153" s="1" t="str">
+      <c r="L153" s="1">
         <f>VLOOKUP(J153,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>eye-la</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -21998,11 +21996,11 @@
       </c>
       <c r="H154" s="1" t="str">
         <f>VLOOKUP(J154,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Madden</v>
+        <v>Maganzini</v>
       </c>
       <c r="I154" s="1" t="str">
         <f>VLOOKUP(J154,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Lilyana</v>
+        <v>Rosalia</v>
       </c>
       <c r="J154">
         <v>141</v>
@@ -22011,9 +22009,9 @@
         <f>VLOOKUP(J153,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L154" s="1">
+      <c r="L154" s="1" t="str">
         <f>VLOOKUP(J154,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Rose uh Leah - Mag An Zee Knee</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -22046,7 +22044,7 @@
       </c>
       <c r="I155" s="1" t="str">
         <f>VLOOKUP(J155,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Rosalia</v>
+        <v>Trent</v>
       </c>
       <c r="J155">
         <v>142</v>
@@ -22055,9 +22053,9 @@
         <f>VLOOKUP(J154,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L155" s="1" t="str">
+      <c r="L155" s="1">
         <f>VLOOKUP(J155,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Rose uh Leah - Mag An Zee Knee</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -22086,18 +22084,18 @@
       </c>
       <c r="H156" s="1" t="str">
         <f>VLOOKUP(J156,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Maganzini</v>
+        <v>Mahoney</v>
       </c>
       <c r="I156" s="1" t="str">
         <f>VLOOKUP(J156,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Trent</v>
+        <v>Emma</v>
       </c>
       <c r="J156">
         <v>143</v>
       </c>
       <c r="K156" t="str">
         <f>VLOOKUP(J155,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="L156" s="1">
         <f>VLOOKUP(J156,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -22130,22 +22128,22 @@
       </c>
       <c r="H157" s="1" t="str">
         <f>VLOOKUP(J157,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Mahoney</v>
+        <v>Maness</v>
       </c>
       <c r="I157" s="1" t="str">
         <f>VLOOKUP(J157,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Emma</v>
+        <v>Charles</v>
       </c>
       <c r="J157">
         <v>144</v>
       </c>
       <c r="K157" t="str">
         <f>VLOOKUP(J156,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Joseph</v>
-      </c>
-      <c r="L157" s="1">
+        <v/>
+      </c>
+      <c r="L157" s="1" t="str">
         <f>VLOOKUP(J157,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>May-ness</v>
       </c>
     </row>
     <row r="158" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -22174,11 +22172,11 @@
       </c>
       <c r="H158" s="1" t="str">
         <f>VLOOKUP(J158,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Maness</v>
+        <v>Manfredi</v>
       </c>
       <c r="I158" s="1" t="str">
         <f>VLOOKUP(J158,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Charles</v>
+        <v>Evan</v>
       </c>
       <c r="J158" s="3">
         <v>145</v>
@@ -22187,9 +22185,9 @@
         <f>VLOOKUP(J157,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L158" s="1" t="str">
+      <c r="L158" s="1">
         <f>VLOOKUP(J158,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>May-ness</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -22218,11 +22216,11 @@
       </c>
       <c r="H159" s="1" t="str">
         <f>VLOOKUP(J159,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Manfredi</v>
+        <v>Manning</v>
       </c>
       <c r="I159" s="1" t="str">
         <f>VLOOKUP(J159,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Evan</v>
+        <v>Syler</v>
       </c>
       <c r="J159">
         <v>146</v>
@@ -22262,11 +22260,11 @@
       </c>
       <c r="H160" s="1" t="str">
         <f>VLOOKUP(J160,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Manning</v>
+        <v>Marchlik</v>
       </c>
       <c r="I160" s="1" t="str">
         <f>VLOOKUP(J160,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Syler</v>
+        <v>Tyler</v>
       </c>
       <c r="J160">
         <v>147</v>
@@ -22275,9 +22273,9 @@
         <f>VLOOKUP(J159,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L160" s="1">
+      <c r="L160" s="1" t="str">
         <f>VLOOKUP(J160,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>Tyler Marchlik</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -22300,17 +22298,17 @@
       <c r="F161" s="8">
         <v>11</v>
       </c>
-      <c r="G161" s="6">
+      <c r="G161" s="6" t="e">
         <f>VLOOKUP(J161,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H161" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="H161" s="1" t="e">
         <f>VLOOKUP(J161,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Marchlik</v>
-      </c>
-      <c r="I161" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I161" s="1" t="e">
         <f>VLOOKUP(J161,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Tyler</v>
+        <v>#N/A</v>
       </c>
       <c r="J161">
         <v>148</v>
@@ -22319,9 +22317,9 @@
         <f>VLOOKUP(J160,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L161" s="1" t="str">
+      <c r="L161" s="1" t="e">
         <f>VLOOKUP(J161,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Tyler Marchlik</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="162" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -22359,9 +22357,9 @@
       <c r="J162">
         <v>149</v>
       </c>
-      <c r="K162" t="str">
+      <c r="K162" t="e">
         <f>VLOOKUP(J161,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
+        <v>#N/A</v>
       </c>
       <c r="L162" s="1">
         <f>VLOOKUP(J162,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -30242,11 +30240,11 @@
       </c>
       <c r="H69" s="6" t="str">
         <f>'Grad Raw Data'!I69</f>
-        <v>Hans</v>
+        <v>Walick</v>
       </c>
       <c r="I69" s="6" t="str">
         <f>'Grad Raw Data'!H69</f>
-        <v>Dankers</v>
+        <v>Silva</v>
       </c>
       <c r="J69" s="6">
         <f>'Grad Raw Data'!G69</f>
@@ -30278,11 +30276,11 @@
       </c>
       <c r="H70" s="6" t="str">
         <f>'Grad Raw Data'!I70</f>
-        <v>Walick</v>
+        <v>Cooper</v>
       </c>
       <c r="I70" s="6" t="str">
         <f>'Grad Raw Data'!H70</f>
-        <v>Silva</v>
+        <v>Dean</v>
       </c>
       <c r="J70" s="6">
         <f>'Grad Raw Data'!G70</f>
@@ -30314,11 +30312,11 @@
       </c>
       <c r="H71" s="6" t="str">
         <f>'Grad Raw Data'!I71</f>
-        <v>Cooper</v>
+        <v>Happiness</v>
       </c>
       <c r="I71" s="6" t="str">
         <f>'Grad Raw Data'!H71</f>
-        <v>Dean</v>
+        <v>Deji</v>
       </c>
       <c r="J71" s="6">
         <f>'Grad Raw Data'!G71</f>
@@ -30350,11 +30348,11 @@
       </c>
       <c r="H72" s="6" t="str">
         <f>'Grad Raw Data'!I72</f>
-        <v>Happiness</v>
+        <v>Jack</v>
       </c>
       <c r="I72" s="6" t="str">
         <f>'Grad Raw Data'!H72</f>
-        <v>Deji</v>
+        <v>Denmark</v>
       </c>
       <c r="J72" s="6">
         <f>'Grad Raw Data'!G72</f>
@@ -30386,11 +30384,11 @@
       </c>
       <c r="H73" s="6" t="str">
         <f>'Grad Raw Data'!I73</f>
-        <v>Jack</v>
+        <v>Julie</v>
       </c>
       <c r="I73" s="6" t="str">
         <f>'Grad Raw Data'!H73</f>
-        <v>Denmark</v>
+        <v>DiDonato</v>
       </c>
       <c r="J73" s="6">
         <f>'Grad Raw Data'!G73</f>
@@ -30422,11 +30420,11 @@
       </c>
       <c r="H74" s="6" t="str">
         <f>'Grad Raw Data'!I74</f>
-        <v>Julie</v>
+        <v>Dante</v>
       </c>
       <c r="I74" s="6" t="str">
         <f>'Grad Raw Data'!H74</f>
-        <v>DiDonato</v>
+        <v>DiSerio</v>
       </c>
       <c r="J74" s="6">
         <f>'Grad Raw Data'!G74</f>
@@ -30458,7 +30456,7 @@
       </c>
       <c r="H75" s="6" t="str">
         <f>'Grad Raw Data'!I75</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="I75" s="6" t="str">
         <f>'Grad Raw Data'!H75</f>
@@ -30494,11 +30492,11 @@
       </c>
       <c r="H76" s="6" t="str">
         <f>'Grad Raw Data'!I76</f>
-        <v>Antonio</v>
+        <v>Caitlin</v>
       </c>
       <c r="I76" s="6" t="str">
         <f>'Grad Raw Data'!H76</f>
-        <v>DiSerio</v>
+        <v>Donaghey</v>
       </c>
       <c r="J76" s="6">
         <f>'Grad Raw Data'!G76</f>
@@ -30530,11 +30528,11 @@
       </c>
       <c r="H77" s="6" t="str">
         <f>'Grad Raw Data'!I77</f>
-        <v>Caitlin</v>
+        <v>Quinn</v>
       </c>
       <c r="I77" s="6" t="str">
         <f>'Grad Raw Data'!H77</f>
-        <v>Donaghey</v>
+        <v>Donahue</v>
       </c>
       <c r="J77" s="6">
         <f>'Grad Raw Data'!G77</f>
@@ -30566,11 +30564,11 @@
       </c>
       <c r="H78" s="6" t="str">
         <f>'Grad Raw Data'!I78</f>
-        <v>Quinn</v>
+        <v>Alana</v>
       </c>
       <c r="I78" s="6" t="str">
         <f>'Grad Raw Data'!H78</f>
-        <v>Donahue</v>
+        <v>Doroquez</v>
       </c>
       <c r="J78" s="6">
         <f>'Grad Raw Data'!G78</f>
@@ -30602,11 +30600,11 @@
       </c>
       <c r="H79" s="6" t="str">
         <f>'Grad Raw Data'!I79</f>
-        <v>Alana</v>
+        <v>Cassidy</v>
       </c>
       <c r="I79" s="6" t="str">
         <f>'Grad Raw Data'!H79</f>
-        <v>Doroquez</v>
+        <v>Duca</v>
       </c>
       <c r="J79" s="6">
         <f>'Grad Raw Data'!G79</f>
@@ -30638,11 +30636,11 @@
       </c>
       <c r="H80" s="6" t="str">
         <f>'Grad Raw Data'!I80</f>
-        <v>Cassidy</v>
+        <v>Kyle</v>
       </c>
       <c r="I80" s="6" t="str">
         <f>'Grad Raw Data'!H80</f>
-        <v>Duca</v>
+        <v>DuRoss</v>
       </c>
       <c r="J80" s="6">
         <f>'Grad Raw Data'!G80</f>
@@ -30674,7 +30672,7 @@
       </c>
       <c r="H81" s="6" t="str">
         <f>'Grad Raw Data'!I81</f>
-        <v>Kyle</v>
+        <v>Sean</v>
       </c>
       <c r="I81" s="6" t="str">
         <f>'Grad Raw Data'!H81</f>
@@ -30710,11 +30708,11 @@
       </c>
       <c r="H82" s="6" t="str">
         <f>'Grad Raw Data'!I82</f>
-        <v>Sean</v>
+        <v>William</v>
       </c>
       <c r="I82" s="6" t="str">
         <f>'Grad Raw Data'!H82</f>
-        <v>DuRoss</v>
+        <v>Dyment</v>
       </c>
       <c r="J82" s="6">
         <f>'Grad Raw Data'!G82</f>
@@ -30746,11 +30744,11 @@
       </c>
       <c r="H83" s="6" t="str">
         <f>'Grad Raw Data'!I83</f>
-        <v>William</v>
+        <v>Luca</v>
       </c>
       <c r="I83" s="6" t="str">
         <f>'Grad Raw Data'!H83</f>
-        <v>Dyment</v>
+        <v>Eliet</v>
       </c>
       <c r="J83" s="6">
         <f>'Grad Raw Data'!G83</f>
@@ -30782,11 +30780,11 @@
       </c>
       <c r="H84" s="6" t="str">
         <f>'Grad Raw Data'!I84</f>
-        <v>Luca</v>
+        <v>Finn</v>
       </c>
       <c r="I84" s="6" t="str">
         <f>'Grad Raw Data'!H84</f>
-        <v>Eliet</v>
+        <v>Ellis</v>
       </c>
       <c r="J84" s="6">
         <f>'Grad Raw Data'!G84</f>
@@ -30818,11 +30816,11 @@
       </c>
       <c r="H85" s="6" t="str">
         <f>'Grad Raw Data'!I85</f>
-        <v>Finn</v>
+        <v>Levi</v>
       </c>
       <c r="I85" s="6" t="str">
         <f>'Grad Raw Data'!H85</f>
-        <v>Ellis</v>
+        <v>Emmanuel</v>
       </c>
       <c r="J85" s="6">
         <f>'Grad Raw Data'!G85</f>
@@ -30854,11 +30852,11 @@
       </c>
       <c r="H86" s="6" t="str">
         <f>'Grad Raw Data'!I86</f>
-        <v>Levi</v>
+        <v>Kamryn</v>
       </c>
       <c r="I86" s="6" t="str">
         <f>'Grad Raw Data'!H86</f>
-        <v>Emmanuel</v>
+        <v>Encarnacao</v>
       </c>
       <c r="J86" s="6">
         <f>'Grad Raw Data'!G86</f>
@@ -30890,11 +30888,11 @@
       </c>
       <c r="H87" s="6" t="str">
         <f>'Grad Raw Data'!I87</f>
-        <v>Kamryn</v>
+        <v>Samuel</v>
       </c>
       <c r="I87" s="6" t="str">
         <f>'Grad Raw Data'!H87</f>
-        <v>Encarnacao</v>
+        <v>Fortes</v>
       </c>
       <c r="J87" s="6">
         <f>'Grad Raw Data'!G87</f>
@@ -30926,11 +30924,11 @@
       </c>
       <c r="H88" s="6" t="str">
         <f>'Grad Raw Data'!I88</f>
-        <v>Samuel</v>
+        <v>Kaylie</v>
       </c>
       <c r="I88" s="6" t="str">
         <f>'Grad Raw Data'!H88</f>
-        <v>Fortes</v>
+        <v>Fantasia</v>
       </c>
       <c r="J88" s="6">
         <f>'Grad Raw Data'!G88</f>
@@ -30962,11 +30960,11 @@
       </c>
       <c r="H89" s="6" t="str">
         <f>'Grad Raw Data'!I89</f>
-        <v>Kaylie</v>
+        <v>Vince</v>
       </c>
       <c r="I89" s="6" t="str">
         <f>'Grad Raw Data'!H89</f>
-        <v>Fantasia</v>
+        <v>Farnham</v>
       </c>
       <c r="J89" s="6">
         <f>'Grad Raw Data'!G89</f>
@@ -30998,11 +30996,11 @@
       </c>
       <c r="H90" s="6" t="str">
         <f>'Grad Raw Data'!I90</f>
-        <v>Vince</v>
+        <v>Colby</v>
       </c>
       <c r="I90" s="6" t="str">
         <f>'Grad Raw Data'!H90</f>
-        <v>Farnham</v>
+        <v>Farris</v>
       </c>
       <c r="J90" s="6">
         <f>'Grad Raw Data'!G90</f>
@@ -31034,11 +31032,11 @@
       </c>
       <c r="H91" s="6" t="str">
         <f>'Grad Raw Data'!I91</f>
-        <v>Colby</v>
+        <v>Bryan</v>
       </c>
       <c r="I91" s="6" t="str">
         <f>'Grad Raw Data'!H91</f>
-        <v>Farris</v>
+        <v>Fernandez</v>
       </c>
       <c r="J91" s="6">
         <f>'Grad Raw Data'!G91</f>
@@ -31070,11 +31068,11 @@
       </c>
       <c r="H92" s="6" t="str">
         <f>'Grad Raw Data'!I92</f>
-        <v>Bryan</v>
+        <v>Thomas</v>
       </c>
       <c r="I92" s="6" t="str">
         <f>'Grad Raw Data'!H92</f>
-        <v>Fernandez</v>
+        <v>Fiore</v>
       </c>
       <c r="J92" s="6">
         <f>'Grad Raw Data'!G92</f>
@@ -31106,11 +31104,11 @@
       </c>
       <c r="H93" s="6" t="str">
         <f>'Grad Raw Data'!I93</f>
-        <v>Thomas</v>
+        <v>Finn</v>
       </c>
       <c r="I93" s="6" t="str">
         <f>'Grad Raw Data'!H93</f>
-        <v>Fiore</v>
+        <v>Flaherty</v>
       </c>
       <c r="J93" s="6">
         <f>'Grad Raw Data'!G93</f>
@@ -31142,11 +31140,11 @@
       </c>
       <c r="H94" s="6" t="str">
         <f>'Grad Raw Data'!I94</f>
-        <v>Finn</v>
+        <v>Matthew</v>
       </c>
       <c r="I94" s="6" t="str">
         <f>'Grad Raw Data'!H94</f>
-        <v>Flaherty</v>
+        <v>Forse</v>
       </c>
       <c r="J94" s="6">
         <f>'Grad Raw Data'!G94</f>
@@ -31178,11 +31176,11 @@
       </c>
       <c r="H95" s="6" t="str">
         <f>'Grad Raw Data'!I95</f>
-        <v>Matthew</v>
+        <v>Jacob</v>
       </c>
       <c r="I95" s="6" t="str">
         <f>'Grad Raw Data'!H95</f>
-        <v>Forse</v>
+        <v>Frank</v>
       </c>
       <c r="J95" s="6">
         <f>'Grad Raw Data'!G95</f>
@@ -31214,11 +31212,11 @@
       </c>
       <c r="H96" s="6" t="str">
         <f>'Grad Raw Data'!I96</f>
-        <v>Jacob</v>
+        <v>Anthony</v>
       </c>
       <c r="I96" s="6" t="str">
         <f>'Grad Raw Data'!H96</f>
-        <v>Frank</v>
+        <v>Fratto</v>
       </c>
       <c r="J96" s="6">
         <f>'Grad Raw Data'!G96</f>
@@ -31250,11 +31248,11 @@
       </c>
       <c r="H97" s="6" t="str">
         <f>'Grad Raw Data'!I97</f>
-        <v>Anthony</v>
+        <v>Gavin</v>
       </c>
       <c r="I97" s="6" t="str">
         <f>'Grad Raw Data'!H97</f>
-        <v>Fratto</v>
+        <v>Fucarile</v>
       </c>
       <c r="J97" s="6">
         <f>'Grad Raw Data'!G97</f>
@@ -31286,11 +31284,11 @@
       </c>
       <c r="H98" s="6" t="str">
         <f>'Grad Raw Data'!I98</f>
-        <v>Gavin</v>
+        <v>Cole</v>
       </c>
       <c r="I98" s="6" t="str">
         <f>'Grad Raw Data'!H98</f>
-        <v>Fucarile</v>
+        <v>Fusco</v>
       </c>
       <c r="J98" s="6">
         <f>'Grad Raw Data'!G98</f>
@@ -31322,11 +31320,11 @@
       </c>
       <c r="H99" s="6" t="str">
         <f>'Grad Raw Data'!I99</f>
-        <v>Cole</v>
+        <v>Paul</v>
       </c>
       <c r="I99" s="6" t="str">
         <f>'Grad Raw Data'!H99</f>
-        <v>Fusco</v>
+        <v>Gaeta</v>
       </c>
       <c r="J99" s="6">
         <f>'Grad Raw Data'!G99</f>
@@ -31358,11 +31356,11 @@
       </c>
       <c r="H100" s="6" t="str">
         <f>'Grad Raw Data'!I100</f>
-        <v>Paul</v>
+        <v>Lucas</v>
       </c>
       <c r="I100" s="6" t="str">
         <f>'Grad Raw Data'!H100</f>
-        <v>Gaeta</v>
+        <v>Gager</v>
       </c>
       <c r="J100" s="6">
         <f>'Grad Raw Data'!G100</f>
@@ -31394,11 +31392,11 @@
       </c>
       <c r="H101" s="6" t="str">
         <f>'Grad Raw Data'!I101</f>
-        <v>Lucas</v>
+        <v>Nevaeh</v>
       </c>
       <c r="I101" s="6" t="str">
         <f>'Grad Raw Data'!H101</f>
-        <v>Gager</v>
+        <v>Galindo</v>
       </c>
       <c r="J101" s="6">
         <f>'Grad Raw Data'!G101</f>
@@ -31430,11 +31428,11 @@
       </c>
       <c r="H102" s="6" t="str">
         <f>'Grad Raw Data'!I102</f>
-        <v>Nevaeh</v>
+        <v>Joseph</v>
       </c>
       <c r="I102" s="6" t="str">
         <f>'Grad Raw Data'!H102</f>
-        <v>Galindo</v>
+        <v>Gallagher</v>
       </c>
       <c r="J102" s="6">
         <f>'Grad Raw Data'!G102</f>
@@ -31467,11 +31465,11 @@
       </c>
       <c r="H103" s="6" t="str">
         <f>'Grad Raw Data'!I103</f>
-        <v>Joseph</v>
+        <v>Brendan</v>
       </c>
       <c r="I103" s="6" t="str">
         <f>'Grad Raw Data'!H103</f>
-        <v>Gallagher</v>
+        <v>Gauvin</v>
       </c>
       <c r="J103" s="6">
         <f>'Grad Raw Data'!G103</f>
@@ -31504,11 +31502,11 @@
       </c>
       <c r="H104" s="6" t="str">
         <f>'Grad Raw Data'!I104</f>
-        <v>Brendan</v>
+        <v>Bereket</v>
       </c>
       <c r="I104" s="6" t="str">
         <f>'Grad Raw Data'!H104</f>
-        <v>Gauvin</v>
+        <v>Gebeyaw</v>
       </c>
       <c r="J104" s="6">
         <f>'Grad Raw Data'!G104</f>
@@ -31541,11 +31539,11 @@
       </c>
       <c r="H105" s="6" t="str">
         <f>'Grad Raw Data'!I105</f>
-        <v>Bereket</v>
+        <v>Alix</v>
       </c>
       <c r="I105" s="6" t="str">
         <f>'Grad Raw Data'!H105</f>
-        <v>Gebeyaw</v>
+        <v>Gellot</v>
       </c>
       <c r="J105" s="6">
         <f>'Grad Raw Data'!G105</f>
@@ -31578,11 +31576,11 @@
       </c>
       <c r="H106" s="6" t="str">
         <f>'Grad Raw Data'!I106</f>
-        <v>Alix</v>
+        <v>Cameron</v>
       </c>
       <c r="I106" s="6" t="str">
         <f>'Grad Raw Data'!H106</f>
-        <v>Gellot</v>
+        <v>Gigler</v>
       </c>
       <c r="J106" s="6">
         <f>'Grad Raw Data'!G106</f>
@@ -31615,11 +31613,11 @@
       </c>
       <c r="H107" s="6" t="str">
         <f>'Grad Raw Data'!I107</f>
-        <v>Cameron</v>
+        <v>Alex</v>
       </c>
       <c r="I107" s="6" t="str">
         <f>'Grad Raw Data'!H107</f>
-        <v>Gigler</v>
+        <v>Gisetto</v>
       </c>
       <c r="J107" s="6">
         <f>'Grad Raw Data'!G107</f>
@@ -31652,11 +31650,11 @@
       </c>
       <c r="H108" s="6" t="str">
         <f>'Grad Raw Data'!I108</f>
-        <v>Alex</v>
+        <v>Benjamin</v>
       </c>
       <c r="I108" s="6" t="str">
         <f>'Grad Raw Data'!H108</f>
-        <v>Gisetto</v>
+        <v>Goldlust</v>
       </c>
       <c r="J108" s="6">
         <f>'Grad Raw Data'!G108</f>
@@ -31689,11 +31687,11 @@
       </c>
       <c r="H109" s="6" t="str">
         <f>'Grad Raw Data'!I109</f>
-        <v>Benjamin</v>
+        <v>Jack</v>
       </c>
       <c r="I109" s="6" t="str">
         <f>'Grad Raw Data'!H109</f>
-        <v>Goldlust</v>
+        <v>Goodfellow</v>
       </c>
       <c r="J109" s="6">
         <f>'Grad Raw Data'!G109</f>
@@ -31726,11 +31724,11 @@
       </c>
       <c r="H110" s="6" t="str">
         <f>'Grad Raw Data'!I110</f>
-        <v>Jack</v>
+        <v>Drew</v>
       </c>
       <c r="I110" s="6" t="str">
         <f>'Grad Raw Data'!H110</f>
-        <v>Goodfellow</v>
+        <v>Gorski</v>
       </c>
       <c r="J110" s="6">
         <f>'Grad Raw Data'!G110</f>
@@ -31763,11 +31761,11 @@
       </c>
       <c r="H111" s="6" t="str">
         <f>'Grad Raw Data'!I111</f>
-        <v>Drew</v>
+        <v>Lila</v>
       </c>
       <c r="I111" s="6" t="str">
         <f>'Grad Raw Data'!H111</f>
-        <v>Gorski</v>
+        <v>Gosdanian</v>
       </c>
       <c r="J111" s="6">
         <f>'Grad Raw Data'!G111</f>
@@ -31800,11 +31798,11 @@
       </c>
       <c r="H112" s="6" t="str">
         <f>'Grad Raw Data'!I112</f>
-        <v>Lila</v>
+        <v>Cole</v>
       </c>
       <c r="I112" s="6" t="str">
         <f>'Grad Raw Data'!H112</f>
-        <v>Gosdanian</v>
+        <v>Grant</v>
       </c>
       <c r="J112" s="6">
         <f>'Grad Raw Data'!G112</f>
@@ -31837,11 +31835,11 @@
       </c>
       <c r="H113" s="6" t="str">
         <f>'Grad Raw Data'!I113</f>
-        <v>Cole</v>
+        <v>Kendall</v>
       </c>
       <c r="I113" s="6" t="str">
         <f>'Grad Raw Data'!H113</f>
-        <v>Grant</v>
+        <v>Graves</v>
       </c>
       <c r="J113" s="6">
         <f>'Grad Raw Data'!G113</f>
@@ -31874,11 +31872,11 @@
       </c>
       <c r="H114" s="6" t="str">
         <f>'Grad Raw Data'!I114</f>
-        <v>Kendall</v>
+        <v>Griffin</v>
       </c>
       <c r="I114" s="6" t="str">
         <f>'Grad Raw Data'!H114</f>
-        <v>Graves</v>
+        <v>Haggerty</v>
       </c>
       <c r="J114" s="6">
         <f>'Grad Raw Data'!G114</f>
@@ -31911,11 +31909,11 @@
       </c>
       <c r="H115" s="6" t="str">
         <f>'Grad Raw Data'!I115</f>
-        <v>Griffin</v>
+        <v>Andrea</v>
       </c>
       <c r="I115" s="6" t="str">
         <f>'Grad Raw Data'!H115</f>
-        <v>Haggerty</v>
+        <v>Hall</v>
       </c>
       <c r="J115" s="6">
         <f>'Grad Raw Data'!G115</f>
@@ -31948,11 +31946,11 @@
       </c>
       <c r="H116" s="6" t="str">
         <f>'Grad Raw Data'!I116</f>
-        <v>Andrea</v>
+        <v>Sarah</v>
       </c>
       <c r="I116" s="6" t="str">
         <f>'Grad Raw Data'!H116</f>
-        <v>Hall</v>
+        <v>Hamilton</v>
       </c>
       <c r="J116" s="6">
         <f>'Grad Raw Data'!G116</f>
@@ -31985,11 +31983,11 @@
       </c>
       <c r="H117" s="6" t="str">
         <f>'Grad Raw Data'!I117</f>
-        <v>Sarah</v>
+        <v>Margaret</v>
       </c>
       <c r="I117" s="6" t="str">
         <f>'Grad Raw Data'!H117</f>
-        <v>Hamilton</v>
+        <v>Hanifan</v>
       </c>
       <c r="J117" s="6">
         <f>'Grad Raw Data'!G117</f>
@@ -32022,11 +32020,11 @@
       </c>
       <c r="H118" s="6" t="str">
         <f>'Grad Raw Data'!I118</f>
-        <v>Margaret</v>
+        <v>Cameron</v>
       </c>
       <c r="I118" s="6" t="str">
         <f>'Grad Raw Data'!H118</f>
-        <v>Hanifan</v>
+        <v>Harrigan</v>
       </c>
       <c r="J118" s="6">
         <f>'Grad Raw Data'!G118</f>
@@ -32059,11 +32057,11 @@
       </c>
       <c r="H119" s="6" t="str">
         <f>'Grad Raw Data'!I119</f>
-        <v>Cameron</v>
+        <v>Victoria</v>
       </c>
       <c r="I119" s="6" t="str">
         <f>'Grad Raw Data'!H119</f>
-        <v>Harrigan</v>
+        <v>Henri</v>
       </c>
       <c r="J119" s="6">
         <f>'Grad Raw Data'!G119</f>
@@ -32096,11 +32094,11 @@
       </c>
       <c r="H120" s="6" t="str">
         <f>'Grad Raw Data'!I120</f>
-        <v>Victoria</v>
+        <v>Kayke</v>
       </c>
       <c r="I120" s="6" t="str">
         <f>'Grad Raw Data'!H120</f>
-        <v>Henri</v>
+        <v>Henrique</v>
       </c>
       <c r="J120" s="6">
         <f>'Grad Raw Data'!G120</f>
@@ -32133,11 +32131,11 @@
       </c>
       <c r="H121" s="6" t="str">
         <f>'Grad Raw Data'!I121</f>
-        <v>Kayke</v>
+        <v>Jahkye</v>
       </c>
       <c r="I121" s="6" t="str">
         <f>'Grad Raw Data'!H121</f>
-        <v>Henrique</v>
+        <v>Hobson</v>
       </c>
       <c r="J121" s="6">
         <f>'Grad Raw Data'!G121</f>
@@ -32170,11 +32168,11 @@
       </c>
       <c r="H122" s="6" t="str">
         <f>'Grad Raw Data'!I122</f>
-        <v>Jahkye</v>
+        <v>Sam</v>
       </c>
       <c r="I122" s="6" t="str">
         <f>'Grad Raw Data'!H122</f>
-        <v>Hobson</v>
+        <v>Holt</v>
       </c>
       <c r="J122" s="6">
         <f>'Grad Raw Data'!G122</f>
@@ -32207,11 +32205,11 @@
       </c>
       <c r="H123" s="6" t="str">
         <f>'Grad Raw Data'!I123</f>
-        <v>Sam</v>
+        <v>Benjamin</v>
       </c>
       <c r="I123" s="6" t="str">
         <f>'Grad Raw Data'!H123</f>
-        <v>Holt</v>
+        <v>Houle</v>
       </c>
       <c r="J123" s="6">
         <f>'Grad Raw Data'!G123</f>
@@ -32244,11 +32242,11 @@
       </c>
       <c r="H124" s="6" t="str">
         <f>'Grad Raw Data'!I124</f>
-        <v>Benjamin</v>
+        <v>Evin</v>
       </c>
       <c r="I124" s="6" t="str">
         <f>'Grad Raw Data'!H124</f>
-        <v>Houle</v>
+        <v>Howell</v>
       </c>
       <c r="J124" s="6">
         <f>'Grad Raw Data'!G124</f>
@@ -32281,11 +32279,11 @@
       </c>
       <c r="H125" s="6" t="str">
         <f>'Grad Raw Data'!I125</f>
-        <v>Evin</v>
+        <v>Paul</v>
       </c>
       <c r="I125" s="6" t="str">
         <f>'Grad Raw Data'!H125</f>
-        <v>Howell</v>
+        <v>Iosua</v>
       </c>
       <c r="J125" s="6">
         <f>'Grad Raw Data'!G125</f>
@@ -32318,11 +32316,11 @@
       </c>
       <c r="H126" s="6" t="str">
         <f>'Grad Raw Data'!I126</f>
-        <v>Paul</v>
+        <v>Leah</v>
       </c>
       <c r="I126" s="6" t="str">
         <f>'Grad Raw Data'!H126</f>
-        <v>Iosua</v>
+        <v>Jackvony</v>
       </c>
       <c r="J126" s="6">
         <f>'Grad Raw Data'!G126</f>
@@ -32355,11 +32353,11 @@
       </c>
       <c r="H127" s="6" t="str">
         <f>'Grad Raw Data'!I127</f>
-        <v>Leah</v>
+        <v>Wayne</v>
       </c>
       <c r="I127" s="6" t="str">
         <f>'Grad Raw Data'!H127</f>
-        <v>Jackvony</v>
+        <v>Jankun</v>
       </c>
       <c r="J127" s="6">
         <f>'Grad Raw Data'!G127</f>
@@ -32392,11 +32390,11 @@
       </c>
       <c r="H128" s="6" t="str">
         <f>'Grad Raw Data'!I128</f>
-        <v>Wayne</v>
+        <v>Tristan</v>
       </c>
       <c r="I128" s="6" t="str">
         <f>'Grad Raw Data'!H128</f>
-        <v>Jankun</v>
+        <v>Jenkins</v>
       </c>
       <c r="J128" s="6">
         <f>'Grad Raw Data'!G128</f>
@@ -32429,11 +32427,11 @@
       </c>
       <c r="H129" s="6" t="str">
         <f>'Grad Raw Data'!I129</f>
-        <v>Tristan</v>
+        <v>Evan</v>
       </c>
       <c r="I129" s="6" t="str">
         <f>'Grad Raw Data'!H129</f>
-        <v>Jenkins</v>
+        <v>Jenney</v>
       </c>
       <c r="J129" s="6">
         <f>'Grad Raw Data'!G129</f>
@@ -32466,7 +32464,7 @@
       </c>
       <c r="H130" s="6" t="str">
         <f>'Grad Raw Data'!I130</f>
-        <v>Evan</v>
+        <v>Michael</v>
       </c>
       <c r="I130" s="6" t="str">
         <f>'Grad Raw Data'!H130</f>
@@ -32503,11 +32501,11 @@
       </c>
       <c r="H131" s="6" t="str">
         <f>'Grad Raw Data'!I131</f>
-        <v>Michael</v>
+        <v>Luke</v>
       </c>
       <c r="I131" s="6" t="str">
         <f>'Grad Raw Data'!H131</f>
-        <v>Jenney</v>
+        <v>Johnson</v>
       </c>
       <c r="J131" s="6">
         <f>'Grad Raw Data'!G131</f>
@@ -32540,11 +32538,11 @@
       </c>
       <c r="H132" s="6" t="str">
         <f>'Grad Raw Data'!I132</f>
-        <v>Luke</v>
+        <v>Maeve</v>
       </c>
       <c r="I132" s="6" t="str">
         <f>'Grad Raw Data'!H132</f>
-        <v>Johnson</v>
+        <v>Jones</v>
       </c>
       <c r="J132" s="6">
         <f>'Grad Raw Data'!G132</f>
@@ -32577,11 +32575,11 @@
       </c>
       <c r="H133" s="6" t="str">
         <f>'Grad Raw Data'!I133</f>
-        <v>Maeve</v>
+        <v>Nolan</v>
       </c>
       <c r="I133" s="6" t="str">
         <f>'Grad Raw Data'!H133</f>
-        <v>Jones</v>
+        <v>Jordan</v>
       </c>
       <c r="J133" s="6">
         <f>'Grad Raw Data'!G133</f>
@@ -32614,11 +32612,11 @@
       </c>
       <c r="H134" s="6" t="str">
         <f>'Grad Raw Data'!I134</f>
-        <v>Nolan</v>
+        <v>Emma</v>
       </c>
       <c r="I134" s="6" t="str">
         <f>'Grad Raw Data'!H134</f>
-        <v>Jordan</v>
+        <v>Kaberle</v>
       </c>
       <c r="J134" s="6">
         <f>'Grad Raw Data'!G134</f>
@@ -32651,11 +32649,11 @@
       </c>
       <c r="H135" s="6" t="str">
         <f>'Grad Raw Data'!I135</f>
-        <v>Emma</v>
+        <v>Azra</v>
       </c>
       <c r="I135" s="6" t="str">
         <f>'Grad Raw Data'!H135</f>
-        <v>Kaberle</v>
+        <v>Kadric</v>
       </c>
       <c r="J135" s="6">
         <f>'Grad Raw Data'!G135</f>
@@ -32688,11 +32686,11 @@
       </c>
       <c r="H136" s="6" t="str">
         <f>'Grad Raw Data'!I136</f>
-        <v>Azra</v>
+        <v>Brady</v>
       </c>
       <c r="I136" s="6" t="str">
         <f>'Grad Raw Data'!H136</f>
-        <v>Kadric</v>
+        <v>Keaveney</v>
       </c>
       <c r="J136" s="6">
         <f>'Grad Raw Data'!G136</f>
@@ -32725,11 +32723,11 @@
       </c>
       <c r="H137" s="6" t="str">
         <f>'Grad Raw Data'!I137</f>
-        <v>Brady</v>
+        <v>Hannah</v>
       </c>
       <c r="I137" s="6" t="str">
         <f>'Grad Raw Data'!H137</f>
-        <v>Keaveney</v>
+        <v>Kenton</v>
       </c>
       <c r="J137" s="6">
         <f>'Grad Raw Data'!G137</f>
@@ -32762,11 +32760,11 @@
       </c>
       <c r="H138" s="6" t="str">
         <f>'Grad Raw Data'!I138</f>
-        <v>Hannah</v>
+        <v>Aiden</v>
       </c>
       <c r="I138" s="6" t="str">
         <f>'Grad Raw Data'!H138</f>
-        <v>Kenton</v>
+        <v>Kiley</v>
       </c>
       <c r="J138" s="6">
         <f>'Grad Raw Data'!G138</f>
@@ -32799,11 +32797,11 @@
       </c>
       <c r="H139" s="6" t="str">
         <f>'Grad Raw Data'!I139</f>
-        <v>Aiden</v>
+        <v>Clinton</v>
       </c>
       <c r="I139" s="6" t="str">
         <f>'Grad Raw Data'!H139</f>
-        <v>Kiley</v>
+        <v>King</v>
       </c>
       <c r="J139" s="6">
         <f>'Grad Raw Data'!G139</f>
@@ -32836,11 +32834,11 @@
       </c>
       <c r="H140" s="6" t="str">
         <f>'Grad Raw Data'!I140</f>
-        <v>Clinton</v>
+        <v>Kyle</v>
       </c>
       <c r="I140" s="6" t="str">
         <f>'Grad Raw Data'!H140</f>
-        <v>King</v>
+        <v>Koster</v>
       </c>
       <c r="J140" s="6">
         <f>'Grad Raw Data'!G140</f>
@@ -32873,11 +32871,11 @@
       </c>
       <c r="H141" s="6" t="str">
         <f>'Grad Raw Data'!I141</f>
-        <v>Kyle</v>
+        <v>Enzo</v>
       </c>
       <c r="I141" s="6" t="str">
         <f>'Grad Raw Data'!H141</f>
-        <v>Koster</v>
+        <v>Lalicata</v>
       </c>
       <c r="J141" s="6">
         <f>'Grad Raw Data'!G141</f>
@@ -32910,11 +32908,11 @@
       </c>
       <c r="H142" s="6" t="str">
         <f>'Grad Raw Data'!I142</f>
-        <v>Enzo</v>
+        <v>Matthew</v>
       </c>
       <c r="I142" s="6" t="str">
         <f>'Grad Raw Data'!H142</f>
-        <v>Lalicata</v>
+        <v>Laurino</v>
       </c>
       <c r="J142" s="6">
         <f>'Grad Raw Data'!G142</f>
@@ -32947,7 +32945,7 @@
       </c>
       <c r="H143" s="6" t="str">
         <f>'Grad Raw Data'!I143</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="I143" s="6" t="str">
         <f>'Grad Raw Data'!H143</f>
@@ -32984,11 +32982,11 @@
       </c>
       <c r="H144" s="6" t="str">
         <f>'Grad Raw Data'!I144</f>
-        <v>Jonathan</v>
+        <v>Asad</v>
       </c>
       <c r="I144" s="6" t="str">
         <f>'Grad Raw Data'!H144</f>
-        <v>Laurino</v>
+        <v>Layne</v>
       </c>
       <c r="J144" s="6">
         <f>'Grad Raw Data'!G144</f>
@@ -33021,11 +33019,11 @@
       </c>
       <c r="H145" s="6" t="str">
         <f>'Grad Raw Data'!I145</f>
-        <v>Asad</v>
+        <v>Jonathan</v>
       </c>
       <c r="I145" s="6" t="str">
         <f>'Grad Raw Data'!H145</f>
-        <v>Layne</v>
+        <v>Lee</v>
       </c>
       <c r="J145" s="6">
         <f>'Grad Raw Data'!G145</f>
@@ -33058,7 +33056,7 @@
       </c>
       <c r="H146" s="6" t="str">
         <f>'Grad Raw Data'!I146</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="I146" s="6" t="str">
         <f>'Grad Raw Data'!H146</f>
@@ -33095,11 +33093,11 @@
       </c>
       <c r="H147" s="6" t="str">
         <f>'Grad Raw Data'!I147</f>
-        <v>Austin</v>
+        <v>Desmond</v>
       </c>
       <c r="I147" s="6" t="str">
         <f>'Grad Raw Data'!H147</f>
-        <v>Lee</v>
+        <v>Lethin</v>
       </c>
       <c r="J147" s="6">
         <f>'Grad Raw Data'!G147</f>
@@ -33132,11 +33130,11 @@
       </c>
       <c r="H148" s="6" t="str">
         <f>'Grad Raw Data'!I148</f>
-        <v>Desmond</v>
+        <v>Katie</v>
       </c>
       <c r="I148" s="6" t="str">
         <f>'Grad Raw Data'!H148</f>
-        <v>Lethin</v>
+        <v>Lewis</v>
       </c>
       <c r="J148" s="6">
         <f>'Grad Raw Data'!G148</f>
@@ -33169,11 +33167,11 @@
       </c>
       <c r="H149" s="6" t="str">
         <f>'Grad Raw Data'!I149</f>
-        <v>Katie</v>
+        <v>Isabelle</v>
       </c>
       <c r="I149" s="6" t="str">
         <f>'Grad Raw Data'!H149</f>
-        <v>Lewis</v>
+        <v>Lightbody</v>
       </c>
       <c r="J149" s="6">
         <f>'Grad Raw Data'!G149</f>
@@ -33206,11 +33204,11 @@
       </c>
       <c r="H150" s="6" t="str">
         <f>'Grad Raw Data'!I150</f>
-        <v>Isabelle</v>
+        <v>Steven</v>
       </c>
       <c r="I150" s="6" t="str">
         <f>'Grad Raw Data'!H150</f>
-        <v>Lightbody</v>
+        <v>Lin</v>
       </c>
       <c r="J150" s="6">
         <f>'Grad Raw Data'!G150</f>
@@ -33243,11 +33241,11 @@
       </c>
       <c r="H151" s="6" t="str">
         <f>'Grad Raw Data'!I151</f>
-        <v>Steven</v>
+        <v>Zackary</v>
       </c>
       <c r="I151" s="6" t="str">
         <f>'Grad Raw Data'!H151</f>
-        <v>Lin</v>
+        <v>Lizotte</v>
       </c>
       <c r="J151" s="6">
         <f>'Grad Raw Data'!G151</f>
@@ -33280,11 +33278,11 @@
       </c>
       <c r="H152" s="6" t="str">
         <f>'Grad Raw Data'!I152</f>
-        <v>Zackary</v>
+        <v>Isla</v>
       </c>
       <c r="I152" s="6" t="str">
         <f>'Grad Raw Data'!H152</f>
-        <v>Lizotte</v>
+        <v>Lusk</v>
       </c>
       <c r="J152" s="6">
         <f>'Grad Raw Data'!G152</f>
@@ -33317,11 +33315,11 @@
       </c>
       <c r="H153" s="6" t="str">
         <f>'Grad Raw Data'!I153</f>
-        <v>Isla</v>
+        <v>Lilyana</v>
       </c>
       <c r="I153" s="6" t="str">
         <f>'Grad Raw Data'!H153</f>
-        <v>Lusk</v>
+        <v>Madden</v>
       </c>
       <c r="J153" s="6">
         <f>'Grad Raw Data'!G153</f>
@@ -33354,11 +33352,11 @@
       </c>
       <c r="H154" s="6" t="str">
         <f>'Grad Raw Data'!I154</f>
-        <v>Lilyana</v>
+        <v>Rosalia</v>
       </c>
       <c r="I154" s="6" t="str">
         <f>'Grad Raw Data'!H154</f>
-        <v>Madden</v>
+        <v>Maganzini</v>
       </c>
       <c r="J154" s="6">
         <f>'Grad Raw Data'!G154</f>
@@ -33391,7 +33389,7 @@
       </c>
       <c r="H155" s="6" t="str">
         <f>'Grad Raw Data'!I155</f>
-        <v>Rosalia</v>
+        <v>Trent</v>
       </c>
       <c r="I155" s="6" t="str">
         <f>'Grad Raw Data'!H155</f>
@@ -33428,11 +33426,11 @@
       </c>
       <c r="H156" s="6" t="str">
         <f>'Grad Raw Data'!I156</f>
-        <v>Trent</v>
+        <v>Emma</v>
       </c>
       <c r="I156" s="6" t="str">
         <f>'Grad Raw Data'!H156</f>
-        <v>Maganzini</v>
+        <v>Mahoney</v>
       </c>
       <c r="J156" s="6">
         <f>'Grad Raw Data'!G156</f>
@@ -33465,11 +33463,11 @@
       </c>
       <c r="H157" s="6" t="str">
         <f>'Grad Raw Data'!I157</f>
-        <v>Emma</v>
+        <v>Charles</v>
       </c>
       <c r="I157" s="6" t="str">
         <f>'Grad Raw Data'!H157</f>
-        <v>Mahoney</v>
+        <v>Maness</v>
       </c>
       <c r="J157" s="6">
         <f>'Grad Raw Data'!G157</f>
@@ -33502,11 +33500,11 @@
       </c>
       <c r="H158" s="6" t="str">
         <f>'Grad Raw Data'!I158</f>
-        <v>Charles</v>
+        <v>Evan</v>
       </c>
       <c r="I158" s="6" t="str">
         <f>'Grad Raw Data'!H158</f>
-        <v>Maness</v>
+        <v>Manfredi</v>
       </c>
       <c r="J158" s="6">
         <f>'Grad Raw Data'!G158</f>
@@ -33539,11 +33537,11 @@
       </c>
       <c r="H159" s="6" t="str">
         <f>'Grad Raw Data'!I159</f>
-        <v>Evan</v>
+        <v>Syler</v>
       </c>
       <c r="I159" s="6" t="str">
         <f>'Grad Raw Data'!H159</f>
-        <v>Manfredi</v>
+        <v>Manning</v>
       </c>
       <c r="J159" s="6">
         <f>'Grad Raw Data'!G159</f>
@@ -33576,11 +33574,11 @@
       </c>
       <c r="H160" s="6" t="str">
         <f>'Grad Raw Data'!I160</f>
-        <v>Syler</v>
+        <v>Tyler</v>
       </c>
       <c r="I160" s="6" t="str">
         <f>'Grad Raw Data'!H160</f>
-        <v>Manning</v>
+        <v>Marchlik</v>
       </c>
       <c r="J160" s="6">
         <f>'Grad Raw Data'!G160</f>
@@ -33611,17 +33609,17 @@
       <c r="G161" s="8">
         <v>11</v>
       </c>
-      <c r="H161" s="6" t="str">
+      <c r="H161" s="6" t="e">
         <f>'Grad Raw Data'!I161</f>
-        <v>Tyler</v>
-      </c>
-      <c r="I161" s="6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I161" s="6" t="e">
         <f>'Grad Raw Data'!H161</f>
-        <v>Marchlik</v>
-      </c>
-      <c r="J161" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="J161" s="6" t="e">
         <f>'Grad Raw Data'!G161</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -41143,15 +41141,15 @@
     <row r="136" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="20" t="str">
         <f>'Grad Raw Data'!I69</f>
-        <v>Hans</v>
+        <v>Walick</v>
       </c>
       <c r="B136" s="20" t="str">
         <f>'Grad Raw Data'!K70</f>
-        <v/>
+        <v>Da</v>
       </c>
       <c r="C136" s="20" t="str">
         <f>'Grad Raw Data'!H69</f>
-        <v>Dankers</v>
+        <v>Silva</v>
       </c>
       <c r="D136" s="20" cm="1">
         <f t="array" aca="1" ref="D136" ca="1">IF(I136="","",INDIRECT("'Grad Raw Data'!G"&amp;I136))</f>
@@ -41174,9 +41172,9 @@
       </c>
     </row>
     <row r="137" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="16">
+      <c r="A137" s="16" t="str">
         <f>'Grad Raw Data'!L69</f>
-        <v>0</v>
+        <v>Wall-lick Duh Silva</v>
       </c>
       <c r="B137" s="20"/>
       <c r="C137" s="20"/>
@@ -41195,15 +41193,15 @@
     <row r="138" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="20" t="str">
         <f>'Grad Raw Data'!I70</f>
-        <v>Walick</v>
+        <v>Cooper</v>
       </c>
       <c r="B138" s="20" t="str">
         <f>'Grad Raw Data'!K71</f>
-        <v>Da</v>
+        <v>Joseph</v>
       </c>
       <c r="C138" s="20" t="str">
         <f>'Grad Raw Data'!H70</f>
-        <v>Silva</v>
+        <v>Dean</v>
       </c>
       <c r="D138" s="20" cm="1">
         <f t="array" aca="1" ref="D138" ca="1">IF(I138="","",INDIRECT("'Grad Raw Data'!G"&amp;I138))</f>
@@ -41228,7 +41226,7 @@
     <row r="139" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="16" t="str">
         <f>'Grad Raw Data'!L70</f>
-        <v>Wall-lick Duh Silva</v>
+        <v>(Coo-pur) (Joe-Sef) (Deen)</v>
       </c>
       <c r="B139" s="20"/>
       <c r="C139" s="20"/>
@@ -41247,15 +41245,15 @@
     <row r="140" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="20" t="str">
         <f>'Grad Raw Data'!I71</f>
-        <v>Cooper</v>
+        <v>Happiness</v>
       </c>
       <c r="B140" s="20" t="str">
         <f>'Grad Raw Data'!K72</f>
-        <v>Joseph</v>
+        <v>osarugue</v>
       </c>
       <c r="C140" s="20" t="str">
         <f>'Grad Raw Data'!H71</f>
-        <v>Dean</v>
+        <v>Deji</v>
       </c>
       <c r="D140" s="20" cm="1">
         <f t="array" aca="1" ref="D140" ca="1">IF(I140="","",INDIRECT("'Grad Raw Data'!G"&amp;I140))</f>
@@ -41280,7 +41278,7 @@
     <row r="141" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="16" t="str">
         <f>'Grad Raw Data'!L71</f>
-        <v>(Coo-pur) (Joe-Sef) (Deen)</v>
+        <v xml:space="preserve">o sa ru gue </v>
       </c>
       <c r="B141" s="20"/>
       <c r="C141" s="20"/>
@@ -41299,15 +41297,15 @@
     <row r="142" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="20" t="str">
         <f>'Grad Raw Data'!I72</f>
-        <v>Happiness</v>
+        <v>Jack</v>
       </c>
       <c r="B142" s="20" t="str">
         <f>'Grad Raw Data'!K73</f>
-        <v>osarugue</v>
+        <v/>
       </c>
       <c r="C142" s="20" t="str">
         <f>'Grad Raw Data'!H72</f>
-        <v>Deji</v>
+        <v>Denmark</v>
       </c>
       <c r="D142" s="20" cm="1">
         <f t="array" aca="1" ref="D142" ca="1">IF(I142="","",INDIRECT("'Grad Raw Data'!G"&amp;I142))</f>
@@ -41330,9 +41328,9 @@
       </c>
     </row>
     <row r="143" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="16" t="str">
+      <c r="A143" s="16">
         <f>'Grad Raw Data'!L72</f>
-        <v xml:space="preserve">o sa ru gue </v>
+        <v>0</v>
       </c>
       <c r="B143" s="20"/>
       <c r="C143" s="20"/>
@@ -41351,7 +41349,7 @@
     <row r="144" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="20" t="str">
         <f>'Grad Raw Data'!I73</f>
-        <v>Jack</v>
+        <v>Julie</v>
       </c>
       <c r="B144" s="20" t="str">
         <f>'Grad Raw Data'!K74</f>
@@ -41359,7 +41357,7 @@
       </c>
       <c r="C144" s="20" t="str">
         <f>'Grad Raw Data'!H73</f>
-        <v>Denmark</v>
+        <v>DiDonato</v>
       </c>
       <c r="D144" s="20" cm="1">
         <f t="array" aca="1" ref="D144" ca="1">IF(I144="","",INDIRECT("'Grad Raw Data'!G"&amp;I144))</f>
@@ -41382,9 +41380,9 @@
       </c>
     </row>
     <row r="145" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="16">
+      <c r="A145" s="16" t="str">
         <f>'Grad Raw Data'!L73</f>
-        <v>0</v>
+        <v>Dee-doe-na-to</v>
       </c>
       <c r="B145" s="20"/>
       <c r="C145" s="20"/>
@@ -41403,7 +41401,7 @@
     <row r="146" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="20" t="str">
         <f>'Grad Raw Data'!I74</f>
-        <v>Julie</v>
+        <v>Dante</v>
       </c>
       <c r="B146" s="20" t="str">
         <f>'Grad Raw Data'!K75</f>
@@ -41411,7 +41409,7 @@
       </c>
       <c r="C146" s="20" t="str">
         <f>'Grad Raw Data'!H74</f>
-        <v>DiDonato</v>
+        <v>DiSerio</v>
       </c>
       <c r="D146" s="20" cm="1">
         <f t="array" aca="1" ref="D146" ca="1">IF(I146="","",INDIRECT("'Grad Raw Data'!G"&amp;I146))</f>
@@ -41434,9 +41432,9 @@
       </c>
     </row>
     <row r="147" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="16" t="str">
+      <c r="A147" s="16">
         <f>'Grad Raw Data'!L74</f>
-        <v>Dee-doe-na-to</v>
+        <v>0</v>
       </c>
       <c r="B147" s="20"/>
       <c r="C147" s="20"/>
@@ -41455,11 +41453,11 @@
     <row r="148" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="20" t="str">
         <f>'Grad Raw Data'!I75</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="B148" s="20" t="str">
         <f>'Grad Raw Data'!K76</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="C148" s="20" t="str">
         <f>'Grad Raw Data'!H75</f>
@@ -41486,9 +41484,9 @@
       </c>
     </row>
     <row r="149" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="16">
+      <c r="A149" s="16" t="str">
         <f>'Grad Raw Data'!L75</f>
-        <v>0</v>
+        <v>Dis-ear-e-o</v>
       </c>
       <c r="B149" s="20"/>
       <c r="C149" s="20"/>
@@ -41507,15 +41505,15 @@
     <row r="150" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="20" t="str">
         <f>'Grad Raw Data'!I76</f>
-        <v>Antonio</v>
+        <v>Caitlin</v>
       </c>
       <c r="B150" s="20" t="str">
         <f>'Grad Raw Data'!K77</f>
-        <v>Joseph</v>
+        <v>Anne</v>
       </c>
       <c r="C150" s="20" t="str">
         <f>'Grad Raw Data'!H76</f>
-        <v>DiSerio</v>
+        <v>Donaghey</v>
       </c>
       <c r="D150" s="20" cm="1">
         <f t="array" aca="1" ref="D150" ca="1">IF(I150="","",INDIRECT("'Grad Raw Data'!G"&amp;I150))</f>
@@ -41540,7 +41538,7 @@
     <row r="151" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="16" t="str">
         <f>'Grad Raw Data'!L76</f>
-        <v>Dis-ear-e-o</v>
+        <v>Don-a-hee</v>
       </c>
       <c r="B151" s="20"/>
       <c r="C151" s="20"/>
@@ -41559,15 +41557,15 @@
     <row r="152" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="20" t="str">
         <f>'Grad Raw Data'!I77</f>
-        <v>Caitlin</v>
+        <v>Quinn</v>
       </c>
       <c r="B152" s="20" t="str">
         <f>'Grad Raw Data'!K78</f>
-        <v>Anne</v>
+        <v>Kendall</v>
       </c>
       <c r="C152" s="20" t="str">
         <f>'Grad Raw Data'!H77</f>
-        <v>Donaghey</v>
+        <v>Donahue</v>
       </c>
       <c r="D152" s="20" cm="1">
         <f t="array" aca="1" ref="D152" ca="1">IF(I152="","",INDIRECT("'Grad Raw Data'!G"&amp;I152))</f>
@@ -41590,9 +41588,9 @@
       </c>
     </row>
     <row r="153" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="16" t="str">
+      <c r="A153" s="16">
         <f>'Grad Raw Data'!L77</f>
-        <v>Don-a-hee</v>
+        <v>0</v>
       </c>
       <c r="B153" s="20"/>
       <c r="C153" s="20"/>
@@ -41611,15 +41609,15 @@
     <row r="154" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="20" t="str">
         <f>'Grad Raw Data'!I78</f>
-        <v>Quinn</v>
+        <v>Alana</v>
       </c>
       <c r="B154" s="20" t="str">
         <f>'Grad Raw Data'!K79</f>
-        <v>Kendall</v>
+        <v>Mei-Lin Yamaki</v>
       </c>
       <c r="C154" s="20" t="str">
         <f>'Grad Raw Data'!H78</f>
-        <v>Donahue</v>
+        <v>Doroquez</v>
       </c>
       <c r="D154" s="20" cm="1">
         <f t="array" aca="1" ref="D154" ca="1">IF(I154="","",INDIRECT("'Grad Raw Data'!G"&amp;I154))</f>
@@ -41642,9 +41640,9 @@
       </c>
     </row>
     <row r="155" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="16">
+      <c r="A155" s="16" t="str">
         <f>'Grad Raw Data'!L78</f>
-        <v>0</v>
+        <v>Ah-lah-na May-Lynn Yah-mah-key Door-o-kez</v>
       </c>
       <c r="B155" s="20"/>
       <c r="C155" s="20"/>
@@ -41663,15 +41661,15 @@
     <row r="156" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="20" t="str">
         <f>'Grad Raw Data'!I79</f>
-        <v>Alana</v>
+        <v>Cassidy</v>
       </c>
       <c r="B156" s="20" t="str">
         <f>'Grad Raw Data'!K80</f>
-        <v>Mei-Lin Yamaki</v>
+        <v/>
       </c>
       <c r="C156" s="20" t="str">
         <f>'Grad Raw Data'!H79</f>
-        <v>Doroquez</v>
+        <v>Duca</v>
       </c>
       <c r="D156" s="20" cm="1">
         <f t="array" aca="1" ref="D156" ca="1">IF(I156="","",INDIRECT("'Grad Raw Data'!G"&amp;I156))</f>
@@ -41694,9 +41692,9 @@
       </c>
     </row>
     <row r="157" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="16" t="str">
+      <c r="A157" s="16">
         <f>'Grad Raw Data'!L79</f>
-        <v>Ah-lah-na May-Lynn Yah-mah-key Door-o-kez</v>
+        <v>0</v>
       </c>
       <c r="B157" s="20"/>
       <c r="C157" s="20"/>
@@ -41715,7 +41713,7 @@
     <row r="158" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="20" t="str">
         <f>'Grad Raw Data'!I80</f>
-        <v>Cassidy</v>
+        <v>Kyle</v>
       </c>
       <c r="B158" s="20" t="str">
         <f>'Grad Raw Data'!K81</f>
@@ -41723,7 +41721,7 @@
       </c>
       <c r="C158" s="20" t="str">
         <f>'Grad Raw Data'!H80</f>
-        <v>Duca</v>
+        <v>DuRoss</v>
       </c>
       <c r="D158" s="20" cm="1">
         <f t="array" aca="1" ref="D158" ca="1">IF(I158="","",INDIRECT("'Grad Raw Data'!G"&amp;I158))</f>
@@ -41746,9 +41744,9 @@
       </c>
     </row>
     <row r="159" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="16">
+      <c r="A159" s="16" t="str">
         <f>'Grad Raw Data'!L80</f>
-        <v>0</v>
+        <v>Dew-Ross</v>
       </c>
       <c r="B159" s="20"/>
       <c r="C159" s="20"/>
@@ -41767,7 +41765,7 @@
     <row r="160" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="20" t="str">
         <f>'Grad Raw Data'!I81</f>
-        <v>Kyle</v>
+        <v>Sean</v>
       </c>
       <c r="B160" s="20" t="str">
         <f>'Grad Raw Data'!K82</f>
@@ -41798,9 +41796,9 @@
       </c>
     </row>
     <row r="161" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="16" t="str">
+      <c r="A161" s="16">
         <f>'Grad Raw Data'!L81</f>
-        <v>Dew-Ross</v>
+        <v>0</v>
       </c>
       <c r="B161" s="20"/>
       <c r="C161" s="20"/>
@@ -41819,7 +41817,7 @@
     <row r="162" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="20" t="str">
         <f>'Grad Raw Data'!I82</f>
-        <v>Sean</v>
+        <v>William</v>
       </c>
       <c r="B162" s="20" t="str">
         <f>'Grad Raw Data'!K83</f>
@@ -41827,7 +41825,7 @@
       </c>
       <c r="C162" s="20" t="str">
         <f>'Grad Raw Data'!H82</f>
-        <v>DuRoss</v>
+        <v>Dyment</v>
       </c>
       <c r="D162" s="20" cm="1">
         <f t="array" aca="1" ref="D162" ca="1">IF(I162="","",INDIRECT("'Grad Raw Data'!G"&amp;I162))</f>
@@ -41871,7 +41869,7 @@
     <row r="164" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="20" t="str">
         <f>'Grad Raw Data'!I83</f>
-        <v>William</v>
+        <v>Luca</v>
       </c>
       <c r="B164" s="20" t="str">
         <f>'Grad Raw Data'!K84</f>
@@ -41879,7 +41877,7 @@
       </c>
       <c r="C164" s="20" t="str">
         <f>'Grad Raw Data'!H83</f>
-        <v>Dyment</v>
+        <v>Eliet</v>
       </c>
       <c r="D164" s="20" cm="1">
         <f t="array" aca="1" ref="D164" ca="1">IF(I164="","",INDIRECT("'Grad Raw Data'!G"&amp;I164))</f>
@@ -41923,7 +41921,7 @@
     <row r="166" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="20" t="str">
         <f>'Grad Raw Data'!I84</f>
-        <v>Luca</v>
+        <v>Finn</v>
       </c>
       <c r="B166" s="20" t="str">
         <f>'Grad Raw Data'!K85</f>
@@ -41931,7 +41929,7 @@
       </c>
       <c r="C166" s="20" t="str">
         <f>'Grad Raw Data'!H84</f>
-        <v>Eliet</v>
+        <v>Ellis</v>
       </c>
       <c r="D166" s="20" cm="1">
         <f t="array" aca="1" ref="D166" ca="1">IF(I166="","",INDIRECT("'Grad Raw Data'!G"&amp;I166))</f>
@@ -41975,7 +41973,7 @@
     <row r="168" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="20" t="str">
         <f>'Grad Raw Data'!I85</f>
-        <v>Finn</v>
+        <v>Levi</v>
       </c>
       <c r="B168" s="20" t="str">
         <f>'Grad Raw Data'!K86</f>
@@ -41983,7 +41981,7 @@
       </c>
       <c r="C168" s="20" t="str">
         <f>'Grad Raw Data'!H85</f>
-        <v>Ellis</v>
+        <v>Emmanuel</v>
       </c>
       <c r="D168" s="20" cm="1">
         <f t="array" aca="1" ref="D168" ca="1">IF(I168="","",INDIRECT("'Grad Raw Data'!G"&amp;I168))</f>
@@ -42027,7 +42025,7 @@
     <row r="170" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="20" t="str">
         <f>'Grad Raw Data'!I86</f>
-        <v>Levi</v>
+        <v>Kamryn</v>
       </c>
       <c r="B170" s="20" t="str">
         <f>'Grad Raw Data'!K87</f>
@@ -42035,7 +42033,7 @@
       </c>
       <c r="C170" s="20" t="str">
         <f>'Grad Raw Data'!H86</f>
-        <v>Emmanuel</v>
+        <v>Encarnacao</v>
       </c>
       <c r="D170" s="20" cm="1">
         <f t="array" aca="1" ref="D170" ca="1">IF(I170="","",INDIRECT("'Grad Raw Data'!G"&amp;I170))</f>
@@ -42058,9 +42056,9 @@
       </c>
     </row>
     <row r="171" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="16">
+      <c r="A171" s="16" t="str">
         <f>'Grad Raw Data'!L86</f>
-        <v>0</v>
+        <v>In - car - naw - see - oh</v>
       </c>
       <c r="B171" s="20"/>
       <c r="C171" s="20"/>
@@ -42079,7 +42077,7 @@
     <row r="172" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="20" t="str">
         <f>'Grad Raw Data'!I87</f>
-        <v>Kamryn</v>
+        <v>Samuel</v>
       </c>
       <c r="B172" s="20" t="str">
         <f>'Grad Raw Data'!K88</f>
@@ -42087,7 +42085,7 @@
       </c>
       <c r="C172" s="20" t="str">
         <f>'Grad Raw Data'!H87</f>
-        <v>Encarnacao</v>
+        <v>Fortes</v>
       </c>
       <c r="D172" s="20" cm="1">
         <f t="array" aca="1" ref="D172" ca="1">IF(I172="","",INDIRECT("'Grad Raw Data'!G"&amp;I172))</f>
@@ -42112,7 +42110,7 @@
     <row r="173" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="16" t="str">
         <f>'Grad Raw Data'!L87</f>
-        <v>In - car - naw - see - oh</v>
+        <v xml:space="preserve">Eee-wald </v>
       </c>
       <c r="B173" s="20"/>
       <c r="C173" s="20"/>
@@ -42131,7 +42129,7 @@
     <row r="174" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="20" t="str">
         <f>'Grad Raw Data'!I88</f>
-        <v>Samuel</v>
+        <v>Kaylie</v>
       </c>
       <c r="B174" s="20" t="str">
         <f>'Grad Raw Data'!K89</f>
@@ -42139,7 +42137,7 @@
       </c>
       <c r="C174" s="20" t="str">
         <f>'Grad Raw Data'!H88</f>
-        <v>Fortes</v>
+        <v>Fantasia</v>
       </c>
       <c r="D174" s="20" cm="1">
         <f t="array" aca="1" ref="D174" ca="1">IF(I174="","",INDIRECT("'Grad Raw Data'!G"&amp;I174))</f>
@@ -42164,7 +42162,7 @@
     <row r="175" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="16" t="str">
         <f>'Grad Raw Data'!L88</f>
-        <v xml:space="preserve">Eee-wald </v>
+        <v>kay-lee</v>
       </c>
       <c r="B175" s="20"/>
       <c r="C175" s="20"/>
@@ -42183,7 +42181,7 @@
     <row r="176" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="20" t="str">
         <f>'Grad Raw Data'!I89</f>
-        <v>Kaylie</v>
+        <v>Vince</v>
       </c>
       <c r="B176" s="20" t="str">
         <f>'Grad Raw Data'!K90</f>
@@ -42191,7 +42189,7 @@
       </c>
       <c r="C176" s="20" t="str">
         <f>'Grad Raw Data'!H89</f>
-        <v>Fantasia</v>
+        <v>Farnham</v>
       </c>
       <c r="D176" s="20" cm="1">
         <f t="array" aca="1" ref="D176" ca="1">IF(I176="","",INDIRECT("'Grad Raw Data'!G"&amp;I176))</f>
@@ -42214,9 +42212,9 @@
       </c>
     </row>
     <row r="177" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="16" t="str">
+      <c r="A177" s="16">
         <f>'Grad Raw Data'!L89</f>
-        <v>kay-lee</v>
+        <v>0</v>
       </c>
       <c r="B177" s="20"/>
       <c r="C177" s="20"/>
@@ -42235,7 +42233,7 @@
     <row r="178" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="20" t="str">
         <f>'Grad Raw Data'!I90</f>
-        <v>Vince</v>
+        <v>Colby</v>
       </c>
       <c r="B178" s="20" t="str">
         <f>'Grad Raw Data'!K91</f>
@@ -42243,7 +42241,7 @@
       </c>
       <c r="C178" s="20" t="str">
         <f>'Grad Raw Data'!H90</f>
-        <v>Farnham</v>
+        <v>Farris</v>
       </c>
       <c r="D178" s="20" cm="1">
         <f t="array" aca="1" ref="D178" ca="1">IF(I178="","",INDIRECT("'Grad Raw Data'!G"&amp;I178))</f>
@@ -42287,7 +42285,7 @@
     <row r="180" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="20" t="str">
         <f>'Grad Raw Data'!I91</f>
-        <v>Colby</v>
+        <v>Bryan</v>
       </c>
       <c r="B180" s="20" t="str">
         <f>'Grad Raw Data'!K92</f>
@@ -42295,7 +42293,7 @@
       </c>
       <c r="C180" s="20" t="str">
         <f>'Grad Raw Data'!H91</f>
-        <v>Farris</v>
+        <v>Fernandez</v>
       </c>
       <c r="D180" s="20" cm="1">
         <f t="array" aca="1" ref="D180" ca="1">IF(I180="","",INDIRECT("'Grad Raw Data'!G"&amp;I180))</f>
@@ -42339,7 +42337,7 @@
     <row r="182" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="20" t="str">
         <f>'Grad Raw Data'!I92</f>
-        <v>Bryan</v>
+        <v>Thomas</v>
       </c>
       <c r="B182" s="20" t="str">
         <f>'Grad Raw Data'!K93</f>
@@ -42347,7 +42345,7 @@
       </c>
       <c r="C182" s="20" t="str">
         <f>'Grad Raw Data'!H92</f>
-        <v>Fernandez</v>
+        <v>Fiore</v>
       </c>
       <c r="D182" s="20" cm="1">
         <f t="array" aca="1" ref="D182" ca="1">IF(I182="","",INDIRECT("'Grad Raw Data'!G"&amp;I182))</f>
@@ -42391,15 +42389,15 @@
     <row r="184" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="20" t="str">
         <f>'Grad Raw Data'!I93</f>
-        <v>Thomas</v>
+        <v>Finn</v>
       </c>
       <c r="B184" s="20" t="str">
         <f>'Grad Raw Data'!K94</f>
-        <v/>
+        <v>Patrick</v>
       </c>
       <c r="C184" s="20" t="str">
         <f>'Grad Raw Data'!H93</f>
-        <v>Fiore</v>
+        <v>Flaherty</v>
       </c>
       <c r="D184" s="20" cm="1">
         <f t="array" aca="1" ref="D184" ca="1">IF(I184="","",INDIRECT("'Grad Raw Data'!G"&amp;I184))</f>
@@ -42443,15 +42441,15 @@
     <row r="186" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="20" t="str">
         <f>'Grad Raw Data'!I94</f>
-        <v>Finn</v>
+        <v>Matthew</v>
       </c>
       <c r="B186" s="20" t="str">
         <f>'Grad Raw Data'!K95</f>
-        <v>Patrick</v>
+        <v/>
       </c>
       <c r="C186" s="20" t="str">
         <f>'Grad Raw Data'!H94</f>
-        <v>Flaherty</v>
+        <v>Forse</v>
       </c>
       <c r="D186" s="20" cm="1">
         <f t="array" aca="1" ref="D186" ca="1">IF(I186="","",INDIRECT("'Grad Raw Data'!G"&amp;I186))</f>
@@ -42474,9 +42472,9 @@
       </c>
     </row>
     <row r="187" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="16">
+      <c r="A187" s="16" t="str">
         <f>'Grad Raw Data'!L94</f>
-        <v>0</v>
+        <v xml:space="preserve">"Force",   rhymes with HORSE </v>
       </c>
       <c r="B187" s="20"/>
       <c r="C187" s="20"/>
@@ -42495,7 +42493,7 @@
     <row r="188" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="20" t="str">
         <f>'Grad Raw Data'!I95</f>
-        <v>Matthew</v>
+        <v>Jacob</v>
       </c>
       <c r="B188" s="20" t="str">
         <f>'Grad Raw Data'!K96</f>
@@ -42503,7 +42501,7 @@
       </c>
       <c r="C188" s="20" t="str">
         <f>'Grad Raw Data'!H95</f>
-        <v>Forse</v>
+        <v>Frank</v>
       </c>
       <c r="D188" s="20" cm="1">
         <f t="array" aca="1" ref="D188" ca="1">IF(I188="","",INDIRECT("'Grad Raw Data'!G"&amp;I188))</f>
@@ -42526,9 +42524,9 @@
       </c>
     </row>
     <row r="189" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="16" t="str">
+      <c r="A189" s="16">
         <f>'Grad Raw Data'!L95</f>
-        <v xml:space="preserve">"Force",   rhymes with HORSE </v>
+        <v>0</v>
       </c>
       <c r="B189" s="20"/>
       <c r="C189" s="20"/>
@@ -42547,7 +42545,7 @@
     <row r="190" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="20" t="str">
         <f>'Grad Raw Data'!I96</f>
-        <v>Jacob</v>
+        <v>Anthony</v>
       </c>
       <c r="B190" s="20" t="str">
         <f>'Grad Raw Data'!K97</f>
@@ -42555,7 +42553,7 @@
       </c>
       <c r="C190" s="20" t="str">
         <f>'Grad Raw Data'!H96</f>
-        <v>Frank</v>
+        <v>Fratto</v>
       </c>
       <c r="D190" s="20" cm="1">
         <f t="array" aca="1" ref="D190" ca="1">IF(I190="","",INDIRECT("'Grad Raw Data'!G"&amp;I190))</f>
@@ -42599,7 +42597,7 @@
     <row r="192" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="20" t="str">
         <f>'Grad Raw Data'!I97</f>
-        <v>Anthony</v>
+        <v>Gavin</v>
       </c>
       <c r="B192" s="20" t="str">
         <f>'Grad Raw Data'!K98</f>
@@ -42607,7 +42605,7 @@
       </c>
       <c r="C192" s="20" t="str">
         <f>'Grad Raw Data'!H97</f>
-        <v>Fratto</v>
+        <v>Fucarile</v>
       </c>
       <c r="D192" s="20" cm="1">
         <f t="array" aca="1" ref="D192" ca="1">IF(I192="","",INDIRECT("'Grad Raw Data'!G"&amp;I192))</f>
@@ -42630,9 +42628,9 @@
       </c>
     </row>
     <row r="193" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="16">
+      <c r="A193" s="16" t="str">
         <f>'Grad Raw Data'!L97</f>
-        <v>0</v>
+        <v>Fuke-ah-rill</v>
       </c>
       <c r="B193" s="20"/>
       <c r="C193" s="20"/>
@@ -42651,7 +42649,7 @@
     <row r="194" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="20" t="str">
         <f>'Grad Raw Data'!I98</f>
-        <v>Gavin</v>
+        <v>Cole</v>
       </c>
       <c r="B194" s="20" t="str">
         <f>'Grad Raw Data'!K99</f>
@@ -42659,7 +42657,7 @@
       </c>
       <c r="C194" s="20" t="str">
         <f>'Grad Raw Data'!H98</f>
-        <v>Fucarile</v>
+        <v>Fusco</v>
       </c>
       <c r="D194" s="20" cm="1">
         <f t="array" aca="1" ref="D194" ca="1">IF(I194="","",INDIRECT("'Grad Raw Data'!G"&amp;I194))</f>
@@ -42682,9 +42680,9 @@
       </c>
     </row>
     <row r="195" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="16" t="str">
+      <c r="A195" s="16">
         <f>'Grad Raw Data'!L98</f>
-        <v>Fuke-ah-rill</v>
+        <v>0</v>
       </c>
       <c r="B195" s="20"/>
       <c r="C195" s="20"/>
@@ -42703,15 +42701,15 @@
     <row r="196" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="20" t="str">
         <f>'Grad Raw Data'!I99</f>
-        <v>Cole</v>
+        <v>Paul</v>
       </c>
       <c r="B196" s="20" t="str">
         <f>'Grad Raw Data'!K100</f>
-        <v/>
+        <v>Richard</v>
       </c>
       <c r="C196" s="20" t="str">
         <f>'Grad Raw Data'!H99</f>
-        <v>Fusco</v>
+        <v>Gaeta</v>
       </c>
       <c r="D196" s="20" cm="1">
         <f t="array" aca="1" ref="D196" ca="1">IF(I196="","",INDIRECT("'Grad Raw Data'!G"&amp;I196))</f>
@@ -42755,15 +42753,15 @@
     <row r="198" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="20" t="str">
         <f>'Grad Raw Data'!I100</f>
-        <v>Paul</v>
+        <v>Lucas</v>
       </c>
       <c r="B198" s="20" t="str">
         <f>'Grad Raw Data'!K101</f>
-        <v>Richard</v>
+        <v/>
       </c>
       <c r="C198" s="20" t="str">
         <f>'Grad Raw Data'!H100</f>
-        <v>Gaeta</v>
+        <v>Gager</v>
       </c>
       <c r="D198" s="20" cm="1">
         <f t="array" aca="1" ref="D198" ca="1">IF(I198="","",INDIRECT("'Grad Raw Data'!G"&amp;I198))</f>
@@ -42786,9 +42784,9 @@
       </c>
     </row>
     <row r="199" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="16">
+      <c r="A199" s="16" t="str">
         <f>'Grad Raw Data'!L100</f>
-        <v>0</v>
+        <v>Gay-jer</v>
       </c>
       <c r="B199" s="20"/>
       <c r="C199" s="20"/>
@@ -42807,7 +42805,7 @@
     <row r="200" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="20" t="str">
         <f>'Grad Raw Data'!I101</f>
-        <v>Lucas</v>
+        <v>Nevaeh</v>
       </c>
       <c r="B200" s="20" t="str">
         <f>'Grad Raw Data'!K102</f>
@@ -42815,7 +42813,7 @@
       </c>
       <c r="C200" s="20" t="str">
         <f>'Grad Raw Data'!H101</f>
-        <v>Gager</v>
+        <v>Galindo</v>
       </c>
       <c r="D200" s="20" cm="1">
         <f t="array" aca="1" ref="D200" ca="1">IF(I200="","",INDIRECT("'Grad Raw Data'!G"&amp;I200))</f>
@@ -42838,9 +42836,9 @@
       </c>
     </row>
     <row r="201" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="16" t="str">
+      <c r="A201" s="16">
         <f>'Grad Raw Data'!L101</f>
-        <v>Gay-jer</v>
+        <v>0</v>
       </c>
       <c r="B201" s="20"/>
       <c r="C201" s="20"/>
@@ -42859,7 +42857,7 @@
     <row r="202" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="20" t="str">
         <f>'Grad Raw Data'!I102</f>
-        <v>Nevaeh</v>
+        <v>Joseph</v>
       </c>
       <c r="B202" s="20" t="str">
         <f>'Grad Raw Data'!K103</f>
@@ -42867,7 +42865,7 @@
       </c>
       <c r="C202" s="20" t="str">
         <f>'Grad Raw Data'!H102</f>
-        <v>Galindo</v>
+        <v>Gallagher</v>
       </c>
       <c r="D202" s="20" cm="1">
         <f t="array" aca="1" ref="D202" ca="1">IF(I202="","",INDIRECT("'Grad Raw Data'!G"&amp;I202))</f>
@@ -42890,9 +42888,9 @@
       </c>
     </row>
     <row r="203" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="16">
+      <c r="A203" s="16" t="str">
         <f>'Grad Raw Data'!L102</f>
-        <v>0</v>
+        <v>Joseph Gallagher</v>
       </c>
       <c r="B203" s="20"/>
       <c r="C203" s="20"/>
@@ -42911,7 +42909,7 @@
     <row r="204" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="20" t="str">
         <f>'Grad Raw Data'!I103</f>
-        <v>Joseph</v>
+        <v>Brendan</v>
       </c>
       <c r="B204" s="20" t="str">
         <f>'Grad Raw Data'!K104</f>
@@ -42919,7 +42917,7 @@
       </c>
       <c r="C204" s="20" t="str">
         <f>'Grad Raw Data'!H103</f>
-        <v>Gallagher</v>
+        <v>Gauvin</v>
       </c>
       <c r="D204" s="20" cm="1">
         <f t="array" aca="1" ref="D204" ca="1">IF(I204="","",INDIRECT("'Grad Raw Data'!G"&amp;I204))</f>
@@ -42944,7 +42942,7 @@
     <row r="205" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="16" t="str">
         <f>'Grad Raw Data'!L103</f>
-        <v>Joseph Gallagher</v>
+        <v>Gau-vin</v>
       </c>
       <c r="B205" s="20"/>
       <c r="C205" s="20"/>
@@ -42963,7 +42961,7 @@
     <row r="206" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="20" t="str">
         <f>'Grad Raw Data'!I104</f>
-        <v>Brendan</v>
+        <v>Bereket</v>
       </c>
       <c r="B206" s="20" t="str">
         <f>'Grad Raw Data'!K105</f>
@@ -42971,7 +42969,7 @@
       </c>
       <c r="C206" s="20" t="str">
         <f>'Grad Raw Data'!H104</f>
-        <v>Gauvin</v>
+        <v>Gebeyaw</v>
       </c>
       <c r="D206" s="20" cm="1">
         <f t="array" aca="1" ref="D206" ca="1">IF(I206="","",INDIRECT("'Grad Raw Data'!G"&amp;I206))</f>
@@ -42994,9 +42992,9 @@
       </c>
     </row>
     <row r="207" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="16" t="str">
+      <c r="A207" s="16">
         <f>'Grad Raw Data'!L104</f>
-        <v>Gau-vin</v>
+        <v>0</v>
       </c>
       <c r="B207" s="20"/>
       <c r="C207" s="20"/>
@@ -43015,7 +43013,7 @@
     <row r="208" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="20" t="str">
         <f>'Grad Raw Data'!I105</f>
-        <v>Bereket</v>
+        <v>Alix</v>
       </c>
       <c r="B208" s="20" t="str">
         <f>'Grad Raw Data'!K106</f>
@@ -43023,7 +43021,7 @@
       </c>
       <c r="C208" s="20" t="str">
         <f>'Grad Raw Data'!H105</f>
-        <v>Gebeyaw</v>
+        <v>Gellot</v>
       </c>
       <c r="D208" s="20" cm="1">
         <f t="array" aca="1" ref="D208" ca="1">IF(I208="","",INDIRECT("'Grad Raw Data'!G"&amp;I208))</f>
@@ -43067,7 +43065,7 @@
     <row r="210" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="20" t="str">
         <f>'Grad Raw Data'!I106</f>
-        <v>Alix</v>
+        <v>Cameron</v>
       </c>
       <c r="B210" s="20" t="str">
         <f>'Grad Raw Data'!K107</f>
@@ -43075,7 +43073,7 @@
       </c>
       <c r="C210" s="20" t="str">
         <f>'Grad Raw Data'!H106</f>
-        <v>Gellot</v>
+        <v>Gigler</v>
       </c>
       <c r="D210" s="20" cm="1">
         <f t="array" aca="1" ref="D210" ca="1">IF(I210="","",INDIRECT("'Grad Raw Data'!G"&amp;I210))</f>
@@ -43119,7 +43117,7 @@
     <row r="212" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="20" t="str">
         <f>'Grad Raw Data'!I107</f>
-        <v>Cameron</v>
+        <v>Alex</v>
       </c>
       <c r="B212" s="20" t="str">
         <f>'Grad Raw Data'!K108</f>
@@ -43127,7 +43125,7 @@
       </c>
       <c r="C212" s="20" t="str">
         <f>'Grad Raw Data'!H107</f>
-        <v>Gigler</v>
+        <v>Gisetto</v>
       </c>
       <c r="D212" s="20" cm="1">
         <f t="array" aca="1" ref="D212" ca="1">IF(I212="","",INDIRECT("'Grad Raw Data'!G"&amp;I212))</f>
@@ -43171,7 +43169,7 @@
     <row r="214" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="20" t="str">
         <f>'Grad Raw Data'!I108</f>
-        <v>Alex</v>
+        <v>Benjamin</v>
       </c>
       <c r="B214" s="20" t="str">
         <f>'Grad Raw Data'!K109</f>
@@ -43179,7 +43177,7 @@
       </c>
       <c r="C214" s="20" t="str">
         <f>'Grad Raw Data'!H108</f>
-        <v>Gisetto</v>
+        <v>Goldlust</v>
       </c>
       <c r="D214" s="20" cm="1">
         <f t="array" aca="1" ref="D214" ca="1">IF(I214="","",INDIRECT("'Grad Raw Data'!G"&amp;I214))</f>
@@ -43223,7 +43221,7 @@
     <row r="216" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="20" t="str">
         <f>'Grad Raw Data'!I109</f>
-        <v>Benjamin</v>
+        <v>Jack</v>
       </c>
       <c r="B216" s="20" t="str">
         <f>'Grad Raw Data'!K110</f>
@@ -43231,7 +43229,7 @@
       </c>
       <c r="C216" s="20" t="str">
         <f>'Grad Raw Data'!H109</f>
-        <v>Goldlust</v>
+        <v>Goodfellow</v>
       </c>
       <c r="D216" s="20" cm="1">
         <f t="array" aca="1" ref="D216" ca="1">IF(I216="","",INDIRECT("'Grad Raw Data'!G"&amp;I216))</f>
@@ -43275,7 +43273,7 @@
     <row r="218" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="20" t="str">
         <f>'Grad Raw Data'!I110</f>
-        <v>Jack</v>
+        <v>Drew</v>
       </c>
       <c r="B218" s="20" t="str">
         <f>'Grad Raw Data'!K111</f>
@@ -43283,7 +43281,7 @@
       </c>
       <c r="C218" s="20" t="str">
         <f>'Grad Raw Data'!H110</f>
-        <v>Goodfellow</v>
+        <v>Gorski</v>
       </c>
       <c r="D218" s="20" cm="1">
         <f t="array" aca="1" ref="D218" ca="1">IF(I218="","",INDIRECT("'Grad Raw Data'!G"&amp;I218))</f>
@@ -43306,9 +43304,9 @@
       </c>
     </row>
     <row r="219" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="16">
+      <c r="A219" s="16" t="str">
         <f>'Grad Raw Data'!L110</f>
-        <v>0</v>
+        <v>Drew</v>
       </c>
       <c r="B219" s="20"/>
       <c r="C219" s="20"/>
@@ -43327,7 +43325,7 @@
     <row r="220" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="20" t="str">
         <f>'Grad Raw Data'!I111</f>
-        <v>Drew</v>
+        <v>Lila</v>
       </c>
       <c r="B220" s="20" t="str">
         <f>'Grad Raw Data'!K112</f>
@@ -43335,7 +43333,7 @@
       </c>
       <c r="C220" s="20" t="str">
         <f>'Grad Raw Data'!H111</f>
-        <v>Gorski</v>
+        <v>Gosdanian</v>
       </c>
       <c r="D220" s="20" cm="1">
         <f t="array" aca="1" ref="D220" ca="1">IF(I220="","",INDIRECT("'Grad Raw Data'!G"&amp;I220))</f>
@@ -43360,7 +43358,7 @@
     <row r="221" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="16" t="str">
         <f>'Grad Raw Data'!L111</f>
-        <v>Drew</v>
+        <v>Lylah Gosdainian</v>
       </c>
       <c r="B221" s="20"/>
       <c r="C221" s="20"/>
@@ -43379,15 +43377,15 @@
     <row r="222" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="20" t="str">
         <f>'Grad Raw Data'!I112</f>
-        <v>Lila</v>
+        <v>Cole</v>
       </c>
       <c r="B222" s="20" t="str">
         <f>'Grad Raw Data'!K113</f>
-        <v/>
+        <v>Sebastian</v>
       </c>
       <c r="C222" s="20" t="str">
         <f>'Grad Raw Data'!H112</f>
-        <v>Gosdanian</v>
+        <v>Grant</v>
       </c>
       <c r="D222" s="20" cm="1">
         <f t="array" aca="1" ref="D222" ca="1">IF(I222="","",INDIRECT("'Grad Raw Data'!G"&amp;I222))</f>
@@ -43410,9 +43408,9 @@
       </c>
     </row>
     <row r="223" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="16" t="str">
+      <c r="A223" s="16">
         <f>'Grad Raw Data'!L112</f>
-        <v>Lylah Gosdainian</v>
+        <v>0</v>
       </c>
       <c r="B223" s="20"/>
       <c r="C223" s="20"/>
@@ -43431,15 +43429,15 @@
     <row r="224" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="20" t="str">
         <f>'Grad Raw Data'!I113</f>
-        <v>Cole</v>
+        <v>Kendall</v>
       </c>
       <c r="B224" s="20" t="str">
         <f>'Grad Raw Data'!K114</f>
-        <v>Sebastian</v>
+        <v/>
       </c>
       <c r="C224" s="20" t="str">
         <f>'Grad Raw Data'!H113</f>
-        <v>Grant</v>
+        <v>Graves</v>
       </c>
       <c r="D224" s="20" cm="1">
         <f t="array" aca="1" ref="D224" ca="1">IF(I224="","",INDIRECT("'Grad Raw Data'!G"&amp;I224))</f>
@@ -43483,15 +43481,15 @@
     <row r="226" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="20" t="str">
         <f>'Grad Raw Data'!I114</f>
-        <v>Kendall</v>
+        <v>Griffin</v>
       </c>
       <c r="B226" s="20" t="str">
         <f>'Grad Raw Data'!K115</f>
-        <v/>
+        <v>James</v>
       </c>
       <c r="C226" s="20" t="str">
         <f>'Grad Raw Data'!H114</f>
-        <v>Graves</v>
+        <v>Haggerty</v>
       </c>
       <c r="D226" s="20" cm="1">
         <f t="array" aca="1" ref="D226" ca="1">IF(I226="","",INDIRECT("'Grad Raw Data'!G"&amp;I226))</f>
@@ -43535,15 +43533,15 @@
     <row r="228" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="20" t="str">
         <f>'Grad Raw Data'!I115</f>
-        <v>Griffin</v>
+        <v>Andrea</v>
       </c>
       <c r="B228" s="20" t="str">
         <f>'Grad Raw Data'!K116</f>
-        <v>James</v>
+        <v/>
       </c>
       <c r="C228" s="20" t="str">
         <f>'Grad Raw Data'!H115</f>
-        <v>Haggerty</v>
+        <v>Hall</v>
       </c>
       <c r="D228" s="20" cm="1">
         <f t="array" aca="1" ref="D228" ca="1">IF(I228="","",INDIRECT("'Grad Raw Data'!G"&amp;I228))</f>
@@ -43566,9 +43564,9 @@
       </c>
     </row>
     <row r="229" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="16">
+      <c r="A229" s="16" t="str">
         <f>'Grad Raw Data'!L115</f>
-        <v>0</v>
+        <v>Alpha, November, Delta, Romeo, Echo, alpha</v>
       </c>
       <c r="B229" s="20"/>
       <c r="C229" s="20"/>
@@ -43587,7 +43585,7 @@
     <row r="230" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="20" t="str">
         <f>'Grad Raw Data'!I116</f>
-        <v>Andrea</v>
+        <v>Sarah</v>
       </c>
       <c r="B230" s="20" t="str">
         <f>'Grad Raw Data'!K117</f>
@@ -43595,7 +43593,7 @@
       </c>
       <c r="C230" s="20" t="str">
         <f>'Grad Raw Data'!H116</f>
-        <v>Hall</v>
+        <v>Hamilton</v>
       </c>
       <c r="D230" s="20" cm="1">
         <f t="array" aca="1" ref="D230" ca="1">IF(I230="","",INDIRECT("'Grad Raw Data'!G"&amp;I230))</f>
@@ -43618,9 +43616,9 @@
       </c>
     </row>
     <row r="231" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="16" t="str">
+      <c r="A231" s="16">
         <f>'Grad Raw Data'!L116</f>
-        <v>Alpha, November, Delta, Romeo, Echo, alpha</v>
+        <v>0</v>
       </c>
       <c r="B231" s="20"/>
       <c r="C231" s="20"/>
@@ -43639,7 +43637,7 @@
     <row r="232" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="20" t="str">
         <f>'Grad Raw Data'!I117</f>
-        <v>Sarah</v>
+        <v>Margaret</v>
       </c>
       <c r="B232" s="20" t="str">
         <f>'Grad Raw Data'!K118</f>
@@ -43647,7 +43645,7 @@
       </c>
       <c r="C232" s="20" t="str">
         <f>'Grad Raw Data'!H117</f>
-        <v>Hamilton</v>
+        <v>Hanifan</v>
       </c>
       <c r="D232" s="20" cm="1">
         <f t="array" aca="1" ref="D232" ca="1">IF(I232="","",INDIRECT("'Grad Raw Data'!G"&amp;I232))</f>
@@ -43691,7 +43689,7 @@
     <row r="234" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="20" t="str">
         <f>'Grad Raw Data'!I118</f>
-        <v>Margaret</v>
+        <v>Cameron</v>
       </c>
       <c r="B234" s="20" t="str">
         <f>'Grad Raw Data'!K119</f>
@@ -43699,7 +43697,7 @@
       </c>
       <c r="C234" s="20" t="str">
         <f>'Grad Raw Data'!H118</f>
-        <v>Hanifan</v>
+        <v>Harrigan</v>
       </c>
       <c r="D234" s="20" cm="1">
         <f t="array" aca="1" ref="D234" ca="1">IF(I234="","",INDIRECT("'Grad Raw Data'!G"&amp;I234))</f>
@@ -43743,7 +43741,7 @@
     <row r="236" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="20" t="str">
         <f>'Grad Raw Data'!I119</f>
-        <v>Cameron</v>
+        <v>Victoria</v>
       </c>
       <c r="B236" s="20" t="str">
         <f>'Grad Raw Data'!K120</f>
@@ -43751,7 +43749,7 @@
       </c>
       <c r="C236" s="20" t="str">
         <f>'Grad Raw Data'!H119</f>
-        <v>Harrigan</v>
+        <v>Henri</v>
       </c>
       <c r="D236" s="20" cm="1">
         <f t="array" aca="1" ref="D236" ca="1">IF(I236="","",INDIRECT("'Grad Raw Data'!G"&amp;I236))</f>
@@ -43774,9 +43772,9 @@
       </c>
     </row>
     <row r="237" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="16">
+      <c r="A237" s="16" t="str">
         <f>'Grad Raw Data'!L119</f>
-        <v>0</v>
+        <v>Vic-tor-ee-a Hen-ree</v>
       </c>
       <c r="B237" s="20"/>
       <c r="C237" s="20"/>
@@ -43795,7 +43793,7 @@
     <row r="238" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="20" t="str">
         <f>'Grad Raw Data'!I120</f>
-        <v>Victoria</v>
+        <v>Kayke</v>
       </c>
       <c r="B238" s="20" t="str">
         <f>'Grad Raw Data'!K121</f>
@@ -43803,7 +43801,7 @@
       </c>
       <c r="C238" s="20" t="str">
         <f>'Grad Raw Data'!H120</f>
-        <v>Henri</v>
+        <v>Henrique</v>
       </c>
       <c r="D238" s="20" cm="1">
         <f t="array" aca="1" ref="D238" ca="1">IF(I238="","",INDIRECT("'Grad Raw Data'!G"&amp;I238))</f>
@@ -43826,9 +43824,9 @@
       </c>
     </row>
     <row r="239" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="16" t="str">
+      <c r="A239" s="16">
         <f>'Grad Raw Data'!L120</f>
-        <v>Vic-tor-ee-a Hen-ree</v>
+        <v>0</v>
       </c>
       <c r="B239" s="20"/>
       <c r="C239" s="20"/>
@@ -43847,7 +43845,7 @@
     <row r="240" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="20" t="str">
         <f>'Grad Raw Data'!I121</f>
-        <v>Kayke</v>
+        <v>Jahkye</v>
       </c>
       <c r="B240" s="20" t="str">
         <f>'Grad Raw Data'!K122</f>
@@ -43855,7 +43853,7 @@
       </c>
       <c r="C240" s="20" t="str">
         <f>'Grad Raw Data'!H121</f>
-        <v>Henrique</v>
+        <v>Hobson</v>
       </c>
       <c r="D240" s="20" cm="1">
         <f t="array" aca="1" ref="D240" ca="1">IF(I240="","",INDIRECT("'Grad Raw Data'!G"&amp;I240))</f>
@@ -43878,9 +43876,9 @@
       </c>
     </row>
     <row r="241" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="16">
+      <c r="A241" s="16" t="str">
         <f>'Grad Raw Data'!L121</f>
-        <v>0</v>
+        <v>JAH-KIA</v>
       </c>
       <c r="B241" s="20"/>
       <c r="C241" s="20"/>
@@ -43899,7 +43897,7 @@
     <row r="242" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="20" t="str">
         <f>'Grad Raw Data'!I122</f>
-        <v>Jahkye</v>
+        <v>Sam</v>
       </c>
       <c r="B242" s="20" t="str">
         <f>'Grad Raw Data'!K123</f>
@@ -43907,7 +43905,7 @@
       </c>
       <c r="C242" s="20" t="str">
         <f>'Grad Raw Data'!H122</f>
-        <v>Hobson</v>
+        <v>Holt</v>
       </c>
       <c r="D242" s="20" cm="1">
         <f t="array" aca="1" ref="D242" ca="1">IF(I242="","",INDIRECT("'Grad Raw Data'!G"&amp;I242))</f>
@@ -43930,9 +43928,9 @@
       </c>
     </row>
     <row r="243" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="16" t="str">
+      <c r="A243" s="16">
         <f>'Grad Raw Data'!L122</f>
-        <v>JAH-KIA</v>
+        <v>0</v>
       </c>
       <c r="B243" s="20"/>
       <c r="C243" s="20"/>
@@ -43951,7 +43949,7 @@
     <row r="244" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="20" t="str">
         <f>'Grad Raw Data'!I123</f>
-        <v>Sam</v>
+        <v>Benjamin</v>
       </c>
       <c r="B244" s="20" t="str">
         <f>'Grad Raw Data'!K124</f>
@@ -43959,7 +43957,7 @@
       </c>
       <c r="C244" s="20" t="str">
         <f>'Grad Raw Data'!H123</f>
-        <v>Holt</v>
+        <v>Houle</v>
       </c>
       <c r="D244" s="20" cm="1">
         <f t="array" aca="1" ref="D244" ca="1">IF(I244="","",INDIRECT("'Grad Raw Data'!G"&amp;I244))</f>
@@ -43982,9 +43980,9 @@
       </c>
     </row>
     <row r="245" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="16">
+      <c r="A245" s="16" t="str">
         <f>'Grad Raw Data'!L123</f>
-        <v>0</v>
+        <v>H-oo-l</v>
       </c>
       <c r="B245" s="20"/>
       <c r="C245" s="20"/>
@@ -44003,7 +44001,7 @@
     <row r="246" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="20" t="str">
         <f>'Grad Raw Data'!I124</f>
-        <v>Benjamin</v>
+        <v>Evin</v>
       </c>
       <c r="B246" s="20" t="str">
         <f>'Grad Raw Data'!K125</f>
@@ -44011,7 +44009,7 @@
       </c>
       <c r="C246" s="20" t="str">
         <f>'Grad Raw Data'!H124</f>
-        <v>Houle</v>
+        <v>Howell</v>
       </c>
       <c r="D246" s="20" cm="1">
         <f t="array" aca="1" ref="D246" ca="1">IF(I246="","",INDIRECT("'Grad Raw Data'!G"&amp;I246))</f>
@@ -44034,9 +44032,9 @@
       </c>
     </row>
     <row r="247" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="16" t="str">
+      <c r="A247" s="16">
         <f>'Grad Raw Data'!L124</f>
-        <v>H-oo-l</v>
+        <v>0</v>
       </c>
       <c r="B247" s="20"/>
       <c r="C247" s="20"/>
@@ -44055,15 +44053,15 @@
     <row r="248" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="20" t="str">
         <f>'Grad Raw Data'!I125</f>
-        <v>Evin</v>
+        <v>Paul</v>
       </c>
       <c r="B248" s="20" t="str">
         <f>'Grad Raw Data'!K126</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="C248" s="20" t="str">
         <f>'Grad Raw Data'!H125</f>
-        <v>Howell</v>
+        <v>Iosua</v>
       </c>
       <c r="D248" s="20" cm="1">
         <f t="array" aca="1" ref="D248" ca="1">IF(I248="","",INDIRECT("'Grad Raw Data'!G"&amp;I248))</f>
@@ -44086,9 +44084,9 @@
       </c>
     </row>
     <row r="249" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="16">
+      <c r="A249" s="16" t="str">
         <f>'Grad Raw Data'!L125</f>
-        <v>0</v>
+        <v>I-osh-u-ah</v>
       </c>
       <c r="B249" s="20"/>
       <c r="C249" s="20"/>
@@ -44107,15 +44105,15 @@
     <row r="250" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="20" t="str">
         <f>'Grad Raw Data'!I126</f>
-        <v>Paul</v>
+        <v>Leah</v>
       </c>
       <c r="B250" s="20" t="str">
         <f>'Grad Raw Data'!K127</f>
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="C250" s="20" t="str">
         <f>'Grad Raw Data'!H126</f>
-        <v>Iosua</v>
+        <v>Jackvony</v>
       </c>
       <c r="D250" s="20" cm="1">
         <f t="array" aca="1" ref="D250" ca="1">IF(I250="","",INDIRECT("'Grad Raw Data'!G"&amp;I250))</f>
@@ -44138,9 +44136,9 @@
       </c>
     </row>
     <row r="251" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="16" t="str">
+      <c r="A251" s="16">
         <f>'Grad Raw Data'!L126</f>
-        <v>I-osh-u-ah</v>
+        <v>0</v>
       </c>
       <c r="B251" s="20"/>
       <c r="C251" s="20"/>
@@ -44159,7 +44157,7 @@
     <row r="252" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="20" t="str">
         <f>'Grad Raw Data'!I127</f>
-        <v>Leah</v>
+        <v>Wayne</v>
       </c>
       <c r="B252" s="20" t="str">
         <f>'Grad Raw Data'!K128</f>
@@ -44167,7 +44165,7 @@
       </c>
       <c r="C252" s="20" t="str">
         <f>'Grad Raw Data'!H127</f>
-        <v>Jackvony</v>
+        <v>Jankun</v>
       </c>
       <c r="D252" s="20" cm="1">
         <f t="array" aca="1" ref="D252" ca="1">IF(I252="","",INDIRECT("'Grad Raw Data'!G"&amp;I252))</f>
@@ -44211,7 +44209,7 @@
     <row r="254" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="20" t="str">
         <f>'Grad Raw Data'!I128</f>
-        <v>Wayne</v>
+        <v>Tristan</v>
       </c>
       <c r="B254" s="20" t="str">
         <f>'Grad Raw Data'!K129</f>
@@ -44219,7 +44217,7 @@
       </c>
       <c r="C254" s="20" t="str">
         <f>'Grad Raw Data'!H128</f>
-        <v>Jankun</v>
+        <v>Jenkins</v>
       </c>
       <c r="D254" s="20" cm="1">
         <f t="array" aca="1" ref="D254" ca="1">IF(I254="","",INDIRECT("'Grad Raw Data'!G"&amp;I254))</f>
@@ -44263,7 +44261,7 @@
     <row r="256" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="20" t="str">
         <f>'Grad Raw Data'!I129</f>
-        <v>Tristan</v>
+        <v>Evan</v>
       </c>
       <c r="B256" s="20" t="str">
         <f>'Grad Raw Data'!K130</f>
@@ -44271,7 +44269,7 @@
       </c>
       <c r="C256" s="20" t="str">
         <f>'Grad Raw Data'!H129</f>
-        <v>Jenkins</v>
+        <v>Jenney</v>
       </c>
       <c r="D256" s="20" cm="1">
         <f t="array" aca="1" ref="D256" ca="1">IF(I256="","",INDIRECT("'Grad Raw Data'!G"&amp;I256))</f>
@@ -44315,7 +44313,7 @@
     <row r="258" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="20" t="str">
         <f>'Grad Raw Data'!I130</f>
-        <v>Evan</v>
+        <v>Michael</v>
       </c>
       <c r="B258" s="20" t="str">
         <f>'Grad Raw Data'!K131</f>
@@ -44367,7 +44365,7 @@
     <row r="260" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="20" t="str">
         <f>'Grad Raw Data'!I131</f>
-        <v>Michael</v>
+        <v>Luke</v>
       </c>
       <c r="B260" s="20" t="str">
         <f>'Grad Raw Data'!K132</f>
@@ -44375,7 +44373,7 @@
       </c>
       <c r="C260" s="20" t="str">
         <f>'Grad Raw Data'!H131</f>
-        <v>Jenney</v>
+        <v>Johnson</v>
       </c>
       <c r="D260" s="20" cm="1">
         <f t="array" aca="1" ref="D260" ca="1">IF(I260="","",INDIRECT("'Grad Raw Data'!G"&amp;I260))</f>
@@ -44419,7 +44417,7 @@
     <row r="262" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="20" t="str">
         <f>'Grad Raw Data'!I132</f>
-        <v>Luke</v>
+        <v>Maeve</v>
       </c>
       <c r="B262" s="20" t="str">
         <f>'Grad Raw Data'!K133</f>
@@ -44427,7 +44425,7 @@
       </c>
       <c r="C262" s="20" t="str">
         <f>'Grad Raw Data'!H132</f>
-        <v>Johnson</v>
+        <v>Jones</v>
       </c>
       <c r="D262" s="20" cm="1">
         <f t="array" aca="1" ref="D262" ca="1">IF(I262="","",INDIRECT("'Grad Raw Data'!G"&amp;I262))</f>
@@ -44471,7 +44469,7 @@
     <row r="264" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="20" t="str">
         <f>'Grad Raw Data'!I133</f>
-        <v>Maeve</v>
+        <v>Nolan</v>
       </c>
       <c r="B264" s="20" t="str">
         <f>'Grad Raw Data'!K134</f>
@@ -44479,7 +44477,7 @@
       </c>
       <c r="C264" s="20" t="str">
         <f>'Grad Raw Data'!H133</f>
-        <v>Jones</v>
+        <v>Jordan</v>
       </c>
       <c r="D264" s="20" cm="1">
         <f t="array" aca="1" ref="D264" ca="1">IF(I264="","",INDIRECT("'Grad Raw Data'!G"&amp;I264))</f>
@@ -44523,7 +44521,7 @@
     <row r="266" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="20" t="str">
         <f>'Grad Raw Data'!I134</f>
-        <v>Nolan</v>
+        <v>Emma</v>
       </c>
       <c r="B266" s="20" t="str">
         <f>'Grad Raw Data'!K135</f>
@@ -44531,7 +44529,7 @@
       </c>
       <c r="C266" s="20" t="str">
         <f>'Grad Raw Data'!H134</f>
-        <v>Jordan</v>
+        <v>Kaberle</v>
       </c>
       <c r="D266" s="20" cm="1">
         <f t="array" aca="1" ref="D266" ca="1">IF(I266="","",INDIRECT("'Grad Raw Data'!G"&amp;I266))</f>
@@ -44554,9 +44552,9 @@
       </c>
     </row>
     <row r="267" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="16">
+      <c r="A267" s="16" t="str">
         <f>'Grad Raw Data'!L134</f>
-        <v>0</v>
+        <v xml:space="preserve">K-ber-le </v>
       </c>
       <c r="B267" s="20"/>
       <c r="C267" s="20"/>
@@ -44575,7 +44573,7 @@
     <row r="268" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="20" t="str">
         <f>'Grad Raw Data'!I135</f>
-        <v>Emma</v>
+        <v>Azra</v>
       </c>
       <c r="B268" s="20" t="str">
         <f>'Grad Raw Data'!K136</f>
@@ -44583,7 +44581,7 @@
       </c>
       <c r="C268" s="20" t="str">
         <f>'Grad Raw Data'!H135</f>
-        <v>Kaberle</v>
+        <v>Kadric</v>
       </c>
       <c r="D268" s="20" cm="1">
         <f t="array" aca="1" ref="D268" ca="1">IF(I268="","",INDIRECT("'Grad Raw Data'!G"&amp;I268))</f>
@@ -44608,7 +44606,7 @@
     <row r="269" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="16" t="str">
         <f>'Grad Raw Data'!L135</f>
-        <v xml:space="preserve">K-ber-le </v>
+        <v xml:space="preserve">(Uh-zra) - The "Uh" part is more slower than the next part "zra". The zra part is quicker, and you roll the r. "Kud-reech" - you also roll the r, and my last name goes by slower. If you can't pronounce it, you can say, "Ah-zra" "Kadrick" </v>
       </c>
       <c r="B269" s="20"/>
       <c r="C269" s="20"/>
@@ -44627,7 +44625,7 @@
     <row r="270" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="20" t="str">
         <f>'Grad Raw Data'!I136</f>
-        <v>Azra</v>
+        <v>Brady</v>
       </c>
       <c r="B270" s="20" t="str">
         <f>'Grad Raw Data'!K137</f>
@@ -44635,7 +44633,7 @@
       </c>
       <c r="C270" s="20" t="str">
         <f>'Grad Raw Data'!H136</f>
-        <v>Kadric</v>
+        <v>Keaveney</v>
       </c>
       <c r="D270" s="20" cm="1">
         <f t="array" aca="1" ref="D270" ca="1">IF(I270="","",INDIRECT("'Grad Raw Data'!G"&amp;I270))</f>
@@ -44660,7 +44658,7 @@
     <row r="271" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="16" t="str">
         <f>'Grad Raw Data'!L136</f>
-        <v xml:space="preserve">(Uh-zra) - The "Uh" part is more slower than the next part "zra". The zra part is quicker, and you roll the r. "Kud-reech" - you also roll the r, and my last name goes by slower. If you can't pronounce it, you can say, "Ah-zra" "Kadrick" </v>
+        <v>Key van e</v>
       </c>
       <c r="B271" s="20"/>
       <c r="C271" s="20"/>
@@ -44679,7 +44677,7 @@
     <row r="272" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="20" t="str">
         <f>'Grad Raw Data'!I137</f>
-        <v>Brady</v>
+        <v>Hannah</v>
       </c>
       <c r="B272" s="20" t="str">
         <f>'Grad Raw Data'!K138</f>
@@ -44687,7 +44685,7 @@
       </c>
       <c r="C272" s="20" t="str">
         <f>'Grad Raw Data'!H137</f>
-        <v>Keaveney</v>
+        <v>Kenton</v>
       </c>
       <c r="D272" s="20" cm="1">
         <f t="array" aca="1" ref="D272" ca="1">IF(I272="","",INDIRECT("'Grad Raw Data'!G"&amp;I272))</f>
@@ -44712,7 +44710,7 @@
     <row r="273" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="16" t="str">
         <f>'Grad Raw Data'!L137</f>
-        <v>Key van e</v>
+        <v xml:space="preserve">Ken-tin </v>
       </c>
       <c r="B273" s="20"/>
       <c r="C273" s="20"/>
@@ -44731,7 +44729,7 @@
     <row r="274" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="20" t="str">
         <f>'Grad Raw Data'!I138</f>
-        <v>Hannah</v>
+        <v>Aiden</v>
       </c>
       <c r="B274" s="20" t="str">
         <f>'Grad Raw Data'!K139</f>
@@ -44739,7 +44737,7 @@
       </c>
       <c r="C274" s="20" t="str">
         <f>'Grad Raw Data'!H138</f>
-        <v>Kenton</v>
+        <v>Kiley</v>
       </c>
       <c r="D274" s="20" cm="1">
         <f t="array" aca="1" ref="D274" ca="1">IF(I274="","",INDIRECT("'Grad Raw Data'!G"&amp;I274))</f>
@@ -44764,7 +44762,7 @@
     <row r="275" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="16" t="str">
         <f>'Grad Raw Data'!L138</f>
-        <v xml:space="preserve">Ken-tin </v>
+        <v>Aiden Liley</v>
       </c>
       <c r="B275" s="20"/>
       <c r="C275" s="20"/>
@@ -44783,7 +44781,7 @@
     <row r="276" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="20" t="str">
         <f>'Grad Raw Data'!I139</f>
-        <v>Aiden</v>
+        <v>Clinton</v>
       </c>
       <c r="B276" s="20" t="str">
         <f>'Grad Raw Data'!K140</f>
@@ -44791,7 +44789,7 @@
       </c>
       <c r="C276" s="20" t="str">
         <f>'Grad Raw Data'!H139</f>
-        <v>Kiley</v>
+        <v>King</v>
       </c>
       <c r="D276" s="20" cm="1">
         <f t="array" aca="1" ref="D276" ca="1">IF(I276="","",INDIRECT("'Grad Raw Data'!G"&amp;I276))</f>
@@ -44814,9 +44812,9 @@
       </c>
     </row>
     <row r="277" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="16" t="str">
+      <c r="A277" s="16">
         <f>'Grad Raw Data'!L139</f>
-        <v>Aiden Liley</v>
+        <v>0</v>
       </c>
       <c r="B277" s="20"/>
       <c r="C277" s="20"/>
@@ -44835,7 +44833,7 @@
     <row r="278" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="20" t="str">
         <f>'Grad Raw Data'!I140</f>
-        <v>Clinton</v>
+        <v>Kyle</v>
       </c>
       <c r="B278" s="20" t="str">
         <f>'Grad Raw Data'!K141</f>
@@ -44843,7 +44841,7 @@
       </c>
       <c r="C278" s="20" t="str">
         <f>'Grad Raw Data'!H140</f>
-        <v>King</v>
+        <v>Koster</v>
       </c>
       <c r="D278" s="20" cm="1">
         <f t="array" aca="1" ref="D278" ca="1">IF(I278="","",INDIRECT("'Grad Raw Data'!G"&amp;I278))</f>
@@ -44887,15 +44885,15 @@
     <row r="280" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="20" t="str">
         <f>'Grad Raw Data'!I141</f>
-        <v>Kyle</v>
+        <v>Enzo</v>
       </c>
       <c r="B280" s="20" t="str">
         <f>'Grad Raw Data'!K142</f>
-        <v/>
+        <v>George</v>
       </c>
       <c r="C280" s="20" t="str">
         <f>'Grad Raw Data'!H141</f>
-        <v>Koster</v>
+        <v>Lalicata</v>
       </c>
       <c r="D280" s="20" cm="1">
         <f t="array" aca="1" ref="D280" ca="1">IF(I280="","",INDIRECT("'Grad Raw Data'!G"&amp;I280))</f>
@@ -44918,9 +44916,9 @@
       </c>
     </row>
     <row r="281" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A281" s="16">
+      <c r="A281" s="16" t="str">
         <f>'Grad Raw Data'!L141</f>
-        <v>0</v>
+        <v>Enzo George Lahlicatah</v>
       </c>
       <c r="B281" s="20"/>
       <c r="C281" s="20"/>
@@ -44939,15 +44937,15 @@
     <row r="282" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="20" t="str">
         <f>'Grad Raw Data'!I142</f>
-        <v>Enzo</v>
+        <v>Matthew</v>
       </c>
       <c r="B282" s="20" t="str">
         <f>'Grad Raw Data'!K143</f>
-        <v>George</v>
+        <v/>
       </c>
       <c r="C282" s="20" t="str">
         <f>'Grad Raw Data'!H142</f>
-        <v>Lalicata</v>
+        <v>Laurino</v>
       </c>
       <c r="D282" s="20" cm="1">
         <f t="array" aca="1" ref="D282" ca="1">IF(I282="","",INDIRECT("'Grad Raw Data'!G"&amp;I282))</f>
@@ -44972,7 +44970,7 @@
     <row r="283" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="16" t="str">
         <f>'Grad Raw Data'!L142</f>
-        <v>Enzo George Lahlicatah</v>
+        <v>Matthew La-Ree-No</v>
       </c>
       <c r="B283" s="20"/>
       <c r="C283" s="20"/>
@@ -44991,7 +44989,7 @@
     <row r="284" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="20" t="str">
         <f>'Grad Raw Data'!I143</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="B284" s="20" t="str">
         <f>'Grad Raw Data'!K144</f>
@@ -45022,9 +45020,9 @@
       </c>
     </row>
     <row r="285" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="16" t="str">
+      <c r="A285" s="16">
         <f>'Grad Raw Data'!L143</f>
-        <v>Matthew La-Ree-No</v>
+        <v>0</v>
       </c>
       <c r="B285" s="20"/>
       <c r="C285" s="20"/>
@@ -45043,7 +45041,7 @@
     <row r="286" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="20" t="str">
         <f>'Grad Raw Data'!I144</f>
-        <v>Jonathan</v>
+        <v>Asad</v>
       </c>
       <c r="B286" s="20" t="str">
         <f>'Grad Raw Data'!K145</f>
@@ -45051,7 +45049,7 @@
       </c>
       <c r="C286" s="20" t="str">
         <f>'Grad Raw Data'!H144</f>
-        <v>Laurino</v>
+        <v>Layne</v>
       </c>
       <c r="D286" s="20" cm="1">
         <f t="array" aca="1" ref="D286" ca="1">IF(I286="","",INDIRECT("'Grad Raw Data'!G"&amp;I286))</f>
@@ -45074,9 +45072,9 @@
       </c>
     </row>
     <row r="287" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="16">
+      <c r="A287" s="16" t="str">
         <f>'Grad Raw Data'!L144</f>
-        <v>0</v>
+        <v>Uh-Sod</v>
       </c>
       <c r="B287" s="20"/>
       <c r="C287" s="20"/>
@@ -45095,7 +45093,7 @@
     <row r="288" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="20" t="str">
         <f>'Grad Raw Data'!I145</f>
-        <v>Asad</v>
+        <v>Jonathan</v>
       </c>
       <c r="B288" s="20" t="str">
         <f>'Grad Raw Data'!K146</f>
@@ -45103,7 +45101,7 @@
       </c>
       <c r="C288" s="20" t="str">
         <f>'Grad Raw Data'!H145</f>
-        <v>Layne</v>
+        <v>Lee</v>
       </c>
       <c r="D288" s="20" cm="1">
         <f t="array" aca="1" ref="D288" ca="1">IF(I288="","",INDIRECT("'Grad Raw Data'!G"&amp;I288))</f>
@@ -45126,9 +45124,9 @@
       </c>
     </row>
     <row r="289" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="16" t="str">
+      <c r="A289" s="16">
         <f>'Grad Raw Data'!L145</f>
-        <v>Uh-Sod</v>
+        <v>0</v>
       </c>
       <c r="B289" s="20"/>
       <c r="C289" s="20"/>
@@ -45147,11 +45145,11 @@
     <row r="290" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="20" t="str">
         <f>'Grad Raw Data'!I146</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="B290" s="20" t="str">
         <f>'Grad Raw Data'!K147</f>
-        <v/>
+        <v>James</v>
       </c>
       <c r="C290" s="20" t="str">
         <f>'Grad Raw Data'!H146</f>
@@ -45199,15 +45197,15 @@
     <row r="292" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="20" t="str">
         <f>'Grad Raw Data'!I147</f>
-        <v>Austin</v>
+        <v>Desmond</v>
       </c>
       <c r="B292" s="20" t="str">
         <f>'Grad Raw Data'!K148</f>
-        <v>James</v>
+        <v/>
       </c>
       <c r="C292" s="20" t="str">
         <f>'Grad Raw Data'!H147</f>
-        <v>Lee</v>
+        <v>Lethin</v>
       </c>
       <c r="D292" s="20" cm="1">
         <f t="array" aca="1" ref="D292" ca="1">IF(I292="","",INDIRECT("'Grad Raw Data'!G"&amp;I292))</f>
@@ -45251,7 +45249,7 @@
     <row r="294" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="20" t="str">
         <f>'Grad Raw Data'!I148</f>
-        <v>Desmond</v>
+        <v>Katie</v>
       </c>
       <c r="B294" s="20" t="str">
         <f>'Grad Raw Data'!K149</f>
@@ -45259,7 +45257,7 @@
       </c>
       <c r="C294" s="20" t="str">
         <f>'Grad Raw Data'!H148</f>
-        <v>Lethin</v>
+        <v>Lewis</v>
       </c>
       <c r="D294" s="20" cm="1">
         <f t="array" aca="1" ref="D294" ca="1">IF(I294="","",INDIRECT("'Grad Raw Data'!G"&amp;I294))</f>
@@ -45303,7 +45301,7 @@
     <row r="296" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="20" t="str">
         <f>'Grad Raw Data'!I149</f>
-        <v>Katie</v>
+        <v>Isabelle</v>
       </c>
       <c r="B296" s="20" t="str">
         <f>'Grad Raw Data'!K150</f>
@@ -45311,7 +45309,7 @@
       </c>
       <c r="C296" s="20" t="str">
         <f>'Grad Raw Data'!H149</f>
-        <v>Lewis</v>
+        <v>Lightbody</v>
       </c>
       <c r="D296" s="20" cm="1">
         <f t="array" aca="1" ref="D296" ca="1">IF(I296="","",INDIRECT("'Grad Raw Data'!G"&amp;I296))</f>
@@ -45355,7 +45353,7 @@
     <row r="298" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="20" t="str">
         <f>'Grad Raw Data'!I150</f>
-        <v>Isabelle</v>
+        <v>Steven</v>
       </c>
       <c r="B298" s="20" t="str">
         <f>'Grad Raw Data'!K151</f>
@@ -45363,7 +45361,7 @@
       </c>
       <c r="C298" s="20" t="str">
         <f>'Grad Raw Data'!H150</f>
-        <v>Lightbody</v>
+        <v>Lin</v>
       </c>
       <c r="D298" s="20" cm="1">
         <f t="array" aca="1" ref="D298" ca="1">IF(I298="","",INDIRECT("'Grad Raw Data'!G"&amp;I298))</f>
@@ -45407,7 +45405,7 @@
     <row r="300" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="20" t="str">
         <f>'Grad Raw Data'!I151</f>
-        <v>Steven</v>
+        <v>Zackary</v>
       </c>
       <c r="B300" s="20" t="str">
         <f>'Grad Raw Data'!K152</f>
@@ -45415,7 +45413,7 @@
       </c>
       <c r="C300" s="20" t="str">
         <f>'Grad Raw Data'!H151</f>
-        <v>Lin</v>
+        <v>Lizotte</v>
       </c>
       <c r="D300" s="20" cm="1">
         <f t="array" aca="1" ref="D300" ca="1">IF(I300="","",INDIRECT("'Grad Raw Data'!G"&amp;I300))</f>
@@ -45438,9 +45436,9 @@
       </c>
     </row>
     <row r="301" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A301" s="16">
+      <c r="A301" s="16" t="str">
         <f>'Grad Raw Data'!L151</f>
-        <v>0</v>
+        <v>Liz-ought</v>
       </c>
       <c r="B301" s="20"/>
       <c r="C301" s="20"/>
@@ -45459,7 +45457,7 @@
     <row r="302" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="20" t="str">
         <f>'Grad Raw Data'!I152</f>
-        <v>Zackary</v>
+        <v>Isla</v>
       </c>
       <c r="B302" s="20" t="str">
         <f>'Grad Raw Data'!K153</f>
@@ -45467,7 +45465,7 @@
       </c>
       <c r="C302" s="20" t="str">
         <f>'Grad Raw Data'!H152</f>
-        <v>Lizotte</v>
+        <v>Lusk</v>
       </c>
       <c r="D302" s="20" cm="1">
         <f t="array" aca="1" ref="D302" ca="1">IF(I302="","",INDIRECT("'Grad Raw Data'!G"&amp;I302))</f>
@@ -45492,7 +45490,7 @@
     <row r="303" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="16" t="str">
         <f>'Grad Raw Data'!L152</f>
-        <v>Liz-ought</v>
+        <v>eye-la</v>
       </c>
       <c r="B303" s="20"/>
       <c r="C303" s="20"/>
@@ -45511,7 +45509,7 @@
     <row r="304" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="20" t="str">
         <f>'Grad Raw Data'!I153</f>
-        <v>Isla</v>
+        <v>Lilyana</v>
       </c>
       <c r="B304" s="20" t="str">
         <f>'Grad Raw Data'!K154</f>
@@ -45519,7 +45517,7 @@
       </c>
       <c r="C304" s="20" t="str">
         <f>'Grad Raw Data'!H153</f>
-        <v>Lusk</v>
+        <v>Madden</v>
       </c>
       <c r="D304" s="20" cm="1">
         <f t="array" aca="1" ref="D304" ca="1">IF(I304="","",INDIRECT("'Grad Raw Data'!G"&amp;I304))</f>
@@ -45542,9 +45540,9 @@
       </c>
     </row>
     <row r="305" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A305" s="16" t="str">
+      <c r="A305" s="16">
         <f>'Grad Raw Data'!L153</f>
-        <v>eye-la</v>
+        <v>0</v>
       </c>
       <c r="B305" s="20"/>
       <c r="C305" s="20"/>
@@ -45563,7 +45561,7 @@
     <row r="306" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="20" t="str">
         <f>'Grad Raw Data'!I154</f>
-        <v>Lilyana</v>
+        <v>Rosalia</v>
       </c>
       <c r="B306" s="20" t="str">
         <f>'Grad Raw Data'!K155</f>
@@ -45571,7 +45569,7 @@
       </c>
       <c r="C306" s="20" t="str">
         <f>'Grad Raw Data'!H154</f>
-        <v>Madden</v>
+        <v>Maganzini</v>
       </c>
       <c r="D306" s="20" cm="1">
         <f t="array" aca="1" ref="D306" ca="1">IF(I306="","",INDIRECT("'Grad Raw Data'!G"&amp;I306))</f>
@@ -45594,9 +45592,9 @@
       </c>
     </row>
     <row r="307" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="16">
+      <c r="A307" s="16" t="str">
         <f>'Grad Raw Data'!L154</f>
-        <v>0</v>
+        <v>Rose uh Leah - Mag An Zee Knee</v>
       </c>
       <c r="B307" s="20"/>
       <c r="C307" s="20"/>
@@ -45615,11 +45613,11 @@
     <row r="308" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="20" t="str">
         <f>'Grad Raw Data'!I155</f>
-        <v>Rosalia</v>
+        <v>Trent</v>
       </c>
       <c r="B308" s="20" t="str">
         <f>'Grad Raw Data'!K156</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="C308" s="20" t="str">
         <f>'Grad Raw Data'!H155</f>
@@ -45646,9 +45644,9 @@
       </c>
     </row>
     <row r="309" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A309" s="16" t="str">
+      <c r="A309" s="16">
         <f>'Grad Raw Data'!L155</f>
-        <v>Rose uh Leah - Mag An Zee Knee</v>
+        <v>0</v>
       </c>
       <c r="B309" s="20"/>
       <c r="C309" s="20"/>
@@ -45667,15 +45665,15 @@
     <row r="310" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="20" t="str">
         <f>'Grad Raw Data'!I156</f>
-        <v>Trent</v>
+        <v>Emma</v>
       </c>
       <c r="B310" s="20" t="str">
         <f>'Grad Raw Data'!K157</f>
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="C310" s="20" t="str">
         <f>'Grad Raw Data'!H156</f>
-        <v>Maganzini</v>
+        <v>Mahoney</v>
       </c>
       <c r="D310" s="20" cm="1">
         <f t="array" aca="1" ref="D310" ca="1">IF(I310="","",INDIRECT("'Grad Raw Data'!G"&amp;I310))</f>
@@ -45719,7 +45717,7 @@
     <row r="312" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="20" t="str">
         <f>'Grad Raw Data'!I157</f>
-        <v>Emma</v>
+        <v>Charles</v>
       </c>
       <c r="B312" s="20" t="str">
         <f>'Grad Raw Data'!K158</f>
@@ -45727,7 +45725,7 @@
       </c>
       <c r="C312" s="20" t="str">
         <f>'Grad Raw Data'!H157</f>
-        <v>Mahoney</v>
+        <v>Maness</v>
       </c>
       <c r="D312" s="20" cm="1">
         <f t="array" aca="1" ref="D312" ca="1">IF(I312="","",INDIRECT("'Grad Raw Data'!G"&amp;I312))</f>
@@ -45750,9 +45748,9 @@
       </c>
     </row>
     <row r="313" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A313" s="16">
+      <c r="A313" s="16" t="str">
         <f>'Grad Raw Data'!L157</f>
-        <v>0</v>
+        <v>May-ness</v>
       </c>
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
@@ -45771,7 +45769,7 @@
     <row r="314" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="20" t="str">
         <f>'Grad Raw Data'!I158</f>
-        <v>Charles</v>
+        <v>Evan</v>
       </c>
       <c r="B314" s="20" t="str">
         <f>'Grad Raw Data'!K159</f>
@@ -45779,7 +45777,7 @@
       </c>
       <c r="C314" s="20" t="str">
         <f>'Grad Raw Data'!H158</f>
-        <v>Maness</v>
+        <v>Manfredi</v>
       </c>
       <c r="D314" s="20" cm="1">
         <f t="array" aca="1" ref="D314" ca="1">IF(I314="","",INDIRECT("'Grad Raw Data'!G"&amp;I314))</f>
@@ -45802,9 +45800,9 @@
       </c>
     </row>
     <row r="315" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A315" s="16" t="str">
+      <c r="A315" s="16">
         <f>'Grad Raw Data'!L158</f>
-        <v>May-ness</v>
+        <v>0</v>
       </c>
       <c r="B315" s="20"/>
       <c r="C315" s="20"/>
@@ -45823,7 +45821,7 @@
     <row r="316" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="20" t="str">
         <f>'Grad Raw Data'!I159</f>
-        <v>Evan</v>
+        <v>Syler</v>
       </c>
       <c r="B316" s="20" t="str">
         <f>'Grad Raw Data'!K160</f>
@@ -45831,7 +45829,7 @@
       </c>
       <c r="C316" s="20" t="str">
         <f>'Grad Raw Data'!H159</f>
-        <v>Manfredi</v>
+        <v>Manning</v>
       </c>
       <c r="D316" s="20" cm="1">
         <f t="array" aca="1" ref="D316" ca="1">IF(I316="","",INDIRECT("'Grad Raw Data'!G"&amp;I316))</f>
@@ -45875,7 +45873,7 @@
     <row r="318" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="20" t="str">
         <f>'Grad Raw Data'!I160</f>
-        <v>Syler</v>
+        <v>Tyler</v>
       </c>
       <c r="B318" s="20" t="str">
         <f>'Grad Raw Data'!K161</f>
@@ -45883,7 +45881,7 @@
       </c>
       <c r="C318" s="20" t="str">
         <f>'Grad Raw Data'!H160</f>
-        <v>Manning</v>
+        <v>Marchlik</v>
       </c>
       <c r="D318" s="20" cm="1">
         <f t="array" aca="1" ref="D318" ca="1">IF(I318="","",INDIRECT("'Grad Raw Data'!G"&amp;I318))</f>
@@ -45906,9 +45904,9 @@
       </c>
     </row>
     <row r="319" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A319" s="16">
+      <c r="A319" s="16" t="str">
         <f>'Grad Raw Data'!L160</f>
-        <v>0</v>
+        <v>Tyler Marchlik</v>
       </c>
       <c r="B319" s="20"/>
       <c r="C319" s="20"/>
@@ -45925,21 +45923,21 @@
       </c>
     </row>
     <row r="320" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A320" s="20" t="str">
+      <c r="A320" s="20" t="e">
         <f>'Grad Raw Data'!I161</f>
-        <v>Tyler</v>
-      </c>
-      <c r="B320" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B320" s="20" t="e">
         <f>'Grad Raw Data'!K162</f>
-        <v/>
-      </c>
-      <c r="C320" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C320" s="20" t="e">
         <f>'Grad Raw Data'!H161</f>
-        <v>Marchlik</v>
-      </c>
-      <c r="D320" s="20" cm="1">
+        <v>#N/A</v>
+      </c>
+      <c r="D320" s="20" t="e" cm="1">
         <f t="array" aca="1" ref="D320" ca="1">IF(I320="","",INDIRECT("'Grad Raw Data'!G"&amp;I320))</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="E320" s="44" t="str">
         <f>'Grad Raw Data'!D161</f>
@@ -45958,9 +45956,9 @@
       </c>
     </row>
     <row r="321" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A321" s="16" t="str">
+      <c r="A321" s="16" t="e">
         <f>'Grad Raw Data'!L161</f>
-        <v>Tyler Marchlik</v>
+        <v>#N/A</v>
       </c>
       <c r="B321" s="20"/>
       <c r="C321" s="20"/>
@@ -46062,9 +46060,9 @@
       </c>
     </row>
     <row r="325" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="16" t="str">
+      <c r="A325" s="16">
         <f>'Grad Raw Data'!L153</f>
-        <v>eye-la</v>
+        <v>0</v>
       </c>
       <c r="B325" s="20"/>
       <c r="C325" s="20"/>
@@ -53147,15 +53145,15 @@
     <row r="136" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="20" t="str">
         <f>'Grad Raw Data'!I69</f>
-        <v>Hans</v>
+        <v>Walick</v>
       </c>
       <c r="B136" s="20" t="str">
         <f>'Grad Raw Data'!K70</f>
-        <v/>
+        <v>Da</v>
       </c>
       <c r="C136" s="20" t="str">
         <f>'Grad Raw Data'!H69</f>
-        <v>Dankers</v>
+        <v>Silva</v>
       </c>
       <c r="D136" s="20"/>
       <c r="E136" s="20" t="str">
@@ -53178,15 +53176,15 @@
     <row r="138" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="20" t="str">
         <f>'Grad Raw Data'!I70</f>
-        <v>Walick</v>
+        <v>Cooper</v>
       </c>
       <c r="B138" s="20" t="str">
         <f>'Grad Raw Data'!K71</f>
-        <v>Da</v>
+        <v>Joseph</v>
       </c>
       <c r="C138" s="20" t="str">
         <f>'Grad Raw Data'!H70</f>
-        <v>Silva</v>
+        <v>Dean</v>
       </c>
       <c r="D138" s="20"/>
       <c r="E138" s="20" t="str">
@@ -53209,15 +53207,15 @@
     <row r="140" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="20" t="str">
         <f>'Grad Raw Data'!I71</f>
-        <v>Cooper</v>
+        <v>Happiness</v>
       </c>
       <c r="B140" s="20" t="str">
         <f>'Grad Raw Data'!K72</f>
-        <v>Joseph</v>
+        <v>osarugue</v>
       </c>
       <c r="C140" s="20" t="str">
         <f>'Grad Raw Data'!H71</f>
-        <v>Dean</v>
+        <v>Deji</v>
       </c>
       <c r="D140" s="20"/>
       <c r="E140" s="20" t="str">
@@ -53240,15 +53238,15 @@
     <row r="142" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="20" t="str">
         <f>'Grad Raw Data'!I72</f>
-        <v>Happiness</v>
+        <v>Jack</v>
       </c>
       <c r="B142" s="20" t="str">
         <f>'Grad Raw Data'!K73</f>
-        <v>osarugue</v>
+        <v/>
       </c>
       <c r="C142" s="20" t="str">
         <f>'Grad Raw Data'!H72</f>
-        <v>Deji</v>
+        <v>Denmark</v>
       </c>
       <c r="D142" s="20"/>
       <c r="E142" s="20" t="str">
@@ -53271,7 +53269,7 @@
     <row r="144" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="20" t="str">
         <f>'Grad Raw Data'!I73</f>
-        <v>Jack</v>
+        <v>Julie</v>
       </c>
       <c r="B144" s="20" t="str">
         <f>'Grad Raw Data'!K74</f>
@@ -53279,7 +53277,7 @@
       </c>
       <c r="C144" s="20" t="str">
         <f>'Grad Raw Data'!H73</f>
-        <v>Denmark</v>
+        <v>DiDonato</v>
       </c>
       <c r="D144" s="20"/>
       <c r="E144" s="20" t="str">
@@ -53302,7 +53300,7 @@
     <row r="146" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="20" t="str">
         <f>'Grad Raw Data'!I74</f>
-        <v>Julie</v>
+        <v>Dante</v>
       </c>
       <c r="B146" s="20" t="str">
         <f>'Grad Raw Data'!K75</f>
@@ -53310,7 +53308,7 @@
       </c>
       <c r="C146" s="20" t="str">
         <f>'Grad Raw Data'!H74</f>
-        <v>DiDonato</v>
+        <v>DiSerio</v>
       </c>
       <c r="D146" s="20"/>
       <c r="E146" s="20" t="str">
@@ -53333,11 +53331,11 @@
     <row r="148" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="20" t="str">
         <f>'Grad Raw Data'!I75</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="B148" s="20" t="str">
         <f>'Grad Raw Data'!K76</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="C148" s="20" t="str">
         <f>'Grad Raw Data'!H75</f>
@@ -53364,15 +53362,15 @@
     <row r="150" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="20" t="str">
         <f>'Grad Raw Data'!I76</f>
-        <v>Antonio</v>
+        <v>Caitlin</v>
       </c>
       <c r="B150" s="20" t="str">
         <f>'Grad Raw Data'!K77</f>
-        <v>Joseph</v>
+        <v>Anne</v>
       </c>
       <c r="C150" s="20" t="str">
         <f>'Grad Raw Data'!H76</f>
-        <v>DiSerio</v>
+        <v>Donaghey</v>
       </c>
       <c r="D150" s="20"/>
       <c r="E150" s="20" t="str">
@@ -53395,15 +53393,15 @@
     <row r="152" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="20" t="str">
         <f>'Grad Raw Data'!I77</f>
-        <v>Caitlin</v>
+        <v>Quinn</v>
       </c>
       <c r="B152" s="20" t="str">
         <f>'Grad Raw Data'!K78</f>
-        <v>Anne</v>
+        <v>Kendall</v>
       </c>
       <c r="C152" s="20" t="str">
         <f>'Grad Raw Data'!H77</f>
-        <v>Donaghey</v>
+        <v>Donahue</v>
       </c>
       <c r="D152" s="20"/>
       <c r="E152" s="20" t="str">
@@ -53426,15 +53424,15 @@
     <row r="154" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="20" t="str">
         <f>'Grad Raw Data'!I78</f>
-        <v>Quinn</v>
+        <v>Alana</v>
       </c>
       <c r="B154" s="20" t="str">
         <f>'Grad Raw Data'!K79</f>
-        <v>Kendall</v>
+        <v>Mei-Lin Yamaki</v>
       </c>
       <c r="C154" s="20" t="str">
         <f>'Grad Raw Data'!H78</f>
-        <v>Donahue</v>
+        <v>Doroquez</v>
       </c>
       <c r="D154" s="20"/>
       <c r="E154" s="20" t="str">
@@ -53457,15 +53455,15 @@
     <row r="156" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="20" t="str">
         <f>'Grad Raw Data'!I79</f>
-        <v>Alana</v>
+        <v>Cassidy</v>
       </c>
       <c r="B156" s="20" t="str">
         <f>'Grad Raw Data'!K80</f>
-        <v>Mei-Lin Yamaki</v>
+        <v/>
       </c>
       <c r="C156" s="20" t="str">
         <f>'Grad Raw Data'!H79</f>
-        <v>Doroquez</v>
+        <v>Duca</v>
       </c>
       <c r="D156" s="20"/>
       <c r="E156" s="20" t="str">
@@ -53488,7 +53486,7 @@
     <row r="158" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="20" t="str">
         <f>'Grad Raw Data'!I80</f>
-        <v>Cassidy</v>
+        <v>Kyle</v>
       </c>
       <c r="B158" s="20" t="str">
         <f>'Grad Raw Data'!K81</f>
@@ -53496,7 +53494,7 @@
       </c>
       <c r="C158" s="20" t="str">
         <f>'Grad Raw Data'!H80</f>
-        <v>Duca</v>
+        <v>DuRoss</v>
       </c>
       <c r="D158" s="20"/>
       <c r="E158" s="20" t="str">
@@ -53519,7 +53517,7 @@
     <row r="160" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="20" t="str">
         <f>'Grad Raw Data'!I81</f>
-        <v>Kyle</v>
+        <v>Sean</v>
       </c>
       <c r="B160" s="20" t="str">
         <f>'Grad Raw Data'!K82</f>
@@ -53550,7 +53548,7 @@
     <row r="162" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="20" t="str">
         <f>'Grad Raw Data'!I82</f>
-        <v>Sean</v>
+        <v>William</v>
       </c>
       <c r="B162" s="20" t="str">
         <f>'Grad Raw Data'!K83</f>
@@ -53558,7 +53556,7 @@
       </c>
       <c r="C162" s="20" t="str">
         <f>'Grad Raw Data'!H82</f>
-        <v>DuRoss</v>
+        <v>Dyment</v>
       </c>
       <c r="D162" s="20"/>
       <c r="E162" s="20" t="str">
@@ -53581,7 +53579,7 @@
     <row r="164" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="20" t="str">
         <f>'Grad Raw Data'!I83</f>
-        <v>William</v>
+        <v>Luca</v>
       </c>
       <c r="B164" s="20" t="str">
         <f>'Grad Raw Data'!K84</f>
@@ -53589,7 +53587,7 @@
       </c>
       <c r="C164" s="20" t="str">
         <f>'Grad Raw Data'!H83</f>
-        <v>Dyment</v>
+        <v>Eliet</v>
       </c>
       <c r="D164" s="20"/>
       <c r="E164" s="20" t="str">
@@ -53612,7 +53610,7 @@
     <row r="166" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="20" t="str">
         <f>'Grad Raw Data'!I84</f>
-        <v>Luca</v>
+        <v>Finn</v>
       </c>
       <c r="B166" s="20" t="str">
         <f>'Grad Raw Data'!K85</f>
@@ -53620,7 +53618,7 @@
       </c>
       <c r="C166" s="20" t="str">
         <f>'Grad Raw Data'!H84</f>
-        <v>Eliet</v>
+        <v>Ellis</v>
       </c>
       <c r="D166" s="20"/>
       <c r="E166" s="20" t="str">
@@ -53643,7 +53641,7 @@
     <row r="168" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="20" t="str">
         <f>'Grad Raw Data'!I85</f>
-        <v>Finn</v>
+        <v>Levi</v>
       </c>
       <c r="B168" s="20" t="str">
         <f>'Grad Raw Data'!K86</f>
@@ -53651,7 +53649,7 @@
       </c>
       <c r="C168" s="20" t="str">
         <f>'Grad Raw Data'!H85</f>
-        <v>Ellis</v>
+        <v>Emmanuel</v>
       </c>
       <c r="D168" s="20"/>
       <c r="E168" s="20" t="str">
@@ -53674,7 +53672,7 @@
     <row r="170" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="20" t="str">
         <f>'Grad Raw Data'!I86</f>
-        <v>Levi</v>
+        <v>Kamryn</v>
       </c>
       <c r="B170" s="20" t="str">
         <f>'Grad Raw Data'!K87</f>
@@ -53682,7 +53680,7 @@
       </c>
       <c r="C170" s="20" t="str">
         <f>'Grad Raw Data'!H86</f>
-        <v>Emmanuel</v>
+        <v>Encarnacao</v>
       </c>
       <c r="D170" s="20"/>
       <c r="E170" s="20" t="str">
@@ -53705,7 +53703,7 @@
     <row r="172" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="20" t="str">
         <f>'Grad Raw Data'!I87</f>
-        <v>Kamryn</v>
+        <v>Samuel</v>
       </c>
       <c r="B172" s="20" t="str">
         <f>'Grad Raw Data'!K88</f>
@@ -53713,7 +53711,7 @@
       </c>
       <c r="C172" s="20" t="str">
         <f>'Grad Raw Data'!H87</f>
-        <v>Encarnacao</v>
+        <v>Fortes</v>
       </c>
       <c r="D172" s="20"/>
       <c r="E172" s="20" t="str">
@@ -53736,7 +53734,7 @@
     <row r="174" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="20" t="str">
         <f>'Grad Raw Data'!I88</f>
-        <v>Samuel</v>
+        <v>Kaylie</v>
       </c>
       <c r="B174" s="20" t="str">
         <f>'Grad Raw Data'!K89</f>
@@ -53744,7 +53742,7 @@
       </c>
       <c r="C174" s="20" t="str">
         <f>'Grad Raw Data'!H88</f>
-        <v>Fortes</v>
+        <v>Fantasia</v>
       </c>
       <c r="D174" s="20"/>
       <c r="E174" s="20" t="str">
@@ -53767,7 +53765,7 @@
     <row r="176" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="20" t="str">
         <f>'Grad Raw Data'!I89</f>
-        <v>Kaylie</v>
+        <v>Vince</v>
       </c>
       <c r="B176" s="20" t="str">
         <f>'Grad Raw Data'!K90</f>
@@ -53775,7 +53773,7 @@
       </c>
       <c r="C176" s="20" t="str">
         <f>'Grad Raw Data'!H89</f>
-        <v>Fantasia</v>
+        <v>Farnham</v>
       </c>
       <c r="D176" s="20"/>
       <c r="E176" s="20" t="str">
@@ -53798,7 +53796,7 @@
     <row r="178" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="20" t="str">
         <f>'Grad Raw Data'!I90</f>
-        <v>Vince</v>
+        <v>Colby</v>
       </c>
       <c r="B178" s="20" t="str">
         <f>'Grad Raw Data'!K91</f>
@@ -53806,7 +53804,7 @@
       </c>
       <c r="C178" s="20" t="str">
         <f>'Grad Raw Data'!H90</f>
-        <v>Farnham</v>
+        <v>Farris</v>
       </c>
       <c r="D178" s="20"/>
       <c r="E178" s="20" t="str">
@@ -53829,7 +53827,7 @@
     <row r="180" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="20" t="str">
         <f>'Grad Raw Data'!I91</f>
-        <v>Colby</v>
+        <v>Bryan</v>
       </c>
       <c r="B180" s="20" t="str">
         <f>'Grad Raw Data'!K92</f>
@@ -53837,7 +53835,7 @@
       </c>
       <c r="C180" s="20" t="str">
         <f>'Grad Raw Data'!H91</f>
-        <v>Farris</v>
+        <v>Fernandez</v>
       </c>
       <c r="D180" s="20"/>
       <c r="E180" s="20" t="str">
@@ -53860,7 +53858,7 @@
     <row r="182" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="20" t="str">
         <f>'Grad Raw Data'!I92</f>
-        <v>Bryan</v>
+        <v>Thomas</v>
       </c>
       <c r="B182" s="20" t="str">
         <f>'Grad Raw Data'!K93</f>
@@ -53868,7 +53866,7 @@
       </c>
       <c r="C182" s="20" t="str">
         <f>'Grad Raw Data'!H92</f>
-        <v>Fernandez</v>
+        <v>Fiore</v>
       </c>
       <c r="D182" s="20"/>
       <c r="E182" s="20" t="str">
@@ -53891,15 +53889,15 @@
     <row r="184" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="20" t="str">
         <f>'Grad Raw Data'!I93</f>
-        <v>Thomas</v>
+        <v>Finn</v>
       </c>
       <c r="B184" s="20" t="str">
         <f>'Grad Raw Data'!K94</f>
-        <v/>
+        <v>Patrick</v>
       </c>
       <c r="C184" s="20" t="str">
         <f>'Grad Raw Data'!H93</f>
-        <v>Fiore</v>
+        <v>Flaherty</v>
       </c>
       <c r="D184" s="20"/>
       <c r="E184" s="20" t="str">
@@ -53922,15 +53920,15 @@
     <row r="186" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="20" t="str">
         <f>'Grad Raw Data'!I94</f>
-        <v>Finn</v>
+        <v>Matthew</v>
       </c>
       <c r="B186" s="20" t="str">
         <f>'Grad Raw Data'!K95</f>
-        <v>Patrick</v>
+        <v/>
       </c>
       <c r="C186" s="20" t="str">
         <f>'Grad Raw Data'!H94</f>
-        <v>Flaherty</v>
+        <v>Forse</v>
       </c>
       <c r="D186" s="20"/>
       <c r="E186" s="20" t="str">
@@ -53953,7 +53951,7 @@
     <row r="188" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="20" t="str">
         <f>'Grad Raw Data'!I95</f>
-        <v>Matthew</v>
+        <v>Jacob</v>
       </c>
       <c r="B188" s="20" t="str">
         <f>'Grad Raw Data'!K96</f>
@@ -53961,7 +53959,7 @@
       </c>
       <c r="C188" s="20" t="str">
         <f>'Grad Raw Data'!H95</f>
-        <v>Forse</v>
+        <v>Frank</v>
       </c>
       <c r="D188" s="20"/>
       <c r="E188" s="20" t="str">
@@ -53984,7 +53982,7 @@
     <row r="190" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="20" t="str">
         <f>'Grad Raw Data'!I96</f>
-        <v>Jacob</v>
+        <v>Anthony</v>
       </c>
       <c r="B190" s="20" t="str">
         <f>'Grad Raw Data'!K97</f>
@@ -53992,7 +53990,7 @@
       </c>
       <c r="C190" s="20" t="str">
         <f>'Grad Raw Data'!H96</f>
-        <v>Frank</v>
+        <v>Fratto</v>
       </c>
       <c r="D190" s="20"/>
       <c r="E190" s="20" t="str">
@@ -54015,7 +54013,7 @@
     <row r="192" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="20" t="str">
         <f>'Grad Raw Data'!I97</f>
-        <v>Anthony</v>
+        <v>Gavin</v>
       </c>
       <c r="B192" s="20" t="str">
         <f>'Grad Raw Data'!K98</f>
@@ -54023,7 +54021,7 @@
       </c>
       <c r="C192" s="20" t="str">
         <f>'Grad Raw Data'!H97</f>
-        <v>Fratto</v>
+        <v>Fucarile</v>
       </c>
       <c r="D192" s="20"/>
       <c r="E192" s="20" t="str">
@@ -54046,7 +54044,7 @@
     <row r="194" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="20" t="str">
         <f>'Grad Raw Data'!I98</f>
-        <v>Gavin</v>
+        <v>Cole</v>
       </c>
       <c r="B194" s="20" t="str">
         <f>'Grad Raw Data'!K99</f>
@@ -54054,7 +54052,7 @@
       </c>
       <c r="C194" s="20" t="str">
         <f>'Grad Raw Data'!H98</f>
-        <v>Fucarile</v>
+        <v>Fusco</v>
       </c>
       <c r="D194" s="20"/>
       <c r="E194" s="20" t="str">
@@ -54077,15 +54075,15 @@
     <row r="196" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="20" t="str">
         <f>'Grad Raw Data'!I99</f>
-        <v>Cole</v>
+        <v>Paul</v>
       </c>
       <c r="B196" s="20" t="str">
         <f>'Grad Raw Data'!K100</f>
-        <v/>
+        <v>Richard</v>
       </c>
       <c r="C196" s="20" t="str">
         <f>'Grad Raw Data'!H99</f>
-        <v>Fusco</v>
+        <v>Gaeta</v>
       </c>
       <c r="D196" s="20"/>
       <c r="E196" s="20" t="str">
@@ -54108,15 +54106,15 @@
     <row r="198" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="20" t="str">
         <f>'Grad Raw Data'!I100</f>
-        <v>Paul</v>
+        <v>Lucas</v>
       </c>
       <c r="B198" s="20" t="str">
         <f>'Grad Raw Data'!K101</f>
-        <v>Richard</v>
+        <v/>
       </c>
       <c r="C198" s="20" t="str">
         <f>'Grad Raw Data'!H100</f>
-        <v>Gaeta</v>
+        <v>Gager</v>
       </c>
       <c r="D198" s="20"/>
       <c r="E198" s="20" t="str">
@@ -54139,7 +54137,7 @@
     <row r="200" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="20" t="str">
         <f>'Grad Raw Data'!I101</f>
-        <v>Lucas</v>
+        <v>Nevaeh</v>
       </c>
       <c r="B200" s="20" t="str">
         <f>'Grad Raw Data'!K102</f>
@@ -54147,7 +54145,7 @@
       </c>
       <c r="C200" s="20" t="str">
         <f>'Grad Raw Data'!H101</f>
-        <v>Gager</v>
+        <v>Galindo</v>
       </c>
       <c r="D200" s="20"/>
       <c r="E200" s="20" t="str">
@@ -54170,7 +54168,7 @@
     <row r="202" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="20" t="str">
         <f>'Grad Raw Data'!I102</f>
-        <v>Nevaeh</v>
+        <v>Joseph</v>
       </c>
       <c r="B202" s="20" t="str">
         <f>'Grad Raw Data'!K103</f>
@@ -54178,7 +54176,7 @@
       </c>
       <c r="C202" s="20" t="str">
         <f>'Grad Raw Data'!H102</f>
-        <v>Galindo</v>
+        <v>Gallagher</v>
       </c>
       <c r="D202" s="20"/>
       <c r="E202" s="20" t="str">
@@ -54201,7 +54199,7 @@
     <row r="204" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="20" t="str">
         <f>'Grad Raw Data'!I103</f>
-        <v>Joseph</v>
+        <v>Brendan</v>
       </c>
       <c r="B204" s="20" t="str">
         <f>'Grad Raw Data'!K104</f>
@@ -54209,7 +54207,7 @@
       </c>
       <c r="C204" s="20" t="str">
         <f>'Grad Raw Data'!H103</f>
-        <v>Gallagher</v>
+        <v>Gauvin</v>
       </c>
       <c r="D204" s="20"/>
       <c r="E204" s="20" t="str">
@@ -54232,7 +54230,7 @@
     <row r="206" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="20" t="str">
         <f>'Grad Raw Data'!I104</f>
-        <v>Brendan</v>
+        <v>Bereket</v>
       </c>
       <c r="B206" s="20" t="str">
         <f>'Grad Raw Data'!K105</f>
@@ -54240,7 +54238,7 @@
       </c>
       <c r="C206" s="20" t="str">
         <f>'Grad Raw Data'!H104</f>
-        <v>Gauvin</v>
+        <v>Gebeyaw</v>
       </c>
       <c r="D206" s="20"/>
       <c r="E206" s="20" t="str">
@@ -54263,7 +54261,7 @@
     <row r="208" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="20" t="str">
         <f>'Grad Raw Data'!I105</f>
-        <v>Bereket</v>
+        <v>Alix</v>
       </c>
       <c r="B208" s="20" t="str">
         <f>'Grad Raw Data'!K106</f>
@@ -54271,7 +54269,7 @@
       </c>
       <c r="C208" s="20" t="str">
         <f>'Grad Raw Data'!H105</f>
-        <v>Gebeyaw</v>
+        <v>Gellot</v>
       </c>
       <c r="D208" s="20"/>
       <c r="E208" s="20" t="str">
@@ -54294,7 +54292,7 @@
     <row r="210" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="20" t="str">
         <f>'Grad Raw Data'!I106</f>
-        <v>Alix</v>
+        <v>Cameron</v>
       </c>
       <c r="B210" s="20" t="str">
         <f>'Grad Raw Data'!K107</f>
@@ -54302,7 +54300,7 @@
       </c>
       <c r="C210" s="20" t="str">
         <f>'Grad Raw Data'!H106</f>
-        <v>Gellot</v>
+        <v>Gigler</v>
       </c>
       <c r="D210" s="20"/>
       <c r="E210" s="20" t="str">
@@ -54325,7 +54323,7 @@
     <row r="212" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="20" t="str">
         <f>'Grad Raw Data'!I107</f>
-        <v>Cameron</v>
+        <v>Alex</v>
       </c>
       <c r="B212" s="20" t="str">
         <f>'Grad Raw Data'!K108</f>
@@ -54333,7 +54331,7 @@
       </c>
       <c r="C212" s="20" t="str">
         <f>'Grad Raw Data'!H107</f>
-        <v>Gigler</v>
+        <v>Gisetto</v>
       </c>
       <c r="D212" s="20"/>
       <c r="E212" s="20" t="str">
@@ -54356,7 +54354,7 @@
     <row r="214" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="20" t="str">
         <f>'Grad Raw Data'!I108</f>
-        <v>Alex</v>
+        <v>Benjamin</v>
       </c>
       <c r="B214" s="20" t="str">
         <f>'Grad Raw Data'!K109</f>
@@ -54364,7 +54362,7 @@
       </c>
       <c r="C214" s="20" t="str">
         <f>'Grad Raw Data'!H108</f>
-        <v>Gisetto</v>
+        <v>Goldlust</v>
       </c>
       <c r="D214" s="20"/>
       <c r="E214" s="20" t="str">
@@ -54387,7 +54385,7 @@
     <row r="216" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="20" t="str">
         <f>'Grad Raw Data'!I109</f>
-        <v>Benjamin</v>
+        <v>Jack</v>
       </c>
       <c r="B216" s="20" t="str">
         <f>'Grad Raw Data'!K110</f>
@@ -54395,7 +54393,7 @@
       </c>
       <c r="C216" s="20" t="str">
         <f>'Grad Raw Data'!H109</f>
-        <v>Goldlust</v>
+        <v>Goodfellow</v>
       </c>
       <c r="D216" s="20"/>
       <c r="E216" s="20" t="str">
@@ -54418,7 +54416,7 @@
     <row r="218" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="20" t="str">
         <f>'Grad Raw Data'!I110</f>
-        <v>Jack</v>
+        <v>Drew</v>
       </c>
       <c r="B218" s="20" t="str">
         <f>'Grad Raw Data'!K111</f>
@@ -54426,7 +54424,7 @@
       </c>
       <c r="C218" s="20" t="str">
         <f>'Grad Raw Data'!H110</f>
-        <v>Goodfellow</v>
+        <v>Gorski</v>
       </c>
       <c r="D218" s="20"/>
       <c r="E218" s="20" t="str">
@@ -54449,7 +54447,7 @@
     <row r="220" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="20" t="str">
         <f>'Grad Raw Data'!I111</f>
-        <v>Drew</v>
+        <v>Lila</v>
       </c>
       <c r="B220" s="20" t="str">
         <f>'Grad Raw Data'!K112</f>
@@ -54457,7 +54455,7 @@
       </c>
       <c r="C220" s="20" t="str">
         <f>'Grad Raw Data'!H111</f>
-        <v>Gorski</v>
+        <v>Gosdanian</v>
       </c>
       <c r="D220" s="20"/>
       <c r="E220" s="20" t="str">
@@ -54480,15 +54478,15 @@
     <row r="222" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="20" t="str">
         <f>'Grad Raw Data'!I112</f>
-        <v>Lila</v>
+        <v>Cole</v>
       </c>
       <c r="B222" s="20" t="str">
         <f>'Grad Raw Data'!K113</f>
-        <v/>
+        <v>Sebastian</v>
       </c>
       <c r="C222" s="20" t="str">
         <f>'Grad Raw Data'!H112</f>
-        <v>Gosdanian</v>
+        <v>Grant</v>
       </c>
       <c r="D222" s="20"/>
       <c r="E222" s="20" t="str">
@@ -54511,15 +54509,15 @@
     <row r="224" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="20" t="str">
         <f>'Grad Raw Data'!I113</f>
-        <v>Cole</v>
+        <v>Kendall</v>
       </c>
       <c r="B224" s="20" t="str">
         <f>'Grad Raw Data'!K114</f>
-        <v>Sebastian</v>
+        <v/>
       </c>
       <c r="C224" s="20" t="str">
         <f>'Grad Raw Data'!H113</f>
-        <v>Grant</v>
+        <v>Graves</v>
       </c>
       <c r="D224" s="20"/>
       <c r="E224" s="20" t="str">
@@ -54542,15 +54540,15 @@
     <row r="226" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="20" t="str">
         <f>'Grad Raw Data'!I114</f>
-        <v>Kendall</v>
+        <v>Griffin</v>
       </c>
       <c r="B226" s="20" t="str">
         <f>'Grad Raw Data'!K115</f>
-        <v/>
+        <v>James</v>
       </c>
       <c r="C226" s="20" t="str">
         <f>'Grad Raw Data'!H114</f>
-        <v>Graves</v>
+        <v>Haggerty</v>
       </c>
       <c r="D226" s="20"/>
       <c r="E226" s="20" t="str">
@@ -54573,15 +54571,15 @@
     <row r="228" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="20" t="str">
         <f>'Grad Raw Data'!I115</f>
-        <v>Griffin</v>
+        <v>Andrea</v>
       </c>
       <c r="B228" s="20" t="str">
         <f>'Grad Raw Data'!K116</f>
-        <v>James</v>
+        <v/>
       </c>
       <c r="C228" s="20" t="str">
         <f>'Grad Raw Data'!H115</f>
-        <v>Haggerty</v>
+        <v>Hall</v>
       </c>
       <c r="D228" s="20"/>
       <c r="E228" s="20" t="str">
@@ -54604,7 +54602,7 @@
     <row r="230" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="20" t="str">
         <f>'Grad Raw Data'!I116</f>
-        <v>Andrea</v>
+        <v>Sarah</v>
       </c>
       <c r="B230" s="20" t="str">
         <f>'Grad Raw Data'!K117</f>
@@ -54612,7 +54610,7 @@
       </c>
       <c r="C230" s="20" t="str">
         <f>'Grad Raw Data'!H116</f>
-        <v>Hall</v>
+        <v>Hamilton</v>
       </c>
       <c r="D230" s="20"/>
       <c r="E230" s="20" t="str">
@@ -54635,7 +54633,7 @@
     <row r="232" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="20" t="str">
         <f>'Grad Raw Data'!I117</f>
-        <v>Sarah</v>
+        <v>Margaret</v>
       </c>
       <c r="B232" s="20" t="str">
         <f>'Grad Raw Data'!K118</f>
@@ -54643,7 +54641,7 @@
       </c>
       <c r="C232" s="20" t="str">
         <f>'Grad Raw Data'!H117</f>
-        <v>Hamilton</v>
+        <v>Hanifan</v>
       </c>
       <c r="D232" s="20"/>
       <c r="E232" s="20" t="str">
@@ -54666,7 +54664,7 @@
     <row r="234" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="20" t="str">
         <f>'Grad Raw Data'!I118</f>
-        <v>Margaret</v>
+        <v>Cameron</v>
       </c>
       <c r="B234" s="20" t="str">
         <f>'Grad Raw Data'!K119</f>
@@ -54674,7 +54672,7 @@
       </c>
       <c r="C234" s="20" t="str">
         <f>'Grad Raw Data'!H118</f>
-        <v>Hanifan</v>
+        <v>Harrigan</v>
       </c>
       <c r="D234" s="20"/>
       <c r="E234" s="20" t="str">
@@ -54697,7 +54695,7 @@
     <row r="236" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="20" t="str">
         <f>'Grad Raw Data'!I119</f>
-        <v>Cameron</v>
+        <v>Victoria</v>
       </c>
       <c r="B236" s="20" t="str">
         <f>'Grad Raw Data'!K120</f>
@@ -54705,7 +54703,7 @@
       </c>
       <c r="C236" s="20" t="str">
         <f>'Grad Raw Data'!H119</f>
-        <v>Harrigan</v>
+        <v>Henri</v>
       </c>
       <c r="D236" s="20"/>
       <c r="E236" s="20" t="str">
@@ -54728,7 +54726,7 @@
     <row r="238" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="20" t="str">
         <f>'Grad Raw Data'!I120</f>
-        <v>Victoria</v>
+        <v>Kayke</v>
       </c>
       <c r="B238" s="20" t="str">
         <f>'Grad Raw Data'!K121</f>
@@ -54736,7 +54734,7 @@
       </c>
       <c r="C238" s="20" t="str">
         <f>'Grad Raw Data'!H120</f>
-        <v>Henri</v>
+        <v>Henrique</v>
       </c>
       <c r="D238" s="20"/>
       <c r="E238" s="20" t="str">
@@ -54759,7 +54757,7 @@
     <row r="240" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="20" t="str">
         <f>'Grad Raw Data'!I121</f>
-        <v>Kayke</v>
+        <v>Jahkye</v>
       </c>
       <c r="B240" s="20" t="str">
         <f>'Grad Raw Data'!K122</f>
@@ -54767,7 +54765,7 @@
       </c>
       <c r="C240" s="20" t="str">
         <f>'Grad Raw Data'!H121</f>
-        <v>Henrique</v>
+        <v>Hobson</v>
       </c>
       <c r="D240" s="20"/>
       <c r="E240" s="20" t="str">
@@ -54790,7 +54788,7 @@
     <row r="242" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="20" t="str">
         <f>'Grad Raw Data'!I122</f>
-        <v>Jahkye</v>
+        <v>Sam</v>
       </c>
       <c r="B242" s="20" t="str">
         <f>'Grad Raw Data'!K123</f>
@@ -54798,7 +54796,7 @@
       </c>
       <c r="C242" s="20" t="str">
         <f>'Grad Raw Data'!H122</f>
-        <v>Hobson</v>
+        <v>Holt</v>
       </c>
       <c r="D242" s="20"/>
       <c r="E242" s="20" t="str">
@@ -54821,7 +54819,7 @@
     <row r="244" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="20" t="str">
         <f>'Grad Raw Data'!I123</f>
-        <v>Sam</v>
+        <v>Benjamin</v>
       </c>
       <c r="B244" s="20" t="str">
         <f>'Grad Raw Data'!K124</f>
@@ -54829,7 +54827,7 @@
       </c>
       <c r="C244" s="20" t="str">
         <f>'Grad Raw Data'!H123</f>
-        <v>Holt</v>
+        <v>Houle</v>
       </c>
       <c r="D244" s="20"/>
       <c r="E244" s="20" t="str">
@@ -54852,7 +54850,7 @@
     <row r="246" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="20" t="str">
         <f>'Grad Raw Data'!I124</f>
-        <v>Benjamin</v>
+        <v>Evin</v>
       </c>
       <c r="B246" s="20" t="str">
         <f>'Grad Raw Data'!K125</f>
@@ -54860,7 +54858,7 @@
       </c>
       <c r="C246" s="20" t="str">
         <f>'Grad Raw Data'!H124</f>
-        <v>Houle</v>
+        <v>Howell</v>
       </c>
       <c r="D246" s="20"/>
       <c r="E246" s="20" t="str">
@@ -54883,15 +54881,15 @@
     <row r="248" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="20" t="str">
         <f>'Grad Raw Data'!I125</f>
-        <v>Evin</v>
+        <v>Paul</v>
       </c>
       <c r="B248" s="20" t="str">
         <f>'Grad Raw Data'!K126</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="C248" s="20" t="str">
         <f>'Grad Raw Data'!H125</f>
-        <v>Howell</v>
+        <v>Iosua</v>
       </c>
       <c r="D248" s="20"/>
       <c r="E248" s="20" t="str">
@@ -54914,15 +54912,15 @@
     <row r="250" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="20" t="str">
         <f>'Grad Raw Data'!I126</f>
-        <v>Paul</v>
+        <v>Leah</v>
       </c>
       <c r="B250" s="20" t="str">
         <f>'Grad Raw Data'!K127</f>
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="C250" s="20" t="str">
         <f>'Grad Raw Data'!H126</f>
-        <v>Iosua</v>
+        <v>Jackvony</v>
       </c>
       <c r="D250" s="20"/>
       <c r="E250" s="20" t="str">
@@ -54945,7 +54943,7 @@
     <row r="252" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="20" t="str">
         <f>'Grad Raw Data'!I127</f>
-        <v>Leah</v>
+        <v>Wayne</v>
       </c>
       <c r="B252" s="20" t="str">
         <f>'Grad Raw Data'!K128</f>
@@ -54953,7 +54951,7 @@
       </c>
       <c r="C252" s="20" t="str">
         <f>'Grad Raw Data'!H127</f>
-        <v>Jackvony</v>
+        <v>Jankun</v>
       </c>
       <c r="D252" s="20"/>
       <c r="E252" s="20" t="str">
@@ -54976,7 +54974,7 @@
     <row r="254" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="20" t="str">
         <f>'Grad Raw Data'!I128</f>
-        <v>Wayne</v>
+        <v>Tristan</v>
       </c>
       <c r="B254" s="20" t="str">
         <f>'Grad Raw Data'!K129</f>
@@ -54984,7 +54982,7 @@
       </c>
       <c r="C254" s="20" t="str">
         <f>'Grad Raw Data'!H128</f>
-        <v>Jankun</v>
+        <v>Jenkins</v>
       </c>
       <c r="D254" s="20"/>
       <c r="E254" s="20" t="str">
@@ -55007,7 +55005,7 @@
     <row r="256" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="20" t="str">
         <f>'Grad Raw Data'!I129</f>
-        <v>Tristan</v>
+        <v>Evan</v>
       </c>
       <c r="B256" s="20" t="str">
         <f>'Grad Raw Data'!K130</f>
@@ -55015,7 +55013,7 @@
       </c>
       <c r="C256" s="20" t="str">
         <f>'Grad Raw Data'!H129</f>
-        <v>Jenkins</v>
+        <v>Jenney</v>
       </c>
       <c r="D256" s="20"/>
       <c r="E256" s="20" t="str">
@@ -55038,7 +55036,7 @@
     <row r="258" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="20" t="str">
         <f>'Grad Raw Data'!I130</f>
-        <v>Evan</v>
+        <v>Michael</v>
       </c>
       <c r="B258" s="20" t="str">
         <f>'Grad Raw Data'!K131</f>
@@ -55069,7 +55067,7 @@
     <row r="260" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="20" t="str">
         <f>'Grad Raw Data'!I131</f>
-        <v>Michael</v>
+        <v>Luke</v>
       </c>
       <c r="B260" s="20" t="str">
         <f>'Grad Raw Data'!K132</f>
@@ -55077,7 +55075,7 @@
       </c>
       <c r="C260" s="20" t="str">
         <f>'Grad Raw Data'!H131</f>
-        <v>Jenney</v>
+        <v>Johnson</v>
       </c>
       <c r="D260" s="20"/>
       <c r="E260" s="20" t="str">
@@ -55100,7 +55098,7 @@
     <row r="262" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="20" t="str">
         <f>'Grad Raw Data'!I132</f>
-        <v>Luke</v>
+        <v>Maeve</v>
       </c>
       <c r="B262" s="20" t="str">
         <f>'Grad Raw Data'!K133</f>
@@ -55108,7 +55106,7 @@
       </c>
       <c r="C262" s="20" t="str">
         <f>'Grad Raw Data'!H132</f>
-        <v>Johnson</v>
+        <v>Jones</v>
       </c>
       <c r="D262" s="20"/>
       <c r="E262" s="20" t="str">
@@ -55131,7 +55129,7 @@
     <row r="264" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="20" t="str">
         <f>'Grad Raw Data'!I133</f>
-        <v>Maeve</v>
+        <v>Nolan</v>
       </c>
       <c r="B264" s="20" t="str">
         <f>'Grad Raw Data'!K134</f>
@@ -55139,7 +55137,7 @@
       </c>
       <c r="C264" s="20" t="str">
         <f>'Grad Raw Data'!H133</f>
-        <v>Jones</v>
+        <v>Jordan</v>
       </c>
       <c r="D264" s="20"/>
       <c r="E264" s="20" t="str">
@@ -55162,7 +55160,7 @@
     <row r="266" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="20" t="str">
         <f>'Grad Raw Data'!I134</f>
-        <v>Nolan</v>
+        <v>Emma</v>
       </c>
       <c r="B266" s="20" t="str">
         <f>'Grad Raw Data'!K135</f>
@@ -55170,7 +55168,7 @@
       </c>
       <c r="C266" s="20" t="str">
         <f>'Grad Raw Data'!H134</f>
-        <v>Jordan</v>
+        <v>Kaberle</v>
       </c>
       <c r="D266" s="20"/>
       <c r="E266" s="20" t="str">
@@ -55193,7 +55191,7 @@
     <row r="268" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="20" t="str">
         <f>'Grad Raw Data'!I135</f>
-        <v>Emma</v>
+        <v>Azra</v>
       </c>
       <c r="B268" s="20" t="str">
         <f>'Grad Raw Data'!K136</f>
@@ -55201,7 +55199,7 @@
       </c>
       <c r="C268" s="20" t="str">
         <f>'Grad Raw Data'!H135</f>
-        <v>Kaberle</v>
+        <v>Kadric</v>
       </c>
       <c r="D268" s="20"/>
       <c r="E268" s="20" t="str">
@@ -55224,7 +55222,7 @@
     <row r="270" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="20" t="str">
         <f>'Grad Raw Data'!I136</f>
-        <v>Azra</v>
+        <v>Brady</v>
       </c>
       <c r="B270" s="20" t="str">
         <f>'Grad Raw Data'!K137</f>
@@ -55232,7 +55230,7 @@
       </c>
       <c r="C270" s="20" t="str">
         <f>'Grad Raw Data'!H136</f>
-        <v>Kadric</v>
+        <v>Keaveney</v>
       </c>
       <c r="D270" s="20"/>
       <c r="E270" s="20" t="str">
@@ -55255,7 +55253,7 @@
     <row r="272" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="20" t="str">
         <f>'Grad Raw Data'!I137</f>
-        <v>Brady</v>
+        <v>Hannah</v>
       </c>
       <c r="B272" s="20" t="str">
         <f>'Grad Raw Data'!K138</f>
@@ -55263,7 +55261,7 @@
       </c>
       <c r="C272" s="20" t="str">
         <f>'Grad Raw Data'!H137</f>
-        <v>Keaveney</v>
+        <v>Kenton</v>
       </c>
       <c r="D272" s="20"/>
       <c r="E272" s="20" t="str">
@@ -55286,7 +55284,7 @@
     <row r="274" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="20" t="str">
         <f>'Grad Raw Data'!I138</f>
-        <v>Hannah</v>
+        <v>Aiden</v>
       </c>
       <c r="B274" s="20" t="str">
         <f>'Grad Raw Data'!K139</f>
@@ -55294,7 +55292,7 @@
       </c>
       <c r="C274" s="20" t="str">
         <f>'Grad Raw Data'!H138</f>
-        <v>Kenton</v>
+        <v>Kiley</v>
       </c>
       <c r="D274" s="20"/>
       <c r="E274" s="20" t="str">
@@ -55317,7 +55315,7 @@
     <row r="276" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="20" t="str">
         <f>'Grad Raw Data'!I139</f>
-        <v>Aiden</v>
+        <v>Clinton</v>
       </c>
       <c r="B276" s="20" t="str">
         <f>'Grad Raw Data'!K140</f>
@@ -55325,7 +55323,7 @@
       </c>
       <c r="C276" s="20" t="str">
         <f>'Grad Raw Data'!H139</f>
-        <v>Kiley</v>
+        <v>King</v>
       </c>
       <c r="D276" s="20"/>
       <c r="E276" s="20" t="str">
@@ -55348,7 +55346,7 @@
     <row r="278" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="20" t="str">
         <f>'Grad Raw Data'!I140</f>
-        <v>Clinton</v>
+        <v>Kyle</v>
       </c>
       <c r="B278" s="20" t="str">
         <f>'Grad Raw Data'!K141</f>
@@ -55356,7 +55354,7 @@
       </c>
       <c r="C278" s="20" t="str">
         <f>'Grad Raw Data'!H140</f>
-        <v>King</v>
+        <v>Koster</v>
       </c>
       <c r="D278" s="20"/>
       <c r="E278" s="20" t="str">
@@ -55379,15 +55377,15 @@
     <row r="280" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="20" t="str">
         <f>'Grad Raw Data'!I141</f>
-        <v>Kyle</v>
+        <v>Enzo</v>
       </c>
       <c r="B280" s="20" t="str">
         <f>'Grad Raw Data'!K142</f>
-        <v/>
+        <v>George</v>
       </c>
       <c r="C280" s="20" t="str">
         <f>'Grad Raw Data'!H141</f>
-        <v>Koster</v>
+        <v>Lalicata</v>
       </c>
       <c r="D280" s="20"/>
       <c r="E280" s="20" t="str">
@@ -55410,15 +55408,15 @@
     <row r="282" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="20" t="str">
         <f>'Grad Raw Data'!I142</f>
-        <v>Enzo</v>
+        <v>Matthew</v>
       </c>
       <c r="B282" s="20" t="str">
         <f>'Grad Raw Data'!K143</f>
-        <v>George</v>
+        <v/>
       </c>
       <c r="C282" s="20" t="str">
         <f>'Grad Raw Data'!H142</f>
-        <v>Lalicata</v>
+        <v>Laurino</v>
       </c>
       <c r="D282" s="20"/>
       <c r="E282" s="20" t="str">
@@ -55441,7 +55439,7 @@
     <row r="284" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="20" t="str">
         <f>'Grad Raw Data'!I143</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="B284" s="20" t="str">
         <f>'Grad Raw Data'!K144</f>
@@ -55472,7 +55470,7 @@
     <row r="286" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="20" t="str">
         <f>'Grad Raw Data'!I144</f>
-        <v>Jonathan</v>
+        <v>Asad</v>
       </c>
       <c r="B286" s="20" t="str">
         <f>'Grad Raw Data'!K145</f>
@@ -55480,7 +55478,7 @@
       </c>
       <c r="C286" s="20" t="str">
         <f>'Grad Raw Data'!H144</f>
-        <v>Laurino</v>
+        <v>Layne</v>
       </c>
       <c r="D286" s="20"/>
       <c r="E286" s="20" t="str">
@@ -55503,7 +55501,7 @@
     <row r="288" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="20" t="str">
         <f>'Grad Raw Data'!I145</f>
-        <v>Asad</v>
+        <v>Jonathan</v>
       </c>
       <c r="B288" s="20" t="str">
         <f>'Grad Raw Data'!K146</f>
@@ -55511,7 +55509,7 @@
       </c>
       <c r="C288" s="20" t="str">
         <f>'Grad Raw Data'!H145</f>
-        <v>Layne</v>
+        <v>Lee</v>
       </c>
       <c r="D288" s="20"/>
       <c r="E288" s="20" t="str">
@@ -55534,11 +55532,11 @@
     <row r="290" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="20" t="str">
         <f>'Grad Raw Data'!I146</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="B290" s="20" t="str">
         <f>'Grad Raw Data'!K147</f>
-        <v/>
+        <v>James</v>
       </c>
       <c r="C290" s="20" t="str">
         <f>'Grad Raw Data'!H146</f>
@@ -55565,15 +55563,15 @@
     <row r="292" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="20" t="str">
         <f>'Grad Raw Data'!I147</f>
-        <v>Austin</v>
+        <v>Desmond</v>
       </c>
       <c r="B292" s="20" t="str">
         <f>'Grad Raw Data'!K148</f>
-        <v>James</v>
+        <v/>
       </c>
       <c r="C292" s="20" t="str">
         <f>'Grad Raw Data'!H147</f>
-        <v>Lee</v>
+        <v>Lethin</v>
       </c>
       <c r="D292" s="20"/>
       <c r="E292" s="20" t="str">
@@ -55596,7 +55594,7 @@
     <row r="294" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="20" t="str">
         <f>'Grad Raw Data'!I148</f>
-        <v>Desmond</v>
+        <v>Katie</v>
       </c>
       <c r="B294" s="20" t="str">
         <f>'Grad Raw Data'!K149</f>
@@ -55604,7 +55602,7 @@
       </c>
       <c r="C294" s="20" t="str">
         <f>'Grad Raw Data'!H148</f>
-        <v>Lethin</v>
+        <v>Lewis</v>
       </c>
       <c r="D294" s="20"/>
       <c r="E294" s="20" t="str">
@@ -55627,7 +55625,7 @@
     <row r="296" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="20" t="str">
         <f>'Grad Raw Data'!I149</f>
-        <v>Katie</v>
+        <v>Isabelle</v>
       </c>
       <c r="B296" s="20" t="str">
         <f>'Grad Raw Data'!K150</f>
@@ -55635,7 +55633,7 @@
       </c>
       <c r="C296" s="20" t="str">
         <f>'Grad Raw Data'!H149</f>
-        <v>Lewis</v>
+        <v>Lightbody</v>
       </c>
       <c r="D296" s="20"/>
       <c r="E296" s="20" t="str">
@@ -55658,7 +55656,7 @@
     <row r="298" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="20" t="str">
         <f>'Grad Raw Data'!I150</f>
-        <v>Isabelle</v>
+        <v>Steven</v>
       </c>
       <c r="B298" s="20" t="str">
         <f>'Grad Raw Data'!K151</f>
@@ -55666,7 +55664,7 @@
       </c>
       <c r="C298" s="20" t="str">
         <f>'Grad Raw Data'!H150</f>
-        <v>Lightbody</v>
+        <v>Lin</v>
       </c>
       <c r="D298" s="20"/>
       <c r="E298" s="20" t="str">
@@ -55689,7 +55687,7 @@
     <row r="300" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="20" t="str">
         <f>'Grad Raw Data'!I151</f>
-        <v>Steven</v>
+        <v>Zackary</v>
       </c>
       <c r="B300" s="20" t="str">
         <f>'Grad Raw Data'!K152</f>
@@ -55697,7 +55695,7 @@
       </c>
       <c r="C300" s="20" t="str">
         <f>'Grad Raw Data'!H151</f>
-        <v>Lin</v>
+        <v>Lizotte</v>
       </c>
       <c r="D300" s="20"/>
       <c r="E300" s="20" t="str">
@@ -55720,7 +55718,7 @@
     <row r="302" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="20" t="str">
         <f>'Grad Raw Data'!I152</f>
-        <v>Zackary</v>
+        <v>Isla</v>
       </c>
       <c r="B302" s="20" t="str">
         <f>'Grad Raw Data'!K153</f>
@@ -55728,7 +55726,7 @@
       </c>
       <c r="C302" s="20" t="str">
         <f>'Grad Raw Data'!H152</f>
-        <v>Lizotte</v>
+        <v>Lusk</v>
       </c>
       <c r="D302" s="20"/>
       <c r="E302" s="20" t="str">
@@ -55751,7 +55749,7 @@
     <row r="304" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="20" t="str">
         <f>'Grad Raw Data'!I153</f>
-        <v>Isla</v>
+        <v>Lilyana</v>
       </c>
       <c r="B304" s="20" t="str">
         <f>'Grad Raw Data'!K154</f>
@@ -55759,7 +55757,7 @@
       </c>
       <c r="C304" s="20" t="str">
         <f>'Grad Raw Data'!H153</f>
-        <v>Lusk</v>
+        <v>Madden</v>
       </c>
       <c r="D304" s="20"/>
       <c r="E304" s="20" t="str">
@@ -55782,7 +55780,7 @@
     <row r="306" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="20" t="str">
         <f>'Grad Raw Data'!I154</f>
-        <v>Lilyana</v>
+        <v>Rosalia</v>
       </c>
       <c r="B306" s="20" t="str">
         <f>'Grad Raw Data'!K155</f>
@@ -55790,7 +55788,7 @@
       </c>
       <c r="C306" s="20" t="str">
         <f>'Grad Raw Data'!H154</f>
-        <v>Madden</v>
+        <v>Maganzini</v>
       </c>
       <c r="D306" s="20"/>
       <c r="E306" s="20" t="str">
@@ -55813,11 +55811,11 @@
     <row r="308" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="20" t="str">
         <f>'Grad Raw Data'!I155</f>
-        <v>Rosalia</v>
+        <v>Trent</v>
       </c>
       <c r="B308" s="20" t="str">
         <f>'Grad Raw Data'!K156</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="C308" s="20" t="str">
         <f>'Grad Raw Data'!H155</f>
@@ -55844,15 +55842,15 @@
     <row r="310" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="20" t="str">
         <f>'Grad Raw Data'!I156</f>
-        <v>Trent</v>
+        <v>Emma</v>
       </c>
       <c r="B310" s="20" t="str">
         <f>'Grad Raw Data'!K157</f>
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="C310" s="20" t="str">
         <f>'Grad Raw Data'!H156</f>
-        <v>Maganzini</v>
+        <v>Mahoney</v>
       </c>
       <c r="D310" s="20"/>
       <c r="E310" s="20" t="str">
@@ -55875,7 +55873,7 @@
     <row r="312" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="20" t="str">
         <f>'Grad Raw Data'!I157</f>
-        <v>Emma</v>
+        <v>Charles</v>
       </c>
       <c r="B312" s="20" t="str">
         <f>'Grad Raw Data'!K158</f>
@@ -55883,7 +55881,7 @@
       </c>
       <c r="C312" s="20" t="str">
         <f>'Grad Raw Data'!H157</f>
-        <v>Mahoney</v>
+        <v>Maness</v>
       </c>
       <c r="D312" s="20"/>
       <c r="E312" s="20" t="str">
@@ -55906,7 +55904,7 @@
     <row r="314" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="20" t="str">
         <f>'Grad Raw Data'!I158</f>
-        <v>Charles</v>
+        <v>Evan</v>
       </c>
       <c r="B314" s="20" t="str">
         <f>'Grad Raw Data'!K159</f>
@@ -55914,7 +55912,7 @@
       </c>
       <c r="C314" s="20" t="str">
         <f>'Grad Raw Data'!H158</f>
-        <v>Maness</v>
+        <v>Manfredi</v>
       </c>
       <c r="D314" s="20"/>
       <c r="E314" s="20" t="str">
@@ -55937,7 +55935,7 @@
     <row r="316" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="20" t="str">
         <f>'Grad Raw Data'!I159</f>
-        <v>Evan</v>
+        <v>Syler</v>
       </c>
       <c r="B316" s="20" t="str">
         <f>'Grad Raw Data'!K160</f>
@@ -55945,7 +55943,7 @@
       </c>
       <c r="C316" s="20" t="str">
         <f>'Grad Raw Data'!H159</f>
-        <v>Manfredi</v>
+        <v>Manning</v>
       </c>
       <c r="D316" s="20"/>
       <c r="E316" s="20" t="str">
@@ -55968,7 +55966,7 @@
     <row r="318" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="20" t="str">
         <f>'Grad Raw Data'!I160</f>
-        <v>Syler</v>
+        <v>Tyler</v>
       </c>
       <c r="B318" s="20" t="str">
         <f>'Grad Raw Data'!K161</f>
@@ -55976,7 +55974,7 @@
       </c>
       <c r="C318" s="20" t="str">
         <f>'Grad Raw Data'!H160</f>
-        <v>Manning</v>
+        <v>Marchlik</v>
       </c>
       <c r="D318" s="20"/>
       <c r="E318" s="20" t="str">
@@ -55997,17 +55995,17 @@
       <c r="F319" s="20"/>
     </row>
     <row r="320" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A320" s="20" t="str">
+      <c r="A320" s="20" t="e">
         <f>'Grad Raw Data'!I161</f>
-        <v>Tyler</v>
-      </c>
-      <c r="B320" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B320" s="20" t="e">
         <f>'Grad Raw Data'!K162</f>
-        <v/>
-      </c>
-      <c r="C320" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C320" s="20" t="e">
         <f>'Grad Raw Data'!H161</f>
-        <v>Marchlik</v>
+        <v>#N/A</v>
       </c>
       <c r="D320" s="20"/>
       <c r="E320" s="20" t="str">
@@ -61476,11 +61474,11 @@
       </c>
       <c r="G57" s="31" t="str">
         <f>VLOOKUP(I57,'Names with Seat Code'!B:E,2)</f>
-        <v>Hans</v>
+        <v>Walick</v>
       </c>
       <c r="H57" s="31" t="str">
         <f>VLOOKUP(I57,'Names with Seat Code'!B:E,4)</f>
-        <v>Dankers</v>
+        <v>Silva</v>
       </c>
       <c r="I57" s="25">
         <f>IF(B56+1&lt;DIRECTIONS!$E$24,B56+1,0)</f>
@@ -61508,11 +61506,11 @@
       </c>
       <c r="G58" s="31" t="str">
         <f>VLOOKUP(I58,'Names with Seat Code'!B:E,2)</f>
-        <v>Walick</v>
+        <v>Cooper</v>
       </c>
       <c r="H58" s="31" t="str">
         <f>VLOOKUP(I58,'Names with Seat Code'!B:E,4)</f>
-        <v>Silva</v>
+        <v>Dean</v>
       </c>
       <c r="I58" s="25">
         <f>IF(B57+1&lt;DIRECTIONS!$E$24,B57+1,0)</f>
@@ -61540,11 +61538,11 @@
       </c>
       <c r="G59" s="31" t="str">
         <f>VLOOKUP(I59,'Names with Seat Code'!B:E,2)</f>
-        <v>Cooper</v>
+        <v>Happiness</v>
       </c>
       <c r="H59" s="31" t="str">
         <f>VLOOKUP(I59,'Names with Seat Code'!B:E,4)</f>
-        <v>Dean</v>
+        <v>Deji</v>
       </c>
       <c r="I59" s="25">
         <f>IF(B58+1&lt;DIRECTIONS!$E$24,B58+1,0)</f>
@@ -61572,11 +61570,11 @@
       </c>
       <c r="G60" s="31" t="str">
         <f>VLOOKUP(I60,'Names with Seat Code'!B:E,2)</f>
-        <v>Happiness</v>
+        <v>Jack</v>
       </c>
       <c r="H60" s="31" t="str">
         <f>VLOOKUP(I60,'Names with Seat Code'!B:E,4)</f>
-        <v>Deji</v>
+        <v>Denmark</v>
       </c>
       <c r="I60" s="25">
         <f>IF(B59+1&lt;DIRECTIONS!$E$24,B59+1,0)</f>
@@ -61604,11 +61602,11 @@
       </c>
       <c r="G61" s="31" t="str">
         <f>VLOOKUP(I61,'Names with Seat Code'!B:E,2)</f>
-        <v>Jack</v>
+        <v>Julie</v>
       </c>
       <c r="H61" s="31" t="str">
         <f>VLOOKUP(I61,'Names with Seat Code'!B:E,4)</f>
-        <v>Denmark</v>
+        <v>DiDonato</v>
       </c>
       <c r="I61" s="25">
         <f>IF(B60+1&lt;DIRECTIONS!$E$24,B60+1,0)</f>
@@ -61636,11 +61634,11 @@
       </c>
       <c r="G62" s="31" t="str">
         <f>VLOOKUP(I62,'Names with Seat Code'!B:E,2)</f>
-        <v>Julie</v>
+        <v>Dante</v>
       </c>
       <c r="H62" s="31" t="str">
         <f>VLOOKUP(I62,'Names with Seat Code'!B:E,4)</f>
-        <v>DiDonato</v>
+        <v>DiSerio</v>
       </c>
       <c r="I62" s="25">
         <f>IF(B61+1&lt;DIRECTIONS!$E$24,B61+1,0)</f>
@@ -61668,7 +61666,7 @@
       </c>
       <c r="G63" s="31" t="str">
         <f>VLOOKUP(I63,'Names with Seat Code'!B:E,2)</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="H63" s="31" t="str">
         <f>VLOOKUP(I63,'Names with Seat Code'!B:E,4)</f>
@@ -61700,11 +61698,11 @@
       </c>
       <c r="G64" s="31" t="str">
         <f>VLOOKUP(I64,'Names with Seat Code'!B:E,2)</f>
-        <v>Antonio</v>
+        <v>Caitlin</v>
       </c>
       <c r="H64" s="31" t="str">
         <f>VLOOKUP(I64,'Names with Seat Code'!B:E,4)</f>
-        <v>DiSerio</v>
+        <v>Donaghey</v>
       </c>
       <c r="I64" s="25">
         <f>IF(B63+1&lt;DIRECTIONS!$E$24,B63+1,0)</f>
@@ -61732,11 +61730,11 @@
       </c>
       <c r="G65" s="31" t="str">
         <f>VLOOKUP(I65,'Names with Seat Code'!B:E,2)</f>
-        <v>Caitlin</v>
+        <v>Quinn</v>
       </c>
       <c r="H65" s="31" t="str">
         <f>VLOOKUP(I65,'Names with Seat Code'!B:E,4)</f>
-        <v>Donaghey</v>
+        <v>Donahue</v>
       </c>
       <c r="I65" s="25">
         <f>IF(B64+1&lt;DIRECTIONS!$E$24,B64+1,0)</f>
@@ -61764,11 +61762,11 @@
       </c>
       <c r="G66" s="31" t="str">
         <f>VLOOKUP(I66,'Names with Seat Code'!B:E,2)</f>
-        <v>Quinn</v>
+        <v>Alana</v>
       </c>
       <c r="H66" s="31" t="str">
         <f>VLOOKUP(I66,'Names with Seat Code'!B:E,4)</f>
-        <v>Donahue</v>
+        <v>Doroquez</v>
       </c>
       <c r="I66" s="25">
         <f>IF(B65+1&lt;DIRECTIONS!$E$24,B65+1,0)</f>
@@ -61796,11 +61794,11 @@
       </c>
       <c r="G67" s="31" t="str">
         <f>VLOOKUP(I67,'Names with Seat Code'!B:E,2)</f>
-        <v>Alana</v>
+        <v>Cassidy</v>
       </c>
       <c r="H67" s="31" t="str">
         <f>VLOOKUP(I67,'Names with Seat Code'!B:E,4)</f>
-        <v>Doroquez</v>
+        <v>Duca</v>
       </c>
       <c r="I67" s="25">
         <f>IF(B66+1&lt;DIRECTIONS!$E$24,B66+1,0)</f>
@@ -61828,11 +61826,11 @@
       </c>
       <c r="G68" s="31" t="str">
         <f>VLOOKUP(I68,'Names with Seat Code'!B:E,2)</f>
-        <v>Cassidy</v>
+        <v>Kyle</v>
       </c>
       <c r="H68" s="31" t="str">
         <f>VLOOKUP(I68,'Names with Seat Code'!B:E,4)</f>
-        <v>Duca</v>
+        <v>DuRoss</v>
       </c>
       <c r="I68" s="25">
         <f>IF(B67+1&lt;DIRECTIONS!$E$24,B67+1,0)</f>
@@ -61860,7 +61858,7 @@
       </c>
       <c r="G69" s="31" t="str">
         <f>VLOOKUP(I69,'Names with Seat Code'!B:E,2)</f>
-        <v>Kyle</v>
+        <v>Sean</v>
       </c>
       <c r="H69" s="31" t="str">
         <f>VLOOKUP(I69,'Names with Seat Code'!B:E,4)</f>
@@ -61892,11 +61890,11 @@
       </c>
       <c r="G70" s="31" t="str">
         <f>VLOOKUP(I70,'Names with Seat Code'!B:E,2)</f>
-        <v>Sean</v>
+        <v>William</v>
       </c>
       <c r="H70" s="31" t="str">
         <f>VLOOKUP(I70,'Names with Seat Code'!B:E,4)</f>
-        <v>DuRoss</v>
+        <v>Dyment</v>
       </c>
       <c r="I70" s="25">
         <f>IF(B69+1&lt;DIRECTIONS!$E$24,B69+1,0)</f>
@@ -61924,11 +61922,11 @@
       </c>
       <c r="G71" s="31" t="str">
         <f>VLOOKUP(I71,'Names with Seat Code'!B:E,2)</f>
-        <v>William</v>
+        <v>Luca</v>
       </c>
       <c r="H71" s="31" t="str">
         <f>VLOOKUP(I71,'Names with Seat Code'!B:E,4)</f>
-        <v>Dyment</v>
+        <v>Eliet</v>
       </c>
       <c r="I71" s="25">
         <f>IF(B70+1&lt;DIRECTIONS!$E$24,B70+1,0)</f>
@@ -61956,11 +61954,11 @@
       </c>
       <c r="G72" s="31" t="str">
         <f>VLOOKUP(I72,'Names with Seat Code'!B:E,2)</f>
-        <v>Luca</v>
+        <v>Finn</v>
       </c>
       <c r="H72" s="31" t="str">
         <f>VLOOKUP(I72,'Names with Seat Code'!B:E,4)</f>
-        <v>Eliet</v>
+        <v>Ellis</v>
       </c>
       <c r="I72" s="25">
         <f>IF(B71+1&lt;DIRECTIONS!$E$24,B71+1,0)</f>
@@ -61988,11 +61986,11 @@
       </c>
       <c r="G73" s="31" t="str">
         <f>VLOOKUP(I73,'Names with Seat Code'!B:E,2)</f>
-        <v>Finn</v>
+        <v>Levi</v>
       </c>
       <c r="H73" s="31" t="str">
         <f>VLOOKUP(I73,'Names with Seat Code'!B:E,4)</f>
-        <v>Ellis</v>
+        <v>Emmanuel</v>
       </c>
       <c r="I73" s="25">
         <f>IF(B72+1&lt;DIRECTIONS!$E$24,B72+1,0)</f>
@@ -62020,11 +62018,11 @@
       </c>
       <c r="G74" s="31" t="str">
         <f>VLOOKUP(I74,'Names with Seat Code'!B:E,2)</f>
-        <v>Levi</v>
+        <v>Kamryn</v>
       </c>
       <c r="H74" s="31" t="str">
         <f>VLOOKUP(I74,'Names with Seat Code'!B:E,4)</f>
-        <v>Emmanuel</v>
+        <v>Encarnacao</v>
       </c>
       <c r="I74" s="25">
         <f>IF(B73+1&lt;DIRECTIONS!$E$24,B73+1,0)</f>
@@ -62052,11 +62050,11 @@
       </c>
       <c r="G75" s="31" t="str">
         <f>VLOOKUP(I75,'Names with Seat Code'!B:E,2)</f>
-        <v>Kamryn</v>
+        <v>Samuel</v>
       </c>
       <c r="H75" s="31" t="str">
         <f>VLOOKUP(I75,'Names with Seat Code'!B:E,4)</f>
-        <v>Encarnacao</v>
+        <v>Fortes</v>
       </c>
       <c r="I75" s="25">
         <f>IF(B74+1&lt;DIRECTIONS!$E$24,B74+1,0)</f>
@@ -62084,11 +62082,11 @@
       </c>
       <c r="G76" s="31" t="str">
         <f>VLOOKUP(I76,'Names with Seat Code'!B:E,2)</f>
-        <v>Samuel</v>
+        <v>Kaylie</v>
       </c>
       <c r="H76" s="31" t="str">
         <f>VLOOKUP(I76,'Names with Seat Code'!B:E,4)</f>
-        <v>Fortes</v>
+        <v>Fantasia</v>
       </c>
       <c r="I76" s="25">
         <f>IF(B75+1&lt;DIRECTIONS!$E$24,B75+1,0)</f>
@@ -62116,11 +62114,11 @@
       </c>
       <c r="G77" s="31" t="str">
         <f>VLOOKUP(I77,'Names with Seat Code'!B:E,2)</f>
-        <v>Kaylie</v>
+        <v>Vince</v>
       </c>
       <c r="H77" s="31" t="str">
         <f>VLOOKUP(I77,'Names with Seat Code'!B:E,4)</f>
-        <v>Fantasia</v>
+        <v>Farnham</v>
       </c>
       <c r="I77" s="25">
         <f>IF(B76+1&lt;DIRECTIONS!$E$24,B76+1,0)</f>
@@ -62148,11 +62146,11 @@
       </c>
       <c r="G78" s="31" t="str">
         <f>VLOOKUP(I78,'Names with Seat Code'!B:E,2)</f>
-        <v>Vince</v>
+        <v>Colby</v>
       </c>
       <c r="H78" s="31" t="str">
         <f>VLOOKUP(I78,'Names with Seat Code'!B:E,4)</f>
-        <v>Farnham</v>
+        <v>Farris</v>
       </c>
       <c r="I78" s="25">
         <f>IF(B77+1&lt;DIRECTIONS!$E$24,B77+1,0)</f>
@@ -62180,11 +62178,11 @@
       </c>
       <c r="G79" s="31" t="str">
         <f>VLOOKUP(I79,'Names with Seat Code'!B:E,2)</f>
-        <v>Colby</v>
+        <v>Bryan</v>
       </c>
       <c r="H79" s="31" t="str">
         <f>VLOOKUP(I79,'Names with Seat Code'!B:E,4)</f>
-        <v>Farris</v>
+        <v>Fernandez</v>
       </c>
       <c r="I79" s="25">
         <f>IF(B78+1&lt;DIRECTIONS!$E$24,B78+1,0)</f>
@@ -62212,11 +62210,11 @@
       </c>
       <c r="G80" s="31" t="str">
         <f>VLOOKUP(I80,'Names with Seat Code'!B:E,2)</f>
-        <v>Bryan</v>
+        <v>Thomas</v>
       </c>
       <c r="H80" s="31" t="str">
         <f>VLOOKUP(I80,'Names with Seat Code'!B:E,4)</f>
-        <v>Fernandez</v>
+        <v>Fiore</v>
       </c>
       <c r="I80" s="25">
         <f>IF(B79+1&lt;DIRECTIONS!$E$24,B79+1,0)</f>
@@ -62244,11 +62242,11 @@
       </c>
       <c r="G81" s="31" t="str">
         <f>VLOOKUP(I81,'Names with Seat Code'!B:E,2)</f>
-        <v>Thomas</v>
+        <v>Finn</v>
       </c>
       <c r="H81" s="31" t="str">
         <f>VLOOKUP(I81,'Names with Seat Code'!B:E,4)</f>
-        <v>Fiore</v>
+        <v>Flaherty</v>
       </c>
       <c r="I81" s="25">
         <f>IF(B80+1&lt;DIRECTIONS!$E$24,B80+1,0)</f>
@@ -62276,11 +62274,11 @@
       </c>
       <c r="G82" s="31" t="str">
         <f>VLOOKUP(I82,'Names with Seat Code'!B:E,2)</f>
-        <v>Finn</v>
+        <v>Matthew</v>
       </c>
       <c r="H82" s="31" t="str">
         <f>VLOOKUP(I82,'Names with Seat Code'!B:E,4)</f>
-        <v>Flaherty</v>
+        <v>Forse</v>
       </c>
       <c r="I82" s="25">
         <f>IF(B81+1&lt;DIRECTIONS!$E$24,B81+1,0)</f>
@@ -62308,11 +62306,11 @@
       </c>
       <c r="G83" s="31" t="str">
         <f>VLOOKUP(I83,'Names with Seat Code'!B:E,2)</f>
-        <v>Matthew</v>
+        <v>Jacob</v>
       </c>
       <c r="H83" s="31" t="str">
         <f>VLOOKUP(I83,'Names with Seat Code'!B:E,4)</f>
-        <v>Forse</v>
+        <v>Frank</v>
       </c>
       <c r="I83" s="25">
         <f>IF(B82+1&lt;DIRECTIONS!$E$24,B82+1,0)</f>
@@ -62340,11 +62338,11 @@
       </c>
       <c r="G84" s="31" t="str">
         <f>VLOOKUP(I84,'Names with Seat Code'!B:E,2)</f>
-        <v>Jacob</v>
+        <v>Anthony</v>
       </c>
       <c r="H84" s="31" t="str">
         <f>VLOOKUP(I84,'Names with Seat Code'!B:E,4)</f>
-        <v>Frank</v>
+        <v>Fratto</v>
       </c>
       <c r="I84" s="25">
         <f>IF(B83+1&lt;DIRECTIONS!$E$24,B83+1,0)</f>
@@ -62372,11 +62370,11 @@
       </c>
       <c r="G85" s="31" t="str">
         <f>VLOOKUP(I85,'Names with Seat Code'!B:E,2)</f>
-        <v>Anthony</v>
+        <v>Gavin</v>
       </c>
       <c r="H85" s="31" t="str">
         <f>VLOOKUP(I85,'Names with Seat Code'!B:E,4)</f>
-        <v>Fratto</v>
+        <v>Fucarile</v>
       </c>
       <c r="I85" s="25">
         <f>IF(B84+1&lt;DIRECTIONS!$E$24,B84+1,0)</f>
@@ -62404,11 +62402,11 @@
       </c>
       <c r="G86" s="31" t="str">
         <f>VLOOKUP(I86,'Names with Seat Code'!B:E,2)</f>
-        <v>Gavin</v>
+        <v>Cole</v>
       </c>
       <c r="H86" s="31" t="str">
         <f>VLOOKUP(I86,'Names with Seat Code'!B:E,4)</f>
-        <v>Fucarile</v>
+        <v>Fusco</v>
       </c>
       <c r="I86" s="25">
         <f>IF(B85+1&lt;DIRECTIONS!$E$24,B85+1,0)</f>
@@ -62436,11 +62434,11 @@
       </c>
       <c r="G87" s="31" t="str">
         <f>VLOOKUP(I87,'Names with Seat Code'!B:E,2)</f>
-        <v>Cole</v>
+        <v>Paul</v>
       </c>
       <c r="H87" s="31" t="str">
         <f>VLOOKUP(I87,'Names with Seat Code'!B:E,4)</f>
-        <v>Fusco</v>
+        <v>Gaeta</v>
       </c>
       <c r="I87" s="25">
         <f>IF(B86+1&lt;DIRECTIONS!$E$24,B86+1,0)</f>
@@ -62468,11 +62466,11 @@
       </c>
       <c r="G88" s="31" t="str">
         <f>VLOOKUP(I88,'Names with Seat Code'!B:E,2)</f>
-        <v>Paul</v>
+        <v>Lucas</v>
       </c>
       <c r="H88" s="31" t="str">
         <f>VLOOKUP(I88,'Names with Seat Code'!B:E,4)</f>
-        <v>Gaeta</v>
+        <v>Gager</v>
       </c>
       <c r="I88" s="25">
         <f>IF(B87+1&lt;DIRECTIONS!$E$24,B87+1,0)</f>
@@ -62500,11 +62498,11 @@
       </c>
       <c r="G89" s="31" t="str">
         <f>VLOOKUP(I89,'Names with Seat Code'!B:E,2)</f>
-        <v>Lucas</v>
+        <v>Nevaeh</v>
       </c>
       <c r="H89" s="31" t="str">
         <f>VLOOKUP(I89,'Names with Seat Code'!B:E,4)</f>
-        <v>Gager</v>
+        <v>Galindo</v>
       </c>
       <c r="I89" s="25">
         <f>IF(B88+1&lt;DIRECTIONS!$E$24,B88+1,0)</f>
@@ -62532,11 +62530,11 @@
       </c>
       <c r="G90" s="31" t="str">
         <f>VLOOKUP(I90,'Names with Seat Code'!B:E,2)</f>
-        <v>Nevaeh</v>
+        <v>Joseph</v>
       </c>
       <c r="H90" s="31" t="str">
         <f>VLOOKUP(I90,'Names with Seat Code'!B:E,4)</f>
-        <v>Galindo</v>
+        <v>Gallagher</v>
       </c>
       <c r="I90" s="25">
         <f>IF(B89+1&lt;DIRECTIONS!$E$24,B89+1,0)</f>
@@ -62564,11 +62562,11 @@
       </c>
       <c r="G91" s="31" t="str">
         <f>VLOOKUP(I91,'Names with Seat Code'!B:E,2)</f>
-        <v>Joseph</v>
+        <v>Brendan</v>
       </c>
       <c r="H91" s="31" t="str">
         <f>VLOOKUP(I91,'Names with Seat Code'!B:E,4)</f>
-        <v>Gallagher</v>
+        <v>Gauvin</v>
       </c>
       <c r="I91" s="25">
         <f>IF(B90+1&lt;DIRECTIONS!$E$24,B90+1,0)</f>
@@ -62596,11 +62594,11 @@
       </c>
       <c r="G92" s="31" t="str">
         <f>VLOOKUP(I92,'Names with Seat Code'!B:E,2)</f>
-        <v>Brendan</v>
+        <v>Bereket</v>
       </c>
       <c r="H92" s="31" t="str">
         <f>VLOOKUP(I92,'Names with Seat Code'!B:E,4)</f>
-        <v>Gauvin</v>
+        <v>Gebeyaw</v>
       </c>
       <c r="I92" s="25">
         <f>IF(B91+1&lt;DIRECTIONS!$E$24,B91+1,0)</f>
@@ -62628,11 +62626,11 @@
       </c>
       <c r="G93" s="31" t="str">
         <f>VLOOKUP(I93,'Names with Seat Code'!B:E,2)</f>
-        <v>Bereket</v>
+        <v>Alix</v>
       </c>
       <c r="H93" s="31" t="str">
         <f>VLOOKUP(I93,'Names with Seat Code'!B:E,4)</f>
-        <v>Gebeyaw</v>
+        <v>Gellot</v>
       </c>
       <c r="I93" s="25">
         <f>IF(B92+1&lt;DIRECTIONS!$E$24,B92+1,0)</f>
@@ -62660,11 +62658,11 @@
       </c>
       <c r="G94" s="31" t="str">
         <f>VLOOKUP(I94,'Names with Seat Code'!B:E,2)</f>
-        <v>Alix</v>
+        <v>Cameron</v>
       </c>
       <c r="H94" s="31" t="str">
         <f>VLOOKUP(I94,'Names with Seat Code'!B:E,4)</f>
-        <v>Gellot</v>
+        <v>Gigler</v>
       </c>
       <c r="I94" s="25">
         <f>IF(B93+1&lt;DIRECTIONS!$E$24,B93+1,0)</f>
@@ -62692,11 +62690,11 @@
       </c>
       <c r="G95" s="31" t="str">
         <f>VLOOKUP(I95,'Names with Seat Code'!B:E,2)</f>
-        <v>Cameron</v>
+        <v>Alex</v>
       </c>
       <c r="H95" s="31" t="str">
         <f>VLOOKUP(I95,'Names with Seat Code'!B:E,4)</f>
-        <v>Gigler</v>
+        <v>Gisetto</v>
       </c>
       <c r="I95" s="25">
         <f>IF(B94+1&lt;DIRECTIONS!$E$24,B94+1,0)</f>
@@ -62724,11 +62722,11 @@
       </c>
       <c r="G96" s="31" t="str">
         <f>VLOOKUP(I96,'Names with Seat Code'!B:E,2)</f>
-        <v>Alex</v>
+        <v>Benjamin</v>
       </c>
       <c r="H96" s="31" t="str">
         <f>VLOOKUP(I96,'Names with Seat Code'!B:E,4)</f>
-        <v>Gisetto</v>
+        <v>Goldlust</v>
       </c>
       <c r="I96" s="25">
         <f>IF(B95+1&lt;DIRECTIONS!$E$24,B95+1,0)</f>
@@ -62756,11 +62754,11 @@
       </c>
       <c r="G97" s="31" t="str">
         <f>VLOOKUP(I97,'Names with Seat Code'!B:E,2)</f>
-        <v>Benjamin</v>
+        <v>Jack</v>
       </c>
       <c r="H97" s="31" t="str">
         <f>VLOOKUP(I97,'Names with Seat Code'!B:E,4)</f>
-        <v>Goldlust</v>
+        <v>Goodfellow</v>
       </c>
       <c r="I97" s="25">
         <f>IF(B96+1&lt;DIRECTIONS!$E$24,B96+1,0)</f>
@@ -62788,11 +62786,11 @@
       </c>
       <c r="G98" s="31" t="str">
         <f>VLOOKUP(I98,'Names with Seat Code'!B:E,2)</f>
-        <v>Jack</v>
+        <v>Drew</v>
       </c>
       <c r="H98" s="31" t="str">
         <f>VLOOKUP(I98,'Names with Seat Code'!B:E,4)</f>
-        <v>Goodfellow</v>
+        <v>Gorski</v>
       </c>
       <c r="I98" s="25">
         <f>IF(B97+1&lt;DIRECTIONS!$E$24,B97+1,0)</f>
@@ -62820,11 +62818,11 @@
       </c>
       <c r="G99" s="31" t="str">
         <f>VLOOKUP(I99,'Names with Seat Code'!B:E,2)</f>
-        <v>Drew</v>
+        <v>Lila</v>
       </c>
       <c r="H99" s="31" t="str">
         <f>VLOOKUP(I99,'Names with Seat Code'!B:E,4)</f>
-        <v>Gorski</v>
+        <v>Gosdanian</v>
       </c>
       <c r="I99" s="25">
         <f>IF(B98+1&lt;DIRECTIONS!$E$24,B98+1,0)</f>
@@ -62852,11 +62850,11 @@
       </c>
       <c r="G100" s="31" t="str">
         <f>VLOOKUP(I100,'Names with Seat Code'!B:E,2)</f>
-        <v>Lila</v>
+        <v>Cole</v>
       </c>
       <c r="H100" s="31" t="str">
         <f>VLOOKUP(I100,'Names with Seat Code'!B:E,4)</f>
-        <v>Gosdanian</v>
+        <v>Grant</v>
       </c>
       <c r="I100" s="25">
         <f>IF(B99+1&lt;DIRECTIONS!$E$24,B99+1,0)</f>
@@ -62884,11 +62882,11 @@
       </c>
       <c r="G101" s="31" t="str">
         <f>VLOOKUP(I101,'Names with Seat Code'!B:E,2)</f>
-        <v>Cole</v>
+        <v>Kendall</v>
       </c>
       <c r="H101" s="31" t="str">
         <f>VLOOKUP(I101,'Names with Seat Code'!B:E,4)</f>
-        <v>Grant</v>
+        <v>Graves</v>
       </c>
       <c r="I101" s="25">
         <f>IF(B100+1&lt;DIRECTIONS!$E$24,B100+1,0)</f>
@@ -62916,11 +62914,11 @@
       </c>
       <c r="G102" s="31" t="str">
         <f>VLOOKUP(I102,'Names with Seat Code'!B:E,2)</f>
-        <v>Kendall</v>
+        <v>Griffin</v>
       </c>
       <c r="H102" s="31" t="str">
         <f>VLOOKUP(I102,'Names with Seat Code'!B:E,4)</f>
-        <v>Graves</v>
+        <v>Haggerty</v>
       </c>
       <c r="I102" s="25">
         <f>IF(B101+1&lt;DIRECTIONS!$E$24,B101+1,0)</f>
@@ -62948,11 +62946,11 @@
       </c>
       <c r="G103" s="31" t="str">
         <f>VLOOKUP(I103,'Names with Seat Code'!B:E,2)</f>
-        <v>Griffin</v>
+        <v>Andrea</v>
       </c>
       <c r="H103" s="31" t="str">
         <f>VLOOKUP(I103,'Names with Seat Code'!B:E,4)</f>
-        <v>Haggerty</v>
+        <v>Hall</v>
       </c>
       <c r="I103" s="25">
         <f>IF(B102+1&lt;DIRECTIONS!$E$24,B102+1,0)</f>
@@ -62980,11 +62978,11 @@
       </c>
       <c r="G104" s="31" t="str">
         <f>VLOOKUP(I104,'Names with Seat Code'!B:E,2)</f>
-        <v>Andrea</v>
+        <v>Sarah</v>
       </c>
       <c r="H104" s="31" t="str">
         <f>VLOOKUP(I104,'Names with Seat Code'!B:E,4)</f>
-        <v>Hall</v>
+        <v>Hamilton</v>
       </c>
       <c r="I104" s="25">
         <f>IF(B103+1&lt;DIRECTIONS!$E$24,B103+1,0)</f>
@@ -63012,11 +63010,11 @@
       </c>
       <c r="G105" s="31" t="str">
         <f>VLOOKUP(I105,'Names with Seat Code'!B:E,2)</f>
-        <v>Sarah</v>
+        <v>Margaret</v>
       </c>
       <c r="H105" s="31" t="str">
         <f>VLOOKUP(I105,'Names with Seat Code'!B:E,4)</f>
-        <v>Hamilton</v>
+        <v>Hanifan</v>
       </c>
       <c r="I105" s="25">
         <f>IF(B104+1&lt;DIRECTIONS!$E$24,B104+1,0)</f>
@@ -63044,11 +63042,11 @@
       </c>
       <c r="G106" s="31" t="str">
         <f>VLOOKUP(I106,'Names with Seat Code'!B:E,2)</f>
-        <v>Margaret</v>
+        <v>Cameron</v>
       </c>
       <c r="H106" s="31" t="str">
         <f>VLOOKUP(I106,'Names with Seat Code'!B:E,4)</f>
-        <v>Hanifan</v>
+        <v>Harrigan</v>
       </c>
       <c r="I106" s="25">
         <f>IF(B105+1&lt;DIRECTIONS!$E$24,B105+1,0)</f>
@@ -63076,11 +63074,11 @@
       </c>
       <c r="G107" s="31" t="str">
         <f>VLOOKUP(I107,'Names with Seat Code'!B:E,2)</f>
-        <v>Cameron</v>
+        <v>Victoria</v>
       </c>
       <c r="H107" s="31" t="str">
         <f>VLOOKUP(I107,'Names with Seat Code'!B:E,4)</f>
-        <v>Harrigan</v>
+        <v>Henri</v>
       </c>
       <c r="I107" s="25">
         <f>IF(B106+1&lt;DIRECTIONS!$E$24,B106+1,0)</f>
@@ -63108,11 +63106,11 @@
       </c>
       <c r="G108" s="31" t="str">
         <f>VLOOKUP(I108,'Names with Seat Code'!B:E,2)</f>
-        <v>Victoria</v>
+        <v>Kayke</v>
       </c>
       <c r="H108" s="31" t="str">
         <f>VLOOKUP(I108,'Names with Seat Code'!B:E,4)</f>
-        <v>Henri</v>
+        <v>Henrique</v>
       </c>
       <c r="I108" s="25">
         <f>IF(B107+1&lt;DIRECTIONS!$E$24,B107+1,0)</f>
@@ -63140,11 +63138,11 @@
       </c>
       <c r="G109" s="31" t="str">
         <f>VLOOKUP(I109,'Names with Seat Code'!B:E,2)</f>
-        <v>Kayke</v>
+        <v>Jahkye</v>
       </c>
       <c r="H109" s="31" t="str">
         <f>VLOOKUP(I109,'Names with Seat Code'!B:E,4)</f>
-        <v>Henrique</v>
+        <v>Hobson</v>
       </c>
       <c r="I109" s="25">
         <f>IF(B108+1&lt;DIRECTIONS!$E$24,B108+1,0)</f>
@@ -63172,11 +63170,11 @@
       </c>
       <c r="G110" s="31" t="str">
         <f>VLOOKUP(I110,'Names with Seat Code'!B:E,2)</f>
-        <v>Jahkye</v>
+        <v>Sam</v>
       </c>
       <c r="H110" s="31" t="str">
         <f>VLOOKUP(I110,'Names with Seat Code'!B:E,4)</f>
-        <v>Hobson</v>
+        <v>Holt</v>
       </c>
       <c r="I110" s="25">
         <f>IF(B109+1&lt;DIRECTIONS!$E$24,B109+1,0)</f>
@@ -63204,11 +63202,11 @@
       </c>
       <c r="G111" s="31" t="str">
         <f>VLOOKUP(I111,'Names with Seat Code'!B:E,2)</f>
-        <v>Sam</v>
+        <v>Benjamin</v>
       </c>
       <c r="H111" s="31" t="str">
         <f>VLOOKUP(I111,'Names with Seat Code'!B:E,4)</f>
-        <v>Holt</v>
+        <v>Houle</v>
       </c>
       <c r="I111" s="25">
         <f>IF(B110+1&lt;DIRECTIONS!$E$24,B110+1,0)</f>
@@ -63236,11 +63234,11 @@
       </c>
       <c r="G112" s="31" t="str">
         <f>VLOOKUP(I112,'Names with Seat Code'!B:E,2)</f>
-        <v>Benjamin</v>
+        <v>Evin</v>
       </c>
       <c r="H112" s="31" t="str">
         <f>VLOOKUP(I112,'Names with Seat Code'!B:E,4)</f>
-        <v>Houle</v>
+        <v>Howell</v>
       </c>
       <c r="I112" s="25">
         <f>IF(B111+1&lt;DIRECTIONS!$E$24,B111+1,0)</f>
@@ -63268,11 +63266,11 @@
       </c>
       <c r="G113" s="31" t="str">
         <f>VLOOKUP(I113,'Names with Seat Code'!B:E,2)</f>
-        <v>Evin</v>
+        <v>Paul</v>
       </c>
       <c r="H113" s="31" t="str">
         <f>VLOOKUP(I113,'Names with Seat Code'!B:E,4)</f>
-        <v>Howell</v>
+        <v>Iosua</v>
       </c>
       <c r="I113" s="25">
         <f>IF(B112+1&lt;DIRECTIONS!$E$24,B112+1,0)</f>
@@ -63300,11 +63298,11 @@
       </c>
       <c r="G114" s="31" t="str">
         <f>VLOOKUP(I114,'Names with Seat Code'!B:E,2)</f>
-        <v>Paul</v>
+        <v>Leah</v>
       </c>
       <c r="H114" s="31" t="str">
         <f>VLOOKUP(I114,'Names with Seat Code'!B:E,4)</f>
-        <v>Iosua</v>
+        <v>Jackvony</v>
       </c>
       <c r="I114" s="25">
         <f>IF(B113+1&lt;DIRECTIONS!$E$24,B113+1,0)</f>
@@ -63332,11 +63330,11 @@
       </c>
       <c r="G115" s="31" t="str">
         <f>VLOOKUP(I115,'Names with Seat Code'!B:E,2)</f>
-        <v>Leah</v>
+        <v>Wayne</v>
       </c>
       <c r="H115" s="31" t="str">
         <f>VLOOKUP(I115,'Names with Seat Code'!B:E,4)</f>
-        <v>Jackvony</v>
+        <v>Jankun</v>
       </c>
       <c r="I115" s="25">
         <f>IF(B114+1&lt;DIRECTIONS!$E$24,B114+1,0)</f>
@@ -63364,11 +63362,11 @@
       </c>
       <c r="G116" s="31" t="str">
         <f>VLOOKUP(I116,'Names with Seat Code'!B:E,2)</f>
-        <v>Wayne</v>
+        <v>Tristan</v>
       </c>
       <c r="H116" s="31" t="str">
         <f>VLOOKUP(I116,'Names with Seat Code'!B:E,4)</f>
-        <v>Jankun</v>
+        <v>Jenkins</v>
       </c>
       <c r="I116" s="25">
         <f>IF(B115+1&lt;DIRECTIONS!$E$24,B115+1,0)</f>
@@ -63396,11 +63394,11 @@
       </c>
       <c r="G117" s="31" t="str">
         <f>VLOOKUP(I117,'Names with Seat Code'!B:E,2)</f>
-        <v>Tristan</v>
+        <v>Evan</v>
       </c>
       <c r="H117" s="31" t="str">
         <f>VLOOKUP(I117,'Names with Seat Code'!B:E,4)</f>
-        <v>Jenkins</v>
+        <v>Jenney</v>
       </c>
       <c r="I117" s="25">
         <f>IF(B116+1&lt;DIRECTIONS!$E$24,B116+1,0)</f>
@@ -63428,7 +63426,7 @@
       </c>
       <c r="G118" s="31" t="str">
         <f>VLOOKUP(I118,'Names with Seat Code'!B:E,2)</f>
-        <v>Evan</v>
+        <v>Michael</v>
       </c>
       <c r="H118" s="31" t="str">
         <f>VLOOKUP(I118,'Names with Seat Code'!B:E,4)</f>
@@ -63460,11 +63458,11 @@
       </c>
       <c r="G119" s="31" t="str">
         <f>VLOOKUP(I119,'Names with Seat Code'!B:E,2)</f>
-        <v>Michael</v>
+        <v>Luke</v>
       </c>
       <c r="H119" s="31" t="str">
         <f>VLOOKUP(I119,'Names with Seat Code'!B:E,4)</f>
-        <v>Jenney</v>
+        <v>Johnson</v>
       </c>
       <c r="I119" s="25">
         <f>IF(B118+1&lt;DIRECTIONS!$E$24,B118+1,0)</f>
@@ -63492,11 +63490,11 @@
       </c>
       <c r="G120" s="31" t="str">
         <f>VLOOKUP(I120,'Names with Seat Code'!B:E,2)</f>
-        <v>Luke</v>
+        <v>Maeve</v>
       </c>
       <c r="H120" s="31" t="str">
         <f>VLOOKUP(I120,'Names with Seat Code'!B:E,4)</f>
-        <v>Johnson</v>
+        <v>Jones</v>
       </c>
       <c r="I120" s="25">
         <f>IF(B119+1&lt;DIRECTIONS!$E$24,B119+1,0)</f>
@@ -63524,11 +63522,11 @@
       </c>
       <c r="G121" s="31" t="str">
         <f>VLOOKUP(I121,'Names with Seat Code'!B:E,2)</f>
-        <v>Maeve</v>
+        <v>Nolan</v>
       </c>
       <c r="H121" s="31" t="str">
         <f>VLOOKUP(I121,'Names with Seat Code'!B:E,4)</f>
-        <v>Jones</v>
+        <v>Jordan</v>
       </c>
       <c r="I121" s="25">
         <f>IF(B120+1&lt;DIRECTIONS!$E$24,B120+1,0)</f>
@@ -63556,11 +63554,11 @@
       </c>
       <c r="G122" s="31" t="str">
         <f>VLOOKUP(I122,'Names with Seat Code'!B:E,2)</f>
-        <v>Nolan</v>
+        <v>Emma</v>
       </c>
       <c r="H122" s="31" t="str">
         <f>VLOOKUP(I122,'Names with Seat Code'!B:E,4)</f>
-        <v>Jordan</v>
+        <v>Kaberle</v>
       </c>
       <c r="I122" s="25">
         <f>IF(B121+1&lt;DIRECTIONS!$E$24,B121+1,0)</f>
@@ -63588,11 +63586,11 @@
       </c>
       <c r="G123" s="31" t="str">
         <f>VLOOKUP(I123,'Names with Seat Code'!B:E,2)</f>
-        <v>Emma</v>
+        <v>Azra</v>
       </c>
       <c r="H123" s="31" t="str">
         <f>VLOOKUP(I123,'Names with Seat Code'!B:E,4)</f>
-        <v>Kaberle</v>
+        <v>Kadric</v>
       </c>
       <c r="I123" s="25">
         <f>IF(B122+1&lt;DIRECTIONS!$E$24,B122+1,0)</f>
@@ -63620,11 +63618,11 @@
       </c>
       <c r="G124" s="31" t="str">
         <f>VLOOKUP(I124,'Names with Seat Code'!B:E,2)</f>
-        <v>Azra</v>
+        <v>Brady</v>
       </c>
       <c r="H124" s="31" t="str">
         <f>VLOOKUP(I124,'Names with Seat Code'!B:E,4)</f>
-        <v>Kadric</v>
+        <v>Keaveney</v>
       </c>
       <c r="I124" s="25">
         <f>IF(B123+1&lt;DIRECTIONS!$E$24,B123+1,0)</f>
@@ -63652,11 +63650,11 @@
       </c>
       <c r="G125" s="31" t="str">
         <f>VLOOKUP(I125,'Names with Seat Code'!B:E,2)</f>
-        <v>Brady</v>
+        <v>Hannah</v>
       </c>
       <c r="H125" s="31" t="str">
         <f>VLOOKUP(I125,'Names with Seat Code'!B:E,4)</f>
-        <v>Keaveney</v>
+        <v>Kenton</v>
       </c>
       <c r="I125" s="25">
         <f>IF(B124+1&lt;DIRECTIONS!$E$24,B124+1,0)</f>
@@ -63684,11 +63682,11 @@
       </c>
       <c r="G126" s="31" t="str">
         <f>VLOOKUP(I126,'Names with Seat Code'!B:E,2)</f>
-        <v>Hannah</v>
+        <v>Aiden</v>
       </c>
       <c r="H126" s="31" t="str">
         <f>VLOOKUP(I126,'Names with Seat Code'!B:E,4)</f>
-        <v>Kenton</v>
+        <v>Kiley</v>
       </c>
       <c r="I126" s="25">
         <f>IF(B125+1&lt;DIRECTIONS!$E$24,B125+1,0)</f>
@@ -63716,11 +63714,11 @@
       </c>
       <c r="G127" s="31" t="str">
         <f>VLOOKUP(I127,'Names with Seat Code'!B:E,2)</f>
-        <v>Aiden</v>
+        <v>Clinton</v>
       </c>
       <c r="H127" s="31" t="str">
         <f>VLOOKUP(I127,'Names with Seat Code'!B:E,4)</f>
-        <v>Kiley</v>
+        <v>King</v>
       </c>
       <c r="I127" s="25">
         <f>IF(B126+1&lt;DIRECTIONS!$E$24,B126+1,0)</f>
@@ -63748,11 +63746,11 @@
       </c>
       <c r="G128" s="31" t="str">
         <f>VLOOKUP(I128,'Names with Seat Code'!B:E,2)</f>
-        <v>Clinton</v>
+        <v>Kyle</v>
       </c>
       <c r="H128" s="31" t="str">
         <f>VLOOKUP(I128,'Names with Seat Code'!B:E,4)</f>
-        <v>King</v>
+        <v>Koster</v>
       </c>
       <c r="I128" s="25">
         <f>IF(B127+1&lt;DIRECTIONS!$E$24,B127+1,0)</f>
@@ -63780,11 +63778,11 @@
       </c>
       <c r="G129" s="31" t="str">
         <f>VLOOKUP(I129,'Names with Seat Code'!B:E,2)</f>
-        <v>Kyle</v>
+        <v>Enzo</v>
       </c>
       <c r="H129" s="31" t="str">
         <f>VLOOKUP(I129,'Names with Seat Code'!B:E,4)</f>
-        <v>Koster</v>
+        <v>Lalicata</v>
       </c>
       <c r="I129" s="25">
         <f>IF(B128+1&lt;DIRECTIONS!$E$24,B128+1,0)</f>
@@ -63812,11 +63810,11 @@
       </c>
       <c r="G130" s="31" t="str">
         <f>VLOOKUP(I130,'Names with Seat Code'!B:E,2)</f>
-        <v>Enzo</v>
+        <v>Matthew</v>
       </c>
       <c r="H130" s="31" t="str">
         <f>VLOOKUP(I130,'Names with Seat Code'!B:E,4)</f>
-        <v>Lalicata</v>
+        <v>Laurino</v>
       </c>
       <c r="I130" s="25">
         <f>IF(B129+1&lt;DIRECTIONS!$E$24,B129+1,0)</f>
@@ -63844,7 +63842,7 @@
       </c>
       <c r="G131" s="31" t="str">
         <f>VLOOKUP(I131,'Names with Seat Code'!B:E,2)</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="H131" s="31" t="str">
         <f>VLOOKUP(I131,'Names with Seat Code'!B:E,4)</f>
@@ -63876,11 +63874,11 @@
       </c>
       <c r="G132" s="31" t="str">
         <f>VLOOKUP(I132,'Names with Seat Code'!B:E,2)</f>
-        <v>Jonathan</v>
+        <v>Asad</v>
       </c>
       <c r="H132" s="31" t="str">
         <f>VLOOKUP(I132,'Names with Seat Code'!B:E,4)</f>
-        <v>Laurino</v>
+        <v>Layne</v>
       </c>
       <c r="I132" s="25">
         <f>IF(B131+1&lt;DIRECTIONS!$E$24,B131+1,0)</f>
@@ -66628,11 +66626,11 @@
       </c>
       <c r="G218" s="31" t="str">
         <f>VLOOKUP(I218,'Names with Seat Code'!B:E,2)</f>
-        <v>Asad</v>
+        <v>Jonathan</v>
       </c>
       <c r="H218" s="31" t="str">
         <f>VLOOKUP(I218,'Names with Seat Code'!B:E,4)</f>
-        <v>Layne</v>
+        <v>Lee</v>
       </c>
       <c r="I218" s="25">
         <f>DIRECTIONS!$E$23+B218</f>
@@ -66660,7 +66658,7 @@
       </c>
       <c r="G219" s="31" t="str">
         <f>VLOOKUP(I219,'Names with Seat Code'!B:E,2)</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="H219" s="31" t="str">
         <f>VLOOKUP(I219,'Names with Seat Code'!B:E,4)</f>
@@ -66692,11 +66690,11 @@
       </c>
       <c r="G220" s="31" t="str">
         <f>VLOOKUP(I220,'Names with Seat Code'!B:E,2)</f>
-        <v>Austin</v>
+        <v>Desmond</v>
       </c>
       <c r="H220" s="31" t="str">
         <f>VLOOKUP(I220,'Names with Seat Code'!B:E,4)</f>
-        <v>Lee</v>
+        <v>Lethin</v>
       </c>
       <c r="I220" s="25">
         <f>DIRECTIONS!$E$23+B220</f>
@@ -66724,11 +66722,11 @@
       </c>
       <c r="G221" s="31" t="str">
         <f>VLOOKUP(I221,'Names with Seat Code'!B:E,2)</f>
-        <v>Desmond</v>
+        <v>Katie</v>
       </c>
       <c r="H221" s="31" t="str">
         <f>VLOOKUP(I221,'Names with Seat Code'!B:E,4)</f>
-        <v>Lethin</v>
+        <v>Lewis</v>
       </c>
       <c r="I221" s="25">
         <f>DIRECTIONS!$E$23+B221</f>
@@ -66756,11 +66754,11 @@
       </c>
       <c r="G222" s="31" t="str">
         <f>VLOOKUP(I222,'Names with Seat Code'!B:E,2)</f>
-        <v>Katie</v>
+        <v>Isabelle</v>
       </c>
       <c r="H222" s="31" t="str">
         <f>VLOOKUP(I222,'Names with Seat Code'!B:E,4)</f>
-        <v>Lewis</v>
+        <v>Lightbody</v>
       </c>
       <c r="I222" s="25">
         <f>DIRECTIONS!$E$23+B222</f>
@@ -66788,11 +66786,11 @@
       </c>
       <c r="G223" s="31" t="str">
         <f>VLOOKUP(I223,'Names with Seat Code'!B:E,2)</f>
-        <v>Isabelle</v>
+        <v>Steven</v>
       </c>
       <c r="H223" s="31" t="str">
         <f>VLOOKUP(I223,'Names with Seat Code'!B:E,4)</f>
-        <v>Lightbody</v>
+        <v>Lin</v>
       </c>
       <c r="I223" s="25">
         <f>DIRECTIONS!$E$23+B223</f>
@@ -66820,11 +66818,11 @@
       </c>
       <c r="G224" s="31" t="str">
         <f>VLOOKUP(I224,'Names with Seat Code'!B:E,2)</f>
-        <v>Steven</v>
+        <v>Zackary</v>
       </c>
       <c r="H224" s="31" t="str">
         <f>VLOOKUP(I224,'Names with Seat Code'!B:E,4)</f>
-        <v>Lin</v>
+        <v>Lizotte</v>
       </c>
       <c r="I224" s="25">
         <f>DIRECTIONS!$E$23+B224</f>
@@ -66852,11 +66850,11 @@
       </c>
       <c r="G225" s="31" t="str">
         <f>VLOOKUP(I225,'Names with Seat Code'!B:E,2)</f>
-        <v>Zackary</v>
+        <v>Isla</v>
       </c>
       <c r="H225" s="31" t="str">
         <f>VLOOKUP(I225,'Names with Seat Code'!B:E,4)</f>
-        <v>Lizotte</v>
+        <v>Lusk</v>
       </c>
       <c r="I225" s="25">
         <f>DIRECTIONS!$E$23+B225</f>
@@ -66884,11 +66882,11 @@
       </c>
       <c r="G226" s="31" t="str">
         <f>VLOOKUP(I226,'Names with Seat Code'!B:E,2)</f>
-        <v>Isla</v>
+        <v>Lilyana</v>
       </c>
       <c r="H226" s="31" t="str">
         <f>VLOOKUP(I226,'Names with Seat Code'!B:E,4)</f>
-        <v>Lusk</v>
+        <v>Madden</v>
       </c>
       <c r="I226" s="25">
         <f>DIRECTIONS!$E$23+B226</f>
@@ -66916,11 +66914,11 @@
       </c>
       <c r="G227" s="31" t="str">
         <f>VLOOKUP(I227,'Names with Seat Code'!B:E,2)</f>
-        <v>Lilyana</v>
+        <v>Rosalia</v>
       </c>
       <c r="H227" s="31" t="str">
         <f>VLOOKUP(I227,'Names with Seat Code'!B:E,4)</f>
-        <v>Madden</v>
+        <v>Maganzini</v>
       </c>
       <c r="I227" s="25">
         <f>DIRECTIONS!$E$23+B227</f>
@@ -66948,7 +66946,7 @@
       </c>
       <c r="G228" s="31" t="str">
         <f>VLOOKUP(I228,'Names with Seat Code'!B:E,2)</f>
-        <v>Rosalia</v>
+        <v>Trent</v>
       </c>
       <c r="H228" s="31" t="str">
         <f>VLOOKUP(I228,'Names with Seat Code'!B:E,4)</f>
@@ -66980,11 +66978,11 @@
       </c>
       <c r="G229" s="31" t="str">
         <f>VLOOKUP(I229,'Names with Seat Code'!B:E,2)</f>
-        <v>Trent</v>
+        <v>Emma</v>
       </c>
       <c r="H229" s="31" t="str">
         <f>VLOOKUP(I229,'Names with Seat Code'!B:E,4)</f>
-        <v>Maganzini</v>
+        <v>Mahoney</v>
       </c>
       <c r="I229" s="25">
         <f>DIRECTIONS!$E$23+B229</f>
@@ -67012,11 +67010,11 @@
       </c>
       <c r="G230" s="31" t="str">
         <f>VLOOKUP(I230,'Names with Seat Code'!B:E,2)</f>
-        <v>Emma</v>
+        <v>Charles</v>
       </c>
       <c r="H230" s="31" t="str">
         <f>VLOOKUP(I230,'Names with Seat Code'!B:E,4)</f>
-        <v>Mahoney</v>
+        <v>Maness</v>
       </c>
       <c r="I230" s="25">
         <f>DIRECTIONS!$E$23+B230</f>
@@ -67044,11 +67042,11 @@
       </c>
       <c r="G231" s="31" t="str">
         <f>VLOOKUP(I231,'Names with Seat Code'!B:E,2)</f>
-        <v>Charles</v>
+        <v>Evan</v>
       </c>
       <c r="H231" s="31" t="str">
         <f>VLOOKUP(I231,'Names with Seat Code'!B:E,4)</f>
-        <v>Maness</v>
+        <v>Manfredi</v>
       </c>
       <c r="I231" s="25">
         <f>DIRECTIONS!$E$23+B231</f>
@@ -67076,11 +67074,11 @@
       </c>
       <c r="G232" s="31" t="str">
         <f>VLOOKUP(I232,'Names with Seat Code'!B:E,2)</f>
-        <v>Evan</v>
+        <v>Syler</v>
       </c>
       <c r="H232" s="31" t="str">
         <f>VLOOKUP(I232,'Names with Seat Code'!B:E,4)</f>
-        <v>Manfredi</v>
+        <v>Manning</v>
       </c>
       <c r="I232" s="25">
         <f>DIRECTIONS!$E$23+B232</f>
@@ -67108,11 +67106,11 @@
       </c>
       <c r="G233" s="31" t="str">
         <f>VLOOKUP(I233,'Names with Seat Code'!B:E,2)</f>
-        <v>Syler</v>
+        <v>Tyler</v>
       </c>
       <c r="H233" s="31" t="str">
         <f>VLOOKUP(I233,'Names with Seat Code'!B:E,4)</f>
-        <v>Manning</v>
+        <v>Marchlik</v>
       </c>
       <c r="I233" s="25">
         <f>DIRECTIONS!$E$23+B233</f>

--- a/data/2026 GSMUD.xlsx
+++ b/data/2026 GSMUD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code Space\Git 2026 Grad\2026-Grad\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A8E40C-65E9-48C9-89FA-A3AE152AD595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE55BCE-4D68-4DB9-925B-E4630921AD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DIRECTIONS" sheetId="9" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3976" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3978" uniqueCount="482">
   <si>
     <t>DIRECTIONS FOR SPREADSHEET USE</t>
   </si>
@@ -539,9 +539,6 @@
   </si>
   <si>
     <t>Cooper Joseph Dean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Happiness osarugue  Deji </t>
   </si>
   <si>
     <t>Jack Denmark</t>
@@ -1246,9 +1243,6 @@
     <t xml:space="preserve">K-ber-le </t>
   </si>
   <si>
-    <t xml:space="preserve">(Uh-zra) - The "Uh" part is more slower than the next part "zra". The zra part is quicker, and you roll the r. "Kud-reech" - you also roll the r, and my last name goes by slower. If you can't pronounce it, you can say, "Ah-zra" "Kadrick" </t>
-  </si>
-  <si>
     <t>Key van e</t>
   </si>
   <si>
@@ -1511,6 +1505,18 @@
   </si>
   <si>
     <t>Mason Buddy Moll</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Happiness Osarugue  Deji </t>
+  </si>
+  <si>
+    <t>Uh-zra - the "Uh" part is slower than "zra" and roll the r. "Kud-reech" - roll the r</t>
   </si>
 </sst>
 </file>
@@ -1779,7 +1785,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1870,6 +1876,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2193,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="24" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -2201,7 +2210,7 @@
         <v>30</v>
       </c>
       <c r="O3" s="24" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -2212,7 +2221,7 @@
         <v>31</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -2223,7 +2232,7 @@
         <v>32</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -2231,7 +2240,7 @@
         <v>33</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -2239,7 +2248,7 @@
         <v>34</v>
       </c>
       <c r="O7" s="24" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -2250,7 +2259,7 @@
         <v>35</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -2258,7 +2267,7 @@
         <v>36</v>
       </c>
       <c r="O9" s="24" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -2266,7 +2275,7 @@
         <v>37</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -2274,7 +2283,7 @@
         <v>38</v>
       </c>
       <c r="O11" s="24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -2282,7 +2291,7 @@
         <v>39</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -2296,7 +2305,7 @@
         <v>40</v>
       </c>
       <c r="O13" s="24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -2310,7 +2319,7 @@
         <v>41</v>
       </c>
       <c r="O14" s="24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -2321,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="N15" s="24" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
@@ -2335,10 +2344,10 @@
         <v>12</v>
       </c>
       <c r="N16" s="24" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="O16" s="24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
@@ -2349,10 +2358,10 @@
         <v>14</v>
       </c>
       <c r="N17" s="24" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="O17" s="24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
@@ -2363,7 +2372,7 @@
         <v>42</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
@@ -2440,7 +2449,7 @@
         <v>Abate</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
@@ -2492,7 +2501,7 @@
         <v>Abubakar</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2505,13 +2514,13 @@
         <v>Luis</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -2538,7 +2547,7 @@
         <v>Ahlert</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2559,7 +2568,7 @@
         <v>Aiello</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2601,7 +2610,7 @@
         <v>Amado</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2679,7 +2688,7 @@
         <v>Aquino</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2719,7 +2728,7 @@
         <v>Araujo</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2740,7 +2749,7 @@
         <v>Aretusi</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2818,7 +2827,7 @@
         <v>Batista</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2839,7 +2848,7 @@
         <v>Beaulieu</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2860,7 +2869,7 @@
         <v>Belfon</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2919,7 +2928,7 @@
         <v>Bhola</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2959,7 +2968,7 @@
         <v>Boucher</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2999,12 +3008,12 @@
         <v>Bowlin</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="45" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B30" s="41"/>
       <c r="C30" s="40" t="str">
@@ -3191,7 +3200,7 @@
         <v>Carcione</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3307,7 +3316,7 @@
         <v>Cirrone</v>
       </c>
       <c r="F45" s="46" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3404,12 +3413,12 @@
         <v>Comenos</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B51" s="41"/>
       <c r="C51" s="40" t="str">
@@ -3603,7 +3612,7 @@
     </row>
     <row r="61" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="47" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B61" s="41"/>
       <c r="C61" s="40" t="str">
@@ -3629,16 +3638,12 @@
         <f t="shared" si="3"/>
         <v>Walick</v>
       </c>
-      <c r="D62" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v>Da</v>
-      </c>
-      <c r="E62" s="40" t="str">
-        <f t="shared" si="5"/>
-        <v>Silva</v>
+      <c r="D62" s="40"/>
+      <c r="E62" s="49" t="s">
+        <v>479</v>
       </c>
       <c r="F62" s="45" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3678,12 +3683,12 @@
         <v>Dean</v>
       </c>
       <c r="F64" s="45" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="41" t="s">
-        <v>156</v>
+        <v>480</v>
       </c>
       <c r="B65" s="41"/>
       <c r="C65" s="40" t="str">
@@ -3692,19 +3697,19 @@
       </c>
       <c r="D65" s="40" t="str">
         <f t="shared" si="4"/>
-        <v>osarugue</v>
+        <v>Osarugue</v>
       </c>
       <c r="E65" s="40" t="str">
         <f t="shared" si="5"/>
         <v>Deji</v>
       </c>
       <c r="F65" s="41" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="45" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B66" s="41"/>
       <c r="C66" s="40" t="str">
@@ -3723,7 +3728,7 @@
     </row>
     <row r="67" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B67" s="41"/>
       <c r="C67" s="40" t="str">
@@ -3739,12 +3744,12 @@
         <v>DiDonato</v>
       </c>
       <c r="F67" s="41" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B68" s="41"/>
       <c r="C68" s="40" t="str">
@@ -3763,7 +3768,7 @@
     </row>
     <row r="69" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B69" s="41"/>
       <c r="C69" s="40" t="str">
@@ -3779,12 +3784,12 @@
         <v>DiSerio</v>
       </c>
       <c r="F69" s="41" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="45" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="40" t="str">
@@ -3800,12 +3805,12 @@
         <v>Donaghey</v>
       </c>
       <c r="F70" s="45" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B71" s="41"/>
       <c r="C71" s="40" t="str">
@@ -3824,7 +3829,7 @@
     </row>
     <row r="72" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B72" s="41"/>
       <c r="C72" s="40" t="str">
@@ -3832,18 +3837,18 @@
         <v>Alana</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E72" s="49" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B73" s="41"/>
       <c r="C73" s="40" t="str">
@@ -3862,7 +3867,7 @@
     </row>
     <row r="74" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="46" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B74" s="41"/>
       <c r="C74" s="40" t="str">
@@ -3878,12 +3883,12 @@
         <v>DuRoss</v>
       </c>
       <c r="F74" s="46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="46" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B75" s="41"/>
       <c r="C75" s="40" t="str">
@@ -3902,7 +3907,7 @@
     </row>
     <row r="76" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B76" s="41"/>
       <c r="C76" s="40" t="str">
@@ -3921,7 +3926,7 @@
     </row>
     <row r="77" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B77" s="41"/>
       <c r="C77" s="40" t="str">
@@ -3940,7 +3945,7 @@
     </row>
     <row r="78" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="45" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B78" s="41"/>
       <c r="C78" s="40" t="str">
@@ -3959,7 +3964,7 @@
     </row>
     <row r="79" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B79" s="41"/>
       <c r="C79" s="40" t="str">
@@ -3978,7 +3983,7 @@
     </row>
     <row r="80" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B80" s="41"/>
       <c r="C80" s="40" t="str">
@@ -3994,12 +3999,12 @@
         <v>Encarnacao</v>
       </c>
       <c r="F80" s="46" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B81" s="41"/>
       <c r="C81" s="40" t="str">
@@ -4015,12 +4020,12 @@
         <v>Ewald</v>
       </c>
       <c r="F81" s="46" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="45" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B82" s="41"/>
       <c r="C82" s="40" t="str">
@@ -4036,12 +4041,12 @@
         <v>Fantasia</v>
       </c>
       <c r="F82" s="45" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B83" s="41"/>
       <c r="C83" s="40" t="str">
@@ -4060,7 +4065,7 @@
     </row>
     <row r="84" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B84" s="41"/>
       <c r="C84" s="40" t="str">
@@ -4079,7 +4084,7 @@
     </row>
     <row r="85" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B85" s="41"/>
       <c r="C85" s="40" t="str">
@@ -4098,7 +4103,7 @@
     </row>
     <row r="86" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="48" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B86" s="41"/>
       <c r="C86" s="40" t="str">
@@ -4117,7 +4122,7 @@
     </row>
     <row r="87" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="41" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B87" s="41"/>
       <c r="C87" s="40" t="str">
@@ -4136,7 +4141,7 @@
     </row>
     <row r="88" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B88" s="41"/>
       <c r="C88" s="40" t="str">
@@ -4155,7 +4160,7 @@
     </row>
     <row r="89" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B89" s="41"/>
       <c r="C89" s="40" t="str">
@@ -4171,12 +4176,12 @@
         <v>Forse</v>
       </c>
       <c r="F89" s="46" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B90" s="41"/>
       <c r="C90" s="40" t="str">
@@ -4195,7 +4200,7 @@
     </row>
     <row r="91" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B91" s="41"/>
       <c r="C91" s="40" t="str">
@@ -4214,7 +4219,7 @@
     </row>
     <row r="92" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B92" s="41"/>
       <c r="C92" s="40" t="str">
@@ -4230,12 +4235,12 @@
         <v>Fucarile</v>
       </c>
       <c r="F92" s="45" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="41" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B93" s="41"/>
       <c r="C93" s="40" t="str">
@@ -4254,7 +4259,7 @@
     </row>
     <row r="94" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="45" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B94" s="41"/>
       <c r="C94" s="40" t="str">
@@ -4273,7 +4278,7 @@
     </row>
     <row r="95" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="41" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B95" s="41"/>
       <c r="C95" s="40" t="str">
@@ -4289,12 +4294,12 @@
         <v>Gager</v>
       </c>
       <c r="F95" s="41" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="45" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B96" s="41"/>
       <c r="C96" s="40" t="str">
@@ -4313,7 +4318,7 @@
     </row>
     <row r="97" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="40" t="str">
@@ -4329,12 +4334,12 @@
         <v>Gallagher</v>
       </c>
       <c r="F97" s="41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A98" s="45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B98" s="41"/>
       <c r="C98" s="40" t="str">
@@ -4350,12 +4355,12 @@
         <v>Gauvin</v>
       </c>
       <c r="F98" s="45" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B99" s="41"/>
       <c r="C99" s="40" t="str">
@@ -4374,7 +4379,7 @@
     </row>
     <row r="100" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B100" s="41"/>
       <c r="C100" s="40" t="str">
@@ -4393,7 +4398,7 @@
     </row>
     <row r="101" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B101" s="41"/>
       <c r="C101" s="40" t="str">
@@ -4412,7 +4417,7 @@
     </row>
     <row r="102" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="45" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B102" s="41"/>
       <c r="C102" s="40" t="str">
@@ -4431,7 +4436,7 @@
     </row>
     <row r="103" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B103" s="41"/>
       <c r="C103" s="40" t="str">
@@ -4450,7 +4455,7 @@
     </row>
     <row r="104" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="46" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B104" s="41"/>
       <c r="C104" s="40" t="str">
@@ -4469,7 +4474,7 @@
     </row>
     <row r="105" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="41" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B105" s="41"/>
       <c r="C105" s="40" t="str">
@@ -4485,12 +4490,12 @@
         <v>Gorski</v>
       </c>
       <c r="F105" s="41" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B106" s="41"/>
       <c r="C106" s="40" t="str">
@@ -4506,12 +4511,12 @@
         <v>Gosdanian</v>
       </c>
       <c r="F106" s="45" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B107" s="41"/>
       <c r="C107" s="40" t="str">
@@ -4530,7 +4535,7 @@
     </row>
     <row r="108" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B108" s="41"/>
       <c r="C108" s="40" t="str">
@@ -4549,7 +4554,7 @@
     </row>
     <row r="109" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="41" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B109" s="41"/>
       <c r="C109" s="40" t="str">
@@ -4568,7 +4573,7 @@
     </row>
     <row r="110" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B110" s="41"/>
       <c r="C110" s="40" t="str">
@@ -4584,12 +4589,12 @@
         <v>Hall</v>
       </c>
       <c r="F110" s="45" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="41" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B111" s="41"/>
       <c r="C111" s="40" t="str">
@@ -4608,7 +4613,7 @@
     </row>
     <row r="112" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A112" s="45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B112" s="41"/>
       <c r="C112" s="40" t="str">
@@ -4627,7 +4632,7 @@
     </row>
     <row r="113" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A113" s="47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B113" s="41"/>
       <c r="C113" s="40" t="str">
@@ -4646,7 +4651,7 @@
     </row>
     <row r="114" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A114" s="45" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B114" s="41"/>
       <c r="C114" s="40" t="str">
@@ -4665,7 +4670,7 @@
     </row>
     <row r="115" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="46" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B115" s="41"/>
       <c r="C115" s="40" t="str">
@@ -4684,7 +4689,7 @@
     </row>
     <row r="116" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="46" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B116" s="41"/>
       <c r="C116" s="40" t="str">
@@ -4700,12 +4705,12 @@
         <v>Henri</v>
       </c>
       <c r="F116" s="46" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B117" s="41"/>
       <c r="C117" s="40" t="str">
@@ -4724,7 +4729,7 @@
     </row>
     <row r="118" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B118" s="41"/>
       <c r="C118" s="40" t="str">
@@ -4743,7 +4748,7 @@
     </row>
     <row r="119" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B119" s="41"/>
       <c r="C119" s="40" t="str">
@@ -4759,12 +4764,12 @@
         <v>Hobson</v>
       </c>
       <c r="F119" s="41" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="45" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B120" s="41"/>
       <c r="C120" s="40" t="str">
@@ -4783,7 +4788,7 @@
     </row>
     <row r="121" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A121" s="46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B121" s="41"/>
       <c r="C121" s="40" t="str">
@@ -4799,12 +4804,12 @@
         <v>Houle</v>
       </c>
       <c r="F121" s="46" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A122" s="45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B122" s="41"/>
       <c r="C122" s="40" t="str">
@@ -4823,7 +4828,7 @@
     </row>
     <row r="123" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B123" s="41"/>
       <c r="C123" s="40" t="str">
@@ -4839,12 +4844,12 @@
         <v>Iosua</v>
       </c>
       <c r="F123" s="41" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="46" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B124" s="41"/>
       <c r="C124" s="40" t="str">
@@ -4863,7 +4868,7 @@
     </row>
     <row r="125" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B125" s="41"/>
       <c r="C125" s="40" t="str">
@@ -4882,7 +4887,7 @@
     </row>
     <row r="126" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="45" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B126" s="41"/>
       <c r="C126" s="40" t="str">
@@ -4901,7 +4906,7 @@
     </row>
     <row r="127" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="41" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B127" s="41"/>
       <c r="C127" s="40" t="str">
@@ -4920,7 +4925,7 @@
     </row>
     <row r="128" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B128" s="41"/>
       <c r="C128" s="40" t="str">
@@ -4939,7 +4944,7 @@
     </row>
     <row r="129" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B129" s="41"/>
       <c r="C129" s="40" t="str">
@@ -4958,7 +4963,7 @@
     </row>
     <row r="130" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="46" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B130" s="41"/>
       <c r="C130" s="40" t="str">
@@ -4977,7 +4982,7 @@
     </row>
     <row r="131" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B131" s="41"/>
       <c r="C131" s="40" t="str">
@@ -4996,7 +5001,7 @@
     </row>
     <row r="132" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="46" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B132" s="41"/>
       <c r="C132" s="40" t="str">
@@ -5012,12 +5017,12 @@
         <v>Kaberle</v>
       </c>
       <c r="F132" s="46" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B133" s="41"/>
       <c r="C133" s="40" t="str">
@@ -5033,12 +5038,12 @@
         <v>Kadric</v>
       </c>
       <c r="F133" s="46" t="s">
-        <v>391</v>
+        <v>481</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A134" s="45" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B134" s="41"/>
       <c r="C134" s="40" t="str">
@@ -5054,12 +5059,12 @@
         <v>Keaveney</v>
       </c>
       <c r="F134" s="45" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A135" s="46" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B135" s="41"/>
       <c r="C135" s="40" t="str">
@@ -5075,12 +5080,12 @@
         <v>Kenton</v>
       </c>
       <c r="F135" s="46" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A136" s="46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B136" s="41"/>
       <c r="C136" s="40" t="str">
@@ -5096,12 +5101,12 @@
         <v>Kiley</v>
       </c>
       <c r="F136" s="46" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A137" s="41" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B137" s="41"/>
       <c r="C137" s="40" t="str">
@@ -5120,7 +5125,7 @@
     </row>
     <row r="138" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A138" s="45" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B138" s="41"/>
       <c r="C138" s="40" t="str">
@@ -5139,7 +5144,7 @@
     </row>
     <row r="139" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A139" s="41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B139" s="41"/>
       <c r="C139" s="40" t="str">
@@ -5155,12 +5160,12 @@
         <v>Lalicata</v>
       </c>
       <c r="F139" s="41" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A140" s="45" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B140" s="41"/>
       <c r="C140" s="40" t="str">
@@ -5176,12 +5181,12 @@
         <v>Laurino</v>
       </c>
       <c r="F140" s="45" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A141" s="41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B141" s="41"/>
       <c r="C141" s="40" t="str">
@@ -5200,7 +5205,7 @@
     </row>
     <row r="142" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A142" s="45" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B142" s="41"/>
       <c r="C142" s="40" t="str">
@@ -5216,12 +5221,12 @@
         <v>Layne</v>
       </c>
       <c r="F142" s="45" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A143" s="41" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B143" s="41"/>
       <c r="C143" s="40" t="str">
@@ -5240,7 +5245,7 @@
     </row>
     <row r="144" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A144" s="45" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B144" s="41"/>
       <c r="C144" s="40" t="str">
@@ -5259,7 +5264,7 @@
     </row>
     <row r="145" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A145" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B145" s="41"/>
       <c r="C145" s="40" t="str">
@@ -5278,7 +5283,7 @@
     </row>
     <row r="146" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A146" s="45" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B146" s="41"/>
       <c r="C146" s="40" t="str">
@@ -5297,7 +5302,7 @@
     </row>
     <row r="147" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A147" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B147" s="41"/>
       <c r="C147" s="40" t="str">
@@ -5316,7 +5321,7 @@
     </row>
     <row r="148" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A148" s="45" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B148" s="41"/>
       <c r="C148" s="40" t="str">
@@ -5335,7 +5340,7 @@
     </row>
     <row r="149" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A149" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B149" s="41"/>
       <c r="C149" s="40" t="str">
@@ -5351,12 +5356,12 @@
         <v>Lizotte</v>
       </c>
       <c r="F149" s="46" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A150" s="46" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B150" s="41"/>
       <c r="C150" s="40" t="str">
@@ -5372,12 +5377,12 @@
         <v>Lusk</v>
       </c>
       <c r="F150" s="46" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A151" s="46" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B151" s="41"/>
       <c r="C151" s="40" t="str">
@@ -5396,7 +5401,7 @@
     </row>
     <row r="152" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A152" s="45" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B152" s="41"/>
       <c r="C152" s="40" t="str">
@@ -5412,12 +5417,12 @@
         <v>Maganzini</v>
       </c>
       <c r="F152" s="45" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A153" s="41" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B153" s="41"/>
       <c r="C153" s="40" t="str">
@@ -5436,7 +5441,7 @@
     </row>
     <row r="154" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A154" s="45" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B154" s="41"/>
       <c r="C154" s="40" t="str">
@@ -5455,7 +5460,7 @@
     </row>
     <row r="155" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A155" s="41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B155" s="41"/>
       <c r="C155" s="40" t="str">
@@ -5471,12 +5476,12 @@
         <v>Maness</v>
       </c>
       <c r="F155" s="41" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A156" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B156" s="41"/>
       <c r="C156" s="40" t="str">
@@ -5495,7 +5500,7 @@
     </row>
     <row r="157" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A157" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B157" s="41"/>
       <c r="C157" s="40" t="str">
@@ -5514,7 +5519,7 @@
     </row>
     <row r="158" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A158" s="46" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B158" s="41"/>
       <c r="C158" s="40" t="str">
@@ -5530,12 +5535,12 @@
         <v>Marchlik</v>
       </c>
       <c r="F158" s="46" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A159" s="41" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B159" s="41"/>
       <c r="C159" s="40" t="e">
@@ -5551,12 +5556,12 @@
         <v>#VALUE!</v>
       </c>
       <c r="F159" s="41" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A160" s="46" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B160" s="41"/>
       <c r="C160" s="40" t="str">
@@ -5575,7 +5580,7 @@
     </row>
     <row r="161" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A161" s="47" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B161" s="41"/>
       <c r="C161" s="40" t="str">
@@ -5594,7 +5599,7 @@
     </row>
     <row r="162" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A162" s="48" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B162" s="41"/>
       <c r="C162" s="40" t="str">
@@ -5613,7 +5618,7 @@
     </row>
     <row r="163" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A163" s="46" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B163" s="41"/>
       <c r="C163" s="40" t="str">
@@ -5632,7 +5637,7 @@
     </row>
     <row r="164" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A164" s="46" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B164" s="41"/>
       <c r="C164" s="40" t="str">
@@ -5651,7 +5656,7 @@
     </row>
     <row r="165" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A165" s="46" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B165" s="41"/>
       <c r="C165" s="40" t="str">
@@ -5670,7 +5675,7 @@
     </row>
     <row r="166" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A166" s="45" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B166" s="41"/>
       <c r="C166" s="40" t="str">
@@ -5689,7 +5694,7 @@
     </row>
     <row r="167" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A167" s="41" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B167" s="41"/>
       <c r="C167" s="40" t="str">
@@ -5705,12 +5710,12 @@
         <v>McLaughlin-Shostak</v>
       </c>
       <c r="F167" s="41" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A168" s="45" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B168" s="41"/>
       <c r="C168" s="40" t="str">
@@ -5726,12 +5731,12 @@
         <v>McMenimen</v>
       </c>
       <c r="F168" s="45" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A169" s="41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B169" s="41"/>
       <c r="C169" s="40" t="str">
@@ -5750,7 +5755,7 @@
     </row>
     <row r="170" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A170" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B170" s="41"/>
       <c r="C170" s="40" t="str">
@@ -5769,7 +5774,7 @@
     </row>
     <row r="171" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A171" s="46" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B171" s="41"/>
       <c r="C171" s="40" t="str">
@@ -5788,7 +5793,7 @@
     </row>
     <row r="172" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A172" s="46" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B172" s="41"/>
       <c r="C172" s="40" t="str">
@@ -5804,12 +5809,12 @@
         <v>Miceli</v>
       </c>
       <c r="F172" s="46" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A173" s="41" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B173" s="41"/>
       <c r="C173" s="40" t="str">
@@ -5828,7 +5833,7 @@
     </row>
     <row r="174" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A174" s="48" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B174" s="41"/>
       <c r="C174" s="40" t="str">
@@ -5847,7 +5852,7 @@
     </row>
     <row r="175" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A175" s="41" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B175" s="41"/>
       <c r="C175" s="40" t="str">
@@ -5863,12 +5868,12 @@
         <v>Moller</v>
       </c>
       <c r="F175" s="41" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A176" s="45" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B176" s="41"/>
       <c r="C176" s="40" t="str">
@@ -5884,12 +5889,12 @@
         <v>Moreira</v>
       </c>
       <c r="F176" s="45" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A177" s="41" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B177" s="41"/>
       <c r="C177" s="40" t="str">
@@ -5908,7 +5913,7 @@
     </row>
     <row r="178" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A178" s="45" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B178" s="41"/>
       <c r="C178" s="40" t="str">
@@ -5927,7 +5932,7 @@
     </row>
     <row r="179" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A179" s="41" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B179" s="41"/>
       <c r="C179" s="40" t="str">
@@ -5946,7 +5951,7 @@
     </row>
     <row r="180" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A180" s="45" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B180" s="41"/>
       <c r="C180" s="40" t="str">
@@ -5962,12 +5967,12 @@
         <v>Muller</v>
       </c>
       <c r="F180" s="45" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A181" s="46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B181" s="41"/>
       <c r="C181" s="40" t="str">
@@ -5983,7 +5988,7 @@
         <v>Mullin</v>
       </c>
       <c r="F181" s="46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6007,7 +6012,7 @@
     </row>
     <row r="183" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A183" s="46" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B183" s="41"/>
       <c r="C183" s="40" t="str">
@@ -6026,7 +6031,7 @@
     </row>
     <row r="184" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A184" s="46" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B184" s="41"/>
       <c r="C184" s="40" t="str">
@@ -6045,7 +6050,7 @@
     </row>
     <row r="185" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A185" s="41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B185" s="41"/>
       <c r="C185" s="40" t="str">
@@ -6061,12 +6066,12 @@
         <v>Nguyen</v>
       </c>
       <c r="F185" s="41" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A186" s="46" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B186" s="41"/>
       <c r="C186" s="40" t="str">
@@ -6085,7 +6090,7 @@
     </row>
     <row r="187" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A187" s="41" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B187" s="41"/>
       <c r="C187" s="40" t="str">
@@ -6101,12 +6106,12 @@
         <v>Norris</v>
       </c>
       <c r="F187" s="41" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A188" s="45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B188" s="41"/>
       <c r="C188" s="40" t="str">
@@ -6125,7 +6130,7 @@
     </row>
     <row r="189" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A189" s="41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B189" s="41"/>
       <c r="C189" s="40" t="str">
@@ -6141,12 +6146,12 @@
         <v>Ortins</v>
       </c>
       <c r="F189" s="41" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A190" s="45" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B190" s="41"/>
       <c r="C190" s="40" t="str">
@@ -6162,12 +6167,12 @@
         <v>Ortiz</v>
       </c>
       <c r="F190" s="45" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A191" s="46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B191" s="41"/>
       <c r="C191" s="40" t="str">
@@ -6186,7 +6191,7 @@
     </row>
     <row r="192" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A192" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B192" s="41"/>
       <c r="C192" s="40" t="str">
@@ -6202,12 +6207,12 @@
         <v>Patel</v>
       </c>
       <c r="F192" s="46" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A193" s="41" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B193" s="41"/>
       <c r="C193" s="40" t="str">
@@ -6226,7 +6231,7 @@
     </row>
     <row r="194" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A194" s="45" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B194" s="41"/>
       <c r="C194" s="40" t="str">
@@ -6242,12 +6247,12 @@
         <v>Petrin</v>
       </c>
       <c r="F194" s="45" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A195" s="41" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B195" s="41"/>
       <c r="C195" s="40" t="str">
@@ -6266,7 +6271,7 @@
     </row>
     <row r="196" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A196" s="48" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B196" s="41"/>
       <c r="C196" s="40" t="str">
@@ -6285,7 +6290,7 @@
     </row>
     <row r="197" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A197" s="46" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B197" s="41"/>
       <c r="C197" s="40" t="str">
@@ -6301,12 +6306,12 @@
         <v>Pomerantz</v>
       </c>
       <c r="F197" s="46" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A198" s="45" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B198" s="41"/>
       <c r="C198" s="40" t="str">
@@ -6322,12 +6327,12 @@
         <v>Poudyal</v>
       </c>
       <c r="F198" s="45" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A199" s="46" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B199" s="41"/>
       <c r="C199" s="40" t="str">
@@ -6343,12 +6348,12 @@
         <v>Pulpi</v>
       </c>
       <c r="F199" s="46" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A200" s="46" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B200" s="41"/>
       <c r="C200" s="40" t="str">
@@ -6364,12 +6369,12 @@
         <v>Rai</v>
       </c>
       <c r="F200" s="46" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A201" s="46" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B201" s="41"/>
       <c r="C201" s="40" t="str">
@@ -6388,7 +6393,7 @@
     </row>
     <row r="202" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A202" s="46" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B202" s="41"/>
       <c r="C202" s="40" t="str">
@@ -6407,7 +6412,7 @@
     </row>
     <row r="203" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A203" s="46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B203" s="41"/>
       <c r="C203" s="40" t="str">
@@ -6426,7 +6431,7 @@
     </row>
     <row r="204" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A204" s="46" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B204" s="41"/>
       <c r="C204" s="40" t="str">
@@ -6442,12 +6447,12 @@
         <v>Richter</v>
       </c>
       <c r="F204" s="46" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A205" s="46" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B205" s="41"/>
       <c r="C205" s="40" t="str">
@@ -6463,12 +6468,12 @@
         <v>Robichaud</v>
       </c>
       <c r="F205" s="46" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A206" s="45" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B206" s="41"/>
       <c r="C206" s="40" t="str">
@@ -6487,7 +6492,7 @@
     </row>
     <row r="207" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A207" s="41" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B207" s="41"/>
       <c r="C207" s="40" t="str">
@@ -6506,7 +6511,7 @@
     </row>
     <row r="208" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A208" s="46" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B208" s="41"/>
       <c r="C208" s="40" t="str">
@@ -6525,7 +6530,7 @@
     </row>
     <row r="209" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A209" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B209" s="41"/>
       <c r="C209" s="40" t="str">
@@ -6544,7 +6549,7 @@
     </row>
     <row r="210" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A210" s="45" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B210" s="41"/>
       <c r="C210" s="40" t="str">
@@ -6563,7 +6568,7 @@
     </row>
     <row r="211" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A211" s="41" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B211" s="41"/>
       <c r="C211" s="40" t="str">
@@ -6579,12 +6584,12 @@
         <v>Rojas</v>
       </c>
       <c r="F211" s="41" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A212" s="46" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B212" s="41"/>
       <c r="C212" s="40" t="str">
@@ -6603,7 +6608,7 @@
     </row>
     <row r="213" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A213" s="41" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B213" s="41"/>
       <c r="C213" s="40" t="str">
@@ -6619,12 +6624,12 @@
         <v>Ryland</v>
       </c>
       <c r="F213" s="41" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A214" s="45" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B214" s="41"/>
       <c r="C214" s="40" t="str">
@@ -6640,12 +6645,12 @@
         <v>Sardinha</v>
       </c>
       <c r="F214" s="45" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A215" s="41" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B215" s="41"/>
       <c r="C215" s="40" t="str">
@@ -6661,12 +6666,12 @@
         <v>Sarre</v>
       </c>
       <c r="F215" s="41" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A216" s="46" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B216" s="41"/>
       <c r="C216" s="40" t="str">
@@ -6685,7 +6690,7 @@
     </row>
     <row r="217" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A217" s="41" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B217" s="41"/>
       <c r="C217" s="40" t="str">
@@ -6704,7 +6709,7 @@
     </row>
     <row r="218" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A218" s="45" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B218" s="41"/>
       <c r="C218" s="40" t="str">
@@ -6720,12 +6725,12 @@
         <v>Schrager</v>
       </c>
       <c r="F218" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A219" s="41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B219" s="41"/>
       <c r="C219" s="40" t="str">
@@ -6744,7 +6749,7 @@
     </row>
     <row r="220" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A220" s="45" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B220" s="41"/>
       <c r="C220" s="40" t="str">
@@ -6763,7 +6768,7 @@
     </row>
     <row r="221" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A221" s="46" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B221" s="41"/>
       <c r="C221" s="40" t="str">
@@ -6779,12 +6784,12 @@
         <v>Selvakumar</v>
       </c>
       <c r="F221" s="46" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A222" s="45" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B222" s="41"/>
       <c r="C222" s="40" t="str">
@@ -6803,7 +6808,7 @@
     </row>
     <row r="223" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A223" s="46" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B223" s="41"/>
       <c r="C223" s="40" t="str">
@@ -6822,7 +6827,7 @@
     </row>
     <row r="224" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A224" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B224" s="41"/>
       <c r="C224" s="40" t="str">
@@ -6838,12 +6843,12 @@
         <v>Shediac</v>
       </c>
       <c r="F224" s="45" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A225" s="41" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B225" s="41"/>
       <c r="C225" s="40" t="str">
@@ -6862,7 +6867,7 @@
     </row>
     <row r="226" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A226" s="45" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B226" s="41"/>
       <c r="C226" s="40" t="str">
@@ -6878,12 +6883,12 @@
         <v>Siciliano</v>
       </c>
       <c r="F226" s="45" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A227" s="46" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B227" s="41"/>
       <c r="C227" s="40" t="str">
@@ -6902,7 +6907,7 @@
     </row>
     <row r="228" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A228" s="46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B228" s="41"/>
       <c r="C228" s="40" t="str">
@@ -6918,12 +6923,12 @@
         <v>Skenderian</v>
       </c>
       <c r="F228" s="46" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A229" s="41" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B229" s="41"/>
       <c r="C229" s="40" t="str">
@@ -6939,12 +6944,12 @@
         <v>Slinn</v>
       </c>
       <c r="F229" s="41" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A230" s="46" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B230" s="41"/>
       <c r="C230" s="40" t="str">
@@ -6963,7 +6968,7 @@
     </row>
     <row r="231" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A231" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B231" s="41"/>
       <c r="C231" s="40" t="str">
@@ -6982,7 +6987,7 @@
     </row>
     <row r="232" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A232" s="45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B232" s="41"/>
       <c r="C232" s="40" t="str">
@@ -6998,12 +7003,12 @@
         <v>Soto</v>
       </c>
       <c r="F232" s="45" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A233" s="41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B233" s="41"/>
       <c r="C233" s="40" t="str">
@@ -7022,7 +7027,7 @@
     </row>
     <row r="234" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A234" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B234" s="41"/>
       <c r="C234" s="40" t="str">
@@ -7041,7 +7046,7 @@
     </row>
     <row r="235" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A235" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B235" s="41"/>
       <c r="C235" s="40" t="str">
@@ -7060,7 +7065,7 @@
     </row>
     <row r="236" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A236" s="46" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B236" s="41"/>
       <c r="C236" s="40" t="str">
@@ -7076,12 +7081,12 @@
         <v>Staffier</v>
       </c>
       <c r="F236" s="46" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A237" s="46" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B237" s="41"/>
       <c r="C237" s="40" t="str">
@@ -7097,12 +7102,12 @@
         <v>Stathoulopoulos</v>
       </c>
       <c r="F237" s="46" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A238" s="45" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B238" s="41"/>
       <c r="C238" s="40" t="str">
@@ -7121,7 +7126,7 @@
     </row>
     <row r="239" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A239" s="41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B239" s="41"/>
       <c r="C239" s="40" t="str">
@@ -7137,12 +7142,12 @@
         <v>Sullivan</v>
       </c>
       <c r="F239" s="41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A240" s="46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B240" s="41"/>
       <c r="C240" s="40" t="str">
@@ -7161,7 +7166,7 @@
     </row>
     <row r="241" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A241" s="41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B241" s="41"/>
       <c r="C241" s="40" t="str">
@@ -7180,7 +7185,7 @@
     </row>
     <row r="242" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A242" s="45" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B242" s="41"/>
       <c r="C242" s="40" t="str">
@@ -7196,12 +7201,12 @@
         <v>Taubman</v>
       </c>
       <c r="F242" s="45" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A243" s="41" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B243" s="41"/>
       <c r="C243" s="40" t="str">
@@ -7217,12 +7222,12 @@
         <v>Tawadros</v>
       </c>
       <c r="F243" s="41" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A244" s="45" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B244" s="41"/>
       <c r="C244" s="40" t="str">
@@ -7238,12 +7243,12 @@
         <v>Toomey</v>
       </c>
       <c r="F244" s="45" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="245" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A245" s="41" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B245" s="41"/>
       <c r="C245" s="40" t="str">
@@ -7262,7 +7267,7 @@
     </row>
     <row r="246" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A246" s="45" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B246" s="41"/>
       <c r="C246" s="40" t="str">
@@ -7278,12 +7283,12 @@
         <v>Travassos</v>
       </c>
       <c r="F246" s="45" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A247" s="46" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B247" s="41"/>
       <c r="C247" s="40" t="str">
@@ -7299,12 +7304,12 @@
         <v>Upton</v>
       </c>
       <c r="F247" s="46" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A248" s="45" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B248" s="41"/>
       <c r="C248" s="40" t="str">
@@ -7323,7 +7328,7 @@
     </row>
     <row r="249" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A249" s="41" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B249" s="41"/>
       <c r="C249" s="40" t="str">
@@ -7332,13 +7337,13 @@
       </c>
       <c r="D249" s="40"/>
       <c r="E249" s="49" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F249" s="41"/>
     </row>
     <row r="250" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A250" s="45" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B250" s="41"/>
       <c r="C250" s="40" t="str">
@@ -7346,16 +7351,16 @@
         <v>Katherine</v>
       </c>
       <c r="D250" s="49" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E250" s="49" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F250" s="45"/>
     </row>
     <row r="251" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A251" s="41" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B251" s="41"/>
       <c r="C251" s="40" t="str">
@@ -7374,7 +7379,7 @@
     </row>
     <row r="252" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A252" s="45" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B252" s="41"/>
       <c r="C252" s="40" t="str">
@@ -7390,12 +7395,12 @@
         <v>Viliott</v>
       </c>
       <c r="F252" s="45" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A253" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B253" s="41"/>
       <c r="C253" s="40" t="str">
@@ -7411,12 +7416,12 @@
         <v>Vitarisi</v>
       </c>
       <c r="F253" s="46" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A254" s="46" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B254" s="41"/>
       <c r="C254" s="40" t="str">
@@ -7435,7 +7440,7 @@
     </row>
     <row r="255" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A255" s="46" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B255" s="41"/>
       <c r="C255" s="40" t="str">
@@ -7454,7 +7459,7 @@
     </row>
     <row r="256" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A256" s="45" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B256" s="41"/>
       <c r="C256" s="40" t="str">
@@ -7473,7 +7478,7 @@
     </row>
     <row r="257" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A257" s="46" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B257" s="41"/>
       <c r="C257" s="40" t="str">
@@ -7492,7 +7497,7 @@
     </row>
     <row r="258" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A258" s="45" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B258" s="41"/>
       <c r="C258" s="40" t="str">
@@ -7511,7 +7516,7 @@
     </row>
     <row r="259" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A259" s="46" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B259" s="41"/>
       <c r="C259" s="40" t="str">
@@ -7530,7 +7535,7 @@
     </row>
     <row r="260" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A260" s="45" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B260" s="41"/>
       <c r="C260" s="40" t="str">
@@ -7549,7 +7554,7 @@
     </row>
     <row r="261" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A261" s="41" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B261" s="41"/>
       <c r="C261" s="40" t="str">
@@ -7568,7 +7573,7 @@
     </row>
     <row r="262" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A262" s="45" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B262" s="41"/>
       <c r="C262" s="40" t="str">
@@ -7587,7 +7592,7 @@
     </row>
     <row r="263" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A263" s="41" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B263" s="41"/>
       <c r="C263" s="40" t="str">
@@ -7603,12 +7608,12 @@
         <v>Williams</v>
       </c>
       <c r="F263" s="41" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="264" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A264" s="45" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B264" s="41"/>
       <c r="C264" s="40" t="str">
@@ -7627,7 +7632,7 @@
     </row>
     <row r="265" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A265" s="41" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C265" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7645,7 +7650,7 @@
     </row>
     <row r="266" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A266" s="45" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C266" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7663,7 +7668,7 @@
     </row>
     <row r="267" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A267" s="41" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C267" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7681,7 +7686,7 @@
     </row>
     <row r="268" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A268" s="45" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C268" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7696,12 +7701,12 @@
         <v>Zani</v>
       </c>
       <c r="F268" s="45" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="269" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A269" s="41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C269" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7716,7 +7721,7 @@
         <v>Zheng</v>
       </c>
       <c r="F269" s="41" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.2">
@@ -7793,7 +7798,7 @@
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="L2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -7824,7 +7829,7 @@
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="L3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -7855,7 +7860,7 @@
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="L4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -7886,7 +7891,7 @@
       <c r="H5" s="42"/>
       <c r="I5" s="42"/>
       <c r="L5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -7945,7 +7950,7 @@
       <c r="H7" s="42"/>
       <c r="I7" s="42"/>
       <c r="L7" s="22" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -7979,7 +7984,7 @@
         <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -8013,7 +8018,7 @@
         <v>87</v>
       </c>
       <c r="M9" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -8047,7 +8052,7 @@
         <v>31</v>
       </c>
       <c r="M10" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -8081,7 +8086,7 @@
         <v>32</v>
       </c>
       <c r="M11" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -8115,7 +8120,7 @@
         <v>33</v>
       </c>
       <c r="M12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -8149,7 +8154,7 @@
         <v>34</v>
       </c>
       <c r="M13" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -8183,7 +8188,7 @@
         <v>35</v>
       </c>
       <c r="M14" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -8217,7 +8222,7 @@
         <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -8251,7 +8256,7 @@
         <v>37</v>
       </c>
       <c r="M16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -8285,7 +8290,7 @@
         <v>38</v>
       </c>
       <c r="M17" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -8319,7 +8324,7 @@
         <v>39</v>
       </c>
       <c r="M18" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -8353,7 +8358,7 @@
         <v>40</v>
       </c>
       <c r="M19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -8387,7 +8392,7 @@
         <v>41</v>
       </c>
       <c r="M20" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -8418,10 +8423,10 @@
       <c r="H21" s="42"/>
       <c r="I21" s="42"/>
       <c r="L21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -8452,10 +8457,10 @@
       <c r="H22" s="42"/>
       <c r="I22" s="42"/>
       <c r="L22" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="M22" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -8486,10 +8491,10 @@
       <c r="H23" s="42"/>
       <c r="I23" s="42"/>
       <c r="L23" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M23" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -8523,7 +8528,7 @@
         <v>42</v>
       </c>
       <c r="M24" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -9561,13 +9566,13 @@
         <f>'Raw Name Splitter'!C62</f>
         <v>Walick</v>
       </c>
-      <c r="D62" s="39" t="str">
+      <c r="D62" s="39">
         <f>'Raw Name Splitter'!D62</f>
-        <v>Da</v>
+        <v>0</v>
       </c>
       <c r="E62" s="39" t="str">
         <f>'Raw Name Splitter'!E62</f>
-        <v>Silva</v>
+        <v>Da Silva</v>
       </c>
       <c r="F62" s="39" t="str">
         <f>'Raw Name Splitter'!F62</f>
@@ -9645,7 +9650,7 @@
       </c>
       <c r="D65" s="39" t="str">
         <f>'Raw Name Splitter'!D65</f>
-        <v>osarugue</v>
+        <v>Osarugue</v>
       </c>
       <c r="E65" s="39" t="str">
         <f>'Raw Name Splitter'!E65</f>
@@ -10094,7 +10099,7 @@
         <v/>
       </c>
       <c r="E81" s="39" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F81" s="39" t="str">
         <f>'Raw Name Splitter'!F81</f>
@@ -11546,7 +11551,7 @@
       </c>
       <c r="F133" s="39" t="str">
         <f>'Raw Name Splitter'!F133</f>
-        <v xml:space="preserve">(Uh-zra) - The "Uh" part is more slower than the next part "zra". The zra part is quicker, and you roll the r. "Kud-reech" - you also roll the r, and my last name goes by slower. If you can't pronounce it, you can say, "Ah-zra" "Kadrick" </v>
+        <v>Uh-zra - the "Uh" part is slower than "zra" and roll the r. "Kud-reech" - roll the r</v>
       </c>
       <c r="H133" s="42"/>
       <c r="I133" s="42"/>
@@ -14767,7 +14772,7 @@
         <v>Colby</v>
       </c>
       <c r="E249" s="39" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F249" s="39">
         <f>'Raw Name Splitter'!F249</f>
@@ -15330,13 +15335,13 @@
         <v>87</v>
       </c>
       <c r="C270" s="39" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E270" s="39" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F270" s="39" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -18283,7 +18288,7 @@
       </c>
       <c r="H69" s="1" t="str">
         <f>VLOOKUP(J69,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Silva</v>
+        <v>Da Silva</v>
       </c>
       <c r="I69" s="1" t="str">
         <f>VLOOKUP(J69,'Names with Seat Code'!A:E,3,FALSE)</f>
@@ -18292,9 +18297,9 @@
       <c r="J69">
         <v>56</v>
       </c>
-      <c r="K69" t="str">
+      <c r="K69">
         <f>VLOOKUP(J69,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Da</v>
+        <v>0</v>
       </c>
       <c r="L69" s="1" t="str">
         <f>VLOOKUP(J69,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -18380,7 +18385,7 @@
       </c>
       <c r="K71" t="str">
         <f>VLOOKUP(J71,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>osarugue</v>
+        <v>Osarugue</v>
       </c>
       <c r="L71" s="1" t="str">
         <f>VLOOKUP(J71,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -21125,7 +21130,7 @@
       </c>
       <c r="L134" s="1" t="str">
         <f>VLOOKUP(J134,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v xml:space="preserve">(Uh-zra) - The "Uh" part is more slower than the next part "zra". The zra part is quicker, and you roll the r. "Kud-reech" - you also roll the r, and my last name goes by slower. If you can't pronounce it, you can say, "Ah-zra" "Kadrick" </v>
+        <v>Uh-zra - the "Uh" part is slower than "zra" and roll the r. "Kud-reech" - roll the r</v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -26384,28 +26389,28 @@
       <c r="F254" s="8">
         <v>8</v>
       </c>
-      <c r="G254" s="6">
+      <c r="G254" s="6" t="e">
         <f>VLOOKUP(J254,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H254" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="H254" s="1" t="e">
         <f>VLOOKUP(J254,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Williams</v>
-      </c>
-      <c r="I254" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I254" s="1" t="e">
         <f>VLOOKUP(J254,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Aidan</v>
+        <v>#N/A</v>
       </c>
       <c r="J254" s="3">
-        <v>241</v>
-      </c>
-      <c r="K254" t="str">
+        <v>999</v>
+      </c>
+      <c r="K254" t="e">
         <f>VLOOKUP(J254,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Auddie</v>
-      </c>
-      <c r="L254" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="L254" s="1" t="e">
         <f>VLOOKUP(J254,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>Auddie(Awd-ie)</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="255" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -26428,28 +26433,28 @@
       <c r="F255" s="8">
         <v>9</v>
       </c>
-      <c r="G255" s="6">
+      <c r="G255" s="6" t="e">
         <f>VLOOKUP(J255,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H255" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="H255" s="1" t="e">
         <f>VLOOKUP(J255,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Wright</v>
-      </c>
-      <c r="I255" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I255" s="1" t="e">
         <f>VLOOKUP(J255,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jared</v>
+        <v>#N/A</v>
       </c>
       <c r="J255">
-        <v>242</v>
-      </c>
-      <c r="K255" t="str">
+        <v>999</v>
+      </c>
+      <c r="K255" t="e">
         <f>VLOOKUP(J255,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="L255" s="1">
+        <v>#N/A</v>
+      </c>
+      <c r="L255" s="1" t="e">
         <f>VLOOKUP(J255,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
@@ -26472,28 +26477,28 @@
       <c r="F256" s="8">
         <v>10</v>
       </c>
-      <c r="G256" s="6">
+      <c r="G256" s="6" t="e">
         <f>VLOOKUP(J256,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H256" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="H256" s="1" t="e">
         <f>VLOOKUP(J256,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Wright</v>
-      </c>
-      <c r="I256" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I256" s="1" t="e">
         <f>VLOOKUP(J256,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jamari</v>
+        <v>#N/A</v>
       </c>
       <c r="J256">
-        <v>243</v>
-      </c>
-      <c r="K256" t="str">
+        <v>999</v>
+      </c>
+      <c r="K256" t="e">
         <f>VLOOKUP(J256,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="L256" s="1">
+        <v>#N/A</v>
+      </c>
+      <c r="L256" s="1" t="e">
         <f>VLOOKUP(J256,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
@@ -26516,28 +26521,28 @@
       <c r="F257" s="8">
         <v>11</v>
       </c>
-      <c r="G257" s="6">
+      <c r="G257" s="6" t="e">
         <f>VLOOKUP(J257,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H257" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="H257" s="1" t="e">
         <f>VLOOKUP(J257,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Yandle</v>
-      </c>
-      <c r="I257" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I257" s="1" t="e">
         <f>VLOOKUP(J257,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Quinn</v>
+        <v>#N/A</v>
       </c>
       <c r="J257">
-        <v>244</v>
-      </c>
-      <c r="K257" t="str">
+        <v>999</v>
+      </c>
+      <c r="K257" t="e">
         <f>VLOOKUP(J257,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="L257" s="1">
+        <v>#N/A</v>
+      </c>
+      <c r="L257" s="1" t="e">
         <f>VLOOKUP(J257,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="258" spans="1:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -26560,31 +26565,31 @@
       <c r="F258" s="5">
         <v>12</v>
       </c>
-      <c r="G258" s="6">
+      <c r="G258" s="6" t="e">
         <f>VLOOKUP(J258,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H258" s="37" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="H258" s="37" t="e">
         <f>VLOOKUP(J258,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Zani</v>
-      </c>
-      <c r="I258" s="2" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I258" s="2" t="e">
         <f>VLOOKUP(J258,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>John</v>
+        <v>#N/A</v>
       </c>
       <c r="J258">
-        <v>245</v>
-      </c>
-      <c r="K258" s="3" t="str">
+        <v>999</v>
+      </c>
+      <c r="K258" s="3" t="e">
         <f>VLOOKUP(J258,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="L258" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="L258" s="1" t="e">
         <f>VLOOKUP(J258,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>John ZAH-nee</v>
-      </c>
-    </row>
-    <row r="259" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
         <v>51</v>
       </c>
@@ -26610,25 +26615,25 @@
       </c>
       <c r="H259" s="1" t="str">
         <f>VLOOKUP(J259,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Zheng</v>
+        <v>Williams</v>
       </c>
       <c r="I259" s="1" t="str">
         <f>VLOOKUP(J259,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jiayu</v>
-      </c>
-      <c r="J259">
-        <v>246</v>
+        <v>Aidan</v>
+      </c>
+      <c r="J259" s="3">
+        <v>241</v>
       </c>
       <c r="K259" t="str">
         <f>VLOOKUP(J259,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
+        <v>Auddie</v>
       </c>
       <c r="L259" s="1" t="str">
         <f>VLOOKUP(J259,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>jah-yoo Jung</v>
-      </c>
-    </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+        <v>Auddie(Awd-ie)</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
         <v>51</v>
       </c>
@@ -26648,24 +26653,24 @@
       <c r="F260" s="8">
         <v>2</v>
       </c>
-      <c r="G260" s="6" t="e">
+      <c r="G260" s="6">
         <f>VLOOKUP(J260,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H260" s="1" t="e">
+        <v>0</v>
+      </c>
+      <c r="H260" s="1" t="str">
         <f>VLOOKUP(J260,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I260" s="1" t="e">
+        <v>Wright</v>
+      </c>
+      <c r="I260" s="1" t="str">
         <f>VLOOKUP(J260,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>Jared</v>
       </c>
       <c r="J260">
-        <v>247</v>
-      </c>
-      <c r="L260" s="1" t="e">
+        <v>242</v>
+      </c>
+      <c r="L260" s="1">
         <f>VLOOKUP(J260,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
@@ -26688,20 +26693,24 @@
       <c r="F261" s="8">
         <v>3</v>
       </c>
-      <c r="G261" s="6" t="e">
+      <c r="G261" s="6">
         <f>VLOOKUP(J261,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H261" s="1" t="e">
+        <v>0</v>
+      </c>
+      <c r="H261" s="1" t="str">
         <f>VLOOKUP(J261,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I261" s="1" t="e">
+        <v>Wright</v>
+      </c>
+      <c r="I261" s="1" t="str">
         <f>VLOOKUP(J261,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>Jamari</v>
       </c>
       <c r="J261">
-        <v>248</v>
+        <v>243</v>
+      </c>
+      <c r="L261" s="1">
+        <f>VLOOKUP(J261,'Names with Seat Code'!A:F,6,FALSE)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
@@ -26724,20 +26733,24 @@
       <c r="F262" s="8">
         <v>4</v>
       </c>
-      <c r="G262" s="6" t="e">
+      <c r="G262" s="6">
         <f>VLOOKUP(J262,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H262" s="1" t="e">
+        <v>0</v>
+      </c>
+      <c r="H262" s="1" t="str">
         <f>VLOOKUP(J262,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I262" s="1" t="e">
+        <v>Yandle</v>
+      </c>
+      <c r="I262" s="1" t="str">
         <f>VLOOKUP(J262,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>Quinn</v>
       </c>
       <c r="J262">
-        <v>249</v>
+        <v>244</v>
+      </c>
+      <c r="L262" s="1">
+        <f>VLOOKUP(J262,'Names with Seat Code'!A:F,6,FALSE)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
@@ -26760,20 +26773,24 @@
       <c r="F263" s="8">
         <v>5</v>
       </c>
-      <c r="G263" s="6" t="e">
+      <c r="G263" s="6">
         <f>VLOOKUP(J263,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H263" s="1" t="e">
+        <v>0</v>
+      </c>
+      <c r="H263" s="1" t="str">
         <f>VLOOKUP(J263,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I263" s="1" t="e">
+        <v>Zani</v>
+      </c>
+      <c r="I263" s="1" t="str">
         <f>VLOOKUP(J263,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>John</v>
       </c>
       <c r="J263">
-        <v>250</v>
+        <v>245</v>
+      </c>
+      <c r="L263" s="1" t="str">
+        <f>VLOOKUP(J263,'Names with Seat Code'!A:F,6,FALSE)</f>
+        <v>John ZAH-nee</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
@@ -26796,20 +26813,24 @@
       <c r="F264" s="8">
         <v>6</v>
       </c>
-      <c r="G264" s="6" t="e">
+      <c r="G264" s="6">
         <f>VLOOKUP(J264,'Names with Seat Code'!A:I,9,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H264" s="1" t="e">
+        <v>0</v>
+      </c>
+      <c r="H264" s="1" t="str">
         <f>VLOOKUP(J264,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I264" s="1" t="e">
+        <v>Zheng</v>
+      </c>
+      <c r="I264" s="1" t="str">
         <f>VLOOKUP(J264,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>#N/A</v>
+        <v>Jiayu</v>
       </c>
       <c r="J264">
-        <v>251</v>
+        <v>246</v>
+      </c>
+      <c r="L264" s="1" t="str">
+        <f>VLOOKUP(J264,'Names with Seat Code'!A:F,6,FALSE)</f>
+        <v>jah-yoo Jung</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
@@ -26845,7 +26866,7 @@
         <v>#N/A</v>
       </c>
       <c r="J265">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
@@ -26881,7 +26902,7 @@
         <v>#N/A</v>
       </c>
       <c r="J266">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
@@ -26917,7 +26938,7 @@
         <v>#N/A</v>
       </c>
       <c r="J267">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
@@ -26953,7 +26974,7 @@
         <v>#N/A</v>
       </c>
       <c r="J268">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
@@ -26989,7 +27010,7 @@
         <v>#N/A</v>
       </c>
       <c r="J269">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
@@ -30229,7 +30250,7 @@
       </c>
       <c r="I69" s="6" t="str">
         <f>'Grad Raw Data'!H69</f>
-        <v>Silva</v>
+        <v>Da Silva</v>
       </c>
       <c r="J69" s="6">
         <f>'Grad Raw Data'!G69</f>
@@ -37035,17 +37056,17 @@
       <c r="G254" s="8">
         <v>8</v>
       </c>
-      <c r="H254" s="6" t="str">
+      <c r="H254" s="6" t="e">
         <f>'Grad Raw Data'!I254</f>
-        <v>Aidan</v>
-      </c>
-      <c r="I254" s="6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I254" s="6" t="e">
         <f>'Grad Raw Data'!H254</f>
-        <v>Williams</v>
-      </c>
-      <c r="J254" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="J254" s="6" t="e">
         <f>'Grad Raw Data'!G254</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="255" spans="1:10" ht="18" x14ac:dyDescent="0.25">
@@ -37072,17 +37093,17 @@
       <c r="G255" s="8">
         <v>9</v>
       </c>
-      <c r="H255" s="6" t="str">
+      <c r="H255" s="6" t="e">
         <f>'Grad Raw Data'!I255</f>
-        <v>Jared</v>
-      </c>
-      <c r="I255" s="6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I255" s="6" t="e">
         <f>'Grad Raw Data'!H255</f>
-        <v>Wright</v>
-      </c>
-      <c r="J255" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="J255" s="6" t="e">
         <f>'Grad Raw Data'!G255</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="256" spans="1:10" ht="18" x14ac:dyDescent="0.25">
@@ -37109,17 +37130,17 @@
       <c r="G256" s="8">
         <v>10</v>
       </c>
-      <c r="H256" s="6" t="str">
+      <c r="H256" s="6" t="e">
         <f>'Grad Raw Data'!I256</f>
-        <v>Jamari</v>
-      </c>
-      <c r="I256" s="6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I256" s="6" t="e">
         <f>'Grad Raw Data'!H256</f>
-        <v>Wright</v>
-      </c>
-      <c r="J256" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="J256" s="6" t="e">
         <f>'Grad Raw Data'!G256</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="18" x14ac:dyDescent="0.25">
@@ -37146,17 +37167,17 @@
       <c r="G257" s="8">
         <v>11</v>
       </c>
-      <c r="H257" s="6" t="str">
+      <c r="H257" s="6" t="e">
         <f>'Grad Raw Data'!I257</f>
-        <v>Quinn</v>
-      </c>
-      <c r="I257" s="6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I257" s="6" t="e">
         <f>'Grad Raw Data'!H257</f>
-        <v>Yandle</v>
-      </c>
-      <c r="J257" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="J257" s="6" t="e">
         <f>'Grad Raw Data'!G257</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="258" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -37183,17 +37204,17 @@
       <c r="G258" s="5">
         <v>12</v>
       </c>
-      <c r="H258" s="6" t="str">
+      <c r="H258" s="6" t="e">
         <f>'Grad Raw Data'!I258</f>
-        <v>John</v>
-      </c>
-      <c r="I258" s="6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="I258" s="6" t="e">
         <f>'Grad Raw Data'!H258</f>
-        <v>Zani</v>
-      </c>
-      <c r="J258" s="6">
+        <v>#N/A</v>
+      </c>
+      <c r="J258" s="6" t="e">
         <f>'Grad Raw Data'!G258</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="259" spans="1:10" ht="18.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -37220,11 +37241,11 @@
       </c>
       <c r="H259" s="6" t="str">
         <f>'Grad Raw Data'!I259</f>
-        <v>Jiayu</v>
+        <v>Aidan</v>
       </c>
       <c r="I259" s="6" t="str">
         <f>'Grad Raw Data'!H259</f>
-        <v>Zheng</v>
+        <v>Williams</v>
       </c>
       <c r="J259" s="6">
         <f>'Grad Raw Data'!G259</f>
@@ -37253,17 +37274,17 @@
       <c r="G260" s="8">
         <v>2</v>
       </c>
-      <c r="H260" s="6" t="e">
+      <c r="H260" s="6" t="str">
         <f>'Grad Raw Data'!I260</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I260" s="6" t="e">
+        <v>Jared</v>
+      </c>
+      <c r="I260" s="6" t="str">
         <f>'Grad Raw Data'!H260</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J260" s="6" t="e">
+        <v>Wright</v>
+      </c>
+      <c r="J260" s="6">
         <f>'Grad Raw Data'!G260</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:10" ht="18" x14ac:dyDescent="0.25">
@@ -37288,17 +37309,17 @@
       <c r="G261" s="8">
         <v>3</v>
       </c>
-      <c r="H261" s="6" t="e">
+      <c r="H261" s="6" t="str">
         <f>'Grad Raw Data'!I261</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I261" s="6" t="e">
+        <v>Jamari</v>
+      </c>
+      <c r="I261" s="6" t="str">
         <f>'Grad Raw Data'!H261</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J261" s="6" t="e">
+        <v>Wright</v>
+      </c>
+      <c r="J261" s="6">
         <f>'Grad Raw Data'!G261</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:10" ht="18" x14ac:dyDescent="0.25">
@@ -37323,17 +37344,17 @@
       <c r="G262" s="8">
         <v>4</v>
       </c>
-      <c r="H262" s="6" t="e">
+      <c r="H262" s="6" t="str">
         <f>'Grad Raw Data'!I262</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I262" s="6" t="e">
+        <v>Quinn</v>
+      </c>
+      <c r="I262" s="6" t="str">
         <f>'Grad Raw Data'!H262</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J262" s="6" t="e">
+        <v>Yandle</v>
+      </c>
+      <c r="J262" s="6">
         <f>'Grad Raw Data'!G262</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:10" ht="18" x14ac:dyDescent="0.25">
@@ -37358,17 +37379,17 @@
       <c r="G263" s="8">
         <v>5</v>
       </c>
-      <c r="H263" s="6" t="e">
+      <c r="H263" s="6" t="str">
         <f>'Grad Raw Data'!I263</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I263" s="6" t="e">
+        <v>John</v>
+      </c>
+      <c r="I263" s="6" t="str">
         <f>'Grad Raw Data'!H263</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J263" s="6" t="e">
+        <v>Zani</v>
+      </c>
+      <c r="J263" s="6">
         <f>'Grad Raw Data'!G263</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:10" ht="18" x14ac:dyDescent="0.25">
@@ -37393,17 +37414,17 @@
       <c r="G264" s="8">
         <v>6</v>
       </c>
-      <c r="H264" s="6" t="e">
+      <c r="H264" s="6" t="str">
         <f>'Grad Raw Data'!I264</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I264" s="6" t="e">
+        <v>Jiayu</v>
+      </c>
+      <c r="I264" s="6" t="str">
         <f>'Grad Raw Data'!H264</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J264" s="6" t="e">
+        <v>Zheng</v>
+      </c>
+      <c r="J264" s="6">
         <f>'Grad Raw Data'!G264</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:10" ht="18" x14ac:dyDescent="0.25">
@@ -37636,14 +37657,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:H521"/>
+  <dimension ref="A1:H528"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" style="17" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" style="17" customWidth="1"/>
+    <col min="2" max="2" width="25" style="17" customWidth="1"/>
     <col min="3" max="3" width="24.85546875" style="17" customWidth="1"/>
     <col min="4" max="5" width="4.85546875" style="44" customWidth="1"/>
     <col min="6" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="18" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -40595,13 +40617,13 @@
         <f>'Grad Raw Data'!I69</f>
         <v>Walick</v>
       </c>
-      <c r="B136" s="20" t="str">
+      <c r="B136" s="20">
         <f>'Grad Raw Data'!K69</f>
-        <v>Da</v>
+        <v>0</v>
       </c>
       <c r="C136" s="20" t="str">
         <f>'Grad Raw Data'!H69</f>
-        <v>Silva</v>
+        <v>Da Silva</v>
       </c>
       <c r="D136" s="44" t="str">
         <f>'Grad Raw Data'!D69</f>
@@ -40685,7 +40707,7 @@
       </c>
       <c r="B140" s="20" t="str">
         <f>'Grad Raw Data'!K71</f>
-        <v>osarugue</v>
+        <v>Osarugue</v>
       </c>
       <c r="C140" s="20" t="str">
         <f>'Grad Raw Data'!H71</f>
@@ -43482,7 +43504,7 @@
     <row r="267" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="16" t="str">
         <f>'Grad Raw Data'!L134</f>
-        <v xml:space="preserve">(Uh-zra) - The "Uh" part is more slower than the next part "zra". The zra part is quicker, and you roll the r. "Kud-reech" - you also roll the r, and my last name goes by slower. If you can't pronounce it, you can say, "Ah-zra" "Kadrick" </v>
+        <v>Uh-zra - the "Uh" part is slower than "zra" and roll the r. "Kud-reech" - roll the r</v>
       </c>
       <c r="B267" s="20"/>
       <c r="C267" s="20"/>
@@ -48731,17 +48753,17 @@
       </c>
     </row>
     <row r="506" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="20" t="str">
+      <c r="A506" s="20" t="e">
         <f>'Grad Raw Data'!I254</f>
-        <v>Aidan</v>
-      </c>
-      <c r="B506" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B506" s="20" t="e">
         <f>'Grad Raw Data'!K254</f>
-        <v>Auddie</v>
-      </c>
-      <c r="C506" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C506" s="20" t="e">
         <f>'Grad Raw Data'!H254</f>
-        <v>Williams</v>
+        <v>#N/A</v>
       </c>
       <c r="D506" s="44" t="str">
         <f>'Grad Raw Data'!D254</f>
@@ -48760,9 +48782,9 @@
       </c>
     </row>
     <row r="507" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="16" t="str">
+      <c r="A507" s="16" t="e">
         <f>'Grad Raw Data'!L254</f>
-        <v>Auddie(Awd-ie)</v>
+        <v>#N/A</v>
       </c>
       <c r="B507" s="20"/>
       <c r="C507" s="20"/>
@@ -48775,17 +48797,17 @@
       </c>
     </row>
     <row r="508" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A508" s="20" t="str">
+      <c r="A508" s="20" t="e">
         <f>'Grad Raw Data'!I255</f>
-        <v>Jared</v>
-      </c>
-      <c r="B508" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B508" s="20" t="e">
         <f>'Grad Raw Data'!K255</f>
-        <v/>
-      </c>
-      <c r="C508" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C508" s="20" t="e">
         <f>'Grad Raw Data'!H255</f>
-        <v>Wright</v>
+        <v>#N/A</v>
       </c>
       <c r="D508" s="44" t="str">
         <f>'Grad Raw Data'!D255</f>
@@ -48804,9 +48826,9 @@
       </c>
     </row>
     <row r="509" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A509" s="16">
+      <c r="A509" s="16" t="e">
         <f>'Grad Raw Data'!L255</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="B509" s="20"/>
       <c r="C509" s="20"/>
@@ -48819,17 +48841,17 @@
       </c>
     </row>
     <row r="510" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A510" s="20" t="str">
+      <c r="A510" s="20" t="e">
         <f>'Grad Raw Data'!I256</f>
-        <v>Jamari</v>
-      </c>
-      <c r="B510" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B510" s="20" t="e">
         <f>'Grad Raw Data'!K256</f>
-        <v/>
-      </c>
-      <c r="C510" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C510" s="20" t="e">
         <f>'Grad Raw Data'!H256</f>
-        <v>Wright</v>
+        <v>#N/A</v>
       </c>
       <c r="D510" s="44" t="str">
         <f>'Grad Raw Data'!D256</f>
@@ -48848,9 +48870,9 @@
       </c>
     </row>
     <row r="511" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A511" s="16">
+      <c r="A511" s="16" t="e">
         <f>'Grad Raw Data'!L256</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="B511" s="20"/>
       <c r="C511" s="20"/>
@@ -48863,17 +48885,17 @@
       </c>
     </row>
     <row r="512" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A512" s="20" t="str">
+      <c r="A512" s="20" t="e">
         <f>'Grad Raw Data'!I257</f>
-        <v>Quinn</v>
-      </c>
-      <c r="B512" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B512" s="20" t="e">
         <f>'Grad Raw Data'!K257</f>
-        <v/>
-      </c>
-      <c r="C512" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C512" s="20" t="e">
         <f>'Grad Raw Data'!H257</f>
-        <v>Yandle</v>
+        <v>#N/A</v>
       </c>
       <c r="D512" s="44" t="str">
         <f>'Grad Raw Data'!D257</f>
@@ -48892,9 +48914,9 @@
       </c>
     </row>
     <row r="513" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A513" s="16">
+      <c r="A513" s="16" t="e">
         <f>'Grad Raw Data'!L257</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="B513" s="20"/>
       <c r="C513" s="20"/>
@@ -48907,17 +48929,17 @@
       </c>
     </row>
     <row r="514" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A514" s="20" t="str">
+      <c r="A514" s="20" t="e">
         <f>'Grad Raw Data'!I258</f>
-        <v>John</v>
-      </c>
-      <c r="B514" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B514" s="20" t="e">
         <f>'Grad Raw Data'!K257</f>
-        <v/>
-      </c>
-      <c r="C514" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C514" s="20" t="e">
         <f>'Grad Raw Data'!H258</f>
-        <v>Zani</v>
+        <v>#N/A</v>
       </c>
       <c r="D514" s="44" t="str">
         <f>'Grad Raw Data'!D258</f>
@@ -48929,9 +48951,9 @@
       </c>
     </row>
     <row r="515" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A515" s="16" t="str">
-        <f>'Grad Raw Data'!L259</f>
-        <v>jah-yoo Jung</v>
+      <c r="A515" s="16" t="e">
+        <f>'Grad Raw Data'!L258</f>
+        <v>#N/A</v>
       </c>
       <c r="B515" s="20"/>
       <c r="C515" s="20"/>
@@ -48939,15 +48961,15 @@
     <row r="516" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A516" s="20" t="str">
         <f>'Grad Raw Data'!I259</f>
-        <v>Jiayu</v>
+        <v>Aidan</v>
       </c>
       <c r="B516" s="20" t="str">
-        <f>'Grad Raw Data'!K258</f>
-        <v/>
+        <f>'Grad Raw Data'!K259</f>
+        <v>Auddie</v>
       </c>
       <c r="C516" s="20" t="str">
         <f>'Grad Raw Data'!H259</f>
-        <v>Zheng</v>
+        <v>Williams</v>
       </c>
       <c r="D516" s="44" t="str">
         <f>'Grad Raw Data'!D261</f>
@@ -48959,25 +48981,22 @@
       </c>
     </row>
     <row r="517" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A517" s="16">
-        <f>'Grad Raw Data'!L261</f>
-        <v>0</v>
+      <c r="A517" s="16" t="str">
+        <f>'Grad Raw Data'!L259</f>
+        <v>Auddie(Awd-ie)</v>
       </c>
       <c r="B517" s="20"/>
       <c r="C517" s="20"/>
     </row>
     <row r="518" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A518" s="20" t="e">
+      <c r="A518" s="20" t="str">
         <f>'Grad Raw Data'!I260</f>
-        <v>#N/A</v>
-      </c>
-      <c r="B518" s="20" t="str">
-        <f>'Grad Raw Data'!K259</f>
-        <v/>
-      </c>
-      <c r="C518" s="20" t="e">
+        <v>Jared</v>
+      </c>
+      <c r="B518" s="20"/>
+      <c r="C518" s="20" t="str">
         <f>'Grad Raw Data'!H260</f>
-        <v>#N/A</v>
+        <v>Wright</v>
       </c>
       <c r="D518" s="44" t="str">
         <f>'Grad Raw Data'!D263</f>
@@ -48990,24 +49009,21 @@
     </row>
     <row r="519" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A519" s="16">
-        <f>'Grad Raw Data'!L263</f>
+        <f>'Grad Raw Data'!L260</f>
         <v>0</v>
       </c>
       <c r="B519" s="20"/>
       <c r="C519" s="20"/>
     </row>
     <row r="520" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A520" s="20" t="e">
+      <c r="A520" s="20" t="str">
         <f>'Grad Raw Data'!I261</f>
-        <v>#N/A</v>
-      </c>
-      <c r="B520" s="20">
-        <f>'Grad Raw Data'!K260</f>
-        <v>0</v>
-      </c>
-      <c r="C520" s="20" t="e">
+        <v>Jamari</v>
+      </c>
+      <c r="B520" s="50"/>
+      <c r="C520" s="20" t="str">
         <f>'Grad Raw Data'!H261</f>
-        <v>#N/A</v>
+        <v>Wright</v>
       </c>
       <c r="D520" s="44" t="str">
         <f>'Grad Raw Data'!D265</f>
@@ -49020,17 +49036,105 @@
     </row>
     <row r="521" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A521" s="16">
-        <f>'Grad Raw Data'!L265</f>
-        <v>0</v>
-      </c>
-      <c r="B521" s="20"/>
+        <f>'Grad Raw Data'!L261</f>
+        <v>0</v>
+      </c>
+      <c r="B521" s="50"/>
       <c r="C521" s="20"/>
     </row>
+    <row r="522" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A522" s="20" t="str">
+        <f>'Grad Raw Data'!I262</f>
+        <v>Quinn</v>
+      </c>
+      <c r="B522" s="50"/>
+      <c r="C522" s="20" t="str">
+        <f>'Grad Raw Data'!H262</f>
+        <v>Yandle</v>
+      </c>
+      <c r="D522" s="44" t="str">
+        <f>'Grad Raw Data'!D267</f>
+        <v>LEFT</v>
+      </c>
+      <c r="E522" s="44">
+        <f>'Grad Raw Data'!E267</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A523" s="16">
+        <f>'Grad Raw Data'!L262</f>
+        <v>0</v>
+      </c>
+      <c r="B523" s="50"/>
+      <c r="C523" s="20"/>
+    </row>
+    <row r="524" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A524" s="20" t="str">
+        <f>'Grad Raw Data'!I263</f>
+        <v>John</v>
+      </c>
+      <c r="B524" s="50"/>
+      <c r="C524" s="20" t="str">
+        <f>'Grad Raw Data'!H263</f>
+        <v>Zani</v>
+      </c>
+      <c r="D524" s="44" t="str">
+        <f>'Grad Raw Data'!D269</f>
+        <v>LEFT</v>
+      </c>
+      <c r="E524" s="44">
+        <f>'Grad Raw Data'!E269</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A525" s="16" t="str">
+        <f>'Grad Raw Data'!L263</f>
+        <v>John ZAH-nee</v>
+      </c>
+      <c r="B525" s="50"/>
+      <c r="C525" s="20"/>
+    </row>
+    <row r="526" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A526" s="20" t="str">
+        <f>'Grad Raw Data'!I264</f>
+        <v>Jiayu</v>
+      </c>
+      <c r="B526" s="52"/>
+      <c r="C526" s="20" t="str">
+        <f>'Grad Raw Data'!H264</f>
+        <v>Zheng</v>
+      </c>
+      <c r="D526" s="44" t="str">
+        <f>'Grad Raw Data'!D272</f>
+        <v>LEFT</v>
+      </c>
+      <c r="E526" s="44">
+        <f>'Grad Raw Data'!E272</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A527" s="16" t="str">
+        <f>'Grad Raw Data'!L264</f>
+        <v>jah-yoo Jung</v>
+      </c>
+      <c r="B527" s="50"/>
+      <c r="C527" s="20"/>
+    </row>
+    <row r="528" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A528" s="51" t="s">
+        <v>478</v>
+      </c>
+      <c r="B528" s="50"/>
+      <c r="C528" s="20"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.25" right="0.2" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <rowBreaks count="21" manualBreakCount="21">
+  <rowBreaks count="22" manualBreakCount="22">
     <brk id="11" max="5" man="1"/>
     <brk id="35" max="5" man="1"/>
     <brk id="59" max="5" man="1"/>
@@ -49052,6 +49156,7 @@
     <brk id="443" max="5" man="1"/>
     <brk id="467" max="16383" man="1"/>
     <brk id="491" max="16383" man="1"/>
+    <brk id="515" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -49062,9 +49167,10 @@
   <dimension ref="A1:F584"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="18" style="17" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" style="17" customWidth="1"/>
-    <col min="4" max="4" width="18" style="17" customWidth="1"/>
+    <col min="1" max="1" width="18" style="17" customWidth="1"/>
+    <col min="2" max="2" width="26" style="17" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="17" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="17" customWidth="1"/>
     <col min="5" max="5" width="10.140625" style="17" customWidth="1"/>
     <col min="6" max="6" width="9.28515625" style="17" customWidth="1"/>
   </cols>
@@ -49619,9 +49725,9 @@
         <f>'Grad Raw Data'!I19</f>
         <v>Alexander</v>
       </c>
-      <c r="B36" s="20" t="e">
-        <f>'Grad Raw Data'!#REF!</f>
-        <v>#REF!</v>
+      <c r="B36" s="20" t="str">
+        <f>'Grad Raw Data'!K19</f>
+        <v/>
       </c>
       <c r="C36" s="20" t="str">
         <f>'Grad Raw Data'!H19</f>
@@ -51169,13 +51275,13 @@
         <f>'Grad Raw Data'!I69</f>
         <v>Walick</v>
       </c>
-      <c r="B136" s="20" t="str">
+      <c r="B136" s="20">
         <f>'Grad Raw Data'!K69</f>
-        <v>Da</v>
+        <v>0</v>
       </c>
       <c r="C136" s="20" t="str">
         <f>'Grad Raw Data'!H69</f>
-        <v>Silva</v>
+        <v>Da Silva</v>
       </c>
       <c r="D136" s="20"/>
       <c r="E136" s="20" t="str">
@@ -51233,7 +51339,7 @@
       </c>
       <c r="B140" s="20" t="str">
         <f>'Grad Raw Data'!K71</f>
-        <v>osarugue</v>
+        <v>Osarugue</v>
       </c>
       <c r="C140" s="20" t="str">
         <f>'Grad Raw Data'!H71</f>
@@ -56900,17 +57006,17 @@
       <c r="F505" s="20"/>
     </row>
     <row r="506" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="20" t="str">
+      <c r="A506" s="20" t="e">
         <f>'Grad Raw Data'!I254</f>
-        <v>Aidan</v>
-      </c>
-      <c r="B506" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B506" s="20" t="e">
         <f>'Grad Raw Data'!K254</f>
-        <v>Auddie</v>
-      </c>
-      <c r="C506" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C506" s="20" t="e">
         <f>'Grad Raw Data'!H254</f>
-        <v>Williams</v>
+        <v>#N/A</v>
       </c>
       <c r="D506" s="20"/>
       <c r="E506" s="20" t="str">
@@ -56931,17 +57037,17 @@
       <c r="F507" s="20"/>
     </row>
     <row r="508" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A508" s="20" t="str">
+      <c r="A508" s="20" t="e">
         <f>'Grad Raw Data'!I255</f>
-        <v>Jared</v>
-      </c>
-      <c r="B508" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B508" s="20" t="e">
         <f>'Grad Raw Data'!K255</f>
-        <v/>
-      </c>
-      <c r="C508" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C508" s="20" t="e">
         <f>'Grad Raw Data'!H255</f>
-        <v>Wright</v>
+        <v>#N/A</v>
       </c>
       <c r="D508" s="20"/>
       <c r="E508" s="20" t="str">
@@ -56962,17 +57068,17 @@
       <c r="F509" s="20"/>
     </row>
     <row r="510" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A510" s="20" t="str">
+      <c r="A510" s="20" t="e">
         <f>'Grad Raw Data'!I256</f>
-        <v>Jamari</v>
-      </c>
-      <c r="B510" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B510" s="20" t="e">
         <f>'Grad Raw Data'!K256</f>
-        <v/>
-      </c>
-      <c r="C510" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C510" s="20" t="e">
         <f>'Grad Raw Data'!H256</f>
-        <v>Wright</v>
+        <v>#N/A</v>
       </c>
       <c r="D510" s="20"/>
       <c r="E510" s="20" t="str">
@@ -56993,17 +57099,17 @@
       <c r="F511" s="20"/>
     </row>
     <row r="512" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A512" s="20" t="str">
+      <c r="A512" s="20" t="e">
         <f>'Grad Raw Data'!I257</f>
-        <v>Quinn</v>
-      </c>
-      <c r="B512" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B512" s="20" t="e">
         <f>'Grad Raw Data'!K257</f>
-        <v/>
-      </c>
-      <c r="C512" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C512" s="20" t="e">
         <f>'Grad Raw Data'!H257</f>
-        <v>Yandle</v>
+        <v>#N/A</v>
       </c>
       <c r="D512" s="20"/>
       <c r="E512" s="20" t="str">
@@ -57024,17 +57130,17 @@
       <c r="F513" s="20"/>
     </row>
     <row r="514" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A514" s="20" t="str">
+      <c r="A514" s="20" t="e">
         <f>'Grad Raw Data'!I258</f>
-        <v>John</v>
-      </c>
-      <c r="B514" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B514" s="20" t="e">
         <f>'Grad Raw Data'!K258</f>
-        <v/>
-      </c>
-      <c r="C514" s="20" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C514" s="20" t="e">
         <f>'Grad Raw Data'!H258</f>
-        <v>Zani</v>
+        <v>#N/A</v>
       </c>
       <c r="D514" s="20"/>
       <c r="E514" s="20" t="str">
@@ -57057,15 +57163,15 @@
     <row r="516" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="20" t="str">
         <f>'Grad Raw Data'!I259</f>
-        <v>Jiayu</v>
+        <v>Aidan</v>
       </c>
       <c r="B516" s="20" t="str">
         <f>'Grad Raw Data'!K259</f>
-        <v/>
+        <v>Auddie</v>
       </c>
       <c r="C516" s="20" t="str">
         <f>'Grad Raw Data'!H259</f>
-        <v>Zheng</v>
+        <v>Williams</v>
       </c>
       <c r="D516" s="20"/>
       <c r="E516" s="20" t="str">
@@ -57086,17 +57192,17 @@
       <c r="F517" s="20"/>
     </row>
     <row r="518" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A518" s="20" t="e">
+      <c r="A518" s="20" t="str">
         <f>'Grad Raw Data'!I260</f>
-        <v>#N/A</v>
+        <v>Jared</v>
       </c>
       <c r="B518" s="20" t="str">
         <f>'Grad Raw Data'!K259</f>
-        <v/>
-      </c>
-      <c r="C518" s="20" t="e">
+        <v>Auddie</v>
+      </c>
+      <c r="C518" s="20" t="str">
         <f>'Grad Raw Data'!H260</f>
-        <v>#N/A</v>
+        <v>Wright</v>
       </c>
       <c r="D518" s="20"/>
       <c r="E518" s="20" t="str">
@@ -57117,14 +57223,14 @@
       <c r="F519" s="20"/>
     </row>
     <row r="520" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A520" s="20" t="e">
+      <c r="A520" s="20" t="str">
         <f>'Grad Raw Data'!I261</f>
-        <v>#N/A</v>
+        <v>Jamari</v>
       </c>
       <c r="B520" s="20"/>
-      <c r="C520" s="20" t="e">
+      <c r="C520" s="20" t="str">
         <f>'Grad Raw Data'!H261</f>
-        <v>#N/A</v>
+        <v>Wright</v>
       </c>
       <c r="D520" s="20"/>
       <c r="E520" s="20" t="str">
@@ -59512,7 +59618,7 @@
       </c>
       <c r="H57" s="31" t="str">
         <f>VLOOKUP(I57,'Names with Seat Code'!B:E,4)</f>
-        <v>Silva</v>
+        <v>Da Silva</v>
       </c>
       <c r="I57" s="25">
         <f>IF(B56+1&lt;DIRECTIONS!$E$24,B56+1,0)</f>

--- a/data/2026 GSMUD.xlsx
+++ b/data/2026 GSMUD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code Space\Git 2026 Grad\2026-Grad\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE55BCE-4D68-4DB9-925B-E4630921AD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027EB726-55DC-47FB-B98A-5253AC41FE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DIRECTIONS" sheetId="9" r:id="rId1"/>
@@ -476,9 +476,6 @@
   </si>
   <si>
     <t>Elsa Chow</t>
-  </si>
-  <si>
-    <t>Will Chite</t>
   </si>
   <si>
     <t>Max Cinelli</t>
@@ -1518,6 +1515,9 @@
   <si>
     <t>Uh-zra - the "Uh" part is slower than "zra" and roll the r. "Kud-reech" - roll the r</t>
   </si>
+  <si>
+    <t>Will Chute</t>
+  </si>
 </sst>
 </file>
 
@@ -1785,7 +1785,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1878,7 +1878,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2202,7 +2201,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -2210,7 +2209,7 @@
         <v>30</v>
       </c>
       <c r="O3" s="24" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -2221,7 +2220,7 @@
         <v>31</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -2232,7 +2231,7 @@
         <v>32</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -2240,7 +2239,7 @@
         <v>33</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -2248,7 +2247,7 @@
         <v>34</v>
       </c>
       <c r="O7" s="24" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -2259,7 +2258,7 @@
         <v>35</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -2267,7 +2266,7 @@
         <v>36</v>
       </c>
       <c r="O9" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -2275,7 +2274,7 @@
         <v>37</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -2283,7 +2282,7 @@
         <v>38</v>
       </c>
       <c r="O11" s="24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -2291,7 +2290,7 @@
         <v>39</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -2305,7 +2304,7 @@
         <v>40</v>
       </c>
       <c r="O13" s="24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -2319,7 +2318,7 @@
         <v>41</v>
       </c>
       <c r="O14" s="24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -2330,10 +2329,10 @@
         <v>10</v>
       </c>
       <c r="N15" s="24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
@@ -2344,10 +2343,10 @@
         <v>12</v>
       </c>
       <c r="N16" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="O16" s="24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
@@ -2358,10 +2357,10 @@
         <v>14</v>
       </c>
       <c r="N17" s="24" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="O17" s="24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
@@ -2372,7 +2371,7 @@
         <v>42</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
@@ -2449,7 +2448,7 @@
         <v>Abate</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
@@ -2501,7 +2500,7 @@
         <v>Abubakar</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2514,13 +2513,13 @@
         <v>Luis</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -2547,7 +2546,7 @@
         <v>Ahlert</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2568,7 +2567,7 @@
         <v>Aiello</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2610,7 +2609,7 @@
         <v>Amado</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2688,7 +2687,7 @@
         <v>Aquino</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2728,7 +2727,7 @@
         <v>Araujo</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2749,7 +2748,7 @@
         <v>Aretusi</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2827,7 +2826,7 @@
         <v>Batista</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2848,7 +2847,7 @@
         <v>Beaulieu</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2869,7 +2868,7 @@
         <v>Belfon</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2928,7 +2927,7 @@
         <v>Bhola</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2968,7 +2967,7 @@
         <v>Boucher</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3008,12 +3007,12 @@
         <v>Bowlin</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="45" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B30" s="41"/>
       <c r="C30" s="40" t="str">
@@ -3200,7 +3199,7 @@
         <v>Carcione</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3262,7 +3261,7 @@
     </row>
     <row r="43" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="41" t="s">
-        <v>135</v>
+        <v>481</v>
       </c>
       <c r="B43" s="41"/>
       <c r="C43" s="40" t="str">
@@ -3275,13 +3274,13 @@
       </c>
       <c r="E43" s="40" t="str">
         <f t="shared" si="5"/>
-        <v>Chite</v>
+        <v>Chute</v>
       </c>
       <c r="F43" s="41"/>
     </row>
     <row r="44" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B44" s="41"/>
       <c r="C44" s="40" t="str">
@@ -3300,7 +3299,7 @@
     </row>
     <row r="45" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="46" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B45" s="41"/>
       <c r="C45" s="40" t="str">
@@ -3316,12 +3315,12 @@
         <v>Cirrone</v>
       </c>
       <c r="F45" s="46" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B46" s="41"/>
       <c r="C46" s="40" t="str">
@@ -3340,7 +3339,7 @@
     </row>
     <row r="47" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B47" s="41"/>
       <c r="C47" s="40" t="str">
@@ -3359,7 +3358,7 @@
     </row>
     <row r="48" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B48" s="41"/>
       <c r="C48" s="40" t="str">
@@ -3378,7 +3377,7 @@
     </row>
     <row r="49" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B49" s="41"/>
       <c r="C49" s="40" t="str">
@@ -3397,7 +3396,7 @@
     </row>
     <row r="50" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B50" s="41"/>
       <c r="C50" s="40" t="str">
@@ -3413,12 +3412,12 @@
         <v>Comenos</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B51" s="41"/>
       <c r="C51" s="40" t="str">
@@ -3434,12 +3433,12 @@
         <v>Connelly</v>
       </c>
       <c r="F51" s="41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="45" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B52" s="41"/>
       <c r="C52" s="40" t="str">
@@ -3458,7 +3457,7 @@
     </row>
     <row r="53" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B53" s="41"/>
       <c r="C53" s="40" t="str">
@@ -3474,12 +3473,12 @@
         <v>Connor</v>
       </c>
       <c r="F53" s="46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B54" s="41"/>
       <c r="C54" s="40" t="str">
@@ -3498,7 +3497,7 @@
     </row>
     <row r="55" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="41" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B55" s="41"/>
       <c r="C55" s="40" t="str">
@@ -3517,7 +3516,7 @@
     </row>
     <row r="56" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="45" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B56" s="41"/>
       <c r="C56" s="40" t="str">
@@ -3536,7 +3535,7 @@
     </row>
     <row r="57" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B57" s="41"/>
       <c r="C57" s="40" t="str">
@@ -3555,7 +3554,7 @@
     </row>
     <row r="58" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="45" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B58" s="41"/>
       <c r="C58" s="40" t="str">
@@ -3574,7 +3573,7 @@
     </row>
     <row r="59" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="46" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B59" s="41"/>
       <c r="C59" s="40" t="str">
@@ -3593,7 +3592,7 @@
     </row>
     <row r="60" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B60" s="41"/>
       <c r="C60" s="40" t="str">
@@ -3612,7 +3611,7 @@
     </row>
     <row r="61" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="47" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B61" s="41"/>
       <c r="C61" s="40" t="str">
@@ -3631,7 +3630,7 @@
     </row>
     <row r="62" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="45" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B62" s="41"/>
       <c r="C62" s="40" t="str">
@@ -3640,15 +3639,15 @@
       </c>
       <c r="D62" s="40"/>
       <c r="E62" s="49" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F62" s="45" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B63" s="41"/>
       <c r="C63" s="40" t="str">
@@ -3667,7 +3666,7 @@
     </row>
     <row r="64" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B64" s="41"/>
       <c r="C64" s="40" t="str">
@@ -3683,12 +3682,12 @@
         <v>Dean</v>
       </c>
       <c r="F64" s="45" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="41" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B65" s="41"/>
       <c r="C65" s="40" t="str">
@@ -3704,12 +3703,12 @@
         <v>Deji</v>
       </c>
       <c r="F65" s="41" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B66" s="41"/>
       <c r="C66" s="40" t="str">
@@ -3728,7 +3727,7 @@
     </row>
     <row r="67" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B67" s="41"/>
       <c r="C67" s="40" t="str">
@@ -3744,7 +3743,7 @@
         <v>DiDonato</v>
       </c>
       <c r="F67" s="41" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3754,11 +3753,11 @@
       <c r="B68" s="41"/>
       <c r="C68" s="40" t="str">
         <f t="shared" si="3"/>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="D68" s="40" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="E68" s="40" t="str">
         <f t="shared" si="5"/>
@@ -3768,28 +3767,28 @@
     </row>
     <row r="69" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="41" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B69" s="41"/>
       <c r="C69" s="40" t="str">
         <f t="shared" ref="C69:C132" si="6">IF(ISERROR( FIND(",",TRIM(A69))),LEFT(TRIM(A69), FIND(" ",TRIM(A69))-1),MID(TRIM(A69),LEN(C69)+3,FIND(" ",TRIM(A69)&amp;" ",LEN(C69)+3)-LEN(C69)-2))</f>
-        <v>Antonio</v>
+        <v>Dante</v>
       </c>
       <c r="D69" s="40" t="str">
         <f t="shared" ref="D69:D132" si="7">IF(ISERROR(FIND(",",TRIM(A69))),IF(LEN(TRIM(A69))-LEN(SUBSTITUTE(TRIM(A69)," ",""))=2,MID(TRIM(A69),LEN(C69)+2,FIND(" ",TRIM(A69),LEN(C69)+2)-LEN(C69)-2),""),MID(TRIM(A69),3+LEN(C69)+LEN(E69),30))</f>
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="E69" s="40" t="str">
         <f t="shared" ref="E69:E132" si="8">IF(ISERROR(FIND(",",TRIM(A69))),MID(TRIM(A69),1+LEN(TRIM(A69))-LEN(SUBSTITUTE(TRIM(A69)," ",""))+LEN(C69)+LEN(D69),30),LEFT(TRIM(A69), FIND(",",TRIM(A69))-1))</f>
         <v>DiSerio</v>
       </c>
       <c r="F69" s="41" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B70" s="41"/>
       <c r="C70" s="40" t="str">
@@ -3805,12 +3804,12 @@
         <v>Donaghey</v>
       </c>
       <c r="F70" s="45" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B71" s="41"/>
       <c r="C71" s="40" t="str">
@@ -3829,7 +3828,7 @@
     </row>
     <row r="72" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B72" s="41"/>
       <c r="C72" s="40" t="str">
@@ -3837,18 +3836,18 @@
         <v>Alana</v>
       </c>
       <c r="D72" s="49" t="s">
+        <v>469</v>
+      </c>
+      <c r="E72" s="49" t="s">
         <v>470</v>
       </c>
-      <c r="E72" s="49" t="s">
-        <v>471</v>
-      </c>
       <c r="F72" s="46" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B73" s="41"/>
       <c r="C73" s="40" t="str">
@@ -3867,7 +3866,7 @@
     </row>
     <row r="74" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="46" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B74" s="41"/>
       <c r="C74" s="40" t="str">
@@ -3883,12 +3882,12 @@
         <v>DuRoss</v>
       </c>
       <c r="F74" s="46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="46" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B75" s="41"/>
       <c r="C75" s="40" t="str">
@@ -3907,7 +3906,7 @@
     </row>
     <row r="76" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B76" s="41"/>
       <c r="C76" s="40" t="str">
@@ -3926,7 +3925,7 @@
     </row>
     <row r="77" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B77" s="41"/>
       <c r="C77" s="40" t="str">
@@ -3945,7 +3944,7 @@
     </row>
     <row r="78" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="45" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B78" s="41"/>
       <c r="C78" s="40" t="str">
@@ -3964,7 +3963,7 @@
     </row>
     <row r="79" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B79" s="41"/>
       <c r="C79" s="40" t="str">
@@ -3983,7 +3982,7 @@
     </row>
     <row r="80" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="46" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B80" s="41"/>
       <c r="C80" s="40" t="str">
@@ -3999,12 +3998,12 @@
         <v>Encarnacao</v>
       </c>
       <c r="F80" s="46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B81" s="41"/>
       <c r="C81" s="40" t="str">
@@ -4020,12 +4019,12 @@
         <v>Ewald</v>
       </c>
       <c r="F81" s="46" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="45" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B82" s="41"/>
       <c r="C82" s="40" t="str">
@@ -4041,12 +4040,12 @@
         <v>Fantasia</v>
       </c>
       <c r="F82" s="45" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B83" s="41"/>
       <c r="C83" s="40" t="str">
@@ -4065,7 +4064,7 @@
     </row>
     <row r="84" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B84" s="41"/>
       <c r="C84" s="40" t="str">
@@ -4084,7 +4083,7 @@
     </row>
     <row r="85" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B85" s="41"/>
       <c r="C85" s="40" t="str">
@@ -4103,7 +4102,7 @@
     </row>
     <row r="86" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B86" s="41"/>
       <c r="C86" s="40" t="str">
@@ -4122,7 +4121,7 @@
     </row>
     <row r="87" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="41" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B87" s="41"/>
       <c r="C87" s="40" t="str">
@@ -4141,7 +4140,7 @@
     </row>
     <row r="88" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B88" s="41"/>
       <c r="C88" s="40" t="str">
@@ -4160,7 +4159,7 @@
     </row>
     <row r="89" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B89" s="41"/>
       <c r="C89" s="40" t="str">
@@ -4176,12 +4175,12 @@
         <v>Forse</v>
       </c>
       <c r="F89" s="46" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B90" s="41"/>
       <c r="C90" s="40" t="str">
@@ -4200,7 +4199,7 @@
     </row>
     <row r="91" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B91" s="41"/>
       <c r="C91" s="40" t="str">
@@ -4219,7 +4218,7 @@
     </row>
     <row r="92" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="45" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B92" s="41"/>
       <c r="C92" s="40" t="str">
@@ -4235,12 +4234,12 @@
         <v>Fucarile</v>
       </c>
       <c r="F92" s="45" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B93" s="41"/>
       <c r="C93" s="40" t="str">
@@ -4259,7 +4258,7 @@
     </row>
     <row r="94" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B94" s="41"/>
       <c r="C94" s="40" t="str">
@@ -4278,7 +4277,7 @@
     </row>
     <row r="95" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B95" s="41"/>
       <c r="C95" s="40" t="str">
@@ -4294,12 +4293,12 @@
         <v>Gager</v>
       </c>
       <c r="F95" s="41" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="45" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B96" s="41"/>
       <c r="C96" s="40" t="str">
@@ -4318,7 +4317,7 @@
     </row>
     <row r="97" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B97" s="41"/>
       <c r="C97" s="40" t="str">
@@ -4334,12 +4333,12 @@
         <v>Gallagher</v>
       </c>
       <c r="F97" s="41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A98" s="45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B98" s="41"/>
       <c r="C98" s="40" t="str">
@@ -4355,12 +4354,12 @@
         <v>Gauvin</v>
       </c>
       <c r="F98" s="45" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="41" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B99" s="41"/>
       <c r="C99" s="40" t="str">
@@ -4379,7 +4378,7 @@
     </row>
     <row r="100" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B100" s="41"/>
       <c r="C100" s="40" t="str">
@@ -4398,7 +4397,7 @@
     </row>
     <row r="101" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B101" s="41"/>
       <c r="C101" s="40" t="str">
@@ -4417,7 +4416,7 @@
     </row>
     <row r="102" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B102" s="41"/>
       <c r="C102" s="40" t="str">
@@ -4436,7 +4435,7 @@
     </row>
     <row r="103" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B103" s="41"/>
       <c r="C103" s="40" t="str">
@@ -4455,7 +4454,7 @@
     </row>
     <row r="104" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B104" s="41"/>
       <c r="C104" s="40" t="str">
@@ -4474,7 +4473,7 @@
     </row>
     <row r="105" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B105" s="41"/>
       <c r="C105" s="40" t="str">
@@ -4490,12 +4489,12 @@
         <v>Gorski</v>
       </c>
       <c r="F105" s="41" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="45" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B106" s="41"/>
       <c r="C106" s="40" t="str">
@@ -4511,12 +4510,12 @@
         <v>Gosdanian</v>
       </c>
       <c r="F106" s="45" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B107" s="41"/>
       <c r="C107" s="40" t="str">
@@ -4535,7 +4534,7 @@
     </row>
     <row r="108" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B108" s="41"/>
       <c r="C108" s="40" t="str">
@@ -4554,7 +4553,7 @@
     </row>
     <row r="109" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="41" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B109" s="41"/>
       <c r="C109" s="40" t="str">
@@ -4573,7 +4572,7 @@
     </row>
     <row r="110" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B110" s="41"/>
       <c r="C110" s="40" t="str">
@@ -4589,12 +4588,12 @@
         <v>Hall</v>
       </c>
       <c r="F110" s="45" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B111" s="41"/>
       <c r="C111" s="40" t="str">
@@ -4613,7 +4612,7 @@
     </row>
     <row r="112" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A112" s="45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B112" s="41"/>
       <c r="C112" s="40" t="str">
@@ -4632,7 +4631,7 @@
     </row>
     <row r="113" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A113" s="47" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B113" s="41"/>
       <c r="C113" s="40" t="str">
@@ -4651,7 +4650,7 @@
     </row>
     <row r="114" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A114" s="45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B114" s="41"/>
       <c r="C114" s="40" t="str">
@@ -4670,7 +4669,7 @@
     </row>
     <row r="115" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="46" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B115" s="41"/>
       <c r="C115" s="40" t="str">
@@ -4689,7 +4688,7 @@
     </row>
     <row r="116" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="46" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B116" s="41"/>
       <c r="C116" s="40" t="str">
@@ -4705,12 +4704,12 @@
         <v>Henri</v>
       </c>
       <c r="F116" s="46" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="41" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B117" s="41"/>
       <c r="C117" s="40" t="str">
@@ -4729,7 +4728,7 @@
     </row>
     <row r="118" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="46" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B118" s="41"/>
       <c r="C118" s="40" t="str">
@@ -4748,7 +4747,7 @@
     </row>
     <row r="119" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B119" s="41"/>
       <c r="C119" s="40" t="str">
@@ -4764,12 +4763,12 @@
         <v>Hobson</v>
       </c>
       <c r="F119" s="41" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="45" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B120" s="41"/>
       <c r="C120" s="40" t="str">
@@ -4788,7 +4787,7 @@
     </row>
     <row r="121" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A121" s="46" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B121" s="41"/>
       <c r="C121" s="40" t="str">
@@ -4804,12 +4803,12 @@
         <v>Houle</v>
       </c>
       <c r="F121" s="46" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A122" s="45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B122" s="41"/>
       <c r="C122" s="40" t="str">
@@ -4828,7 +4827,7 @@
     </row>
     <row r="123" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B123" s="41"/>
       <c r="C123" s="40" t="str">
@@ -4844,12 +4843,12 @@
         <v>Iosua</v>
       </c>
       <c r="F123" s="41" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="46" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B124" s="41"/>
       <c r="C124" s="40" t="str">
@@ -4868,7 +4867,7 @@
     </row>
     <row r="125" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="41" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B125" s="41"/>
       <c r="C125" s="40" t="str">
@@ -4887,7 +4886,7 @@
     </row>
     <row r="126" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="45" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B126" s="41"/>
       <c r="C126" s="40" t="str">
@@ -4906,7 +4905,7 @@
     </row>
     <row r="127" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B127" s="41"/>
       <c r="C127" s="40" t="str">
@@ -4925,7 +4924,7 @@
     </row>
     <row r="128" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B128" s="41"/>
       <c r="C128" s="40" t="str">
@@ -4944,7 +4943,7 @@
     </row>
     <row r="129" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B129" s="41"/>
       <c r="C129" s="40" t="str">
@@ -4963,7 +4962,7 @@
     </row>
     <row r="130" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="46" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B130" s="41"/>
       <c r="C130" s="40" t="str">
@@ -4982,7 +4981,7 @@
     </row>
     <row r="131" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B131" s="41"/>
       <c r="C131" s="40" t="str">
@@ -5001,7 +5000,7 @@
     </row>
     <row r="132" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B132" s="41"/>
       <c r="C132" s="40" t="str">
@@ -5017,12 +5016,12 @@
         <v>Kaberle</v>
       </c>
       <c r="F132" s="46" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="46" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B133" s="41"/>
       <c r="C133" s="40" t="str">
@@ -5038,12 +5037,12 @@
         <v>Kadric</v>
       </c>
       <c r="F133" s="46" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A134" s="45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B134" s="41"/>
       <c r="C134" s="40" t="str">
@@ -5059,12 +5058,12 @@
         <v>Keaveney</v>
       </c>
       <c r="F134" s="45" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A135" s="46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B135" s="41"/>
       <c r="C135" s="40" t="str">
@@ -5080,12 +5079,12 @@
         <v>Kenton</v>
       </c>
       <c r="F135" s="46" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A136" s="46" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B136" s="41"/>
       <c r="C136" s="40" t="str">
@@ -5101,12 +5100,12 @@
         <v>Kiley</v>
       </c>
       <c r="F136" s="46" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A137" s="41" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B137" s="41"/>
       <c r="C137" s="40" t="str">
@@ -5125,7 +5124,7 @@
     </row>
     <row r="138" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A138" s="45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B138" s="41"/>
       <c r="C138" s="40" t="str">
@@ -5144,7 +5143,7 @@
     </row>
     <row r="139" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A139" s="41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B139" s="41"/>
       <c r="C139" s="40" t="str">
@@ -5160,12 +5159,12 @@
         <v>Lalicata</v>
       </c>
       <c r="F139" s="41" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A140" s="45" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B140" s="41"/>
       <c r="C140" s="40" t="str">
@@ -5181,12 +5180,12 @@
         <v>Laurino</v>
       </c>
       <c r="F140" s="45" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A141" s="41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B141" s="41"/>
       <c r="C141" s="40" t="str">
@@ -5205,7 +5204,7 @@
     </row>
     <row r="142" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A142" s="45" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B142" s="41"/>
       <c r="C142" s="40" t="str">
@@ -5221,12 +5220,12 @@
         <v>Layne</v>
       </c>
       <c r="F142" s="45" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A143" s="41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B143" s="41"/>
       <c r="C143" s="40" t="str">
@@ -5245,7 +5244,7 @@
     </row>
     <row r="144" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A144" s="45" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B144" s="41"/>
       <c r="C144" s="40" t="str">
@@ -5264,7 +5263,7 @@
     </row>
     <row r="145" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A145" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B145" s="41"/>
       <c r="C145" s="40" t="str">
@@ -5283,7 +5282,7 @@
     </row>
     <row r="146" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A146" s="45" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B146" s="41"/>
       <c r="C146" s="40" t="str">
@@ -5302,7 +5301,7 @@
     </row>
     <row r="147" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A147" s="41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B147" s="41"/>
       <c r="C147" s="40" t="str">
@@ -5321,7 +5320,7 @@
     </row>
     <row r="148" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A148" s="45" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B148" s="41"/>
       <c r="C148" s="40" t="str">
@@ -5340,7 +5339,7 @@
     </row>
     <row r="149" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A149" s="46" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B149" s="41"/>
       <c r="C149" s="40" t="str">
@@ -5356,12 +5355,12 @@
         <v>Lizotte</v>
       </c>
       <c r="F149" s="46" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A150" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B150" s="41"/>
       <c r="C150" s="40" t="str">
@@ -5377,12 +5376,12 @@
         <v>Lusk</v>
       </c>
       <c r="F150" s="46" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A151" s="46" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B151" s="41"/>
       <c r="C151" s="40" t="str">
@@ -5401,7 +5400,7 @@
     </row>
     <row r="152" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A152" s="45" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B152" s="41"/>
       <c r="C152" s="40" t="str">
@@ -5417,12 +5416,12 @@
         <v>Maganzini</v>
       </c>
       <c r="F152" s="45" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A153" s="41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B153" s="41"/>
       <c r="C153" s="40" t="str">
@@ -5441,7 +5440,7 @@
     </row>
     <row r="154" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A154" s="45" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B154" s="41"/>
       <c r="C154" s="40" t="str">
@@ -5460,7 +5459,7 @@
     </row>
     <row r="155" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A155" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B155" s="41"/>
       <c r="C155" s="40" t="str">
@@ -5476,12 +5475,12 @@
         <v>Maness</v>
       </c>
       <c r="F155" s="41" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A156" s="45" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B156" s="41"/>
       <c r="C156" s="40" t="str">
@@ -5500,7 +5499,7 @@
     </row>
     <row r="157" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A157" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B157" s="41"/>
       <c r="C157" s="40" t="str">
@@ -5519,7 +5518,7 @@
     </row>
     <row r="158" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A158" s="46" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B158" s="41"/>
       <c r="C158" s="40" t="str">
@@ -5535,12 +5534,12 @@
         <v>Marchlik</v>
       </c>
       <c r="F158" s="46" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A159" s="41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B159" s="41"/>
       <c r="C159" s="40" t="e">
@@ -5556,12 +5555,12 @@
         <v>#VALUE!</v>
       </c>
       <c r="F159" s="41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A160" s="46" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B160" s="41"/>
       <c r="C160" s="40" t="str">
@@ -5580,7 +5579,7 @@
     </row>
     <row r="161" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A161" s="47" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B161" s="41"/>
       <c r="C161" s="40" t="str">
@@ -5599,7 +5598,7 @@
     </row>
     <row r="162" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A162" s="48" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B162" s="41"/>
       <c r="C162" s="40" t="str">
@@ -5618,7 +5617,7 @@
     </row>
     <row r="163" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A163" s="46" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B163" s="41"/>
       <c r="C163" s="40" t="str">
@@ -5637,7 +5636,7 @@
     </row>
     <row r="164" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A164" s="46" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B164" s="41"/>
       <c r="C164" s="40" t="str">
@@ -5656,7 +5655,7 @@
     </row>
     <row r="165" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A165" s="46" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B165" s="41"/>
       <c r="C165" s="40" t="str">
@@ -5675,7 +5674,7 @@
     </row>
     <row r="166" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A166" s="45" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B166" s="41"/>
       <c r="C166" s="40" t="str">
@@ -5694,7 +5693,7 @@
     </row>
     <row r="167" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A167" s="41" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B167" s="41"/>
       <c r="C167" s="40" t="str">
@@ -5710,12 +5709,12 @@
         <v>McLaughlin-Shostak</v>
       </c>
       <c r="F167" s="41" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A168" s="45" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B168" s="41"/>
       <c r="C168" s="40" t="str">
@@ -5731,12 +5730,12 @@
         <v>McMenimen</v>
       </c>
       <c r="F168" s="45" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A169" s="41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B169" s="41"/>
       <c r="C169" s="40" t="str">
@@ -5755,7 +5754,7 @@
     </row>
     <row r="170" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A170" s="46" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B170" s="41"/>
       <c r="C170" s="40" t="str">
@@ -5774,7 +5773,7 @@
     </row>
     <row r="171" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A171" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B171" s="41"/>
       <c r="C171" s="40" t="str">
@@ -5793,7 +5792,7 @@
     </row>
     <row r="172" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A172" s="46" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B172" s="41"/>
       <c r="C172" s="40" t="str">
@@ -5809,12 +5808,12 @@
         <v>Miceli</v>
       </c>
       <c r="F172" s="46" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A173" s="41" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B173" s="41"/>
       <c r="C173" s="40" t="str">
@@ -5833,7 +5832,7 @@
     </row>
     <row r="174" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A174" s="48" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B174" s="41"/>
       <c r="C174" s="40" t="str">
@@ -5852,7 +5851,7 @@
     </row>
     <row r="175" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A175" s="41" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B175" s="41"/>
       <c r="C175" s="40" t="str">
@@ -5868,12 +5867,12 @@
         <v>Moller</v>
       </c>
       <c r="F175" s="41" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A176" s="45" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B176" s="41"/>
       <c r="C176" s="40" t="str">
@@ -5889,12 +5888,12 @@
         <v>Moreira</v>
       </c>
       <c r="F176" s="45" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A177" s="41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B177" s="41"/>
       <c r="C177" s="40" t="str">
@@ -5913,7 +5912,7 @@
     </row>
     <row r="178" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A178" s="45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B178" s="41"/>
       <c r="C178" s="40" t="str">
@@ -5932,7 +5931,7 @@
     </row>
     <row r="179" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A179" s="41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B179" s="41"/>
       <c r="C179" s="40" t="str">
@@ -5951,7 +5950,7 @@
     </row>
     <row r="180" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A180" s="45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B180" s="41"/>
       <c r="C180" s="40" t="str">
@@ -5967,12 +5966,12 @@
         <v>Muller</v>
       </c>
       <c r="F180" s="45" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A181" s="46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B181" s="41"/>
       <c r="C181" s="40" t="str">
@@ -5988,7 +5987,7 @@
         <v>Mullin</v>
       </c>
       <c r="F181" s="46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6012,7 +6011,7 @@
     </row>
     <row r="183" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A183" s="46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B183" s="41"/>
       <c r="C183" s="40" t="str">
@@ -6031,7 +6030,7 @@
     </row>
     <row r="184" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A184" s="46" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B184" s="41"/>
       <c r="C184" s="40" t="str">
@@ -6050,7 +6049,7 @@
     </row>
     <row r="185" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A185" s="41" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B185" s="41"/>
       <c r="C185" s="40" t="str">
@@ -6066,12 +6065,12 @@
         <v>Nguyen</v>
       </c>
       <c r="F185" s="41" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A186" s="46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B186" s="41"/>
       <c r="C186" s="40" t="str">
@@ -6090,7 +6089,7 @@
     </row>
     <row r="187" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A187" s="41" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B187" s="41"/>
       <c r="C187" s="40" t="str">
@@ -6106,12 +6105,12 @@
         <v>Norris</v>
       </c>
       <c r="F187" s="41" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A188" s="45" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B188" s="41"/>
       <c r="C188" s="40" t="str">
@@ -6130,7 +6129,7 @@
     </row>
     <row r="189" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A189" s="41" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B189" s="41"/>
       <c r="C189" s="40" t="str">
@@ -6146,12 +6145,12 @@
         <v>Ortins</v>
       </c>
       <c r="F189" s="41" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A190" s="45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B190" s="41"/>
       <c r="C190" s="40" t="str">
@@ -6167,12 +6166,12 @@
         <v>Ortiz</v>
       </c>
       <c r="F190" s="45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A191" s="46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B191" s="41"/>
       <c r="C191" s="40" t="str">
@@ -6191,7 +6190,7 @@
     </row>
     <row r="192" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A192" s="46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B192" s="41"/>
       <c r="C192" s="40" t="str">
@@ -6207,12 +6206,12 @@
         <v>Patel</v>
       </c>
       <c r="F192" s="46" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A193" s="41" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B193" s="41"/>
       <c r="C193" s="40" t="str">
@@ -6231,7 +6230,7 @@
     </row>
     <row r="194" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A194" s="45" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B194" s="41"/>
       <c r="C194" s="40" t="str">
@@ -6247,12 +6246,12 @@
         <v>Petrin</v>
       </c>
       <c r="F194" s="45" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A195" s="41" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B195" s="41"/>
       <c r="C195" s="40" t="str">
@@ -6271,7 +6270,7 @@
     </row>
     <row r="196" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A196" s="48" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B196" s="41"/>
       <c r="C196" s="40" t="str">
@@ -6290,7 +6289,7 @@
     </row>
     <row r="197" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A197" s="46" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B197" s="41"/>
       <c r="C197" s="40" t="str">
@@ -6306,12 +6305,12 @@
         <v>Pomerantz</v>
       </c>
       <c r="F197" s="46" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A198" s="45" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B198" s="41"/>
       <c r="C198" s="40" t="str">
@@ -6327,12 +6326,12 @@
         <v>Poudyal</v>
       </c>
       <c r="F198" s="45" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A199" s="46" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B199" s="41"/>
       <c r="C199" s="40" t="str">
@@ -6348,12 +6347,12 @@
         <v>Pulpi</v>
       </c>
       <c r="F199" s="46" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A200" s="46" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B200" s="41"/>
       <c r="C200" s="40" t="str">
@@ -6369,12 +6368,12 @@
         <v>Rai</v>
       </c>
       <c r="F200" s="46" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A201" s="46" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B201" s="41"/>
       <c r="C201" s="40" t="str">
@@ -6393,7 +6392,7 @@
     </row>
     <row r="202" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A202" s="46" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B202" s="41"/>
       <c r="C202" s="40" t="str">
@@ -6412,7 +6411,7 @@
     </row>
     <row r="203" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A203" s="46" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B203" s="41"/>
       <c r="C203" s="40" t="str">
@@ -6431,7 +6430,7 @@
     </row>
     <row r="204" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A204" s="46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B204" s="41"/>
       <c r="C204" s="40" t="str">
@@ -6447,12 +6446,12 @@
         <v>Richter</v>
       </c>
       <c r="F204" s="46" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A205" s="46" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B205" s="41"/>
       <c r="C205" s="40" t="str">
@@ -6468,12 +6467,12 @@
         <v>Robichaud</v>
       </c>
       <c r="F205" s="46" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A206" s="45" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B206" s="41"/>
       <c r="C206" s="40" t="str">
@@ -6492,7 +6491,7 @@
     </row>
     <row r="207" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A207" s="41" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B207" s="41"/>
       <c r="C207" s="40" t="str">
@@ -6511,7 +6510,7 @@
     </row>
     <row r="208" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A208" s="46" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B208" s="41"/>
       <c r="C208" s="40" t="str">
@@ -6530,7 +6529,7 @@
     </row>
     <row r="209" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A209" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B209" s="41"/>
       <c r="C209" s="40" t="str">
@@ -6549,7 +6548,7 @@
     </row>
     <row r="210" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A210" s="45" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B210" s="41"/>
       <c r="C210" s="40" t="str">
@@ -6568,7 +6567,7 @@
     </row>
     <row r="211" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A211" s="41" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B211" s="41"/>
       <c r="C211" s="40" t="str">
@@ -6584,12 +6583,12 @@
         <v>Rojas</v>
       </c>
       <c r="F211" s="41" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A212" s="46" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B212" s="41"/>
       <c r="C212" s="40" t="str">
@@ -6608,7 +6607,7 @@
     </row>
     <row r="213" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A213" s="41" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B213" s="41"/>
       <c r="C213" s="40" t="str">
@@ -6624,12 +6623,12 @@
         <v>Ryland</v>
       </c>
       <c r="F213" s="41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A214" s="45" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B214" s="41"/>
       <c r="C214" s="40" t="str">
@@ -6645,12 +6644,12 @@
         <v>Sardinha</v>
       </c>
       <c r="F214" s="45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A215" s="41" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B215" s="41"/>
       <c r="C215" s="40" t="str">
@@ -6666,12 +6665,12 @@
         <v>Sarre</v>
       </c>
       <c r="F215" s="41" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A216" s="46" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B216" s="41"/>
       <c r="C216" s="40" t="str">
@@ -6690,7 +6689,7 @@
     </row>
     <row r="217" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A217" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B217" s="41"/>
       <c r="C217" s="40" t="str">
@@ -6709,7 +6708,7 @@
     </row>
     <row r="218" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A218" s="45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B218" s="41"/>
       <c r="C218" s="40" t="str">
@@ -6725,12 +6724,12 @@
         <v>Schrager</v>
       </c>
       <c r="F218" s="45" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A219" s="41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B219" s="41"/>
       <c r="C219" s="40" t="str">
@@ -6749,7 +6748,7 @@
     </row>
     <row r="220" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A220" s="45" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B220" s="41"/>
       <c r="C220" s="40" t="str">
@@ -6768,7 +6767,7 @@
     </row>
     <row r="221" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A221" s="46" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B221" s="41"/>
       <c r="C221" s="40" t="str">
@@ -6784,12 +6783,12 @@
         <v>Selvakumar</v>
       </c>
       <c r="F221" s="46" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A222" s="45" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B222" s="41"/>
       <c r="C222" s="40" t="str">
@@ -6808,7 +6807,7 @@
     </row>
     <row r="223" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A223" s="46" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B223" s="41"/>
       <c r="C223" s="40" t="str">
@@ -6827,7 +6826,7 @@
     </row>
     <row r="224" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A224" s="45" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B224" s="41"/>
       <c r="C224" s="40" t="str">
@@ -6843,12 +6842,12 @@
         <v>Shediac</v>
       </c>
       <c r="F224" s="45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A225" s="41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B225" s="41"/>
       <c r="C225" s="40" t="str">
@@ -6867,7 +6866,7 @@
     </row>
     <row r="226" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A226" s="45" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B226" s="41"/>
       <c r="C226" s="40" t="str">
@@ -6883,12 +6882,12 @@
         <v>Siciliano</v>
       </c>
       <c r="F226" s="45" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A227" s="46" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B227" s="41"/>
       <c r="C227" s="40" t="str">
@@ -6907,7 +6906,7 @@
     </row>
     <row r="228" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A228" s="46" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B228" s="41"/>
       <c r="C228" s="40" t="str">
@@ -6923,12 +6922,12 @@
         <v>Skenderian</v>
       </c>
       <c r="F228" s="46" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A229" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B229" s="41"/>
       <c r="C229" s="40" t="str">
@@ -6944,12 +6943,12 @@
         <v>Slinn</v>
       </c>
       <c r="F229" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A230" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B230" s="41"/>
       <c r="C230" s="40" t="str">
@@ -6968,7 +6967,7 @@
     </row>
     <row r="231" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A231" s="41" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B231" s="41"/>
       <c r="C231" s="40" t="str">
@@ -6987,7 +6986,7 @@
     </row>
     <row r="232" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A232" s="45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B232" s="41"/>
       <c r="C232" s="40" t="str">
@@ -7003,12 +7002,12 @@
         <v>Soto</v>
       </c>
       <c r="F232" s="45" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A233" s="41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B233" s="41"/>
       <c r="C233" s="40" t="str">
@@ -7027,7 +7026,7 @@
     </row>
     <row r="234" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A234" s="45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B234" s="41"/>
       <c r="C234" s="40" t="str">
@@ -7046,7 +7045,7 @@
     </row>
     <row r="235" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A235" s="41" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B235" s="41"/>
       <c r="C235" s="40" t="str">
@@ -7065,7 +7064,7 @@
     </row>
     <row r="236" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A236" s="46" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B236" s="41"/>
       <c r="C236" s="40" t="str">
@@ -7081,12 +7080,12 @@
         <v>Staffier</v>
       </c>
       <c r="F236" s="46" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A237" s="46" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B237" s="41"/>
       <c r="C237" s="40" t="str">
@@ -7102,12 +7101,12 @@
         <v>Stathoulopoulos</v>
       </c>
       <c r="F237" s="46" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A238" s="45" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B238" s="41"/>
       <c r="C238" s="40" t="str">
@@ -7126,7 +7125,7 @@
     </row>
     <row r="239" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A239" s="41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B239" s="41"/>
       <c r="C239" s="40" t="str">
@@ -7142,12 +7141,12 @@
         <v>Sullivan</v>
       </c>
       <c r="F239" s="41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A240" s="46" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B240" s="41"/>
       <c r="C240" s="40" t="str">
@@ -7166,7 +7165,7 @@
     </row>
     <row r="241" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A241" s="41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B241" s="41"/>
       <c r="C241" s="40" t="str">
@@ -7185,7 +7184,7 @@
     </row>
     <row r="242" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A242" s="45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B242" s="41"/>
       <c r="C242" s="40" t="str">
@@ -7201,12 +7200,12 @@
         <v>Taubman</v>
       </c>
       <c r="F242" s="45" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A243" s="41" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B243" s="41"/>
       <c r="C243" s="40" t="str">
@@ -7222,12 +7221,12 @@
         <v>Tawadros</v>
       </c>
       <c r="F243" s="41" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A244" s="45" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B244" s="41"/>
       <c r="C244" s="40" t="str">
@@ -7243,12 +7242,12 @@
         <v>Toomey</v>
       </c>
       <c r="F244" s="45" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="245" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A245" s="41" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B245" s="41"/>
       <c r="C245" s="40" t="str">
@@ -7267,7 +7266,7 @@
     </row>
     <row r="246" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A246" s="45" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B246" s="41"/>
       <c r="C246" s="40" t="str">
@@ -7283,12 +7282,12 @@
         <v>Travassos</v>
       </c>
       <c r="F246" s="45" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A247" s="46" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B247" s="41"/>
       <c r="C247" s="40" t="str">
@@ -7304,12 +7303,12 @@
         <v>Upton</v>
       </c>
       <c r="F247" s="46" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A248" s="45" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B248" s="41"/>
       <c r="C248" s="40" t="str">
@@ -7328,7 +7327,7 @@
     </row>
     <row r="249" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A249" s="41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B249" s="41"/>
       <c r="C249" s="40" t="str">
@@ -7337,13 +7336,13 @@
       </c>
       <c r="D249" s="40"/>
       <c r="E249" s="49" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F249" s="41"/>
     </row>
     <row r="250" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A250" s="45" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B250" s="41"/>
       <c r="C250" s="40" t="str">
@@ -7351,16 +7350,16 @@
         <v>Katherine</v>
       </c>
       <c r="D250" s="49" t="s">
+        <v>467</v>
+      </c>
+      <c r="E250" s="49" t="s">
         <v>468</v>
-      </c>
-      <c r="E250" s="49" t="s">
-        <v>469</v>
       </c>
       <c r="F250" s="45"/>
     </row>
     <row r="251" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A251" s="41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B251" s="41"/>
       <c r="C251" s="40" t="str">
@@ -7379,7 +7378,7 @@
     </row>
     <row r="252" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A252" s="45" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B252" s="41"/>
       <c r="C252" s="40" t="str">
@@ -7395,12 +7394,12 @@
         <v>Viliott</v>
       </c>
       <c r="F252" s="45" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A253" s="46" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B253" s="41"/>
       <c r="C253" s="40" t="str">
@@ -7416,12 +7415,12 @@
         <v>Vitarisi</v>
       </c>
       <c r="F253" s="46" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A254" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B254" s="41"/>
       <c r="C254" s="40" t="str">
@@ -7440,7 +7439,7 @@
     </row>
     <row r="255" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A255" s="46" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B255" s="41"/>
       <c r="C255" s="40" t="str">
@@ -7459,7 +7458,7 @@
     </row>
     <row r="256" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A256" s="45" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B256" s="41"/>
       <c r="C256" s="40" t="str">
@@ -7478,7 +7477,7 @@
     </row>
     <row r="257" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A257" s="46" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B257" s="41"/>
       <c r="C257" s="40" t="str">
@@ -7497,7 +7496,7 @@
     </row>
     <row r="258" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A258" s="45" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B258" s="41"/>
       <c r="C258" s="40" t="str">
@@ -7516,7 +7515,7 @@
     </row>
     <row r="259" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A259" s="46" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B259" s="41"/>
       <c r="C259" s="40" t="str">
@@ -7535,7 +7534,7 @@
     </row>
     <row r="260" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A260" s="45" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B260" s="41"/>
       <c r="C260" s="40" t="str">
@@ -7554,7 +7553,7 @@
     </row>
     <row r="261" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A261" s="41" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B261" s="41"/>
       <c r="C261" s="40" t="str">
@@ -7573,7 +7572,7 @@
     </row>
     <row r="262" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A262" s="45" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B262" s="41"/>
       <c r="C262" s="40" t="str">
@@ -7592,7 +7591,7 @@
     </row>
     <row r="263" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A263" s="41" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B263" s="41"/>
       <c r="C263" s="40" t="str">
@@ -7608,12 +7607,12 @@
         <v>Williams</v>
       </c>
       <c r="F263" s="41" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="264" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A264" s="45" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B264" s="41"/>
       <c r="C264" s="40" t="str">
@@ -7632,7 +7631,7 @@
     </row>
     <row r="265" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A265" s="41" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C265" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7650,7 +7649,7 @@
     </row>
     <row r="266" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A266" s="45" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C266" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7668,7 +7667,7 @@
     </row>
     <row r="267" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A267" s="41" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C267" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7686,7 +7685,7 @@
     </row>
     <row r="268" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A268" s="45" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C268" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7701,12 +7700,12 @@
         <v>Zani</v>
       </c>
       <c r="F268" s="45" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="269" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A269" s="41" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C269" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7721,7 +7720,7 @@
         <v>Zheng</v>
       </c>
       <c r="F269" s="41" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.2">
@@ -7798,7 +7797,7 @@
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="L2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -7829,7 +7828,7 @@
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="L3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -7860,7 +7859,7 @@
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="L4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -7891,7 +7890,7 @@
       <c r="H5" s="42"/>
       <c r="I5" s="42"/>
       <c r="L5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -7950,7 +7949,7 @@
       <c r="H7" s="42"/>
       <c r="I7" s="42"/>
       <c r="L7" s="22" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -7984,7 +7983,7 @@
         <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -8018,7 +8017,7 @@
         <v>87</v>
       </c>
       <c r="M9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -8052,7 +8051,7 @@
         <v>31</v>
       </c>
       <c r="M10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -8086,7 +8085,7 @@
         <v>32</v>
       </c>
       <c r="M11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -8120,7 +8119,7 @@
         <v>33</v>
       </c>
       <c r="M12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -8154,7 +8153,7 @@
         <v>34</v>
       </c>
       <c r="M13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -8188,7 +8187,7 @@
         <v>35</v>
       </c>
       <c r="M14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -8222,7 +8221,7 @@
         <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -8256,7 +8255,7 @@
         <v>37</v>
       </c>
       <c r="M16" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -8290,7 +8289,7 @@
         <v>38</v>
       </c>
       <c r="M17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -8324,7 +8323,7 @@
         <v>39</v>
       </c>
       <c r="M18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -8358,7 +8357,7 @@
         <v>40</v>
       </c>
       <c r="M19" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -8392,7 +8391,7 @@
         <v>41</v>
       </c>
       <c r="M20" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -8423,10 +8422,10 @@
       <c r="H21" s="42"/>
       <c r="I21" s="42"/>
       <c r="L21" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -8457,10 +8456,10 @@
       <c r="H22" s="42"/>
       <c r="I22" s="42"/>
       <c r="L22" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M22" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -8491,10 +8490,10 @@
       <c r="H23" s="42"/>
       <c r="I23" s="42"/>
       <c r="L23" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M23" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -8528,7 +8527,7 @@
         <v>42</v>
       </c>
       <c r="M24" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -9044,7 +9043,7 @@
       </c>
       <c r="E43" s="39" t="str">
         <f>'Raw Name Splitter'!E43</f>
-        <v>Chite</v>
+        <v>Chute</v>
       </c>
       <c r="F43" s="39">
         <f>'Raw Name Splitter'!F43</f>
@@ -9730,11 +9729,11 @@
       </c>
       <c r="C68" s="39" t="str">
         <f>'Raw Name Splitter'!C68</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="D68" s="39" t="str">
         <f>'Raw Name Splitter'!D68</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="E68" s="39" t="str">
         <f>'Raw Name Splitter'!E68</f>
@@ -9758,11 +9757,11 @@
       </c>
       <c r="C69" s="39" t="str">
         <f>'Raw Name Splitter'!C69</f>
-        <v>Antonio</v>
+        <v>Dante</v>
       </c>
       <c r="D69" s="39" t="str">
         <f>'Raw Name Splitter'!D69</f>
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="E69" s="39" t="str">
         <f>'Raw Name Splitter'!E69</f>
@@ -10099,7 +10098,7 @@
         <v/>
       </c>
       <c r="E81" s="39" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F81" s="39" t="str">
         <f>'Raw Name Splitter'!F81</f>
@@ -14772,7 +14771,7 @@
         <v>Colby</v>
       </c>
       <c r="E249" s="39" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F249" s="39">
         <f>'Raw Name Splitter'!F249</f>
@@ -15335,13 +15334,13 @@
         <v>87</v>
       </c>
       <c r="C270" s="39" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E270" s="39" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F270" s="39" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -17557,7 +17556,7 @@
       </c>
       <c r="H52" s="1" t="str">
         <f>VLOOKUP(J52,'Names with Seat Code'!A:E,5,FALSE)</f>
-        <v>Chite</v>
+        <v>Chute</v>
       </c>
       <c r="I52" s="1" t="str">
         <f>VLOOKUP(J52,'Names with Seat Code'!A:E,3,FALSE)</f>
@@ -18507,14 +18506,14 @@
       </c>
       <c r="I74" s="1" t="str">
         <f>VLOOKUP(J74,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="J74" s="3">
         <v>61</v>
       </c>
       <c r="K74" t="str">
         <f>VLOOKUP(J74,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="L74" s="1">
         <f>VLOOKUP(J74,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -18550,14 +18549,14 @@
       </c>
       <c r="I75" s="1" t="str">
         <f>VLOOKUP(J75,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Antonio</v>
+        <v>Dante</v>
       </c>
       <c r="J75">
         <v>62</v>
       </c>
       <c r="K75" t="str">
         <f>VLOOKUP(J75,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="L75" s="1" t="str">
         <f>VLOOKUP(J75,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -29638,7 +29637,7 @@
       </c>
       <c r="I52" s="6" t="str">
         <f>'Grad Raw Data'!H52</f>
-        <v>Chite</v>
+        <v>Chute</v>
       </c>
       <c r="J52" s="6">
         <f>'Grad Raw Data'!G52</f>
@@ -30426,7 +30425,7 @@
       </c>
       <c r="H74" s="6" t="str">
         <f>'Grad Raw Data'!I74</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="I74" s="6" t="str">
         <f>'Grad Raw Data'!H74</f>
@@ -30462,7 +30461,7 @@
       </c>
       <c r="H75" s="6" t="str">
         <f>'Grad Raw Data'!I75</f>
-        <v>Antonio</v>
+        <v>Dante</v>
       </c>
       <c r="I75" s="6" t="str">
         <f>'Grad Raw Data'!H75</f>
@@ -39875,7 +39874,7 @@
       </c>
       <c r="C102" s="20" t="str">
         <f>'Grad Raw Data'!H52</f>
-        <v>Chite</v>
+        <v>Chute</v>
       </c>
       <c r="D102" s="44" t="str">
         <f>'Grad Raw Data'!D52</f>
@@ -40835,11 +40834,11 @@
     <row r="146" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="20" t="str">
         <f>'Grad Raw Data'!I74</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="B146" s="20" t="str">
         <f>'Grad Raw Data'!K74</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="C146" s="20" t="str">
         <f>'Grad Raw Data'!H74</f>
@@ -40879,11 +40878,11 @@
     <row r="148" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="20" t="str">
         <f>'Grad Raw Data'!I75</f>
-        <v>Antonio</v>
+        <v>Dante</v>
       </c>
       <c r="B148" s="20" t="str">
         <f>'Grad Raw Data'!K75</f>
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="C148" s="20" t="str">
         <f>'Grad Raw Data'!H75</f>
@@ -49101,7 +49100,7 @@
         <f>'Grad Raw Data'!I264</f>
         <v>Jiayu</v>
       </c>
-      <c r="B526" s="52"/>
+      <c r="B526" s="20"/>
       <c r="C526" s="20" t="str">
         <f>'Grad Raw Data'!H264</f>
         <v>Zheng</v>
@@ -49125,7 +49124,7 @@
     </row>
     <row r="528" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A528" s="51" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B528" s="50"/>
       <c r="C528" s="20"/>
@@ -50754,7 +50753,7 @@
       </c>
       <c r="C102" s="20" t="str">
         <f>'Grad Raw Data'!H52</f>
-        <v>Chite</v>
+        <v>Chute</v>
       </c>
       <c r="D102" s="20"/>
       <c r="E102" s="20" t="str">
@@ -51428,11 +51427,11 @@
     <row r="146" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="20" t="str">
         <f>'Grad Raw Data'!I74</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="B146" s="20" t="str">
         <f>'Grad Raw Data'!K74</f>
-        <v/>
+        <v>Joseph</v>
       </c>
       <c r="C146" s="20" t="str">
         <f>'Grad Raw Data'!H74</f>
@@ -51459,11 +51458,11 @@
     <row r="148" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="20" t="str">
         <f>'Grad Raw Data'!I75</f>
-        <v>Antonio</v>
+        <v>Dante</v>
       </c>
       <c r="B148" s="20" t="str">
         <f>'Grad Raw Data'!K75</f>
-        <v>Joseph</v>
+        <v/>
       </c>
       <c r="C148" s="20" t="str">
         <f>'Grad Raw Data'!H75</f>
@@ -59074,7 +59073,7 @@
       </c>
       <c r="H40" s="31" t="str">
         <f>VLOOKUP(I40,'Names with Seat Code'!B:E,4)</f>
-        <v>Chite</v>
+        <v>Chute</v>
       </c>
       <c r="I40" s="25">
         <f>IF(B39+1&lt;DIRECTIONS!$E$24,B39+1,0)</f>
@@ -59774,7 +59773,7 @@
       </c>
       <c r="G62" s="31" t="str">
         <f>VLOOKUP(I62,'Names with Seat Code'!B:E,2)</f>
-        <v>Dante</v>
+        <v>Antonio</v>
       </c>
       <c r="H62" s="31" t="str">
         <f>VLOOKUP(I62,'Names with Seat Code'!B:E,4)</f>
@@ -59806,7 +59805,7 @@
       </c>
       <c r="G63" s="31" t="str">
         <f>VLOOKUP(I63,'Names with Seat Code'!B:E,2)</f>
-        <v>Antonio</v>
+        <v>Dante</v>
       </c>
       <c r="H63" s="31" t="str">
         <f>VLOOKUP(I63,'Names with Seat Code'!B:E,4)</f>

--- a/data/2026 GSMUD.xlsx
+++ b/data/2026 GSMUD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code Space\Git 2026 Grad\2026-Grad\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027EB726-55DC-47FB-B98A-5253AC41FE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E3E1FB-9521-4C51-A7A0-F9BF4044B672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DIRECTIONS" sheetId="9" r:id="rId1"/>
@@ -1105,9 +1105,6 @@
     <t>Jessica Wong</t>
   </si>
   <si>
-    <t>Jared Wright</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jamari Wright </t>
   </si>
   <si>
@@ -1517,6 +1514,9 @@
   </si>
   <si>
     <t>Will Chute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jared Wright </t>
   </si>
 </sst>
 </file>
@@ -2201,7 +2201,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="24" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -2209,7 +2209,7 @@
         <v>30</v>
       </c>
       <c r="O3" s="24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -2220,7 +2220,7 @@
         <v>31</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -2231,7 +2231,7 @@
         <v>32</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -2239,7 +2239,7 @@
         <v>33</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -2247,7 +2247,7 @@
         <v>34</v>
       </c>
       <c r="O7" s="24" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -2258,7 +2258,7 @@
         <v>35</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -2266,7 +2266,7 @@
         <v>36</v>
       </c>
       <c r="O9" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -2274,7 +2274,7 @@
         <v>37</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -2282,7 +2282,7 @@
         <v>38</v>
       </c>
       <c r="O11" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -2290,7 +2290,7 @@
         <v>39</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -2304,7 +2304,7 @@
         <v>40</v>
       </c>
       <c r="O13" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -2318,7 +2318,7 @@
         <v>41</v>
       </c>
       <c r="O14" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -2329,10 +2329,10 @@
         <v>10</v>
       </c>
       <c r="N15" s="24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
@@ -2343,10 +2343,10 @@
         <v>12</v>
       </c>
       <c r="N16" s="24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O16" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
@@ -2357,10 +2357,10 @@
         <v>14</v>
       </c>
       <c r="N17" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="O17" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
@@ -2371,7 +2371,7 @@
         <v>42</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
@@ -2448,7 +2448,7 @@
         <v>Abate</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
@@ -2500,7 +2500,7 @@
         <v>Abubakar</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2513,13 +2513,13 @@
         <v>Luis</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -2546,7 +2546,7 @@
         <v>Ahlert</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2567,7 +2567,7 @@
         <v>Aiello</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2609,7 +2609,7 @@
         <v>Amado</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2687,7 +2687,7 @@
         <v>Aquino</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2727,7 +2727,7 @@
         <v>Araujo</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2748,7 +2748,7 @@
         <v>Aretusi</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2826,7 +2826,7 @@
         <v>Batista</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2847,7 +2847,7 @@
         <v>Beaulieu</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2868,7 +2868,7 @@
         <v>Belfon</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2927,7 +2927,7 @@
         <v>Bhola</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2967,7 +2967,7 @@
         <v>Boucher</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3007,12 +3007,12 @@
         <v>Bowlin</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="45" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B30" s="41"/>
       <c r="C30" s="40" t="str">
@@ -3199,7 +3199,7 @@
         <v>Carcione</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3261,7 +3261,7 @@
     </row>
     <row r="43" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="41" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B43" s="41"/>
       <c r="C43" s="40" t="str">
@@ -3315,7 +3315,7 @@
         <v>Cirrone</v>
       </c>
       <c r="F45" s="46" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3412,12 +3412,12 @@
         <v>Comenos</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B51" s="41"/>
       <c r="C51" s="40" t="str">
@@ -3611,7 +3611,7 @@
     </row>
     <row r="61" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="47" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B61" s="41"/>
       <c r="C61" s="40" t="str">
@@ -3639,10 +3639,10 @@
       </c>
       <c r="D62" s="40"/>
       <c r="E62" s="49" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F62" s="45" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3682,12 +3682,12 @@
         <v>Dean</v>
       </c>
       <c r="F64" s="45" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="41" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B65" s="41"/>
       <c r="C65" s="40" t="str">
@@ -3703,7 +3703,7 @@
         <v>Deji</v>
       </c>
       <c r="F65" s="41" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3743,7 +3743,7 @@
         <v>DiDonato</v>
       </c>
       <c r="F67" s="41" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3783,7 +3783,7 @@
         <v>DiSerio</v>
       </c>
       <c r="F69" s="41" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3804,7 +3804,7 @@
         <v>Donaghey</v>
       </c>
       <c r="F70" s="45" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3836,13 +3836,13 @@
         <v>Alana</v>
       </c>
       <c r="D72" s="49" t="s">
+        <v>468</v>
+      </c>
+      <c r="E72" s="49" t="s">
         <v>469</v>
       </c>
-      <c r="E72" s="49" t="s">
-        <v>470</v>
-      </c>
       <c r="F72" s="46" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3882,7 +3882,7 @@
         <v>DuRoss</v>
       </c>
       <c r="F74" s="46" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3944,7 +3944,7 @@
     </row>
     <row r="78" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="45" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B78" s="41"/>
       <c r="C78" s="40" t="str">
@@ -3998,7 +3998,7 @@
         <v>Encarnacao</v>
       </c>
       <c r="F80" s="46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4019,7 +4019,7 @@
         <v>Ewald</v>
       </c>
       <c r="F81" s="46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4040,7 +4040,7 @@
         <v>Fantasia</v>
       </c>
       <c r="F82" s="45" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4121,7 +4121,7 @@
     </row>
     <row r="87" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="41" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B87" s="41"/>
       <c r="C87" s="40" t="str">
@@ -4175,7 +4175,7 @@
         <v>Forse</v>
       </c>
       <c r="F89" s="46" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4234,7 +4234,7 @@
         <v>Fucarile</v>
       </c>
       <c r="F92" s="45" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4293,7 +4293,7 @@
         <v>Gager</v>
       </c>
       <c r="F95" s="41" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4354,7 +4354,7 @@
         <v>Gauvin</v>
       </c>
       <c r="F98" s="45" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4489,7 +4489,7 @@
         <v>Gorski</v>
       </c>
       <c r="F105" s="41" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4510,7 +4510,7 @@
         <v>Gosdanian</v>
       </c>
       <c r="F106" s="45" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4588,7 +4588,7 @@
         <v>Hall</v>
       </c>
       <c r="F110" s="45" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4704,7 +4704,7 @@
         <v>Henri</v>
       </c>
       <c r="F116" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4763,7 +4763,7 @@
         <v>Hobson</v>
       </c>
       <c r="F119" s="41" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4803,7 +4803,7 @@
         <v>Houle</v>
       </c>
       <c r="F121" s="46" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4843,7 +4843,7 @@
         <v>Iosua</v>
       </c>
       <c r="F123" s="41" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5016,7 +5016,7 @@
         <v>Kaberle</v>
       </c>
       <c r="F132" s="46" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5037,7 +5037,7 @@
         <v>Kadric</v>
       </c>
       <c r="F133" s="46" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5058,7 +5058,7 @@
         <v>Keaveney</v>
       </c>
       <c r="F134" s="45" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5079,7 +5079,7 @@
         <v>Kenton</v>
       </c>
       <c r="F135" s="46" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5100,12 +5100,12 @@
         <v>Kiley</v>
       </c>
       <c r="F136" s="46" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A137" s="41" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B137" s="41"/>
       <c r="C137" s="40" t="str">
@@ -5159,17 +5159,17 @@
         <v>Lalicata</v>
       </c>
       <c r="F139" s="41" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A140" s="45" t="s">
-        <v>226</v>
+      <c r="A140" s="41" t="s">
+        <v>227</v>
       </c>
       <c r="B140" s="41"/>
       <c r="C140" s="40" t="str">
         <f t="shared" si="9"/>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="D140" s="40" t="str">
         <f t="shared" si="10"/>
@@ -5179,18 +5179,15 @@
         <f t="shared" si="11"/>
         <v>Laurino</v>
       </c>
-      <c r="F140" s="45" t="s">
-        <v>393</v>
-      </c>
     </row>
     <row r="141" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A141" s="41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B141" s="41"/>
       <c r="C141" s="40" t="str">
         <f t="shared" si="9"/>
-        <v>Jonathan</v>
+        <v>Matthew</v>
       </c>
       <c r="D141" s="40" t="str">
         <f t="shared" si="10"/>
@@ -5200,7 +5197,9 @@
         <f t="shared" si="11"/>
         <v>Laurino</v>
       </c>
-      <c r="F141" s="41"/>
+      <c r="F141" s="45" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="142" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A142" s="45" t="s">
@@ -5220,21 +5219,21 @@
         <v>Layne</v>
       </c>
       <c r="F142" s="45" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A143" s="41" t="s">
-        <v>229</v>
+      <c r="A143" s="45" t="s">
+        <v>230</v>
       </c>
       <c r="B143" s="41"/>
       <c r="C143" s="40" t="str">
         <f t="shared" si="9"/>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="D143" s="40" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>James</v>
       </c>
       <c r="E143" s="40" t="str">
         <f t="shared" si="11"/>
@@ -5244,16 +5243,16 @@
     </row>
     <row r="144" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A144" s="45" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B144" s="41"/>
       <c r="C144" s="40" t="str">
         <f t="shared" si="9"/>
-        <v>Austin</v>
+        <v>Jonathan</v>
       </c>
       <c r="D144" s="40" t="str">
         <f t="shared" si="10"/>
-        <v>James</v>
+        <v/>
       </c>
       <c r="E144" s="40" t="str">
         <f t="shared" si="11"/>
@@ -5355,7 +5354,7 @@
         <v>Lizotte</v>
       </c>
       <c r="F149" s="46" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5376,7 +5375,7 @@
         <v>Lusk</v>
       </c>
       <c r="F150" s="46" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5416,7 +5415,7 @@
         <v>Maganzini</v>
       </c>
       <c r="F152" s="45" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5475,7 +5474,7 @@
         <v>Maness</v>
       </c>
       <c r="F155" s="41" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5579,7 +5578,7 @@
     </row>
     <row r="161" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A161" s="47" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B161" s="41"/>
       <c r="C161" s="40" t="str">
@@ -5598,7 +5597,7 @@
     </row>
     <row r="162" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A162" s="48" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B162" s="41"/>
       <c r="C162" s="40" t="str">
@@ -5709,7 +5708,7 @@
         <v>McLaughlin-Shostak</v>
       </c>
       <c r="F167" s="41" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5730,7 +5729,7 @@
         <v>McMenimen</v>
       </c>
       <c r="F168" s="45" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5808,7 +5807,7 @@
         <v>Miceli</v>
       </c>
       <c r="F172" s="46" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5832,7 +5831,7 @@
     </row>
     <row r="174" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A174" s="48" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B174" s="41"/>
       <c r="C174" s="40" t="str">
@@ -5867,7 +5866,7 @@
         <v>Moller</v>
       </c>
       <c r="F175" s="41" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5888,7 +5887,7 @@
         <v>Moreira</v>
       </c>
       <c r="F176" s="45" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5966,7 +5965,7 @@
         <v>Muller</v>
       </c>
       <c r="F180" s="45" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6065,7 +6064,7 @@
         <v>Nguyen</v>
       </c>
       <c r="F185" s="41" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6105,7 +6104,7 @@
         <v>Norris</v>
       </c>
       <c r="F187" s="41" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6145,7 +6144,7 @@
         <v>Ortins</v>
       </c>
       <c r="F189" s="41" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6206,7 +6205,7 @@
         <v>Patel</v>
       </c>
       <c r="F192" s="46" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6246,7 +6245,7 @@
         <v>Petrin</v>
       </c>
       <c r="F194" s="45" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6270,7 +6269,7 @@
     </row>
     <row r="196" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A196" s="48" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B196" s="41"/>
       <c r="C196" s="40" t="str">
@@ -6305,7 +6304,7 @@
         <v>Pomerantz</v>
       </c>
       <c r="F197" s="46" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6326,12 +6325,12 @@
         <v>Poudyal</v>
       </c>
       <c r="F198" s="45" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A199" s="46" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B199" s="41"/>
       <c r="C199" s="40" t="str">
@@ -6368,7 +6367,7 @@
         <v>Rai</v>
       </c>
       <c r="F200" s="46" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6446,7 +6445,7 @@
         <v>Richter</v>
       </c>
       <c r="F204" s="46" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6467,7 +6466,7 @@
         <v>Robichaud</v>
       </c>
       <c r="F205" s="46" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6583,7 +6582,7 @@
         <v>Rojas</v>
       </c>
       <c r="F211" s="41" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6607,7 +6606,7 @@
     </row>
     <row r="213" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A213" s="41" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B213" s="41"/>
       <c r="C213" s="40" t="str">
@@ -6644,7 +6643,7 @@
         <v>Sardinha</v>
       </c>
       <c r="F214" s="45" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6665,7 +6664,7 @@
         <v>Sarre</v>
       </c>
       <c r="F215" s="41" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6724,7 +6723,7 @@
         <v>Schrager</v>
       </c>
       <c r="F218" s="45" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6783,12 +6782,12 @@
         <v>Selvakumar</v>
       </c>
       <c r="F221" s="46" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A222" s="45" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B222" s="41"/>
       <c r="C222" s="40" t="str">
@@ -6842,7 +6841,7 @@
         <v>Shediac</v>
       </c>
       <c r="F224" s="45" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6882,7 +6881,7 @@
         <v>Siciliano</v>
       </c>
       <c r="F226" s="45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6922,7 +6921,7 @@
         <v>Skenderian</v>
       </c>
       <c r="F228" s="46" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7002,7 +7001,7 @@
         <v>Soto</v>
       </c>
       <c r="F232" s="45" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7080,7 +7079,7 @@
         <v>Staffier</v>
       </c>
       <c r="F236" s="46" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7101,7 +7100,7 @@
         <v>Stathoulopoulos</v>
       </c>
       <c r="F237" s="46" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7200,7 +7199,7 @@
         <v>Taubman</v>
       </c>
       <c r="F242" s="45" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7221,7 +7220,7 @@
         <v>Tawadros</v>
       </c>
       <c r="F243" s="41" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7282,7 +7281,7 @@
         <v>Travassos</v>
       </c>
       <c r="F246" s="45" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7303,7 +7302,7 @@
         <v>Upton</v>
       </c>
       <c r="F247" s="46" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7336,7 +7335,7 @@
       </c>
       <c r="D249" s="40"/>
       <c r="E249" s="49" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F249" s="41"/>
     </row>
@@ -7350,10 +7349,10 @@
         <v>Katherine</v>
       </c>
       <c r="D250" s="49" t="s">
+        <v>466</v>
+      </c>
+      <c r="E250" s="49" t="s">
         <v>467</v>
-      </c>
-      <c r="E250" s="49" t="s">
-        <v>468</v>
       </c>
       <c r="F250" s="45"/>
     </row>
@@ -7394,7 +7393,7 @@
         <v>Viliott</v>
       </c>
       <c r="F252" s="45" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7415,7 +7414,7 @@
         <v>Vitarisi</v>
       </c>
       <c r="F253" s="46" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7591,7 +7590,7 @@
     </row>
     <row r="263" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A263" s="41" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B263" s="41"/>
       <c r="C263" s="40" t="str">
@@ -7607,7 +7606,7 @@
         <v>Williams</v>
       </c>
       <c r="F263" s="41" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="264" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7630,44 +7629,44 @@
       <c r="F264" s="45"/>
     </row>
     <row r="265" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A265" s="41" t="s">
+      <c r="A265" s="45" t="s">
         <v>344</v>
       </c>
       <c r="C265" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>Jared</v>
+        <f>IF(ISERROR( FIND(",",TRIM(A265))),LEFT(TRIM(A265), FIND(" ",TRIM(A265))-1),MID(TRIM(A265),LEN(C265)+3,FIND(" ",TRIM(A265)&amp;" ",LEN(C265)+3)-LEN(C265)-2))</f>
+        <v>Jamari</v>
       </c>
       <c r="D265" s="40" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISERROR(FIND(",",TRIM(A265))),IF(LEN(TRIM(A265))-LEN(SUBSTITUTE(TRIM(A265)," ",""))=2,MID(TRIM(A265),LEN(C265)+2,FIND(" ",TRIM(A265),LEN(C265)+2)-LEN(C265)-2),""),MID(TRIM(A265),3+LEN(C265)+LEN(E265),30))</f>
         <v/>
       </c>
       <c r="E265" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f>IF(ISERROR(FIND(",",TRIM(A265))),MID(TRIM(A265),1+LEN(TRIM(A265))-LEN(SUBSTITUTE(TRIM(A265)," ",""))+LEN(C265)+LEN(D265),30),LEFT(TRIM(A265), FIND(",",TRIM(A265))-1))</f>
         <v>Wright</v>
       </c>
       <c r="F265" s="41"/>
     </row>
     <row r="266" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A266" s="45" t="s">
-        <v>345</v>
+        <v>481</v>
       </c>
       <c r="C266" s="40" t="str">
-        <f t="shared" si="15"/>
-        <v>Jamari</v>
+        <f>IF(ISERROR( FIND(",",TRIM(A266))),LEFT(TRIM(A266), FIND(" ",TRIM(A266))-1),MID(TRIM(A266),LEN(C266)+3,FIND(" ",TRIM(A266)&amp;" ",LEN(C266)+3)-LEN(C266)-2))</f>
+        <v>Jared</v>
       </c>
       <c r="D266" s="40" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(ISERROR(FIND(",",TRIM(A266))),IF(LEN(TRIM(A266))-LEN(SUBSTITUTE(TRIM(A266)," ",""))=2,MID(TRIM(A266),LEN(C266)+2,FIND(" ",TRIM(A266),LEN(C266)+2)-LEN(C266)-2),""),MID(TRIM(A266),3+LEN(C266)+LEN(E266),30))</f>
         <v/>
       </c>
       <c r="E266" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f>IF(ISERROR(FIND(",",TRIM(A266))),MID(TRIM(A266),1+LEN(TRIM(A266))-LEN(SUBSTITUTE(TRIM(A266)," ",""))+LEN(C266)+LEN(D266),30),LEFT(TRIM(A266), FIND(",",TRIM(A266))-1))</f>
         <v>Wright</v>
       </c>
       <c r="F266" s="45"/>
     </row>
     <row r="267" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A267" s="41" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C267" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7685,7 +7684,7 @@
     </row>
     <row r="268" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A268" s="45" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C268" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7700,12 +7699,12 @@
         <v>Zani</v>
       </c>
       <c r="F268" s="45" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="269" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A269" s="41" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C269" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7720,7 +7719,7 @@
         <v>Zheng</v>
       </c>
       <c r="F269" s="41" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.2">
@@ -7797,7 +7796,7 @@
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="L2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -7828,7 +7827,7 @@
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="L3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -7859,7 +7858,7 @@
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="L4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -7890,7 +7889,7 @@
       <c r="H5" s="42"/>
       <c r="I5" s="42"/>
       <c r="L5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -7949,7 +7948,7 @@
       <c r="H7" s="42"/>
       <c r="I7" s="42"/>
       <c r="L7" s="22" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -7983,7 +7982,7 @@
         <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -8017,7 +8016,7 @@
         <v>87</v>
       </c>
       <c r="M9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -8051,7 +8050,7 @@
         <v>31</v>
       </c>
       <c r="M10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -8085,7 +8084,7 @@
         <v>32</v>
       </c>
       <c r="M11" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -8119,7 +8118,7 @@
         <v>33</v>
       </c>
       <c r="M12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -8153,7 +8152,7 @@
         <v>34</v>
       </c>
       <c r="M13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -8187,7 +8186,7 @@
         <v>35</v>
       </c>
       <c r="M14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -8221,7 +8220,7 @@
         <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -8255,7 +8254,7 @@
         <v>37</v>
       </c>
       <c r="M16" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -8289,7 +8288,7 @@
         <v>38</v>
       </c>
       <c r="M17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -8323,7 +8322,7 @@
         <v>39</v>
       </c>
       <c r="M18" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -8357,7 +8356,7 @@
         <v>40</v>
       </c>
       <c r="M19" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -8391,7 +8390,7 @@
         <v>41</v>
       </c>
       <c r="M20" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -8422,10 +8421,10 @@
       <c r="H21" s="42"/>
       <c r="I21" s="42"/>
       <c r="L21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M21" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -8456,10 +8455,10 @@
       <c r="H22" s="42"/>
       <c r="I22" s="42"/>
       <c r="L22" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M22" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -8490,10 +8489,10 @@
       <c r="H23" s="42"/>
       <c r="I23" s="42"/>
       <c r="L23" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M23" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -8527,7 +8526,7 @@
         <v>42</v>
       </c>
       <c r="M24" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -10098,7 +10097,7 @@
         <v/>
       </c>
       <c r="E81" s="39" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F81" s="39" t="str">
         <f>'Raw Name Splitter'!F81</f>
@@ -11734,7 +11733,7 @@
       </c>
       <c r="C140" s="39" t="str">
         <f>'Raw Name Splitter'!C140</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="D140" s="39" t="str">
         <f>'Raw Name Splitter'!D140</f>
@@ -11745,7 +11744,7 @@
         <v>Laurino</v>
       </c>
       <c r="F140" s="39" t="str">
-        <f>'Raw Name Splitter'!F140</f>
+        <f>'Raw Name Splitter'!F141</f>
         <v>Matthew La-Ree-No</v>
       </c>
       <c r="H140" s="42"/>
@@ -11762,7 +11761,7 @@
       </c>
       <c r="C141" s="39" t="str">
         <f>'Raw Name Splitter'!C141</f>
-        <v>Jonathan</v>
+        <v>Matthew</v>
       </c>
       <c r="D141" s="39" t="str">
         <f>'Raw Name Splitter'!D141</f>
@@ -11772,9 +11771,9 @@
         <f>'Raw Name Splitter'!E141</f>
         <v>Laurino</v>
       </c>
-      <c r="F141" s="39">
-        <f>'Raw Name Splitter'!F141</f>
-        <v>0</v>
+      <c r="F141" s="39" t="e">
+        <f>'Raw Name Splitter'!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="H141" s="42"/>
       <c r="I141" s="42"/>
@@ -11818,11 +11817,11 @@
       </c>
       <c r="C143" s="39" t="str">
         <f>'Raw Name Splitter'!C143</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="D143" s="39" t="str">
         <f>'Raw Name Splitter'!D143</f>
-        <v/>
+        <v>James</v>
       </c>
       <c r="E143" s="39" t="str">
         <f>'Raw Name Splitter'!E143</f>
@@ -11846,11 +11845,11 @@
       </c>
       <c r="C144" s="39" t="str">
         <f>'Raw Name Splitter'!C144</f>
-        <v>Austin</v>
+        <v>Jonathan</v>
       </c>
       <c r="D144" s="39" t="str">
         <f>'Raw Name Splitter'!D144</f>
-        <v>James</v>
+        <v/>
       </c>
       <c r="E144" s="39" t="str">
         <f>'Raw Name Splitter'!E144</f>
@@ -14771,7 +14770,7 @@
         <v>Colby</v>
       </c>
       <c r="E249" s="39" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F249" s="39">
         <f>'Raw Name Splitter'!F249</f>
@@ -15205,7 +15204,7 @@
       </c>
       <c r="C265" s="39" t="str">
         <f>'Raw Name Splitter'!C265</f>
-        <v>Jared</v>
+        <v>Jamari</v>
       </c>
       <c r="D265" s="39" t="str">
         <f>'Raw Name Splitter'!D265</f>
@@ -15233,7 +15232,7 @@
       </c>
       <c r="C266" s="39" t="str">
         <f>'Raw Name Splitter'!C266</f>
-        <v>Jamari</v>
+        <v>Jared</v>
       </c>
       <c r="D266" s="39" t="str">
         <f>'Raw Name Splitter'!D266</f>
@@ -15334,13 +15333,13 @@
         <v>87</v>
       </c>
       <c r="C270" s="39" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E270" s="39" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F270" s="39" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -21426,7 +21425,7 @@
       </c>
       <c r="I141" s="1" t="str">
         <f>VLOOKUP(J141,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="J141">
         <v>128</v>
@@ -21470,7 +21469,7 @@
       </c>
       <c r="I142" s="1" t="str">
         <f>VLOOKUP(J142,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jonathan</v>
+        <v>Matthew</v>
       </c>
       <c r="J142">
         <v>129</v>
@@ -21479,9 +21478,9 @@
         <f>VLOOKUP(J142,'Names with Seat Code'!A:E,4,FALSE)</f>
         <v/>
       </c>
-      <c r="L142" s="1">
+      <c r="L142" s="1" t="e">
         <f>VLOOKUP(J142,'Names with Seat Code'!A:F,6,FALSE)</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -21558,14 +21557,14 @@
       </c>
       <c r="I144" s="1" t="str">
         <f>VLOOKUP(J144,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="J144">
         <v>131</v>
       </c>
       <c r="K144" t="str">
         <f>VLOOKUP(J144,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v/>
+        <v>James</v>
       </c>
       <c r="L144" s="1">
         <f>VLOOKUP(J144,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -21602,14 +21601,14 @@
       </c>
       <c r="I145" s="1" t="str">
         <f>VLOOKUP(J145,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Austin</v>
+        <v>Jonathan</v>
       </c>
       <c r="J145">
         <v>132</v>
       </c>
       <c r="K145" t="str">
         <f>VLOOKUP(J145,'Names with Seat Code'!A:E,4,FALSE)</f>
-        <v>James</v>
+        <v/>
       </c>
       <c r="L145" s="1">
         <f>VLOOKUP(J145,'Names with Seat Code'!A:F,6,FALSE)</f>
@@ -26662,7 +26661,7 @@
       </c>
       <c r="I260" s="1" t="str">
         <f>VLOOKUP(J260,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jared</v>
+        <v>Jamari</v>
       </c>
       <c r="J260">
         <v>242</v>
@@ -26680,7 +26679,7 @@
         <v>68</v>
       </c>
       <c r="C261" s="6">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D261" s="7" t="s">
         <v>53</v>
@@ -26702,7 +26701,7 @@
       </c>
       <c r="I261" s="1" t="str">
         <f>VLOOKUP(J261,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Jamari</v>
+        <v>Jared</v>
       </c>
       <c r="J261">
         <v>243</v>
@@ -26720,7 +26719,7 @@
         <v>68</v>
       </c>
       <c r="C262" s="6">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D262" s="7" t="s">
         <v>53</v>
@@ -26760,7 +26759,7 @@
         <v>68</v>
       </c>
       <c r="C263" s="6">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D263" s="7" t="s">
         <v>53</v>
@@ -26800,7 +26799,7 @@
         <v>68</v>
       </c>
       <c r="C264" s="6">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D264" s="7" t="s">
         <v>53</v>
@@ -32876,7 +32875,7 @@
       </c>
       <c r="H141" s="6" t="str">
         <f>'Grad Raw Data'!I141</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="I141" s="6" t="str">
         <f>'Grad Raw Data'!H141</f>
@@ -32913,7 +32912,7 @@
       </c>
       <c r="H142" s="6" t="str">
         <f>'Grad Raw Data'!I142</f>
-        <v>Jonathan</v>
+        <v>Matthew</v>
       </c>
       <c r="I142" s="6" t="str">
         <f>'Grad Raw Data'!H142</f>
@@ -32987,7 +32986,7 @@
       </c>
       <c r="H144" s="6" t="str">
         <f>'Grad Raw Data'!I144</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="I144" s="6" t="str">
         <f>'Grad Raw Data'!H144</f>
@@ -33024,7 +33023,7 @@
       </c>
       <c r="H145" s="6" t="str">
         <f>'Grad Raw Data'!I145</f>
-        <v>Austin</v>
+        <v>Jonathan</v>
       </c>
       <c r="I145" s="6" t="str">
         <f>'Grad Raw Data'!H145</f>
@@ -37275,7 +37274,7 @@
       </c>
       <c r="H260" s="6" t="str">
         <f>'Grad Raw Data'!I260</f>
-        <v>Jared</v>
+        <v>Jamari</v>
       </c>
       <c r="I260" s="6" t="str">
         <f>'Grad Raw Data'!H260</f>
@@ -37310,7 +37309,7 @@
       </c>
       <c r="H261" s="6" t="str">
         <f>'Grad Raw Data'!I261</f>
-        <v>Jamari</v>
+        <v>Jared</v>
       </c>
       <c r="I261" s="6" t="str">
         <f>'Grad Raw Data'!H261</f>
@@ -43782,7 +43781,7 @@
     <row r="280" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="20" t="str">
         <f>'Grad Raw Data'!I141</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="B280" s="20" t="str">
         <f>'Grad Raw Data'!K141</f>
@@ -43826,7 +43825,7 @@
     <row r="282" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="20" t="str">
         <f>'Grad Raw Data'!I142</f>
-        <v>Jonathan</v>
+        <v>Matthew</v>
       </c>
       <c r="B282" s="20" t="str">
         <f>'Grad Raw Data'!K142</f>
@@ -43853,9 +43852,9 @@
       </c>
     </row>
     <row r="283" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="16">
+      <c r="A283" s="16" t="e">
         <f>'Grad Raw Data'!L142</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="B283" s="20"/>
       <c r="C283" s="20"/>
@@ -43914,11 +43913,11 @@
     <row r="286" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="20" t="str">
         <f>'Grad Raw Data'!I144</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="B286" s="20" t="str">
         <f>'Grad Raw Data'!K144</f>
-        <v/>
+        <v>James</v>
       </c>
       <c r="C286" s="20" t="str">
         <f>'Grad Raw Data'!H144</f>
@@ -43958,11 +43957,11 @@
     <row r="288" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="20" t="str">
         <f>'Grad Raw Data'!I145</f>
-        <v>Austin</v>
+        <v>Jonathan</v>
       </c>
       <c r="B288" s="20" t="str">
         <f>'Grad Raw Data'!K145</f>
-        <v>James</v>
+        <v/>
       </c>
       <c r="C288" s="20" t="str">
         <f>'Grad Raw Data'!H145</f>
@@ -48990,7 +48989,7 @@
     <row r="518" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A518" s="20" t="str">
         <f>'Grad Raw Data'!I260</f>
-        <v>Jared</v>
+        <v>Jamari</v>
       </c>
       <c r="B518" s="20"/>
       <c r="C518" s="20" t="str">
@@ -49017,7 +49016,7 @@
     <row r="520" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A520" s="20" t="str">
         <f>'Grad Raw Data'!I261</f>
-        <v>Jamari</v>
+        <v>Jared</v>
       </c>
       <c r="B520" s="50"/>
       <c r="C520" s="20" t="str">
@@ -49124,7 +49123,7 @@
     </row>
     <row r="528" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A528" s="51" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B528" s="50"/>
       <c r="C528" s="20"/>
@@ -53504,7 +53503,7 @@
     <row r="280" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="20" t="str">
         <f>'Grad Raw Data'!I141</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="B280" s="20" t="str">
         <f>'Grad Raw Data'!K141</f>
@@ -53535,7 +53534,7 @@
     <row r="282" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="20" t="str">
         <f>'Grad Raw Data'!I142</f>
-        <v>Jonathan</v>
+        <v>Matthew</v>
       </c>
       <c r="B282" s="20" t="str">
         <f>'Grad Raw Data'!K142</f>
@@ -53597,11 +53596,11 @@
     <row r="286" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="20" t="str">
         <f>'Grad Raw Data'!I144</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="B286" s="20" t="str">
         <f>'Grad Raw Data'!K144</f>
-        <v/>
+        <v>James</v>
       </c>
       <c r="C286" s="20" t="str">
         <f>'Grad Raw Data'!H144</f>
@@ -53628,11 +53627,11 @@
     <row r="288" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="20" t="str">
         <f>'Grad Raw Data'!I145</f>
-        <v>Austin</v>
+        <v>Jonathan</v>
       </c>
       <c r="B288" s="20" t="str">
         <f>'Grad Raw Data'!K145</f>
-        <v>James</v>
+        <v/>
       </c>
       <c r="C288" s="20" t="str">
         <f>'Grad Raw Data'!H145</f>
@@ -57193,7 +57192,7 @@
     <row r="518" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="20" t="str">
         <f>'Grad Raw Data'!I260</f>
-        <v>Jared</v>
+        <v>Jamari</v>
       </c>
       <c r="B518" s="20" t="str">
         <f>'Grad Raw Data'!K259</f>
@@ -57224,7 +57223,7 @@
     <row r="520" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="20" t="str">
         <f>'Grad Raw Data'!I261</f>
-        <v>Jamari</v>
+        <v>Jared</v>
       </c>
       <c r="B520" s="20"/>
       <c r="C520" s="20" t="str">
@@ -61917,7 +61916,7 @@
       </c>
       <c r="G129" s="31" t="str">
         <f>VLOOKUP(I129,'Names with Seat Code'!B:E,2)</f>
-        <v>Matthew</v>
+        <v>Jonathan</v>
       </c>
       <c r="H129" s="31" t="str">
         <f>VLOOKUP(I129,'Names with Seat Code'!B:E,4)</f>
@@ -61949,7 +61948,7 @@
       </c>
       <c r="G130" s="31" t="str">
         <f>VLOOKUP(I130,'Names with Seat Code'!B:E,2)</f>
-        <v>Jonathan</v>
+        <v>Matthew</v>
       </c>
       <c r="H130" s="31" t="str">
         <f>VLOOKUP(I130,'Names with Seat Code'!B:E,4)</f>
@@ -62013,7 +62012,7 @@
       </c>
       <c r="G132" s="31" t="str">
         <f>VLOOKUP(I132,'Names with Seat Code'!B:E,2)</f>
-        <v>Jonathan</v>
+        <v>Austin</v>
       </c>
       <c r="H132" s="31" t="str">
         <f>VLOOKUP(I132,'Names with Seat Code'!B:E,4)</f>
@@ -64765,7 +64764,7 @@
       </c>
       <c r="G218" s="31" t="str">
         <f>VLOOKUP(I218,'Names with Seat Code'!B:E,2)</f>
-        <v>Austin</v>
+        <v>Jonathan</v>
       </c>
       <c r="H218" s="31" t="str">
         <f>VLOOKUP(I218,'Names with Seat Code'!B:E,4)</f>
@@ -68285,7 +68284,7 @@
       </c>
       <c r="G328" s="31" t="str">
         <f>VLOOKUP(I328,'Names with Seat Code'!B:E,2)</f>
-        <v>Jared</v>
+        <v>Jamari</v>
       </c>
       <c r="H328" s="31" t="str">
         <f>VLOOKUP(I328,'Names with Seat Code'!B:E,4)</f>
@@ -68317,7 +68316,7 @@
       </c>
       <c r="G329" s="31" t="str">
         <f>VLOOKUP(I329,'Names with Seat Code'!B:E,2)</f>
-        <v>Jamari</v>
+        <v>Jared</v>
       </c>
       <c r="H329" s="31" t="str">
         <f>VLOOKUP(I329,'Names with Seat Code'!B:E,4)</f>

--- a/data/2026 GSMUD.xlsx
+++ b/data/2026 GSMUD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code Space\Git 2026 Grad\2026-Grad\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E3E1FB-9521-4C51-A7A0-F9BF4044B672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E145ABA0-5420-4FB3-B4B2-73A9BE6FDF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DIRECTIONS" sheetId="9" r:id="rId1"/>
@@ -1084,9 +1084,6 @@
     <t>Jacob Michael Ward</t>
   </si>
   <si>
-    <t xml:space="preserve">Tess  Weaver </t>
-  </si>
-  <si>
     <t>Kyle Weaver</t>
   </si>
   <si>
@@ -1517,6 +1514,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jared Wright </t>
+  </si>
+  <si>
+    <t>Tess Weaver</t>
   </si>
 </sst>
 </file>
@@ -2201,7 +2201,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -2209,7 +2209,7 @@
         <v>30</v>
       </c>
       <c r="O3" s="24" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -2220,7 +2220,7 @@
         <v>31</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -2231,7 +2231,7 @@
         <v>32</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -2239,7 +2239,7 @@
         <v>33</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -2247,7 +2247,7 @@
         <v>34</v>
       </c>
       <c r="O7" s="24" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -2258,7 +2258,7 @@
         <v>35</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -2266,7 +2266,7 @@
         <v>36</v>
       </c>
       <c r="O9" s="24" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -2274,7 +2274,7 @@
         <v>37</v>
       </c>
       <c r="O10" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -2282,7 +2282,7 @@
         <v>38</v>
       </c>
       <c r="O11" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -2290,7 +2290,7 @@
         <v>39</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -2304,7 +2304,7 @@
         <v>40</v>
       </c>
       <c r="O13" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -2318,7 +2318,7 @@
         <v>41</v>
       </c>
       <c r="O14" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -2329,10 +2329,10 @@
         <v>10</v>
       </c>
       <c r="N15" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
@@ -2343,10 +2343,10 @@
         <v>12</v>
       </c>
       <c r="N16" s="24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="O16" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
@@ -2357,10 +2357,10 @@
         <v>14</v>
       </c>
       <c r="N17" s="24" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O17" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
@@ -2371,7 +2371,7 @@
         <v>42</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
@@ -2448,7 +2448,7 @@
         <v>Abate</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
@@ -2500,7 +2500,7 @@
         <v>Abubakar</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2513,13 +2513,13 @@
         <v>Luis</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -2546,7 +2546,7 @@
         <v>Ahlert</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2567,7 +2567,7 @@
         <v>Aiello</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2609,7 +2609,7 @@
         <v>Amado</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2687,7 +2687,7 @@
         <v>Aquino</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2727,7 +2727,7 @@
         <v>Araujo</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -2748,7 +2748,7 @@
         <v>Aretusi</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2826,7 +2826,7 @@
         <v>Batista</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2847,7 +2847,7 @@
         <v>Beaulieu</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2868,7 +2868,7 @@
         <v>Belfon</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2927,7 +2927,7 @@
         <v>Bhola</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -2967,7 +2967,7 @@
         <v>Boucher</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3007,12 +3007,12 @@
         <v>Bowlin</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="45" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B30" s="41"/>
       <c r="C30" s="40" t="str">
@@ -3199,7 +3199,7 @@
         <v>Carcione</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3261,7 +3261,7 @@
     </row>
     <row r="43" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="41" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B43" s="41"/>
       <c r="C43" s="40" t="str">
@@ -3315,7 +3315,7 @@
         <v>Cirrone</v>
       </c>
       <c r="F45" s="46" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3412,12 +3412,12 @@
         <v>Comenos</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B51" s="41"/>
       <c r="C51" s="40" t="str">
@@ -3611,7 +3611,7 @@
     </row>
     <row r="61" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="47" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B61" s="41"/>
       <c r="C61" s="40" t="str">
@@ -3639,10 +3639,10 @@
       </c>
       <c r="D62" s="40"/>
       <c r="E62" s="49" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F62" s="45" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3682,12 +3682,12 @@
         <v>Dean</v>
       </c>
       <c r="F64" s="45" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="41" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B65" s="41"/>
       <c r="C65" s="40" t="str">
@@ -3703,7 +3703,7 @@
         <v>Deji</v>
       </c>
       <c r="F65" s="41" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3743,7 +3743,7 @@
         <v>DiDonato</v>
       </c>
       <c r="F67" s="41" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3783,7 +3783,7 @@
         <v>DiSerio</v>
       </c>
       <c r="F69" s="41" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3804,7 +3804,7 @@
         <v>Donaghey</v>
       </c>
       <c r="F70" s="45" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3836,13 +3836,13 @@
         <v>Alana</v>
       </c>
       <c r="D72" s="49" t="s">
+        <v>467</v>
+      </c>
+      <c r="E72" s="49" t="s">
         <v>468</v>
       </c>
-      <c r="E72" s="49" t="s">
-        <v>469</v>
-      </c>
       <c r="F72" s="46" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3882,7 +3882,7 @@
         <v>DuRoss</v>
       </c>
       <c r="F74" s="46" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -3944,7 +3944,7 @@
     </row>
     <row r="78" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="45" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B78" s="41"/>
       <c r="C78" s="40" t="str">
@@ -3998,7 +3998,7 @@
         <v>Encarnacao</v>
       </c>
       <c r="F80" s="46" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4019,7 +4019,7 @@
         <v>Ewald</v>
       </c>
       <c r="F81" s="46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4040,7 +4040,7 @@
         <v>Fantasia</v>
       </c>
       <c r="F82" s="45" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4121,7 +4121,7 @@
     </row>
     <row r="87" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="41" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B87" s="41"/>
       <c r="C87" s="40" t="str">
@@ -4175,7 +4175,7 @@
         <v>Forse</v>
       </c>
       <c r="F89" s="46" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4234,7 +4234,7 @@
         <v>Fucarile</v>
       </c>
       <c r="F92" s="45" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4293,7 +4293,7 @@
         <v>Gager</v>
       </c>
       <c r="F95" s="41" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4354,7 +4354,7 @@
         <v>Gauvin</v>
       </c>
       <c r="F98" s="45" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4489,7 +4489,7 @@
         <v>Gorski</v>
       </c>
       <c r="F105" s="41" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4510,7 +4510,7 @@
         <v>Gosdanian</v>
       </c>
       <c r="F106" s="45" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4588,7 +4588,7 @@
         <v>Hall</v>
       </c>
       <c r="F110" s="45" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4704,7 +4704,7 @@
         <v>Henri</v>
       </c>
       <c r="F116" s="46" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4763,7 +4763,7 @@
         <v>Hobson</v>
       </c>
       <c r="F119" s="41" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4803,7 +4803,7 @@
         <v>Houle</v>
       </c>
       <c r="F121" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -4843,7 +4843,7 @@
         <v>Iosua</v>
       </c>
       <c r="F123" s="41" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5016,7 +5016,7 @@
         <v>Kaberle</v>
       </c>
       <c r="F132" s="46" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5037,7 +5037,7 @@
         <v>Kadric</v>
       </c>
       <c r="F133" s="46" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5058,7 +5058,7 @@
         <v>Keaveney</v>
       </c>
       <c r="F134" s="45" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5079,7 +5079,7 @@
         <v>Kenton</v>
       </c>
       <c r="F135" s="46" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5100,12 +5100,12 @@
         <v>Kiley</v>
       </c>
       <c r="F136" s="46" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A137" s="41" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B137" s="41"/>
       <c r="C137" s="40" t="str">
@@ -5159,7 +5159,7 @@
         <v>Lalicata</v>
       </c>
       <c r="F139" s="41" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5198,7 +5198,7 @@
         <v>Laurino</v>
       </c>
       <c r="F141" s="45" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5219,7 +5219,7 @@
         <v>Layne</v>
       </c>
       <c r="F142" s="45" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5354,7 +5354,7 @@
         <v>Lizotte</v>
       </c>
       <c r="F149" s="46" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5375,7 +5375,7 @@
         <v>Lusk</v>
       </c>
       <c r="F150" s="46" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5415,7 +5415,7 @@
         <v>Maganzini</v>
       </c>
       <c r="F152" s="45" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5474,7 +5474,7 @@
         <v>Maness</v>
       </c>
       <c r="F155" s="41" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5578,7 +5578,7 @@
     </row>
     <row r="161" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A161" s="47" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B161" s="41"/>
       <c r="C161" s="40" t="str">
@@ -5597,7 +5597,7 @@
     </row>
     <row r="162" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A162" s="48" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B162" s="41"/>
       <c r="C162" s="40" t="str">
@@ -5708,7 +5708,7 @@
         <v>McLaughlin-Shostak</v>
       </c>
       <c r="F167" s="41" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5729,7 +5729,7 @@
         <v>McMenimen</v>
       </c>
       <c r="F168" s="45" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5807,7 +5807,7 @@
         <v>Miceli</v>
       </c>
       <c r="F172" s="46" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5831,7 +5831,7 @@
     </row>
     <row r="174" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A174" s="48" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B174" s="41"/>
       <c r="C174" s="40" t="str">
@@ -5866,7 +5866,7 @@
         <v>Moller</v>
       </c>
       <c r="F175" s="41" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5887,7 +5887,7 @@
         <v>Moreira</v>
       </c>
       <c r="F176" s="45" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -5965,7 +5965,7 @@
         <v>Muller</v>
       </c>
       <c r="F180" s="45" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6064,7 +6064,7 @@
         <v>Nguyen</v>
       </c>
       <c r="F185" s="41" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6104,7 +6104,7 @@
         <v>Norris</v>
       </c>
       <c r="F187" s="41" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6144,7 +6144,7 @@
         <v>Ortins</v>
       </c>
       <c r="F189" s="41" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6205,7 +6205,7 @@
         <v>Patel</v>
       </c>
       <c r="F192" s="46" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6245,7 +6245,7 @@
         <v>Petrin</v>
       </c>
       <c r="F194" s="45" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6269,7 +6269,7 @@
     </row>
     <row r="196" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A196" s="48" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B196" s="41"/>
       <c r="C196" s="40" t="str">
@@ -6304,7 +6304,7 @@
         <v>Pomerantz</v>
       </c>
       <c r="F197" s="46" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6325,12 +6325,12 @@
         <v>Poudyal</v>
       </c>
       <c r="F198" s="45" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A199" s="46" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B199" s="41"/>
       <c r="C199" s="40" t="str">
@@ -6367,7 +6367,7 @@
         <v>Rai</v>
       </c>
       <c r="F200" s="46" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6445,7 +6445,7 @@
         <v>Richter</v>
       </c>
       <c r="F204" s="46" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6466,7 +6466,7 @@
         <v>Robichaud</v>
       </c>
       <c r="F205" s="46" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6582,7 +6582,7 @@
         <v>Rojas</v>
       </c>
       <c r="F211" s="41" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6606,7 +6606,7 @@
     </row>
     <row r="213" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A213" s="41" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B213" s="41"/>
       <c r="C213" s="40" t="str">
@@ -6643,7 +6643,7 @@
         <v>Sardinha</v>
       </c>
       <c r="F214" s="45" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6664,7 +6664,7 @@
         <v>Sarre</v>
       </c>
       <c r="F215" s="41" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6723,7 +6723,7 @@
         <v>Schrager</v>
       </c>
       <c r="F218" s="45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6782,12 +6782,12 @@
         <v>Selvakumar</v>
       </c>
       <c r="F221" s="46" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A222" s="45" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B222" s="41"/>
       <c r="C222" s="40" t="str">
@@ -6841,7 +6841,7 @@
         <v>Shediac</v>
       </c>
       <c r="F224" s="45" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6881,7 +6881,7 @@
         <v>Siciliano</v>
       </c>
       <c r="F226" s="45" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -6921,7 +6921,7 @@
         <v>Skenderian</v>
       </c>
       <c r="F228" s="46" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7001,7 +7001,7 @@
         <v>Soto</v>
       </c>
       <c r="F232" s="45" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7079,7 +7079,7 @@
         <v>Staffier</v>
       </c>
       <c r="F236" s="46" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7100,7 +7100,7 @@
         <v>Stathoulopoulos</v>
       </c>
       <c r="F237" s="46" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7199,7 +7199,7 @@
         <v>Taubman</v>
       </c>
       <c r="F242" s="45" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7220,7 +7220,7 @@
         <v>Tawadros</v>
       </c>
       <c r="F243" s="41" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7281,7 +7281,7 @@
         <v>Travassos</v>
       </c>
       <c r="F246" s="45" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7302,7 +7302,7 @@
         <v>Upton</v>
       </c>
       <c r="F247" s="46" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="D249" s="40"/>
       <c r="E249" s="49" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F249" s="41"/>
     </row>
@@ -7349,10 +7349,10 @@
         <v>Katherine</v>
       </c>
       <c r="D250" s="49" t="s">
+        <v>465</v>
+      </c>
+      <c r="E250" s="49" t="s">
         <v>466</v>
-      </c>
-      <c r="E250" s="49" t="s">
-        <v>467</v>
       </c>
       <c r="F250" s="45"/>
     </row>
@@ -7393,7 +7393,7 @@
         <v>Viliott</v>
       </c>
       <c r="F252" s="45" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7414,7 +7414,7 @@
         <v>Vitarisi</v>
       </c>
       <c r="F253" s="46" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -7475,13 +7475,13 @@
       <c r="F256" s="45"/>
     </row>
     <row r="257" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A257" s="46" t="s">
+      <c r="A257" s="45" t="s">
         <v>337</v>
       </c>
       <c r="B257" s="41"/>
       <c r="C257" s="40" t="str">
         <f t="shared" si="12"/>
-        <v>Tess</v>
+        <v>Kyle</v>
       </c>
       <c r="D257" s="40" t="str">
         <f t="shared" si="13"/>
@@ -7495,12 +7495,12 @@
     </row>
     <row r="258" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A258" s="45" t="s">
-        <v>338</v>
+        <v>481</v>
       </c>
       <c r="B258" s="41"/>
       <c r="C258" s="40" t="str">
         <f t="shared" si="12"/>
-        <v>Kyle</v>
+        <v>Tess</v>
       </c>
       <c r="D258" s="40" t="str">
         <f t="shared" si="13"/>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="259" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A259" s="46" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B259" s="41"/>
       <c r="C259" s="40" t="str">
@@ -7533,7 +7533,7 @@
     </row>
     <row r="260" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A260" s="45" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B260" s="41"/>
       <c r="C260" s="40" t="str">
@@ -7552,7 +7552,7 @@
     </row>
     <row r="261" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A261" s="41" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B261" s="41"/>
       <c r="C261" s="40" t="str">
@@ -7571,7 +7571,7 @@
     </row>
     <row r="262" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A262" s="45" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B262" s="41"/>
       <c r="C262" s="40" t="str">
@@ -7590,7 +7590,7 @@
     </row>
     <row r="263" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A263" s="41" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B263" s="41"/>
       <c r="C263" s="40" t="str">
@@ -7606,12 +7606,12 @@
         <v>Williams</v>
       </c>
       <c r="F263" s="41" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="264" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A264" s="45" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B264" s="41"/>
       <c r="C264" s="40" t="str">
@@ -7630,7 +7630,7 @@
     </row>
     <row r="265" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A265" s="45" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C265" s="40" t="str">
         <f>IF(ISERROR( FIND(",",TRIM(A265))),LEFT(TRIM(A265), FIND(" ",TRIM(A265))-1),MID(TRIM(A265),LEN(C265)+3,FIND(" ",TRIM(A265)&amp;" ",LEN(C265)+3)-LEN(C265)-2))</f>
@@ -7648,7 +7648,7 @@
     </row>
     <row r="266" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A266" s="45" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C266" s="40" t="str">
         <f>IF(ISERROR( FIND(",",TRIM(A266))),LEFT(TRIM(A266), FIND(" ",TRIM(A266))-1),MID(TRIM(A266),LEN(C266)+3,FIND(" ",TRIM(A266)&amp;" ",LEN(C266)+3)-LEN(C266)-2))</f>
@@ -7666,7 +7666,7 @@
     </row>
     <row r="267" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A267" s="41" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C267" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7684,7 +7684,7 @@
     </row>
     <row r="268" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A268" s="45" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C268" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7699,12 +7699,12 @@
         <v>Zani</v>
       </c>
       <c r="F268" s="45" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="269" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A269" s="41" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C269" s="40" t="str">
         <f t="shared" si="15"/>
@@ -7719,7 +7719,7 @@
         <v>Zheng</v>
       </c>
       <c r="F269" s="41" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.2">
@@ -7796,7 +7796,7 @@
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="L2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -7827,7 +7827,7 @@
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="L3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -7858,7 +7858,7 @@
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="L4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -7889,7 +7889,7 @@
       <c r="H5" s="42"/>
       <c r="I5" s="42"/>
       <c r="L5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -7948,7 +7948,7 @@
       <c r="H7" s="42"/>
       <c r="I7" s="42"/>
       <c r="L7" s="22" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -7982,7 +7982,7 @@
         <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -8016,7 +8016,7 @@
         <v>87</v>
       </c>
       <c r="M9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -8050,7 +8050,7 @@
         <v>31</v>
       </c>
       <c r="M10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -8084,7 +8084,7 @@
         <v>32</v>
       </c>
       <c r="M11" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -8118,7 +8118,7 @@
         <v>33</v>
       </c>
       <c r="M12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -8152,7 +8152,7 @@
         <v>34</v>
       </c>
       <c r="M13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -8186,7 +8186,7 @@
         <v>35</v>
       </c>
       <c r="M14" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -8220,7 +8220,7 @@
         <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -8254,7 +8254,7 @@
         <v>37</v>
       </c>
       <c r="M16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -8288,7 +8288,7 @@
         <v>38</v>
       </c>
       <c r="M17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -8322,7 +8322,7 @@
         <v>39</v>
       </c>
       <c r="M18" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -8356,7 +8356,7 @@
         <v>40</v>
       </c>
       <c r="M19" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -8390,7 +8390,7 @@
         <v>41</v>
       </c>
       <c r="M20" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -8421,10 +8421,10 @@
       <c r="H21" s="42"/>
       <c r="I21" s="42"/>
       <c r="L21" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="M21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -8455,10 +8455,10 @@
       <c r="H22" s="42"/>
       <c r="I22" s="42"/>
       <c r="L22" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M22" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -8489,10 +8489,10 @@
       <c r="H23" s="42"/>
       <c r="I23" s="42"/>
       <c r="L23" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M23" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -8526,7 +8526,7 @@
         <v>42</v>
       </c>
       <c r="M24" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -10097,7 +10097,7 @@
         <v/>
       </c>
       <c r="E81" s="39" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F81" s="39" t="str">
         <f>'Raw Name Splitter'!F81</f>
@@ -14770,7 +14770,7 @@
         <v>Colby</v>
       </c>
       <c r="E249" s="39" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F249" s="39">
         <f>'Raw Name Splitter'!F249</f>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="C257" s="39" t="str">
         <f>'Raw Name Splitter'!C257</f>
-        <v>Tess</v>
+        <v>Kyle</v>
       </c>
       <c r="D257" s="39" t="str">
         <f>'Raw Name Splitter'!D257</f>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="C258" s="39" t="str">
         <f>'Raw Name Splitter'!C258</f>
-        <v>Kyle</v>
+        <v>Tess</v>
       </c>
       <c r="D258" s="39" t="str">
         <f>'Raw Name Splitter'!D258</f>
@@ -15333,13 +15333,13 @@
         <v>87</v>
       </c>
       <c r="C270" s="39" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E270" s="39" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F270" s="39" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -26133,7 +26133,7 @@
       </c>
       <c r="I248" s="1" t="str">
         <f>VLOOKUP(J248,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Tess</v>
+        <v>Kyle</v>
       </c>
       <c r="J248">
         <v>235</v>
@@ -26177,7 +26177,7 @@
       </c>
       <c r="I249" s="1" t="str">
         <f>VLOOKUP(J249,'Names with Seat Code'!A:E,3,FALSE)</f>
-        <v>Kyle</v>
+        <v>Tess</v>
       </c>
       <c r="J249">
         <v>236</v>
@@ -36834,7 +36834,7 @@
       </c>
       <c r="H248" s="6" t="str">
         <f>'Grad Raw Data'!I248</f>
-        <v>Tess</v>
+        <v>Kyle</v>
       </c>
       <c r="I248" s="6" t="str">
         <f>'Grad Raw Data'!H248</f>
@@ -36871,7 +36871,7 @@
       </c>
       <c r="H249" s="6" t="str">
         <f>'Grad Raw Data'!I249</f>
-        <v>Kyle</v>
+        <v>Tess</v>
       </c>
       <c r="I249" s="6" t="str">
         <f>'Grad Raw Data'!H249</f>
@@ -48489,7 +48489,7 @@
     <row r="494" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="20" t="str">
         <f>'Grad Raw Data'!I248</f>
-        <v>Tess</v>
+        <v>Kyle</v>
       </c>
       <c r="B494" s="20" t="str">
         <f>'Grad Raw Data'!K248</f>
@@ -48533,7 +48533,7 @@
     <row r="496" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="20" t="str">
         <f>'Grad Raw Data'!I249</f>
-        <v>Kyle</v>
+        <v>Tess</v>
       </c>
       <c r="B496" s="20" t="str">
         <f>'Grad Raw Data'!K249</f>
@@ -49123,7 +49123,7 @@
     </row>
     <row r="528" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A528" s="51" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B528" s="50"/>
       <c r="C528" s="20"/>
@@ -56820,7 +56820,7 @@
     <row r="494" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="20" t="str">
         <f>'Grad Raw Data'!I248</f>
-        <v>Tess</v>
+        <v>Kyle</v>
       </c>
       <c r="B494" s="20" t="str">
         <f>'Grad Raw Data'!K248</f>
@@ -56851,7 +56851,7 @@
     <row r="496" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="20" t="str">
         <f>'Grad Raw Data'!I249</f>
-        <v>Kyle</v>
+        <v>Tess</v>
       </c>
       <c r="B496" s="20" t="str">
         <f>'Grad Raw Data'!K249</f>
@@ -57249,12 +57249,24 @@
       <c r="F521" s="20"/>
     </row>
     <row r="522" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A522" s="20"/>
+      <c r="A522" s="20" t="str">
+        <f>'Grad Raw Data'!I262</f>
+        <v>Quinn</v>
+      </c>
       <c r="B522" s="20"/>
-      <c r="C522" s="20"/>
+      <c r="C522" s="20" t="str">
+        <f>'Grad Raw Data'!H262</f>
+        <v>Yandle</v>
+      </c>
       <c r="D522" s="20"/>
-      <c r="E522" s="20"/>
-      <c r="F522" s="20"/>
+      <c r="E522" s="20" t="str">
+        <f>'Grad Raw Data'!D264</f>
+        <v>LEFT</v>
+      </c>
+      <c r="F522" s="20">
+        <f>'Grad Raw Data'!E264</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="523" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="20"/>
@@ -57265,12 +57277,24 @@
       <c r="F523" s="20"/>
     </row>
     <row r="524" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A524" s="20"/>
+      <c r="A524" s="20" t="str">
+        <f>'Grad Raw Data'!I263</f>
+        <v>John</v>
+      </c>
       <c r="B524" s="20"/>
-      <c r="C524" s="20"/>
+      <c r="C524" s="20" t="str">
+        <f>'Grad Raw Data'!H263</f>
+        <v>Zani</v>
+      </c>
       <c r="D524" s="20"/>
-      <c r="E524" s="20"/>
-      <c r="F524" s="20"/>
+      <c r="E524" s="20" t="str">
+        <f>'Grad Raw Data'!D266</f>
+        <v>LEFT</v>
+      </c>
+      <c r="F524" s="20">
+        <f>'Grad Raw Data'!E266</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="525" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="20"/>
@@ -57281,12 +57305,24 @@
       <c r="F525" s="20"/>
     </row>
     <row r="526" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A526" s="20"/>
+      <c r="A526" s="20" t="str">
+        <f>'Grad Raw Data'!I264</f>
+        <v>Jiayu</v>
+      </c>
       <c r="B526" s="20"/>
-      <c r="C526" s="20"/>
+      <c r="C526" s="20" t="str">
+        <f>'Grad Raw Data'!H264</f>
+        <v>Zheng</v>
+      </c>
       <c r="D526" s="20"/>
-      <c r="E526" s="20"/>
-      <c r="F526" s="20"/>
+      <c r="E526" s="20" t="str">
+        <f>'Grad Raw Data'!D268</f>
+        <v>LEFT</v>
+      </c>
+      <c r="F526" s="20">
+        <f>'Grad Raw Data'!E268</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="527" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="20"/>
@@ -68060,7 +68096,7 @@
       </c>
       <c r="G321" s="31" t="str">
         <f>VLOOKUP(I321,'Names with Seat Code'!B:E,2)</f>
-        <v>Tess</v>
+        <v>Kyle</v>
       </c>
       <c r="H321" s="31" t="str">
         <f>VLOOKUP(I321,'Names with Seat Code'!B:E,4)</f>
@@ -68092,7 +68128,7 @@
       </c>
       <c r="G322" s="31" t="str">
         <f>VLOOKUP(I322,'Names with Seat Code'!B:E,2)</f>
-        <v>Kyle</v>
+        <v>Tess</v>
       </c>
       <c r="H322" s="31" t="str">
         <f>VLOOKUP(I322,'Names with Seat Code'!B:E,4)</f>
